--- a/docs/deepreview/【2】每月必用/月度收益-20260323145627.xlsx
+++ b/docs/deepreview/【2】每月必用/月度收益-20260323145627.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F40021-D6B0-4B5A-BE9D-146F185945BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C63A01-B0A3-4563-A224-FFF276A928E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="月度收益" sheetId="1" r:id="rId1"/>
@@ -156,9 +156,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>000001.SH</t>
-  </si>
-  <si>
     <t>前收盘价</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -168,6 +165,10 @@
   </si>
   <si>
     <t>今收盘价</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>399001.SZ</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -414,14 +415,14 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1118,7 +1119,7 @@
     <col min="1" max="1" width="2.625" customWidth="1"/>
     <col min="2" max="2" width="1.625" customWidth="1"/>
     <col min="3" max="3" width="10.625" customWidth="1"/>
-    <col min="4" max="4" width="18.375" customWidth="1"/>
+    <col min="4" max="4" width="11.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
     <col min="7" max="9" width="11" bestFit="1" customWidth="1"/>
@@ -1133,17 +1134,17 @@
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
       <c r="N1" s="11" t="s">
         <v>6</v>
       </c>
@@ -1183,14 +1184,14 @@
         <v>5</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>25</v>
       </c>
       <c r="F4" s="18" t="str">
         <f>[1]!s_info_name(D4)</f>
-        <v>上证指数</v>
+        <v>深证成指</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>22</v>
@@ -1273,15 +1274,15 @@
       </c>
       <c r="D8" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C8,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.7569540783464861E-2</v>
+        <v>5.0341482603637466E-2</v>
       </c>
       <c r="E8" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C8,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.0911722140417801E-2</v>
+        <v>2.035773535524088E-2</v>
       </c>
       <c r="F8" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C8,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.3979954750093247E-2</v>
+        <v>-7.9308118651993609E-2</v>
       </c>
       <c r="G8" s="12" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C8,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
@@ -1329,51 +1330,51 @@
       </c>
       <c r="D9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.018181774785389E-2</v>
+        <v>-2.4825199189143055E-2</v>
       </c>
       <c r="E9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.162572597735557E-2</v>
+        <v>4.481787314015695E-2</v>
       </c>
       <c r="F9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.4713517638741429E-3</v>
+        <v>-1.0074977289647125E-2</v>
       </c>
       <c r="G9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.7002132836125283E-2</v>
+        <v>-5.754866768393585E-2</v>
       </c>
       <c r="H9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.0876866259957216E-2</v>
+        <v>1.422298371743369E-2</v>
       </c>
       <c r="I9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.8958526593962031E-2</v>
+        <v>4.2277580985608854E-2</v>
       </c>
       <c r="J9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.7388701326572349E-2</v>
+        <v>5.2044181548268842E-2</v>
       </c>
       <c r="K9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.9681670942096217E-2</v>
+        <v>0.15317144951776229</v>
       </c>
       <c r="L9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.4412824357451548E-3</v>
+        <v>6.5402374280261188E-2</v>
       </c>
       <c r="M9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.8546672286698707E-2</v>
+        <v>-1.0963456935093485E-2</v>
       </c>
       <c r="N9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.673762702950099E-2</v>
+        <v>-2.9460663793646868E-2</v>
       </c>
       <c r="O9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.0635698815937742E-2</v>
+        <v>4.1661940366236827E-2</v>
       </c>
       <c r="Q9" s="9"/>
     </row>
@@ -1385,51 +1386,51 @@
       </c>
       <c r="D10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.2652331069575018E-2</v>
+        <v>-0.13773099900002006</v>
       </c>
       <c r="E10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.1269170817990469E-2</v>
+        <v>0.13607935715816866</v>
       </c>
       <c r="F10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.6216331596693507E-3</v>
+        <v>7.5462118192435312E-3</v>
       </c>
       <c r="G10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.0931965292664501E-2</v>
+        <v>1.9814362369642957E-2</v>
       </c>
       <c r="H10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.8010042113492144E-3</v>
+        <v>-2.3234213762426847E-2</v>
       </c>
       <c r="I10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.8684100567919044E-2</v>
+        <v>-5.5067849054147411E-2</v>
       </c>
       <c r="J10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-9.6560871345137134E-3</v>
+        <v>-1.0692181738983675E-2</v>
       </c>
       <c r="K10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.2849042277951379E-2</v>
+        <v>-4.6333773710481418E-2</v>
       </c>
       <c r="L10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.17390779343794716</v>
+        <v>0.26127870933686648</v>
       </c>
       <c r="M10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.6985776760983007E-2</v>
+        <v>5.8369059387963773E-3</v>
       </c>
       <c r="N10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.4217620918973495E-2</v>
+        <v>1.9356602800544298E-3</v>
       </c>
       <c r="O10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.6078872777411988E-3</v>
+        <v>-1.8574530667462841E-2</v>
       </c>
       <c r="Q10" s="9"/>
     </row>
@@ -1441,51 +1442,51 @@
       </c>
       <c r="D11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.3867726614861056E-2</v>
+        <v>8.9440799942919202E-2</v>
       </c>
       <c r="E11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.3521290185134536E-3</v>
+        <v>-1.8120348750580773E-2</v>
       </c>
       <c r="F11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.0566804182198251E-3</v>
+        <v>-4.8710782750638337E-3</v>
       </c>
       <c r="G11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.5403774350031929E-2</v>
+        <v>-3.3064843093288609E-2</v>
       </c>
       <c r="H11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.5720851957283362E-2</v>
+        <v>-4.8049469875036992E-2</v>
       </c>
       <c r="I11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.8079254703078416E-4</v>
+        <v>2.1561927865715091E-2</v>
       </c>
       <c r="J11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.7787560535596167E-2</v>
+        <v>1.4267861977762752E-2</v>
       </c>
       <c r="K11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.2008912198509345E-2</v>
+        <v>-6.8464536194953629E-2</v>
       </c>
       <c r="L11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.0132924496624192E-3</v>
+        <v>-2.9629130148077221E-2</v>
       </c>
       <c r="M11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.9482535996990578E-2</v>
+        <v>-2.4306180481728723E-2</v>
       </c>
       <c r="N11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.6114370532163154E-3</v>
+        <v>-1.3877831203754187E-2</v>
       </c>
       <c r="O11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.8067265153757339E-2</v>
+        <v>-2.079033216213988E-2</v>
       </c>
       <c r="Q11" s="9"/>
     </row>
@@ -1497,51 +1498,51 @@
       </c>
       <c r="D12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.6470570134629767E-2</v>
+        <v>-0.10293153784343978</v>
       </c>
       <c r="E12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.0006993729502218E-2</v>
+        <v>9.5795891732417537E-3</v>
       </c>
       <c r="F12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.0683104187428283E-2</v>
+        <v>-9.9398440807372701E-2</v>
       </c>
       <c r="G12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.3077399014680346E-2</v>
+        <v>-9.0509653688320521E-2</v>
       </c>
       <c r="H12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.5737396122901952E-2</v>
+        <v>4.592736664706476E-2</v>
       </c>
       <c r="I12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.6591512481173787E-2</v>
+        <v>0.11872208704158617</v>
       </c>
       <c r="J12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.2775616816503777E-2</v>
+        <v>-4.8796056576028146E-2</v>
       </c>
       <c r="K12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.5707549481006278E-2</v>
+        <v>-3.677593041467675E-2</v>
       </c>
       <c r="L12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.5508947803557973E-2</v>
+        <v>-8.7778977368145661E-2</v>
       </c>
       <c r="M12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.3283960850954983E-2</v>
+        <v>-3.5400950650939289E-2</v>
       </c>
       <c r="N12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.9114886422864359E-2</v>
+        <v>6.8428678839623336E-2</v>
       </c>
       <c r="O12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.9698760712641428E-2</v>
+        <v>-8.3279582437844057E-3</v>
       </c>
       <c r="Q12" s="9"/>
     </row>
@@ -1553,51 +1554,51 @@
       </c>
       <c r="D13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.8792687781955539E-3</v>
+        <v>2.4277457749886988E-2</v>
       </c>
       <c r="E13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.4678964173320317E-3</v>
+        <v>-2.1221792915779414E-2</v>
       </c>
       <c r="F13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.9141453698239497E-2</v>
+        <v>-5.0234585409741239E-2</v>
       </c>
       <c r="G13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.4366726163643762E-3</v>
+        <v>4.7892700063107752E-2</v>
       </c>
       <c r="H13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.8920198706276175E-2</v>
+        <v>3.8633327024997444E-2</v>
       </c>
       <c r="I13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.7156554958870407E-3</v>
+        <v>1.1024282437704036E-2</v>
       </c>
       <c r="J13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.3976320430207621E-2</v>
+        <v>-4.5409935746196561E-2</v>
       </c>
       <c r="K13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.3146122924835772E-2</v>
+        <v>-1.0006626173552857E-2</v>
       </c>
       <c r="L13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.8360634301898315E-3</v>
+        <v>-1.3517995451517439E-3</v>
       </c>
       <c r="M13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.837927756067951E-3</v>
+        <v>9.9496242672285629E-3</v>
       </c>
       <c r="N13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.6657828673184465E-3</v>
+        <v>2.3828336971509101E-2</v>
       </c>
       <c r="O13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.129365935038563E-2</v>
+        <v>4.1640988094515663E-3</v>
       </c>
       <c r="Q13" s="9"/>
     </row>
@@ -1609,51 +1610,51 @@
       </c>
       <c r="D14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.4128822303617792E-2</v>
+        <v>2.4076639739082584E-2</v>
       </c>
       <c r="E14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.232769749427189E-2</v>
+        <v>2.7979150533463004E-2</v>
       </c>
       <c r="F14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.5136766475814112E-2</v>
+        <v>-9.2750278290932187E-2</v>
       </c>
       <c r="G14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.9917882299368213E-2</v>
+        <v>7.623485959027132E-2</v>
       </c>
       <c r="H14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.7030691635365756E-3</v>
+        <v>2.2661163450887756E-3</v>
       </c>
       <c r="I14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.6390816109881605E-2</v>
+        <v>0.1159744592919514</v>
       </c>
       <c r="J14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.10900097936990827</v>
+        <v>0.13721549480206829</v>
       </c>
       <c r="K14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.588242651487227E-2</v>
+        <v>8.8243317184737435E-3</v>
       </c>
       <c r="L14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.2309266707453839E-2</v>
+        <v>-6.1837884382173192E-2</v>
       </c>
       <c r="M14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.0137647864681973E-3</v>
+        <v>2.5501005113474084E-2</v>
       </c>
       <c r="N14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.1859486607748639E-2</v>
+        <v>3.2750824777448395E-2</v>
       </c>
       <c r="O14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.3974077609553834E-2</v>
+        <v>5.8563725153767177E-2</v>
       </c>
       <c r="Q14" s="9"/>
     </row>
@@ -1665,51 +1666,51 @@
       </c>
       <c r="D15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.6359251840553775E-2</v>
+        <v>3.307088047633866E-2</v>
       </c>
       <c r="E15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.13788795392228126</v>
+        <v>0.20760350353866674</v>
       </c>
       <c r="F15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.0937284359924284E-2</v>
+        <v>9.6871613194907891E-2</v>
       </c>
       <c r="G15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.0181405338106657E-3</v>
+        <v>-2.3451346697111575E-2</v>
       </c>
       <c r="H15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.8357057437698041E-2</v>
+        <v>-7.7713298994248281E-2</v>
       </c>
       <c r="I15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.7661506150989723E-2</v>
+        <v>2.8648173165088497E-2</v>
       </c>
       <c r="J15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.5567134261002424E-2</v>
+        <v>1.6157783235449585E-2</v>
       </c>
       <c r="K15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.5778076210454572E-2</v>
+        <v>4.1881970314481265E-3</v>
       </c>
       <c r="L15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.5665790034876714E-3</v>
+        <v>8.601813319110585E-3</v>
       </c>
       <c r="M15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.2152652914997404E-3</v>
+        <v>2.001758753024041E-2</v>
       </c>
       <c r="N15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.9485731256564165E-2</v>
+        <v>-5.5185764230928358E-3</v>
       </c>
       <c r="O15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.2027806378822881E-2</v>
+        <v>8.8561532259786357E-2</v>
       </c>
       <c r="Q15" s="9"/>
     </row>
@@ -1721,51 +1722,51 @@
       </c>
       <c r="D16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.251051192648859E-2</v>
+        <v>1.0799016344442469E-2</v>
       </c>
       <c r="E16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.3612754347852518E-2</v>
+        <v>-2.9655502543263768E-2</v>
       </c>
       <c r="F16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.7769275893045564E-2</v>
+        <v>3.6869235138945466E-3</v>
       </c>
       <c r="G16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.7348636115170133E-2</v>
+        <v>-5.0069397271966028E-2</v>
       </c>
       <c r="H16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.2962702737847636E-3</v>
+        <v>-2.7835720231160765E-3</v>
       </c>
       <c r="I16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.0134940251632591E-2</v>
+        <v>-8.8993610845817694E-2</v>
       </c>
       <c r="J16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.0178624628395916E-2</v>
+        <v>-2.1397178641631598E-2</v>
       </c>
       <c r="K16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.2548655509042641E-2</v>
+        <v>-7.7713046109850303E-2</v>
       </c>
       <c r="L16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.5262894606472805E-2</v>
+        <v>-7.6050476868998462E-3</v>
       </c>
       <c r="M16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.7468903983238468E-2</v>
+        <v>-0.10930238534662395</v>
       </c>
       <c r="N16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.6077279121825585E-3</v>
+        <v>2.6583417595123171E-2</v>
       </c>
       <c r="O16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.6431402284417103E-2</v>
+        <v>-5.7533808639995465E-2</v>
       </c>
       <c r="Q16" s="9"/>
     </row>
@@ -1777,51 +1778,51 @@
       </c>
       <c r="D17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.789149138013002E-2</v>
+        <v>-1.2291107895865294E-2</v>
       </c>
       <c r="E17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.6135726960849759E-2</v>
+        <v>3.3753772961884199E-2</v>
       </c>
       <c r="F17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.928588013615288E-3</v>
+        <v>3.597089970323486E-3</v>
       </c>
       <c r="G17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.105678851624615E-2</v>
+        <v>-1.8609191530145841E-2</v>
       </c>
       <c r="H17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.1881032824346383E-2</v>
+        <v>-3.6132901705594911E-2</v>
       </c>
       <c r="I17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.4140137274171636E-2</v>
+        <v>6.7387211861919871E-2</v>
       </c>
       <c r="J17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.524768852185777E-2</v>
+        <v>-2.3329830259419815E-3</v>
       </c>
       <c r="K17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.6819810876673511E-2</v>
+        <v>2.9661960482983307E-2</v>
       </c>
       <c r="L17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.5310532105903292E-3</v>
+        <v>2.5011666742259964E-2</v>
       </c>
       <c r="M17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.3257496073910691E-2</v>
+        <v>2.5293405139346969E-2</v>
       </c>
       <c r="N17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.244197806545678E-2</v>
+        <v>-3.7256763491866352E-2</v>
       </c>
       <c r="O17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.0195149603200466E-3</v>
+        <v>8.8039686411813811E-3</v>
       </c>
       <c r="Q17" s="9"/>
     </row>
@@ -1833,51 +1834,51 @@
       </c>
       <c r="D18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.22648792856654443</v>
+        <v>-0.25635327270904051</v>
       </c>
       <c r="E18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.8125730566920017E-2</v>
+        <v>-3.4066155288205779E-2</v>
       </c>
       <c r="F18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.11753663254065616</v>
+        <v>0.14927481175312152</v>
       </c>
       <c r="G18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.1835171767510042E-2</v>
+        <v>-3.0015965959690361E-2</v>
       </c>
       <c r="H18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.3878850664528262E-3</v>
+        <v>1.8136297038093829E-3</v>
       </c>
       <c r="I18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.453791654438044E-3</v>
+        <v>3.2486333080510299E-2</v>
       </c>
       <c r="J18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.6976002916432975E-2</v>
+        <v>-1.5305825275574669E-2</v>
       </c>
       <c r="K18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.5629379536870509E-2</v>
+        <v>4.1477583236643634E-2</v>
       </c>
       <c r="L18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.6183190941085233E-2</v>
+        <v>-1.7689181181227753E-2</v>
       </c>
       <c r="M18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.1879689939405154E-2</v>
+        <v>1.2938349065258814E-2</v>
       </c>
       <c r="N18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.8231700001161171E-2</v>
+        <v>2.8763103140568402E-2</v>
       </c>
       <c r="O18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.5044667225019881E-2</v>
+        <v>-7.58300458410055E-2</v>
       </c>
       <c r="Q18" s="9"/>
     </row>
@@ -1889,51 +1890,51 @@
       </c>
       <c r="D19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.5166701342979092E-3</v>
+        <v>1.2353576481593853E-2</v>
       </c>
       <c r="E19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.1130436028573794E-2</v>
+        <v>5.4435176859843892E-2</v>
       </c>
       <c r="F19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.13219212863595864</v>
+        <v>0.11932452003302707</v>
       </c>
       <c r="G19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.18510530833408256</v>
+        <v>0.12597966181645526</v>
       </c>
       <c r="H19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.8294059308973782E-2</v>
+        <v>8.6499705775968661E-2</v>
       </c>
       <c r="I19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.2537005523290121E-2</v>
+        <v>-0.10946794772418755</v>
       </c>
       <c r="J19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.14343335799342083</v>
+        <v>-0.13695883620862515</v>
       </c>
       <c r="K19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.12493842333607097</v>
+        <v>-0.1474909921842561</v>
       </c>
       <c r="L19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.7786897351843931E-2</v>
+        <v>-5.3171327431380089E-2</v>
       </c>
       <c r="M19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.10802601195093775</v>
+        <v>0.15596335694440966</v>
       </c>
       <c r="N19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.8578703025387888E-2</v>
+        <v>4.2595169551910006E-2</v>
       </c>
       <c r="O19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.7218049966146296E-2</v>
+        <v>5.2088424044246295E-2</v>
       </c>
       <c r="Q19" s="9"/>
     </row>
@@ -1945,51 +1946,51 @@
       </c>
       <c r="D20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.9175738122041004E-2</v>
+        <v>-6.7614914351371791E-2</v>
       </c>
       <c r="E20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.1420586370551655E-2</v>
+        <v>-2.7296842815855094E-2</v>
       </c>
       <c r="F20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.1183182236850442E-2</v>
+        <v>-2.3940917128534411E-2</v>
       </c>
       <c r="G20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.4170951150491735E-3</v>
+        <v>1.714759892722495E-2</v>
       </c>
       <c r="H20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.3434003270892436E-3</v>
+        <v>7.1062465010278686E-3</v>
       </c>
       <c r="I20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.4698638493694265E-3</v>
+        <v>-2.9266124169345931E-3</v>
       </c>
       <c r="J20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.4809832609734617E-2</v>
+        <v>8.3563804978024306E-2</v>
       </c>
       <c r="K20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.1031385897830646E-3</v>
+        <v>-1.4478741551208318E-2</v>
       </c>
       <c r="L20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.6151001262854114E-2</v>
+        <v>3.0432810432328372E-2</v>
       </c>
       <c r="M20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.3820260843447461E-2</v>
+        <v>1.7977695509573399E-2</v>
       </c>
       <c r="N20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.10852796777757678</v>
+        <v>9.4414251486698131E-2</v>
       </c>
       <c r="O20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.20569360396744485</v>
+        <v>0.22354435185871213</v>
       </c>
       <c r="Q20" s="9"/>
     </row>
@@ -2001,51 +2002,51 @@
       </c>
       <c r="D21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.1250524430530131E-2</v>
+        <v>6.0460589850209745E-2</v>
       </c>
       <c r="E21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.3125753011417114E-3</v>
+        <v>-2.7137867316971986E-3</v>
       </c>
       <c r="F21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.4519944893309906E-2</v>
+        <v>-7.7962141739052138E-2</v>
       </c>
       <c r="G21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.624897110417912E-2</v>
+        <v>-2.2315877949134588E-2</v>
       </c>
       <c r="H21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.633055881045701E-2</v>
+        <v>6.5186726259770289E-2</v>
       </c>
       <c r="I21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.13969820850692971</v>
+        <v>-0.16888006187979657</v>
       </c>
       <c r="J21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.3731587313297098E-3</v>
+        <v>9.2183135255909932E-3</v>
       </c>
       <c r="K21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.2454134042599021E-2</v>
+        <v>5.6286247346561513E-2</v>
       </c>
       <c r="L21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.6353247406811562E-2</v>
+        <v>3.8048000355014544E-2</v>
       </c>
       <c r="M21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.5198202941602457E-2</v>
+        <v>-8.2404640798611206E-3</v>
       </c>
       <c r="N21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.6836703532942883E-2</v>
+        <v>1.1629356952917336E-2</v>
       </c>
       <c r="O21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.7073096918537338E-2</v>
+        <v>-4.9261302871441703E-2</v>
       </c>
       <c r="Q21" s="9"/>
     </row>
@@ -2057,51 +2058,51 @@
       </c>
       <c r="D22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.2371683041460662E-2</v>
+        <v>4.3148440331093108E-2</v>
       </c>
       <c r="E22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.9267385207252943E-2</v>
+        <v>8.0742083025703071E-2</v>
       </c>
       <c r="F22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.8231372043581096E-2</v>
+        <v>-6.4106706766737687E-2</v>
       </c>
       <c r="G22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.9010388953803838E-2</v>
+        <v>8.1839485446845148E-2</v>
       </c>
       <c r="H22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.004959279160178E-2</v>
+        <v>-3.8292234887199461E-3</v>
       </c>
       <c r="I22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.1883861372866174E-2</v>
+        <v>-6.3215371432572054E-2</v>
       </c>
       <c r="J22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.4729623160637238E-2</v>
+        <v>-4.6429292833070616E-2</v>
       </c>
       <c r="K22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.6673841552285249E-2</v>
+        <v>-9.3631639972695191E-2</v>
       </c>
       <c r="L22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.8875010866794106E-2</v>
+        <v>5.7024155662517728E-2</v>
       </c>
       <c r="M22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.2874397999394001E-3</v>
+        <v>-2.4129244808778205E-2</v>
       </c>
       <c r="N22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.2903890027454539E-2</v>
+        <v>-6.6890040799093664E-2</v>
       </c>
       <c r="O22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.14595652681129456</v>
+        <v>0.15351062493143641</v>
       </c>
       <c r="Q22" s="9"/>
     </row>
@@ -2113,51 +2114,51 @@
       </c>
       <c r="D23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.190357315700501E-3</v>
+        <v>-3.7232898333610542E-2</v>
       </c>
       <c r="E23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.0978695621949113E-2</v>
+        <v>7.5679442659764895E-2</v>
       </c>
       <c r="F23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.9372045880057307E-3</v>
+        <v>-2.6315497811072119E-2</v>
       </c>
       <c r="G23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.6691839892681894E-3</v>
+        <v>-1.9892698350484461E-2</v>
       </c>
       <c r="H23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.7715392454296029E-2</v>
+        <v>-5.2615160686790056E-2</v>
       </c>
       <c r="I23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.7811882169745985E-3</v>
+        <v>3.8215568933114508E-2</v>
       </c>
       <c r="J23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.1848421259950901E-2</v>
+        <v>-9.9499369619066025E-3</v>
       </c>
       <c r="K23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.9741850496478272E-2</v>
+        <v>-4.9451695969484961E-2</v>
       </c>
       <c r="L23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.1064448027920122E-2</v>
+        <v>-9.696414497203365E-2</v>
       </c>
       <c r="M23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.6214426802078767E-2</v>
+        <v>1.8322180372304153E-2</v>
       </c>
       <c r="N23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.462817785880681E-2</v>
+        <v>-7.5139167278572727E-2</v>
       </c>
       <c r="O23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.7425300439613469E-2</v>
+        <v>-7.9906967483495128E-2</v>
       </c>
       <c r="Q23" s="9"/>
     </row>
@@ -2169,51 +2170,51 @@
       </c>
       <c r="D24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.783484618748251E-2</v>
+        <v>-0.11407076073889211</v>
       </c>
       <c r="E24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.0958474448130371E-2</v>
+        <v>2.4672156783390964E-2</v>
       </c>
       <c r="F24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.872970759938819E-2</v>
+        <v>4.6391091495261438E-3</v>
       </c>
       <c r="G24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.6708248836883985E-2</v>
+        <v>-0.10659322013550121</v>
       </c>
       <c r="H24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-9.7005132356839704E-2</v>
+        <v>-8.5855303323966514E-2</v>
       </c>
       <c r="I24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.4755405461187197E-2</v>
+        <v>-8.0088501038888649E-2</v>
       </c>
       <c r="J24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>9.9706467309047545E-2</v>
+        <v>0.14897394112690865</v>
       </c>
       <c r="K24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.909947021860539E-4</v>
+        <v>5.1307394310762033E-2</v>
       </c>
       <c r="L24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.3892726915815157E-3</v>
+        <v>1.1450063913773567E-2</v>
       </c>
       <c r="M24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.12169375725338138</v>
+        <v>0.16555660121778337</v>
       </c>
       <c r="N24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.3260418922162496E-2</v>
+        <v>-7.7124994277051773E-2</v>
       </c>
       <c r="O24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.2919231070629449E-3</v>
+        <v>9.9109229615910177E-3</v>
       </c>
       <c r="Q24" s="9"/>
     </row>
@@ -2225,51 +2226,51 @@
       </c>
       <c r="D25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>9.3284014488097325E-2</v>
+        <v>8.1677887315930064E-2</v>
       </c>
       <c r="E25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.6313855174447305E-2</v>
+        <v>8.4528446370157648E-2</v>
       </c>
       <c r="F25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.13940548824400412</v>
+        <v>0.18055858772804112</v>
       </c>
       <c r="G25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.3972454221344659E-2</v>
+        <v>5.795654909349901E-2</v>
       </c>
       <c r="H25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.2707032579112809E-2</v>
+        <v>6.5814569530848521E-2</v>
       </c>
       <c r="I25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.12398050840698405</v>
+        <v>0.14205197118460666</v>
       </c>
       <c r="J25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.15297216089143539</v>
+        <v>0.18191214349648299</v>
       </c>
       <c r="K25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.21814287079191408</v>
+        <v>-0.22571111480757644</v>
       </c>
       <c r="L25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.1863446468834109E-2</v>
+        <v>5.8739443282694426E-2</v>
       </c>
       <c r="M25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.7865717597806139E-2</v>
+        <v>9.7290076325660557E-2</v>
       </c>
       <c r="N25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.6576475174975558E-2</v>
+        <v>9.6738662140093634E-2</v>
       </c>
       <c r="O25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.5611984598634008E-2</v>
+        <v>1.5807858558900545E-2</v>
       </c>
       <c r="Q25" s="9"/>
     </row>
@@ -2281,51 +2282,51 @@
       </c>
       <c r="D26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.16690287657868963</v>
+        <v>-0.10411566328008137</v>
       </c>
       <c r="E26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.9504621191849312E-3</v>
+        <v>-2.1331579402069645E-3</v>
       </c>
       <c r="F26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.20140768988601454</v>
+        <v>-0.15936322329986885</v>
       </c>
       <c r="G26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.3464213714176765E-2</v>
+        <v>1.524168520879865E-2</v>
       </c>
       <c r="H26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.0334293139704185E-2</v>
+        <v>-0.10786052602447194</v>
       </c>
       <c r="I26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.20308159310108997</v>
+        <v>-0.22222853941915666</v>
       </c>
       <c r="J26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.4478256118282129E-2</v>
+        <v>1.0624091190720719E-2</v>
       </c>
       <c r="K26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.13630640299425334</v>
+        <v>-0.15480868995750319</v>
       </c>
       <c r="L26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.3207783198998539E-2</v>
+        <v>-5.5592383240690706E-2</v>
       </c>
       <c r="M26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.24631700282153857</v>
+        <v>-0.22752729132936012</v>
       </c>
       <c r="N26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.2352587306930847E-2</v>
+        <v>0.14028735150905192</v>
       </c>
       <c r="O26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.690903377377396E-2</v>
+        <v>-2.5981777012375029E-2</v>
       </c>
       <c r="Q26" s="9"/>
     </row>
@@ -2337,51 +2338,51 @@
       </c>
       <c r="D27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.143602217775233E-2</v>
+        <v>0.14830425540973335</v>
       </c>
       <c r="E27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.4000936714357666E-2</v>
+        <v>5.3290227170717186E-2</v>
       </c>
       <c r="F27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.10513791215980994</v>
+        <v>6.3373019313285317E-2</v>
       </c>
       <c r="G27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.20643608963992577</v>
+        <v>0.27098246280148564</v>
       </c>
       <c r="H27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.9868002057651868E-2</v>
+        <v>0.19127264588369353</v>
       </c>
       <c r="I27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.031029862854643E-2</v>
+        <v>-3.0730221995471596E-2</v>
       </c>
       <c r="J27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.17021186938634081</v>
+        <v>0.21146325944496325</v>
       </c>
       <c r="K27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.16725288479259359</v>
+        <v>0.17583065880451046</v>
       </c>
       <c r="L27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.3898674510066922E-2</v>
+        <v>5.5529981880707791E-2</v>
       </c>
       <c r="M27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.2485983738993953E-2</v>
+        <v>3.5336439795088603E-2</v>
       </c>
       <c r="N27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.18186897383859812</v>
+        <v>-0.19934801602874999</v>
       </c>
       <c r="O27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.0008777083028004E-2</v>
+        <v>0.13192282373741637</v>
       </c>
       <c r="Q27" s="9"/>
     </row>
@@ -2393,51 +2394,51 @@
       </c>
       <c r="D28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.3535089147216635E-2</v>
+        <v>0.13225779190756293</v>
       </c>
       <c r="E28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.2577505115075178E-2</v>
+        <v>3.3707373084990611E-2</v>
       </c>
       <c r="F28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.6580679430029424E-4</v>
+        <v>4.9157456742046746E-2</v>
       </c>
       <c r="G28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.10931876037418299</v>
+        <v>9.4332094565003466E-2</v>
       </c>
       <c r="H28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.13961518459294142</v>
+        <v>0.11537886830011136</v>
       </c>
       <c r="I28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.8833241942362688E-2</v>
+        <v>2.2278164858886562E-3</v>
       </c>
       <c r="J28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.5568477901413154E-2</v>
+        <v>-8.2469383309733968E-2</v>
       </c>
       <c r="K28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.8464104101546761E-2</v>
+        <v>5.8764316925021154E-2</v>
       </c>
       <c r="L28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.6543983678174481E-2</v>
+        <v>3.5402177494753939E-2</v>
       </c>
       <c r="M28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.8828936376128063E-2</v>
+        <v>6.8225578426815758E-2</v>
       </c>
       <c r="N28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.14216376232118422</v>
+        <v>0.22609788540658804</v>
       </c>
       <c r="O28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.2744667361187525</v>
+        <v>0.17295656692832792</v>
       </c>
       <c r="Q28" s="9"/>
     </row>
@@ -2449,51 +2450,51 @@
       </c>
       <c r="D29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.8960312547374771E-2</v>
+        <v>-7.1998357005709224E-3</v>
       </c>
       <c r="E29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>9.5802816357797985E-2</v>
+        <v>0.10863100906128566</v>
       </c>
       <c r="F29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-9.5533471209484078E-2</v>
+        <v>-6.1003732468328027E-2</v>
       </c>
       <c r="G29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.8700750739056526E-2</v>
+        <v>-4.3143501506142101E-3</v>
       </c>
       <c r="H29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.4896984504108985E-2</v>
+        <v>-0.11246274557508663</v>
       </c>
       <c r="I29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.9043345293559888E-2</v>
+        <v>-1.4789068210891876E-2</v>
       </c>
       <c r="J29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.9381315117052988E-3</v>
+        <v>4.6134561250330552E-2</v>
       </c>
       <c r="K29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.3649648717998506E-2</v>
+        <v>2.1769500466135572E-2</v>
       </c>
       <c r="L29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.1782012008964049E-3</v>
+        <v>-1.6039679599570644E-2</v>
       </c>
       <c r="M29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.4340809301375748E-2</v>
+        <v>-8.2951415189715605E-2</v>
       </c>
       <c r="N29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.8966871855030689E-3</v>
+        <v>5.4670937673253484E-3</v>
       </c>
       <c r="O29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.6215948714636532E-2</v>
+        <v>6.9770517328782589E-2</v>
       </c>
       <c r="Q29" s="9"/>
     </row>
@@ -2505,51 +2506,51 @@
       </c>
       <c r="D30" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.2579990968869348E-2</v>
+        <v>6.812841902226463E-2</v>
       </c>
       <c r="E30" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.3018458832396975E-2</v>
+        <v>5.4629043961463175E-2</v>
       </c>
       <c r="F30" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.9733336039692757E-2</v>
+        <v>3.5772431974342211E-2</v>
       </c>
       <c r="G30" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.3850523333695137E-2</v>
+        <v>-0.11008824073437806</v>
       </c>
       <c r="H30" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.4869217410269706E-2</v>
+        <v>-9.8309821655172547E-3</v>
       </c>
       <c r="I30" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.10074130442327489</v>
+        <v>-8.4356538150203719E-2</v>
       </c>
       <c r="J30" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-9.2626872370747959E-3</v>
+        <v>2.2955874047956293E-3</v>
       </c>
       <c r="K30" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.1842401035346968E-2</v>
+        <v>-3.2764507198396742E-2</v>
       </c>
       <c r="L30" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.0711979029284917E-2</v>
+        <v>8.7575004912160428E-2</v>
       </c>
       <c r="M30" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.4531395432089964E-2</v>
+        <v>-6.8781138604573577E-2</v>
       </c>
       <c r="N30" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.5323323256617005E-2</v>
+        <v>3.0024736129299345E-3</v>
       </c>
       <c r="O30" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.5397230399523704E-2</v>
+        <v>-4.911182716703788E-2</v>
       </c>
       <c r="Q30" s="9"/>
     </row>
@@ -2561,51 +2562,51 @@
       </c>
       <c r="D31" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.10471077314249433</v>
+        <v>0.10579458558330002</v>
       </c>
       <c r="E31" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.0789964095571154E-3</v>
+        <v>1.9736374216337005E-3</v>
       </c>
       <c r="F31" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.9554292124249812E-4</v>
+        <v>1.4594204382317288E-2</v>
       </c>
       <c r="G31" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.193273038532233E-3</v>
+        <v>5.1225732697714577E-2</v>
       </c>
       <c r="H31" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.6029587681176478E-2</v>
+        <v>7.4503320397674822E-2</v>
       </c>
       <c r="I31" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.7247498986525806E-2</v>
+        <v>-7.9597201922201433E-2</v>
       </c>
       <c r="J31" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.2461979079745378E-3</v>
+        <v>2.90284038703712E-2</v>
       </c>
       <c r="K31" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.7080952529284117E-2</v>
+        <v>-3.798557023256266E-2</v>
       </c>
       <c r="L31" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.8553203519310686E-2</v>
+        <v>-4.3062731528903712E-2</v>
       </c>
       <c r="M31" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.3793547358357916E-2</v>
+        <v>3.6808151117518451E-2</v>
       </c>
       <c r="N31" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.6284129012543742E-2</v>
+        <v>3.1761677546988221E-2</v>
       </c>
       <c r="O31" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.1440891767611037E-2</v>
+        <v>6.4828933465404415E-2</v>
       </c>
       <c r="Q31" s="9"/>
     </row>
@@ -2617,51 +2618,51 @@
       </c>
       <c r="D32" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-9.3747702723802617E-2</v>
+        <v>-0.10312737546547102</v>
       </c>
       <c r="E32" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.214706385146803E-2</v>
+        <v>1.5688150690465585E-2</v>
       </c>
       <c r="F32" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.1947234244615892E-2</v>
+        <v>4.76680893483723E-2</v>
       </c>
       <c r="G32" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.9805350067491529E-2</v>
+        <v>2.5066952329941161E-2</v>
       </c>
       <c r="H32" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-9.1150406925742514E-2</v>
+        <v>-6.6531938305680716E-2</v>
       </c>
       <c r="I32" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.14317957054441655</v>
+        <v>0.16935358269556033</v>
       </c>
       <c r="J32" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.6839281952728469E-2</v>
+        <v>-4.1005787130898641E-2</v>
       </c>
       <c r="K32" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>9.0966666141920616E-3</v>
+        <v>9.1434866751445298E-3</v>
       </c>
       <c r="L32" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.1001489243485916E-2</v>
+        <v>-5.6132037454140304E-2</v>
       </c>
       <c r="M32" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.6864666436522547E-2</v>
+        <v>-6.4040301782469666E-2</v>
       </c>
       <c r="N32" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.8632964863588368E-2</v>
+        <v>-3.8029974467950645E-2</v>
       </c>
       <c r="O32" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.3360033803241169E-2</v>
+        <v>-5.5266547472231038E-2</v>
       </c>
       <c r="Q32" s="9"/>
     </row>
@@ -2673,51 +2674,51 @@
       </c>
       <c r="D33" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.7960392133598031E-3</v>
+        <v>-1.974225033038679E-3</v>
       </c>
       <c r="E33" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.1522894491979665E-2</v>
+        <v>-6.1185427738265401E-2</v>
       </c>
       <c r="F33" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.8397594912157142E-2</v>
+        <v>0.11516427835351341</v>
       </c>
       <c r="G33" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.033451266698961E-3</v>
+        <v>-3.2902630011441891E-2</v>
       </c>
       <c r="H33" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.4863022748378611E-2</v>
+        <v>1.142632978191771E-2</v>
       </c>
       <c r="I33" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.703505961593299E-3</v>
+        <v>-2.8939356883051048E-2</v>
       </c>
       <c r="J33" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.13422232080824914</v>
+        <v>-0.13947434923305491</v>
       </c>
       <c r="K33" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.48789785035828E-2</v>
+        <v>-4.8974996366109025E-2</v>
       </c>
       <c r="L33" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.7767605272885696E-2</v>
+        <v>-9.3671863261679325E-2</v>
       </c>
       <c r="M33" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.2891050713736438E-2</v>
+        <v>-1.7177600578055618E-2</v>
       </c>
       <c r="N33" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.482361159622771E-2</v>
+        <v>2.1876803097139241E-2</v>
       </c>
       <c r="O33" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.8365222286359215E-2</v>
+        <v>-5.3529105070591158E-2</v>
       </c>
       <c r="Q33" s="9"/>
     </row>
@@ -2729,51 +2730,51 @@
       </c>
       <c r="D34" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.12323976642421242</v>
+        <v>0.17295541863251995</v>
       </c>
       <c r="E34" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.11699110812594406</v>
+        <v>0.13454004104334394</v>
       </c>
       <c r="F34" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.9952233144248792E-2</v>
+        <v>1.073756446017593E-2</v>
       </c>
       <c r="G34" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.0050826979960856E-2</v>
+        <v>3.3284770932634267E-2</v>
       </c>
       <c r="H34" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.1711775882321325E-2</v>
+        <v>-8.5444261045404257E-3</v>
       </c>
       <c r="I34" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.770970898691715E-2</v>
+        <v>4.0386116767585856E-2</v>
       </c>
       <c r="J34" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.949572274553371E-2</v>
+        <v>1.3135020082083892E-2</v>
       </c>
       <c r="K34" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.1563898694316732E-3</v>
+        <v>-1.3857839756851398E-2</v>
       </c>
       <c r="L34" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.4936698464624234E-2</v>
+        <v>-6.2707418079635646E-2</v>
       </c>
       <c r="M34" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.6765283135819384E-2</v>
+        <v>1.0957061740741736E-2</v>
       </c>
       <c r="N34" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.5741969431296834E-2</v>
+        <v>5.6146386006895588E-2</v>
       </c>
       <c r="O34" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.3831652752107626E-3</v>
+        <v>-1.5992359410798351E-2</v>
       </c>
       <c r="Q34" s="9"/>
     </row>
@@ -2785,51 +2786,51 @@
       </c>
       <c r="D35" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.0488357896572764E-2</v>
+        <v>-9.8066772747724684E-3</v>
       </c>
       <c r="E35" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.9294140250098475E-2</v>
+        <v>-5.6531413227119194E-2</v>
       </c>
       <c r="F35" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.2350069306394973E-2</v>
+        <v>4.2410626792000805E-2</v>
       </c>
       <c r="G35" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.2059817590544326E-2</v>
+        <v>-2.7399296834362041E-2</v>
       </c>
       <c r="H35" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.14131071871763301</v>
+        <v>0.17071630548363159</v>
       </c>
       <c r="I35" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.32056098289255447</v>
+        <v>0.438004151240174</v>
       </c>
       <c r="J35" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.207028651117418E-2</v>
+        <v>-0.13979387484918482</v>
       </c>
       <c r="K35" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.6021015836184427E-2</v>
+        <v>2.6905920493998536E-2</v>
       </c>
       <c r="L35" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.4671160507302456E-2</v>
+        <v>-4.4860874503123045E-2</v>
       </c>
       <c r="M35" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.2107923718184503E-2</v>
+        <v>-5.6915630124012233E-2</v>
       </c>
       <c r="N35" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.6252632824281929E-2</v>
+        <v>-5.5591305839701954E-2</v>
       </c>
       <c r="O35" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.7661523945049848E-2</v>
+        <v>-4.6510976425183766E-2</v>
       </c>
       <c r="Q35" s="9"/>
     </row>
@@ -2841,51 +2842,51 @@
       </c>
       <c r="D36" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.4127754580429484E-2</v>
+        <v>-4.6740093537538385E-3</v>
       </c>
       <c r="E36" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.3396701155356183E-2</v>
+        <v>-2.0068499530884187E-2</v>
       </c>
       <c r="F36" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.0240441596976586E-2</v>
+        <v>-4.5089133357163469E-3</v>
       </c>
       <c r="G36" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.0797029161330247E-2</v>
+        <v>2.8957575993241003E-2</v>
       </c>
       <c r="H36" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.0435893313324875E-2</v>
+        <v>9.8566068206484836E-4</v>
       </c>
       <c r="I36" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.1023025695752351E-2</v>
+        <v>-0.10703039110667845</v>
       </c>
       <c r="J36" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.6639013382596435E-2</v>
+        <v>1.8361620093210185E-3</v>
       </c>
       <c r="K36" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.12658029840863416</v>
+        <v>-0.13047738985391322</v>
       </c>
       <c r="L36" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.0569593896140143E-2</v>
+        <v>8.5624406964588395E-3</v>
       </c>
       <c r="M36" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.0580965744519175E-2</v>
+        <v>-5.2090351017185954E-2</v>
       </c>
       <c r="N36" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.4727350991854191E-2</v>
+        <v>2.8377041068777809E-2</v>
       </c>
       <c r="O36" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.0740442049450856E-2</v>
+        <v>-7.8528203098174543E-2</v>
       </c>
       <c r="Q36" s="9"/>
     </row>
@@ -2897,51 +2898,51 @@
       </c>
       <c r="D37" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.204259894571317E-2</v>
+        <v>0.14884654186332291</v>
       </c>
       <c r="E37" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.8291398114729072E-2</v>
+        <v>1.9679899319944294E-2</v>
       </c>
       <c r="F37" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.18682019046923259</v>
+        <v>0.20536383240192624</v>
       </c>
       <c r="G37" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.12889179397335382</v>
+        <v>0.1469154245172033</v>
       </c>
       <c r="H37" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.7895661270429573E-2</v>
+        <v>-7.0342751503960299E-2</v>
       </c>
       <c r="I37" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.7163467897932003E-2</v>
+        <v>4.8974186682851029E-2</v>
       </c>
       <c r="J37" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.8399068362724229E-2</v>
+        <v>-0.10780828921531393</v>
       </c>
       <c r="K37" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.6311188811188879E-2</v>
+        <v>-2.9753018777031404E-2</v>
       </c>
       <c r="L37" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.10128953109746908</v>
+        <v>-0.10956104425476865</v>
       </c>
       <c r="M37" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.5643599363212299E-2</v>
+        <v>0.15484814791647783</v>
       </c>
       <c r="N37" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.453510822243111E-2</v>
+        <v>-5.6335453091372001E-2</v>
       </c>
       <c r="O37" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.779980835851716E-2</v>
+        <v>-1.9596616322579474E-2</v>
       </c>
       <c r="Q37" s="9"/>
     </row>
@@ -2953,51 +2954,51 @@
       </c>
       <c r="D38" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.230744295773369E-2</v>
+        <v>-2.9410275879524161E-2</v>
       </c>
       <c r="E38" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.9012747743556444E-2</v>
+        <v>5.4792948784812667E-2</v>
       </c>
       <c r="F38" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.2393749773934637E-3</v>
+        <v>3.7380220127962716E-3</v>
       </c>
       <c r="G38" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.22424917773504194</v>
+        <v>0.50298026620427372</v>
       </c>
       <c r="H38" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.5067825474191083E-2</v>
+        <v>0.13755391533489791</v>
       </c>
       <c r="I38" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.24951604132680807</v>
+        <v>0.18655525232455752</v>
       </c>
       <c r="J38" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.2662079375717292E-2</v>
+        <v>0.25674836302145221</v>
       </c>
       <c r="K38" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.5245411117879248E-2</v>
+        <v>4.7969960665536604E-2</v>
       </c>
       <c r="L38" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.0977803239260293E-2</v>
+        <v>1.9208361234597904E-2</v>
       </c>
       <c r="M38" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.11557065760543672</v>
+        <v>0.29932714335124433</v>
       </c>
       <c r="N38" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.7577991420175723E-2</v>
+        <v>0.13561417914582852</v>
       </c>
       <c r="O38" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.1122313148690106</v>
+        <v>-0.21108318642222623</v>
       </c>
       <c r="Q38" s="9"/>
     </row>
@@ -3009,51 +3010,51 @@
       </c>
       <c r="D39" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.13163134579468094</v>
+        <v>-9.000432713111195E-2</v>
       </c>
       <c r="E39" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.369398673989942E-2</v>
+        <v>1.5276877188431959E-2</v>
       </c>
       <c r="F39" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.17780286203255291</v>
+        <v>4.3471966755228575E-2</v>
       </c>
       <c r="G39" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.103552216657392</v>
+        <v>-0.11192537764103892</v>
       </c>
       <c r="H39" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.20792164571586233</v>
+        <v>3.8558379739390913E-2</v>
       </c>
       <c r="I39" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-9.9827268704229755E-2</v>
+        <v>-7.0307384664389794E-2</v>
       </c>
       <c r="J39" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.10303212915094019</v>
+        <v>3.0778894472361706E-2</v>
       </c>
       <c r="K39" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.0715980159585996E-2</v>
+        <v>8.1952985060846029E-2</v>
       </c>
       <c r="L39" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.9893074723362769E-3</v>
+        <v>-5.85414142103724E-3</v>
       </c>
       <c r="M39" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.0733496670956075E-3</v>
+        <v>-9.6398159593462651E-3</v>
       </c>
       <c r="N39" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.10620085875202145</v>
+        <v>-5.8549227288880346E-2</v>
       </c>
       <c r="O39" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.13390211186324363</v>
+        <v>-9.0620339170303321E-2</v>
       </c>
       <c r="Q39" s="9"/>
     </row>
@@ -3065,51 +3066,51 @@
       </c>
       <c r="D40" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.6217318301750936E-2</v>
+        <v>-0.17142690237172975</v>
       </c>
       <c r="E40" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>9.4774423888344117E-4</v>
+        <v>1.7181068284984446E-2</v>
       </c>
       <c r="F40" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.6279799735401674E-2</v>
+        <v>-0.16793828009618406</v>
       </c>
       <c r="G40" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.15884507282173588</v>
+        <v>-0.13070697620771632</v>
       </c>
       <c r="H40" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.1259619279060311E-2</v>
+        <v>-1.8981136804239962E-2</v>
       </c>
       <c r="I40" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.15634775105166643</v>
+        <v>-0.14090137204514375</v>
       </c>
       <c r="J40" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.2884570308338128</v>
+        <v>-0.15118862280686407</v>
       </c>
       <c r="K40" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.3518507426928608</v>
+        <v>0.56315431539032224</v>
       </c>
       <c r="L40" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.410897329784838E-3</v>
+        <v>0.1342047844114409</v>
       </c>
       <c r="M40" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.17211653921506664</v>
+        <v>-0.19383935836336164</v>
       </c>
       <c r="N40" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.368072307551385E-2</v>
+        <v>-1.5464140496582623E-2</v>
       </c>
       <c r="O40" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.2253543790868884E-2</v>
+        <v>-6.9257412329840506E-2</v>
       </c>
       <c r="Q40" s="9"/>
     </row>
@@ -3129,43 +3130,43 @@
       </c>
       <c r="F41" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.30896050392572472</v>
+        <v>-8.6837644399799144E-2</v>
       </c>
       <c r="G41" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.46750764113142734</v>
+        <v>-4.9158293141557952E-3</v>
       </c>
       <c r="H41" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.31152946025110761</v>
+        <v>-0.13278197514742618</v>
       </c>
       <c r="I41" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.6506178646256418E-2</v>
+        <v>-6.8569220534515751E-2</v>
       </c>
       <c r="J41" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.12509805868626178</v>
+        <v>-0.10656151365592038</v>
       </c>
       <c r="K41" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.6582110388504878E-2</v>
+        <v>0.11549434663143486</v>
       </c>
       <c r="L41" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.0401036084315463E-3</v>
+        <v>-4.4505190341116323E-2</v>
       </c>
       <c r="M41" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.4749570355060685E-2</v>
+        <v>-4.714405051693616E-2</v>
       </c>
       <c r="N41" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.20877003509977654</v>
+        <v>7.8836355409335201E-2</v>
       </c>
       <c r="O41" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.15344237661559701</v>
+        <v>-2.7738578425161697E-2</v>
       </c>
       <c r="Q41" s="9"/>
     </row>
@@ -3319,7 +3320,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations disablePrompts="1" count="2">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"000001.SH,399001.SZ,399006.SZ,IXIC.GI,000300.SH,HSI.HI,DJI.GI,SPX.GI,000688.SH,000905.SH"</formula1>
     </dataValidation>
@@ -3368,22 +3369,22 @@
   </cols>
   <sheetData>
     <row r="8" spans="9:13" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="J8" s="22" t="s">
+      <c r="K8" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="K8" s="22" t="s">
-        <v>29</v>
-      </c>
     </row>
     <row r="9" spans="9:13" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="I9" s="22">
+      <c r="I9" s="21">
         <v>4162.88</v>
       </c>
-      <c r="J9" s="22"/>
-      <c r="K9" s="22">
+      <c r="J9" s="21"/>
+      <c r="K9" s="21">
         <v>3813.28</v>
       </c>
       <c r="L9">
@@ -3395,14 +3396,14 @@
       </c>
     </row>
     <row r="10" spans="9:13" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="22"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
     </row>
     <row r="11" spans="9:13" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="22"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="21"/>
       <c r="M11">
         <f>I9*(1+M9)</f>
         <v>3765.3249599999999</v>
@@ -3445,13 +3446,13 @@
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C1" s="1" t="str">
         <f>[1]!s_info_name(C2)</f>
-        <v>上证指数</v>
+        <v>深证成指</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C2" s="1" t="str">
         <f>IF(月度收益!D5="",月度收益!D4,月度收益!D5)</f>
-        <v>000001.SH</v>
+        <v>399001.SZ</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -3480,7 +3481,7 @@
       </c>
       <c r="C5" s="3">
         <f>[1]!WSD(C2,C4:C4,"-"&amp;月度收益!I4&amp;LEFT(月度收益!L4,1),"","Per="&amp;LEFT(月度收益!L4,1),"TradingCalendar=SSE","Sort=D","rptType=1","ShowParams=Y","cols=1;rows=424")</f>
-        <v>-8.3979954750093242</v>
+        <v>-7.9308118651993613</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -3492,7 +3493,7 @@
         <v>46080</v>
       </c>
       <c r="C6" s="3">
-        <v>1.0911722140417801</v>
+        <v>2.035773535524088</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -3504,7 +3505,7 @@
         <v>46052</v>
       </c>
       <c r="C7" s="3">
-        <v>3.7569540783464861</v>
+        <v>5.0341482603637466</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -3516,7 +3517,7 @@
         <v>46022</v>
       </c>
       <c r="C8" s="3">
-        <v>2.0635698815937742</v>
+        <v>4.1661940366236827</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -3528,7 +3529,7 @@
         <v>45989</v>
       </c>
       <c r="C9" s="3">
-        <v>-1.673762702950099</v>
+        <v>-2.9460663793646868</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -3540,7 +3541,7 @@
         <v>45961</v>
       </c>
       <c r="C10" s="3">
-        <v>1.8546672286698707</v>
+        <v>-1.0963456935093485</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -3552,7 +3553,7 @@
         <v>45930</v>
       </c>
       <c r="C11" s="3">
-        <v>0.64412824357451548</v>
+        <v>6.5402374280261188</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -3564,7 +3565,7 @@
         <v>45898</v>
       </c>
       <c r="C12" s="3">
-        <v>7.9681670942096217</v>
+        <v>15.317144951776228</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -3576,7 +3577,7 @@
         <v>45869</v>
       </c>
       <c r="C13" s="3">
-        <v>3.7388701326572349</v>
+        <v>5.2044181548268842</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -3588,7 +3589,7 @@
         <v>45838</v>
       </c>
       <c r="C14" s="3">
-        <v>2.8958526593962031</v>
+        <v>4.2277580985608854</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -3600,7 +3601,7 @@
         <v>45807</v>
       </c>
       <c r="C15" s="3">
-        <v>2.0876866259957216</v>
+        <v>1.422298371743369</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -3612,7 +3613,7 @@
         <v>45777</v>
       </c>
       <c r="C16" s="3">
-        <v>-1.7002132836125283</v>
+        <v>-5.754866768393585</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -3624,7 +3625,7 @@
         <v>45747</v>
       </c>
       <c r="C17" s="3">
-        <v>0.44713517638741429</v>
+        <v>-1.0074977289647125</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -3636,7 +3637,7 @@
         <v>45716</v>
       </c>
       <c r="C18" s="3">
-        <v>2.162572597735557</v>
+        <v>4.481787314015695</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -3648,7 +3649,7 @@
         <v>45684</v>
       </c>
       <c r="C19" s="3">
-        <v>-3.018181774785389</v>
+        <v>-2.4825199189143055</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -3660,7 +3661,7 @@
         <v>45657</v>
       </c>
       <c r="C20" s="3">
-        <v>0.76078872777411988</v>
+        <v>-1.8574530667462841</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -3672,7 +3673,7 @@
         <v>45625</v>
       </c>
       <c r="C21" s="3">
-        <v>1.4217620918973495</v>
+        <v>0.19356602800544298</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -3684,7 +3685,7 @@
         <v>45596</v>
       </c>
       <c r="C22" s="3">
-        <v>-1.6985776760983007</v>
+        <v>0.58369059387963773</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -3696,7 +3697,7 @@
         <v>45565</v>
       </c>
       <c r="C23" s="3">
-        <v>17.390779343794716</v>
+        <v>26.127870933686648</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -3708,7 +3709,7 @@
         <v>45534</v>
       </c>
       <c r="C24" s="3">
-        <v>-3.2849042277951379</v>
+        <v>-4.6333773710481418</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -3720,7 +3721,7 @@
         <v>45504</v>
       </c>
       <c r="C25" s="3">
-        <v>-0.96560871345137134</v>
+        <v>-1.0692181738983675</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -3732,7 +3733,7 @@
         <v>45471</v>
       </c>
       <c r="C26" s="3">
-        <v>-3.8684100567919044</v>
+        <v>-5.5067849054147411</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -3744,7 +3745,7 @@
         <v>45443</v>
       </c>
       <c r="C27" s="3">
-        <v>-0.58010042113492144</v>
+        <v>-2.3234213762426847</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -3756,7 +3757,7 @@
         <v>45412</v>
       </c>
       <c r="C28" s="3">
-        <v>2.0931965292664501</v>
+        <v>1.9814362369642957</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -3768,7 +3769,7 @@
         <v>45380</v>
       </c>
       <c r="C29" s="3">
-        <v>0.86216331596693507</v>
+        <v>0.75462118192435312</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -3780,7 +3781,7 @@
         <v>45351</v>
       </c>
       <c r="C30" s="3">
-        <v>8.1269170817990464</v>
+        <v>13.607935715816865</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -3792,7 +3793,7 @@
         <v>45322</v>
       </c>
       <c r="C31" s="3">
-        <v>-6.2652331069575018</v>
+        <v>-13.773099900002006</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -3804,7 +3805,7 @@
         <v>45289</v>
       </c>
       <c r="C32" s="3">
-        <v>-1.8067265153757339</v>
+        <v>-2.079033216213988</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -3816,7 +3817,7 @@
         <v>45260</v>
       </c>
       <c r="C33" s="3">
-        <v>0.36114370532163154</v>
+        <v>-1.3877831203754187</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -3828,7 +3829,7 @@
         <v>45230</v>
       </c>
       <c r="C34" s="3">
-        <v>-2.9482535996990578</v>
+        <v>-2.4306180481728723</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -3840,7 +3841,7 @@
         <v>45197</v>
       </c>
       <c r="C35" s="3">
-        <v>-0.30132924496624192</v>
+        <v>-2.9629130148077221</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -3852,7 +3853,7 @@
         <v>45169</v>
       </c>
       <c r="C36" s="3">
-        <v>-5.2008912198509343</v>
+        <v>-6.8464536194953629</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -3864,7 +3865,7 @@
         <v>45138</v>
       </c>
       <c r="C37" s="3">
-        <v>2.7787560535596167</v>
+        <v>1.4267861977762752</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -3876,7 +3877,7 @@
         <v>45107</v>
       </c>
       <c r="C38" s="3">
-        <v>-7.8079254703078416E-2</v>
+        <v>2.1561927865715091</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
@@ -3888,7 +3889,7 @@
         <v>45077</v>
       </c>
       <c r="C39" s="3">
-        <v>-3.5720851957283362</v>
+        <v>-4.8049469875036994</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
@@ -3900,7 +3901,7 @@
         <v>45044</v>
       </c>
       <c r="C40" s="3">
-        <v>1.5403774350031929</v>
+        <v>-3.3064843093288609</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
@@ -3912,7 +3913,7 @@
         <v>45016</v>
       </c>
       <c r="C41" s="3">
-        <v>-0.20566804182198251</v>
+        <v>-0.48710782750638337</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
@@ -3924,7 +3925,7 @@
         <v>44985</v>
       </c>
       <c r="C42" s="3">
-        <v>0.73521290185134536</v>
+        <v>-1.8120348750580773</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
@@ -3936,7 +3937,7 @@
         <v>44957</v>
       </c>
       <c r="C43" s="3">
-        <v>5.3867726614861056</v>
+        <v>8.9440799942919202</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -3948,7 +3949,7 @@
         <v>44925</v>
       </c>
       <c r="C44" s="3">
-        <v>-1.9698760712641428</v>
+        <v>-0.83279582437844057</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
@@ -3960,7 +3961,7 @@
         <v>44895</v>
       </c>
       <c r="C45" s="3">
-        <v>8.9114886422864359</v>
+        <v>6.8428678839623336</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
@@ -3972,7 +3973,7 @@
         <v>44865</v>
       </c>
       <c r="C46" s="3">
-        <v>-4.3283960850954983</v>
+        <v>-3.5400950650939289</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
@@ -3984,7 +3985,7 @@
         <v>44834</v>
       </c>
       <c r="C47" s="3">
-        <v>-5.5508947803557973</v>
+        <v>-8.7778977368145661</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
@@ -3996,7 +3997,7 @@
         <v>44804</v>
       </c>
       <c r="C48" s="3">
-        <v>-1.5707549481006278</v>
+        <v>-3.677593041467675</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
@@ -4008,7 +4009,7 @@
         <v>44771</v>
       </c>
       <c r="C49" s="3">
-        <v>-4.2775616816503774</v>
+        <v>-4.8796056576028146</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
@@ -4020,7 +4021,7 @@
         <v>44742</v>
       </c>
       <c r="C50" s="3">
-        <v>6.6591512481173787</v>
+        <v>11.872208704158616</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -4032,7 +4033,7 @@
         <v>44712</v>
       </c>
       <c r="C51" s="3">
-        <v>4.5737396122901952</v>
+        <v>4.592736664706476</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
@@ -4044,7 +4045,7 @@
         <v>44680</v>
       </c>
       <c r="C52" s="3">
-        <v>-6.3077399014680342</v>
+        <v>-9.0509653688320526</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
@@ -4056,7 +4057,7 @@
         <v>44651</v>
       </c>
       <c r="C53" s="3">
-        <v>-6.0683104187428283</v>
+        <v>-9.9398440807372701</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
@@ -4068,7 +4069,7 @@
         <v>44620</v>
       </c>
       <c r="C54" s="3">
-        <v>3.0006993729502218</v>
+        <v>0.95795891732417537</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
@@ -4080,7 +4081,7 @@
         <v>44589</v>
       </c>
       <c r="C55" s="3">
-        <v>-7.6470570134629767</v>
+        <v>-10.293153784343978</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
@@ -4092,7 +4093,7 @@
         <v>44561</v>
       </c>
       <c r="C56" s="3">
-        <v>2.129365935038563</v>
+        <v>0.41640988094515663</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
@@ -4104,7 +4105,7 @@
         <v>44530</v>
       </c>
       <c r="C57" s="3">
-        <v>0.46657828673184465</v>
+        <v>2.3828336971509101</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
@@ -4116,7 +4117,7 @@
         <v>44498</v>
       </c>
       <c r="C58" s="3">
-        <v>-0.5837927756067951</v>
+        <v>0.99496242672285629</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
@@ -4128,7 +4129,7 @@
         <v>44469</v>
       </c>
       <c r="C59" s="3">
-        <v>0.68360634301898315</v>
+        <v>-0.13517995451517439</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
@@ -4140,7 +4141,7 @@
         <v>44439</v>
       </c>
       <c r="C60" s="3">
-        <v>4.3146122924835772</v>
+        <v>-1.0006626173552857</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
@@ -4152,7 +4153,7 @@
         <v>44407</v>
       </c>
       <c r="C61" s="3">
-        <v>-5.3976320430207618</v>
+        <v>-4.5409935746196561</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
@@ -4164,7 +4165,7 @@
         <v>44377</v>
       </c>
       <c r="C62" s="3">
-        <v>-0.67156554958870407</v>
+        <v>1.1024282437704036</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
@@ -4176,7 +4177,7 @@
         <v>44347</v>
       </c>
       <c r="C63" s="3">
-        <v>4.8920198706276175</v>
+        <v>3.8633327024997444</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
@@ -4188,7 +4189,7 @@
         <v>44316</v>
       </c>
       <c r="C64" s="3">
-        <v>0.14366726163643762</v>
+        <v>4.7892700063107752</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
@@ -4200,7 +4201,7 @@
         <v>44286</v>
       </c>
       <c r="C65" s="3">
-        <v>-1.9141453698239497</v>
+        <v>-5.0234585409741239</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
@@ -4212,7 +4213,7 @@
         <v>44253</v>
       </c>
       <c r="C66" s="3">
-        <v>0.74678964173320317</v>
+        <v>-2.1221792915779414</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
@@ -4224,7 +4225,7 @@
         <v>44225</v>
       </c>
       <c r="C67" s="3">
-        <v>0.28792687781955539</v>
+        <v>2.4277457749886988</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
@@ -4236,7 +4237,7 @@
         <v>44196</v>
       </c>
       <c r="C68" s="3">
-        <v>2.3974077609553834</v>
+        <v>5.8563725153767177</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
@@ -4248,7 +4249,7 @@
         <v>44165</v>
       </c>
       <c r="C69" s="3">
-        <v>5.1859486607748639</v>
+        <v>3.2750824777448395</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
@@ -4260,7 +4261,7 @@
         <v>44134</v>
       </c>
       <c r="C70" s="3">
-        <v>0.20137647864681973</v>
+        <v>2.5501005113474084</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
@@ -4272,7 +4273,7 @@
         <v>44104</v>
       </c>
       <c r="C71" s="3">
-        <v>-5.2309266707453839</v>
+        <v>-6.1837884382173192</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
@@ -4284,7 +4285,7 @@
         <v>44074</v>
       </c>
       <c r="C72" s="3">
-        <v>2.588242651487227</v>
+        <v>0.88243317184737435</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
@@ -4296,7 +4297,7 @@
         <v>44043</v>
       </c>
       <c r="C73" s="3">
-        <v>10.900097936990827</v>
+        <v>13.721549480206829</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
@@ -4308,7 +4309,7 @@
         <v>44012</v>
       </c>
       <c r="C74" s="3">
-        <v>4.6390816109881605</v>
+        <v>11.597445929195139</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
@@ -4320,7 +4321,7 @@
         <v>43980</v>
       </c>
       <c r="C75" s="3">
-        <v>-0.27030691635365756</v>
+        <v>0.22661163450887756</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
@@ -4332,7 +4333,7 @@
         <v>43951</v>
       </c>
       <c r="C76" s="3">
-        <v>3.9917882299368213</v>
+        <v>7.623485959027132</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
@@ -4344,7 +4345,7 @@
         <v>43921</v>
       </c>
       <c r="C77" s="3">
-        <v>-4.513676647581411</v>
+        <v>-9.2750278290932187</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
@@ -4356,7 +4357,7 @@
         <v>43889</v>
       </c>
       <c r="C78" s="3">
-        <v>-3.232769749427189</v>
+        <v>2.7979150533463004</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
@@ -4368,7 +4369,7 @@
         <v>43853</v>
       </c>
       <c r="C79" s="3">
-        <v>-2.4128822303617792</v>
+        <v>2.4076639739082584</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
@@ -4380,7 +4381,7 @@
         <v>43830</v>
       </c>
       <c r="C80" s="3">
-        <v>6.2027806378822881</v>
+        <v>8.8561532259786357</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
@@ -4392,7 +4393,7 @@
         <v>43798</v>
       </c>
       <c r="C81" s="3">
-        <v>-1.9485731256564165</v>
+        <v>-0.55185764230928358</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
@@ -4404,7 +4405,7 @@
         <v>43769</v>
       </c>
       <c r="C82" s="3">
-        <v>0.82152652914997404</v>
+        <v>2.001758753024041</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
@@ -4416,7 +4417,7 @@
         <v>43738</v>
       </c>
       <c r="C83" s="3">
-        <v>0.65665790034876714</v>
+        <v>0.8601813319110585</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
@@ -4428,7 +4429,7 @@
         <v>43707</v>
       </c>
       <c r="C84" s="3">
-        <v>-1.5778076210454572</v>
+        <v>0.41881970314481265</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
@@ -4440,7 +4441,7 @@
         <v>43677</v>
       </c>
       <c r="C85" s="3">
-        <v>-1.5567134261002424</v>
+        <v>1.6157783235449585</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
@@ -4452,7 +4453,7 @@
         <v>43644</v>
       </c>
       <c r="C86" s="3">
-        <v>2.7661506150989723</v>
+        <v>2.8648173165088497</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
@@ -4464,7 +4465,7 @@
         <v>43616</v>
       </c>
       <c r="C87" s="3">
-        <v>-5.8357057437698039</v>
+        <v>-7.7713298994248277</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
@@ -4476,7 +4477,7 @@
         <v>43585</v>
       </c>
       <c r="C88" s="3">
-        <v>-0.40181405338106657</v>
+        <v>-2.3451346697111575</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
@@ -4488,7 +4489,7 @@
         <v>43553</v>
       </c>
       <c r="C89" s="3">
-        <v>5.0937284359924284</v>
+        <v>9.6871613194907891</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
@@ -4500,7 +4501,7 @@
         <v>43524</v>
       </c>
       <c r="C90" s="3">
-        <v>13.788795392228126</v>
+        <v>20.760350353866674</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
@@ -4512,7 +4513,7 @@
         <v>43496</v>
       </c>
       <c r="C91" s="3">
-        <v>3.6359251840553775</v>
+        <v>3.307088047633866</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
@@ -4524,7 +4525,7 @@
         <v>43462</v>
       </c>
       <c r="C92" s="3">
-        <v>-3.6431402284417103</v>
+        <v>-5.7533808639995465</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
@@ -4536,7 +4537,7 @@
         <v>43434</v>
       </c>
       <c r="C93" s="3">
-        <v>-0.56077279121825585</v>
+        <v>2.6583417595123171</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
@@ -4548,7 +4549,7 @@
         <v>43404</v>
       </c>
       <c r="C94" s="3">
-        <v>-7.7468903983238473</v>
+        <v>-10.930238534662395</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.2">
@@ -4560,7 +4561,7 @@
         <v>43371</v>
       </c>
       <c r="C95" s="3">
-        <v>3.5262894606472805</v>
+        <v>-0.76050476868998462</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.2">
@@ -4572,7 +4573,7 @@
         <v>43343</v>
       </c>
       <c r="C96" s="3">
-        <v>-5.2548655509042641</v>
+        <v>-7.7713046109850303</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.2">
@@ -4584,7 +4585,7 @@
         <v>43312</v>
       </c>
       <c r="C97" s="3">
-        <v>1.0178624628395916</v>
+        <v>-2.1397178641631598</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
@@ -4596,7 +4597,7 @@
         <v>43280</v>
       </c>
       <c r="C98" s="3">
-        <v>-8.0134940251632596</v>
+        <v>-8.8993610845817699</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
@@ -4608,7 +4609,7 @@
         <v>43251</v>
       </c>
       <c r="C99" s="3">
-        <v>0.42962702737847636</v>
+        <v>-0.27835720231160765</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
@@ -4620,7 +4621,7 @@
         <v>43217</v>
       </c>
       <c r="C100" s="3">
-        <v>-2.7348636115170133</v>
+        <v>-5.0069397271966025</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
@@ -4632,7 +4633,7 @@
         <v>43189</v>
       </c>
       <c r="C101" s="3">
-        <v>-2.7769275893045564</v>
+        <v>0.36869235138945466</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.2">
@@ -4644,7 +4645,7 @@
         <v>43159</v>
       </c>
       <c r="C102" s="3">
-        <v>-6.3612754347852523</v>
+        <v>-2.9655502543263768</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.2">
@@ -4656,7 +4657,7 @@
         <v>43131</v>
       </c>
       <c r="C103" s="3">
-        <v>5.251051192648859</v>
+        <v>1.0799016344442469</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.2">
@@ -4668,7 +4669,7 @@
         <v>43098</v>
       </c>
       <c r="C104" s="3">
-        <v>-0.30195149603200466</v>
+        <v>0.88039686411813811</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
@@ -4680,7 +4681,7 @@
         <v>43069</v>
       </c>
       <c r="C105" s="3">
-        <v>-2.244197806545678</v>
+        <v>-3.7256763491866352</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
@@ -4692,7 +4693,7 @@
         <v>43039</v>
       </c>
       <c r="C106" s="3">
-        <v>1.3257496073910691</v>
+        <v>2.5293405139346969</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
@@ -4704,7 +4705,7 @@
         <v>43007</v>
       </c>
       <c r="C107" s="3">
-        <v>-0.35310532105903292</v>
+        <v>2.5011666742259964</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.2">
@@ -4716,7 +4717,7 @@
         <v>42978</v>
       </c>
       <c r="C108" s="3">
-        <v>2.6819810876673511</v>
+        <v>2.9661960482983307</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
@@ -4728,7 +4729,7 @@
         <v>42947</v>
       </c>
       <c r="C109" s="3">
-        <v>2.524768852185777</v>
+        <v>-0.23329830259419815</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
@@ -4740,7 +4741,7 @@
         <v>42916</v>
       </c>
       <c r="C110" s="3">
-        <v>2.4140137274171636</v>
+        <v>6.7387211861919871</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
@@ -4752,7 +4753,7 @@
         <v>42886</v>
       </c>
       <c r="C111" s="3">
-        <v>-1.1881032824346383</v>
+        <v>-3.6132901705594911</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
@@ -4764,7 +4765,7 @@
         <v>42853</v>
       </c>
       <c r="C112" s="3">
-        <v>-2.105678851624615</v>
+        <v>-1.8609191530145841</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.2">
@@ -4776,7 +4777,7 @@
         <v>42825</v>
       </c>
       <c r="C113" s="3">
-        <v>-0.5928588013615288</v>
+        <v>0.3597089970323486</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.2">
@@ -4788,7 +4789,7 @@
         <v>42794</v>
       </c>
       <c r="C114" s="3">
-        <v>2.6135726960849759</v>
+        <v>3.3753772961884199</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.2">
@@ -4800,7 +4801,7 @@
         <v>42761</v>
       </c>
       <c r="C115" s="3">
-        <v>1.789149138013002</v>
+        <v>-1.2291107895865294</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.2">
@@ -4812,7 +4813,7 @@
         <v>42734</v>
       </c>
       <c r="C116" s="3">
-        <v>-4.5044667225019879</v>
+        <v>-7.58300458410055</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.2">
@@ -4824,7 +4825,7 @@
         <v>42704</v>
       </c>
       <c r="C117" s="3">
-        <v>4.8231700001161171</v>
+        <v>2.8763103140568402</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.2">
@@ -4836,7 +4837,7 @@
         <v>42674</v>
       </c>
       <c r="C118" s="3">
-        <v>3.1879689939405154</v>
+        <v>1.2938349065258814</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.2">
@@ -4848,7 +4849,7 @@
         <v>42643</v>
       </c>
       <c r="C119" s="3">
-        <v>-2.6183190941085233</v>
+        <v>-1.7689181181227753</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
@@ -4860,7 +4861,7 @@
         <v>42613</v>
       </c>
       <c r="C120" s="3">
-        <v>3.5629379536870509</v>
+        <v>4.1477583236643634</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
@@ -4872,7 +4873,7 @@
         <v>42580</v>
       </c>
       <c r="C121" s="3">
-        <v>1.6976002916432975</v>
+        <v>-1.5305825275574669</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
@@ -4884,7 +4885,7 @@
         <v>42551</v>
       </c>
       <c r="C122" s="3">
-        <v>0.4453791654438044</v>
+        <v>3.2486333080510299</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
@@ -4896,7 +4897,7 @@
         <v>42521</v>
       </c>
       <c r="C123" s="3">
-        <v>-0.73878850664528262</v>
+        <v>0.18136297038093829</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.2">
@@ -4908,7 +4909,7 @@
         <v>42489</v>
       </c>
       <c r="C124" s="3">
-        <v>-2.1835171767510042</v>
+        <v>-3.0015965959690361</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.2">
@@ -4920,7 +4921,7 @@
         <v>42460</v>
       </c>
       <c r="C125" s="3">
-        <v>11.753663254065616</v>
+        <v>14.927481175312153</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.2">
@@ -4932,7 +4933,7 @@
         <v>42429</v>
       </c>
       <c r="C126" s="3">
-        <v>-1.8125730566920017</v>
+        <v>-3.4066155288205779</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.2">
@@ -4944,7 +4945,7 @@
         <v>42398</v>
       </c>
       <c r="C127" s="3">
-        <v>-22.648792856654442</v>
+        <v>-25.63532727090405</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.2">
@@ -4956,7 +4957,7 @@
         <v>42369</v>
       </c>
       <c r="C128" s="3">
-        <v>2.7218049966146296</v>
+        <v>5.2088424044246295</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.2">
@@ -4968,7 +4969,7 @@
         <v>42338</v>
       </c>
       <c r="C129" s="3">
-        <v>1.8578703025387888</v>
+        <v>4.2595169551910006</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.2">
@@ -4980,7 +4981,7 @@
         <v>42307</v>
       </c>
       <c r="C130" s="3">
-        <v>10.802601195093775</v>
+        <v>15.596335694440967</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
@@ -4992,7 +4993,7 @@
         <v>42277</v>
       </c>
       <c r="C131" s="3">
-        <v>-4.7786897351843933</v>
+        <v>-5.3171327431380089</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
@@ -5004,7 +5005,7 @@
         <v>42247</v>
       </c>
       <c r="C132" s="3">
-        <v>-12.493842333607097</v>
+        <v>-14.749099218425609</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
@@ -5016,7 +5017,7 @@
         <v>42216</v>
       </c>
       <c r="C133" s="3">
-        <v>-14.343335799342082</v>
+        <v>-13.695883620862514</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
@@ -5028,7 +5029,7 @@
         <v>42185</v>
       </c>
       <c r="C134" s="3">
-        <v>-7.2537005523290121</v>
+        <v>-10.946794772418755</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.2">
@@ -5040,7 +5041,7 @@
         <v>42153</v>
       </c>
       <c r="C135" s="3">
-        <v>3.8294059308973782</v>
+        <v>8.6499705775968661</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.2">
@@ -5052,7 +5053,7 @@
         <v>42124</v>
       </c>
       <c r="C136" s="3">
-        <v>18.510530833408257</v>
+        <v>12.597966181645525</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.2">
@@ -5064,7 +5065,7 @@
         <v>42094</v>
       </c>
       <c r="C137" s="3">
-        <v>13.219212863595864</v>
+        <v>11.932452003302707</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.2">
@@ -5076,7 +5077,7 @@
         <v>42062</v>
       </c>
       <c r="C138" s="3">
-        <v>3.1130436028573794</v>
+        <v>5.4435176859843892</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.2">
@@ -5088,7 +5089,7 @@
         <v>42034</v>
       </c>
       <c r="C139" s="3">
-        <v>-0.75166701342979092</v>
+        <v>1.2353576481593853</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.2">
@@ -5100,7 +5101,7 @@
         <v>42004</v>
       </c>
       <c r="C140" s="3">
-        <v>20.569360396744486</v>
+        <v>22.354435185871214</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.2">
@@ -5112,7 +5113,7 @@
         <v>41971</v>
       </c>
       <c r="C141" s="3">
-        <v>10.852796777757678</v>
+        <v>9.4414251486698131</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
@@ -5124,7 +5125,7 @@
         <v>41943</v>
       </c>
       <c r="C142" s="3">
-        <v>2.3820260843447461</v>
+        <v>1.7977695509573399</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
@@ -5136,7 +5137,7 @@
         <v>41912</v>
       </c>
       <c r="C143" s="3">
-        <v>6.6151001262854114</v>
+        <v>3.0432810432328372</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.2">
@@ -5148,7 +5149,7 @@
         <v>41880</v>
       </c>
       <c r="C144" s="3">
-        <v>0.71031385897830646</v>
+        <v>-1.4478741551208318</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
@@ -5160,7 +5161,7 @@
         <v>41851</v>
       </c>
       <c r="C145" s="3">
-        <v>7.4809832609734617</v>
+        <v>8.3563804978024301</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.2">
@@ -5172,7 +5173,7 @@
         <v>41820</v>
       </c>
       <c r="C146" s="3">
-        <v>0.44698638493694265</v>
+        <v>-0.29266124169345931</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.2">
@@ -5184,7 +5185,7 @@
         <v>41789</v>
       </c>
       <c r="C147" s="3">
-        <v>0.63434003270892436</v>
+        <v>0.71062465010278686</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.2">
@@ -5196,7 +5197,7 @@
         <v>41759</v>
       </c>
       <c r="C148" s="3">
-        <v>-0.34170951150491735</v>
+        <v>1.714759892722495</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.2">
@@ -5208,7 +5209,7 @@
         <v>41729</v>
       </c>
       <c r="C149" s="3">
-        <v>-1.1183182236850442</v>
+        <v>-2.3940917128534411</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.2">
@@ -5220,7 +5221,7 @@
         <v>41698</v>
       </c>
       <c r="C150" s="3">
-        <v>1.1420586370551655</v>
+        <v>-2.7296842815855094</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.2">
@@ -5232,7 +5233,7 @@
         <v>41669</v>
       </c>
       <c r="C151" s="3">
-        <v>-3.9175738122041004</v>
+        <v>-6.7614914351371791</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.2">
@@ -5244,7 +5245,7 @@
         <v>41639</v>
       </c>
       <c r="C152" s="3">
-        <v>-4.7073096918537338</v>
+        <v>-4.9261302871441703</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
@@ -5256,7 +5257,7 @@
         <v>41607</v>
       </c>
       <c r="C153" s="3">
-        <v>3.6836703532942883</v>
+        <v>1.1629356952917336</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
@@ -5268,7 +5269,7 @@
         <v>41578</v>
       </c>
       <c r="C154" s="3">
-        <v>-1.5198202941602457</v>
+        <v>-0.82404640798611206</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.2">
@@ -5280,7 +5281,7 @@
         <v>41547</v>
       </c>
       <c r="C155" s="3">
-        <v>3.6353247406811562</v>
+        <v>3.8048000355014544</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
@@ -5292,7 +5293,7 @@
         <v>41516</v>
       </c>
       <c r="C156" s="3">
-        <v>5.2454134042599021</v>
+        <v>5.6286247346561513</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.2">
@@ -5304,7 +5305,7 @@
         <v>41486</v>
       </c>
       <c r="C157" s="3">
-        <v>0.73731587313297098</v>
+        <v>0.92183135255909932</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.2">
@@ -5316,7 +5317,7 @@
         <v>41453</v>
       </c>
       <c r="C158" s="3">
-        <v>-13.969820850692971</v>
+        <v>-16.888006187979656</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.2">
@@ -5328,7 +5329,7 @@
         <v>41425</v>
       </c>
       <c r="C159" s="3">
-        <v>5.633055881045701</v>
+        <v>6.5186726259770289</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.2">
@@ -5340,7 +5341,7 @@
         <v>41390</v>
       </c>
       <c r="C160" s="3">
-        <v>-2.624897110417912</v>
+        <v>-2.2315877949134588</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.2">
@@ -5352,7 +5353,7 @@
         <v>41362</v>
       </c>
       <c r="C161" s="3">
-        <v>-5.4519944893309908</v>
+        <v>-7.7962141739052138</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.2">
@@ -5364,7 +5365,7 @@
         <v>41333</v>
       </c>
       <c r="C162" s="3">
-        <v>-0.83125753011417114</v>
+        <v>-0.27137867316971986</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.2">
@@ -5376,7 +5377,7 @@
         <v>41305</v>
       </c>
       <c r="C163" s="3">
-        <v>5.1250524430530131</v>
+        <v>6.0460589850209745</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
@@ -5388,7 +5389,7 @@
         <v>41274</v>
       </c>
       <c r="C164" s="3">
-        <v>14.595652681129456</v>
+        <v>15.35106249314364</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
@@ -5400,7 +5401,7 @@
         <v>41243</v>
       </c>
       <c r="C165" s="3">
-        <v>-4.2903890027454539</v>
+        <v>-6.6890040799093669</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.2">
@@ -5412,7 +5413,7 @@
         <v>41213</v>
       </c>
       <c r="C166" s="3">
-        <v>-0.82874397999394001</v>
+        <v>-2.4129244808778205</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
@@ -5424,7 +5425,7 @@
         <v>41180</v>
       </c>
       <c r="C167" s="3">
-        <v>1.8875010866794106</v>
+        <v>5.7024155662517728</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.2">
@@ -5436,7 +5437,7 @@
         <v>41152</v>
       </c>
       <c r="C168" s="3">
-        <v>-2.6673841552285249</v>
+        <v>-9.3631639972695186</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.2">
@@ -5448,7 +5449,7 @@
         <v>41121</v>
       </c>
       <c r="C169" s="3">
-        <v>-5.4729623160637235</v>
+        <v>-4.6429292833070619</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.2">
@@ -5460,7 +5461,7 @@
         <v>41089</v>
       </c>
       <c r="C170" s="3">
-        <v>-6.1883861372866171</v>
+        <v>-6.3215371432572054</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.2">
@@ -5472,7 +5473,7 @@
         <v>41060</v>
       </c>
       <c r="C171" s="3">
-        <v>-1.004959279160178</v>
+        <v>-0.38292234887199461</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.2">
@@ -5484,7 +5485,7 @@
         <v>41026</v>
       </c>
       <c r="C172" s="3">
-        <v>5.9010388953803838</v>
+        <v>8.1839485446845153</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.2">
@@ -5496,7 +5497,7 @@
         <v>40998</v>
       </c>
       <c r="C173" s="3">
-        <v>-6.82313720435811</v>
+        <v>-6.4106706766737691</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.2">
@@ -5508,7 +5509,7 @@
         <v>40968</v>
       </c>
       <c r="C174" s="3">
-        <v>5.9267385207252943</v>
+        <v>8.0742083025703071</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
@@ -5520,7 +5521,7 @@
         <v>40939</v>
       </c>
       <c r="C175" s="3">
-        <v>4.2371683041460662</v>
+        <v>4.3148440331093108</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
@@ -5532,7 +5533,7 @@
         <v>40907</v>
       </c>
       <c r="C176" s="3">
-        <v>-5.7425300439613469</v>
+        <v>-7.9906967483495128</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.2">
@@ -5544,7 +5545,7 @@
         <v>40877</v>
       </c>
       <c r="C177" s="3">
-        <v>-5.4628177858806808</v>
+        <v>-7.5139167278572732</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
@@ -5556,7 +5557,7 @@
         <v>40847</v>
       </c>
       <c r="C178" s="3">
-        <v>4.6214426802078767</v>
+        <v>1.8322180372304153</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.2">
@@ -5568,7 +5569,7 @@
         <v>40816</v>
       </c>
       <c r="C179" s="3">
-        <v>-8.1064448027920122</v>
+        <v>-9.6964144972033655</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.2">
@@ -5580,7 +5581,7 @@
         <v>40786</v>
       </c>
       <c r="C180" s="3">
-        <v>-4.9741850496478275</v>
+        <v>-4.9451695969484959</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.2">
@@ -5592,7 +5593,7 @@
         <v>40753</v>
       </c>
       <c r="C181" s="3">
-        <v>-2.1848421259950901</v>
+        <v>-0.99499369619066025</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.2">
@@ -5604,7 +5605,7 @@
         <v>40724</v>
       </c>
       <c r="C182" s="3">
-        <v>0.67811882169745985</v>
+        <v>3.8215568933114508</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.2">
@@ -5616,7 +5617,7 @@
         <v>40694</v>
       </c>
       <c r="C183" s="3">
-        <v>-5.7715392454296026</v>
+        <v>-5.2615160686790059</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.2">
@@ -5628,7 +5629,7 @@
         <v>40662</v>
       </c>
       <c r="C184" s="3">
-        <v>-0.56691839892681894</v>
+        <v>-1.9892698350484461</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.2">
@@ -5640,7 +5641,7 @@
         <v>40633</v>
       </c>
       <c r="C185" s="3">
-        <v>0.79372045880057307</v>
+        <v>-2.6315497811072119</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.2">
@@ -5652,7 +5653,7 @@
         <v>40602</v>
       </c>
       <c r="C186" s="3">
-        <v>4.0978695621949113</v>
+        <v>7.5679442659764895</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
@@ -5664,7 +5665,7 @@
         <v>40574</v>
       </c>
       <c r="C187" s="3">
-        <v>-0.6190357315700501</v>
+        <v>-3.7232898333610542</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.2">
@@ -5676,7 +5677,7 @@
         <v>40543</v>
       </c>
       <c r="C188" s="3">
-        <v>-0.42919231070629449</v>
+        <v>0.99109229615910177</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
@@ -5688,7 +5689,7 @@
         <v>40512</v>
       </c>
       <c r="C189" s="3">
-        <v>-5.3260418922162494</v>
+        <v>-7.7124994277051773</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.2">
@@ -5700,7 +5701,7 @@
         <v>40480</v>
       </c>
       <c r="C190" s="3">
-        <v>12.169375725338138</v>
+        <v>16.555660121778338</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.2">
@@ -5712,7 +5713,7 @@
         <v>40451</v>
       </c>
       <c r="C191" s="3">
-        <v>0.63892726915815157</v>
+        <v>1.1450063913773567</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.2">
@@ -5724,7 +5725,7 @@
         <v>40421</v>
       </c>
       <c r="C192" s="3">
-        <v>4.909947021860539E-2</v>
+        <v>5.1307394310762033</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.2">
@@ -5736,7 +5737,7 @@
         <v>40389</v>
       </c>
       <c r="C193" s="3">
-        <v>9.970646730904754</v>
+        <v>14.897394112690865</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.2">
@@ -5748,7 +5749,7 @@
         <v>40359</v>
       </c>
       <c r="C194" s="3">
-        <v>-7.4755405461187197</v>
+        <v>-8.0088501038888644</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.2">
@@ -5760,7 +5761,7 @@
         <v>40329</v>
       </c>
       <c r="C195" s="3">
-        <v>-9.7005132356839709</v>
+        <v>-8.585530332396651</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.2">
@@ -5772,7 +5773,7 @@
         <v>40298</v>
       </c>
       <c r="C196" s="3">
-        <v>-7.6708248836883985</v>
+        <v>-10.659322013550121</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.2">
@@ -5784,7 +5785,7 @@
         <v>40268</v>
       </c>
       <c r="C197" s="3">
-        <v>1.872970759938819</v>
+        <v>0.46391091495261438</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
@@ -5796,7 +5797,7 @@
         <v>40235</v>
       </c>
       <c r="C198" s="3">
-        <v>2.0958474448130371</v>
+        <v>2.4672156783390964</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.2">
@@ -5808,7 +5809,7 @@
         <v>40207</v>
       </c>
       <c r="C199" s="3">
-        <v>-8.7834846187482505</v>
+        <v>-11.407076073889211</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
@@ -5820,7 +5821,7 @@
         <v>40178</v>
       </c>
       <c r="C200" s="3">
-        <v>2.5611984598634008</v>
+        <v>1.5807858558900545</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.2">
@@ -5832,7 +5833,7 @@
         <v>40147</v>
       </c>
       <c r="C201" s="3">
-        <v>6.6576475174975558</v>
+        <v>9.6738662140093634</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.2">
@@ -5844,7 +5845,7 @@
         <v>40116</v>
       </c>
       <c r="C202" s="3">
-        <v>7.7865717597806139</v>
+        <v>9.7290076325660557</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.2">
@@ -5856,7 +5857,7 @@
         <v>40086</v>
       </c>
       <c r="C203" s="3">
-        <v>4.1863446468834109</v>
+        <v>5.8739443282694426</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.2">
@@ -5868,7 +5869,7 @@
         <v>40056</v>
       </c>
       <c r="C204" s="3">
-        <v>-21.814287079191409</v>
+        <v>-22.571111480757644</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.2">
@@ -5880,7 +5881,7 @@
         <v>40025</v>
       </c>
       <c r="C205" s="3">
-        <v>15.297216089143539</v>
+        <v>18.191214349648298</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.2">
@@ -5892,7 +5893,7 @@
         <v>39994</v>
       </c>
       <c r="C206" s="3">
-        <v>12.398050840698405</v>
+        <v>14.205197118460667</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.2">
@@ -5904,7 +5905,7 @@
         <v>39960</v>
       </c>
       <c r="C207" s="3">
-        <v>6.2707032579112809</v>
+        <v>6.5814569530848521</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.2">
@@ -5916,7 +5917,7 @@
         <v>39933</v>
       </c>
       <c r="C208" s="3">
-        <v>4.3972454221344659</v>
+        <v>5.795654909349901</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
@@ -5928,7 +5929,7 @@
         <v>39903</v>
       </c>
       <c r="C209" s="3">
-        <v>13.940548824400413</v>
+        <v>18.055858772804111</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.2">
@@ -5940,7 +5941,7 @@
         <v>39871</v>
       </c>
       <c r="C210" s="3">
-        <v>4.6313855174447305</v>
+        <v>8.4528446370157653</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
@@ -5952,7 +5953,7 @@
         <v>39836</v>
       </c>
       <c r="C211" s="3">
-        <v>9.328401448809732</v>
+        <v>8.1677887315930064</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.2">
@@ -5964,7 +5965,7 @@
         <v>39813</v>
       </c>
       <c r="C212" s="3">
-        <v>-2.690903377377396</v>
+        <v>-2.5981777012375029</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.2">
@@ -5976,7 +5977,7 @@
         <v>39780</v>
       </c>
       <c r="C213" s="3">
-        <v>8.2352587306930847</v>
+        <v>14.028735150905192</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.2">
@@ -5988,7 +5989,7 @@
         <v>39752</v>
       </c>
       <c r="C214" s="3">
-        <v>-24.631700282153858</v>
+        <v>-22.752729132936011</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.2">
@@ -6000,7 +6001,7 @@
         <v>39717</v>
       </c>
       <c r="C215" s="3">
-        <v>-4.3207783198998539</v>
+        <v>-5.5592383240690708</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.2">
@@ -6012,7 +6013,7 @@
         <v>39689</v>
       </c>
       <c r="C216" s="3">
-        <v>-13.630640299425334</v>
+        <v>-15.480868995750319</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.2">
@@ -6024,7 +6025,7 @@
         <v>39660</v>
       </c>
       <c r="C217" s="3">
-        <v>1.4478256118282129</v>
+        <v>1.0624091190720719</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.2">
@@ -6036,7 +6037,7 @@
         <v>39629</v>
       </c>
       <c r="C218" s="3">
-        <v>-20.308159310108998</v>
+        <v>-22.222853941915666</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.2">
@@ -6048,7 +6049,7 @@
         <v>39598</v>
       </c>
       <c r="C219" s="3">
-        <v>-7.0334293139704185</v>
+        <v>-10.786052602447194</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
@@ -6060,7 +6061,7 @@
         <v>39568</v>
       </c>
       <c r="C220" s="3">
-        <v>6.3464213714176765</v>
+        <v>1.524168520879865</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.2">
@@ -6072,7 +6073,7 @@
         <v>39538</v>
       </c>
       <c r="C221" s="3">
-        <v>-20.140768988601454</v>
+        <v>-15.936322329986885</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
@@ -6084,7 +6085,7 @@
         <v>39507</v>
       </c>
       <c r="C222" s="3">
-        <v>-0.79504621191849312</v>
+        <v>-0.21331579402069645</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.2">
@@ -6096,7 +6097,7 @@
         <v>39478</v>
       </c>
       <c r="C223" s="3">
-        <v>-16.690287657868964</v>
+        <v>-10.411566328008137</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.2">
@@ -6108,7 +6109,7 @@
         <v>39444</v>
       </c>
       <c r="C224" s="3">
-        <v>8.0008777083028004</v>
+        <v>13.192282373741637</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.2">
@@ -6120,7 +6121,7 @@
         <v>39416</v>
       </c>
       <c r="C225" s="3">
-        <v>-18.186897383859812</v>
+        <v>-19.934801602874998</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.2">
@@ -6132,7 +6133,7 @@
         <v>39386</v>
       </c>
       <c r="C226" s="3">
-        <v>7.2485983738993953</v>
+        <v>3.5336439795088603</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.2">
@@ -6144,7 +6145,7 @@
         <v>39353</v>
       </c>
       <c r="C227" s="3">
-        <v>6.3898674510066922</v>
+        <v>5.5529981880707791</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.2">
@@ -6156,7 +6157,7 @@
         <v>39325</v>
       </c>
       <c r="C228" s="3">
-        <v>16.725288479259358</v>
+        <v>17.583065880451045</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.2">
@@ -6168,7 +6169,7 @@
         <v>39294</v>
       </c>
       <c r="C229" s="3">
-        <v>17.021186938634081</v>
+        <v>21.146325944496326</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.2">
@@ -6180,7 +6181,7 @@
         <v>39262</v>
       </c>
       <c r="C230" s="3">
-        <v>-7.031029862854643</v>
+        <v>-3.0730221995471596</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
@@ -6192,7 +6193,7 @@
         <v>39233</v>
       </c>
       <c r="C231" s="3">
-        <v>6.9868002057651868</v>
+        <v>19.127264588369354</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.2">
@@ -6204,7 +6205,7 @@
         <v>39202</v>
       </c>
       <c r="C232" s="3">
-        <v>20.643608963992577</v>
+        <v>27.098246280148565</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
@@ -6216,7 +6217,7 @@
         <v>39171</v>
       </c>
       <c r="C233" s="3">
-        <v>10.513791215980994</v>
+        <v>6.3373019313285317</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.2">
@@ -6228,7 +6229,7 @@
         <v>39141</v>
       </c>
       <c r="C234" s="3">
-        <v>3.4000936714357666</v>
+        <v>5.3290227170717186</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.2">
@@ -6240,7 +6241,7 @@
         <v>39113</v>
       </c>
       <c r="C235" s="3">
-        <v>4.143602217775233</v>
+        <v>14.830425540973335</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.2">
@@ -6252,7 +6253,7 @@
         <v>39080</v>
       </c>
       <c r="C236" s="3">
-        <v>27.446673611875248</v>
+        <v>17.295656692832793</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.2">
@@ -6264,7 +6265,7 @@
         <v>39051</v>
       </c>
       <c r="C237" s="3">
-        <v>14.216376232118421</v>
+        <v>22.609788540658805</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.2">
@@ -6276,7 +6277,7 @@
         <v>39021</v>
       </c>
       <c r="C238" s="3">
-        <v>4.8828936376128063</v>
+        <v>6.8225578426815758</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.2">
@@ -6288,7 +6289,7 @@
         <v>38989</v>
       </c>
       <c r="C239" s="3">
-        <v>5.6543983678174481</v>
+        <v>3.5402177494753939</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.2">
@@ -6300,7 +6301,7 @@
         <v>38960</v>
       </c>
       <c r="C240" s="3">
-        <v>2.8464104101546761</v>
+        <v>5.8764316925021154</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.2">
@@ -6312,7 +6313,7 @@
         <v>38929</v>
       </c>
       <c r="C241" s="3">
-        <v>-3.5568477901413154</v>
+        <v>-8.2469383309733963</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
@@ -6324,7 +6325,7 @@
         <v>38898</v>
       </c>
       <c r="C242" s="3">
-        <v>1.8833241942362688</v>
+        <v>0.22278164858886562</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.2">
@@ -6336,7 +6337,7 @@
         <v>38868</v>
       </c>
       <c r="C243" s="3">
-        <v>13.961518459294142</v>
+        <v>11.537886830011136</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
@@ -6348,7 +6349,7 @@
         <v>38835</v>
       </c>
       <c r="C244" s="3">
-        <v>10.931876037418299</v>
+        <v>9.4332094565003466</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.2">
@@ -6360,7 +6361,7 @@
         <v>38807</v>
       </c>
       <c r="C245" s="3">
-        <v>-5.6580679430029424E-2</v>
+        <v>4.9157456742046746</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.2">
@@ -6372,7 +6373,7 @@
         <v>38776</v>
       </c>
       <c r="C246" s="3">
-        <v>3.2577505115075178</v>
+        <v>3.3707373084990611</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.2">
@@ -6384,7 +6385,7 @@
         <v>38742</v>
       </c>
       <c r="C247" s="3">
-        <v>8.3535089147216635</v>
+        <v>13.225779190756292</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.2">
@@ -6396,7 +6397,7 @@
         <v>38716</v>
       </c>
       <c r="C248" s="3">
-        <v>5.6215948714636532</v>
+        <v>6.9770517328782589</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.2">
@@ -6408,7 +6409,7 @@
         <v>38686</v>
       </c>
       <c r="C249" s="3">
-        <v>0.58966871855030689</v>
+        <v>0.54670937673253484</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.2">
@@ -6420,7 +6421,7 @@
         <v>38656</v>
       </c>
       <c r="C250" s="3">
-        <v>-5.4340809301375748</v>
+        <v>-8.29514151897156</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.2">
@@ -6432,7 +6433,7 @@
         <v>38625</v>
       </c>
       <c r="C251" s="3">
-        <v>-0.61782012008964049</v>
+        <v>-1.6039679599570644</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.2">
@@ -6444,7 +6445,7 @@
         <v>38595</v>
       </c>
       <c r="C252" s="3">
-        <v>7.3649648717998506</v>
+        <v>2.1769500466135572</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
@@ -6456,7 +6457,7 @@
         <v>38562</v>
       </c>
       <c r="C253" s="3">
-        <v>0.19381315117052988</v>
+        <v>4.6134561250330552</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.2">
@@ -6468,7 +6469,7 @@
         <v>38533</v>
       </c>
       <c r="C254" s="3">
-        <v>1.9043345293559888</v>
+        <v>-1.4789068210891876</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
@@ -6480,7 +6481,7 @@
         <v>38503</v>
       </c>
       <c r="C255" s="3">
-        <v>-8.4896984504108985</v>
+        <v>-11.246274557508663</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.2">
@@ -6492,7 +6493,7 @@
         <v>38471</v>
       </c>
       <c r="C256" s="3">
-        <v>-1.8700750739056526</v>
+        <v>-0.43143501506142101</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.2">
@@ -6504,7 +6505,7 @@
         <v>38442</v>
       </c>
       <c r="C257" s="3">
-        <v>-9.5533471209484073</v>
+        <v>-6.1003732468328025</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.2">
@@ -6516,7 +6517,7 @@
         <v>38411</v>
       </c>
       <c r="C258" s="3">
-        <v>9.580281635779798</v>
+        <v>10.863100906128565</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.2">
@@ -6528,7 +6529,7 @@
         <v>38383</v>
       </c>
       <c r="C259" s="3">
-        <v>-5.8960312547374771</v>
+        <v>-0.71998357005709224</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.2">
@@ -6540,7 +6541,7 @@
         <v>38352</v>
       </c>
       <c r="C260" s="3">
-        <v>-5.5397230399523707</v>
+        <v>-4.911182716703788</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.2">
@@ -6552,7 +6553,7 @@
         <v>38321</v>
       </c>
       <c r="C261" s="3">
-        <v>1.5323323256617005</v>
+        <v>0.30024736129299345</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.2">
@@ -6564,7 +6565,7 @@
         <v>38289</v>
       </c>
       <c r="C262" s="3">
-        <v>-5.4531395432089962</v>
+        <v>-6.8781138604573577</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.2">
@@ -6576,7 +6577,7 @@
         <v>38260</v>
       </c>
       <c r="C263" s="3">
-        <v>4.0711979029284917</v>
+        <v>8.7575004912160423</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
@@ -6588,7 +6589,7 @@
         <v>38230</v>
       </c>
       <c r="C264" s="3">
-        <v>-3.1842401035346968</v>
+        <v>-3.2764507198396742</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.2">
@@ -6600,7 +6601,7 @@
         <v>38198</v>
       </c>
       <c r="C265" s="3">
-        <v>-0.92626872370747959</v>
+        <v>0.22955874047956293</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
@@ -6612,7 +6613,7 @@
         <v>38168</v>
       </c>
       <c r="C266" s="3">
-        <v>-10.074130442327489</v>
+        <v>-8.4356538150203715</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.2">
@@ -6624,7 +6625,7 @@
         <v>38138</v>
       </c>
       <c r="C267" s="3">
-        <v>-2.4869217410269706</v>
+        <v>-0.98309821655172547</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.2">
@@ -6636,7 +6637,7 @@
         <v>38107</v>
       </c>
       <c r="C268" s="3">
-        <v>-8.3850523333695133</v>
+        <v>-11.008824073437806</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.2">
@@ -6648,7 +6649,7 @@
         <v>38077</v>
       </c>
       <c r="C269" s="3">
-        <v>3.9733336039692757</v>
+        <v>3.5772431974342211</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.2">
@@ -6660,7 +6661,7 @@
         <v>38044</v>
       </c>
       <c r="C270" s="3">
-        <v>5.3018458832396975</v>
+        <v>5.4629043961463175</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.2">
@@ -6672,7 +6673,7 @@
         <v>38016</v>
       </c>
       <c r="C271" s="3">
-        <v>6.2579990968869348</v>
+        <v>6.812841902226463</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.2">
@@ -6684,7 +6685,7 @@
         <v>37986</v>
       </c>
       <c r="C272" s="3">
-        <v>7.1440891767611037</v>
+        <v>6.4828933465404415</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.2">
@@ -6696,7 +6697,7 @@
         <v>37953</v>
       </c>
       <c r="C273" s="3">
-        <v>3.6284129012543742</v>
+        <v>3.1761677546988221</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.2">
@@ -6708,7 +6709,7 @@
         <v>37925</v>
       </c>
       <c r="C274" s="3">
-        <v>-1.3793547358357916</v>
+        <v>3.6808151117518451</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
@@ -6720,7 +6721,7 @@
         <v>37894</v>
       </c>
       <c r="C275" s="3">
-        <v>-3.8553203519310686</v>
+        <v>-4.3062731528903715</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.2">
@@ -6732,7 +6733,7 @@
         <v>37862</v>
       </c>
       <c r="C276" s="3">
-        <v>-3.7080952529284117</v>
+        <v>-3.798557023256266</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
@@ -6744,7 +6745,7 @@
         <v>37833</v>
       </c>
       <c r="C277" s="3">
-        <v>-0.62461979079745378</v>
+        <v>2.90284038703712</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.2">
@@ -6756,7 +6757,7 @@
         <v>37802</v>
       </c>
       <c r="C278" s="3">
-        <v>-5.7247498986525809</v>
+        <v>-7.9597201922201428</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.2">
@@ -6768,7 +6769,7 @@
         <v>37771</v>
       </c>
       <c r="C279" s="3">
-        <v>3.6029587681176478</v>
+        <v>7.4503320397674822</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.2">
@@ -6780,7 +6781,7 @@
         <v>37741</v>
       </c>
       <c r="C280" s="3">
-        <v>0.7193273038532233</v>
+        <v>5.1225732697714577</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.2">
@@ -6792,7 +6793,7 @@
         <v>37711</v>
       </c>
       <c r="C281" s="3">
-        <v>-8.9554292124249812E-2</v>
+        <v>1.4594204382317288</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.2">
@@ -6804,7 +6805,7 @@
         <v>37680</v>
       </c>
       <c r="C282" s="3">
-        <v>0.80789964095571154</v>
+        <v>0.19736374216337005</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.2">
@@ -6816,7 +6817,7 @@
         <v>37650</v>
       </c>
       <c r="C283" s="3">
-        <v>10.471077314249433</v>
+        <v>10.579458558330002</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.2">
@@ -6828,7 +6829,7 @@
         <v>37621</v>
       </c>
       <c r="C284" s="3">
-        <v>-5.3360033803241169</v>
+        <v>-5.5266547472231036</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.2">
@@ -6840,7 +6841,7 @@
         <v>37589</v>
       </c>
       <c r="C285" s="3">
-        <v>-4.8632964863588368</v>
+        <v>-3.8029974467950645</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
@@ -6852,7 +6853,7 @@
         <v>37560</v>
       </c>
       <c r="C286" s="3">
-        <v>-4.6864666436522544</v>
+        <v>-6.4040301782469662</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.2">
@@ -6864,7 +6865,7 @@
         <v>37526</v>
       </c>
       <c r="C287" s="3">
-        <v>-5.1001489243485914</v>
+        <v>-5.6132037454140304</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
@@ -6876,7 +6877,7 @@
         <v>37498</v>
       </c>
       <c r="C288" s="3">
-        <v>0.90966666141920616</v>
+        <v>0.91434866751445298</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.2">
@@ -6888,7 +6889,7 @@
         <v>37468</v>
       </c>
       <c r="C289" s="3">
-        <v>-4.6839281952728467</v>
+        <v>-4.1005787130898641</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.2">
@@ -6900,7 +6901,7 @@
         <v>37435</v>
       </c>
       <c r="C290" s="3">
-        <v>14.317957054441655</v>
+        <v>16.935358269556033</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.2">
@@ -6912,7 +6913,7 @@
         <v>37407</v>
       </c>
       <c r="C291" s="3">
-        <v>-9.1150406925742509</v>
+        <v>-6.6531938305680711</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.2">
@@ -6924,7 +6925,7 @@
         <v>37376</v>
       </c>
       <c r="C292" s="3">
-        <v>3.9805350067491529</v>
+        <v>2.5066952329941161</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.2">
@@ -6936,7 +6937,7 @@
         <v>37344</v>
       </c>
       <c r="C293" s="3">
-        <v>5.1947234244615892</v>
+        <v>4.76680893483723</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.2">
@@ -6948,7 +6949,7 @@
         <v>37315</v>
       </c>
       <c r="C294" s="3">
-        <v>2.214706385146803</v>
+        <v>1.5688150690465585</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.2">
@@ -6960,7 +6961,7 @@
         <v>37287</v>
       </c>
       <c r="C295" s="3">
-        <v>-9.3747702723802622</v>
+        <v>-10.312737546547101</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.2">
@@ -6972,7 +6973,7 @@
         <v>37256</v>
       </c>
       <c r="C296" s="3">
-        <v>-5.8365222286359213</v>
+        <v>-5.3529105070591161</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
@@ -6984,7 +6985,7 @@
         <v>37225</v>
       </c>
       <c r="C297" s="3">
-        <v>3.482361159622771</v>
+        <v>2.1876803097139241</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.2">
@@ -6996,7 +6997,7 @@
         <v>37195</v>
       </c>
       <c r="C298" s="3">
-        <v>-4.2891050713736441</v>
+        <v>-1.7177600578055618</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
@@ -7008,7 +7009,7 @@
         <v>37162</v>
       </c>
       <c r="C299" s="3">
-        <v>-3.7767605272885696</v>
+        <v>-9.367186326167932</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.2">
@@ -7020,7 +7021,7 @@
         <v>37134</v>
       </c>
       <c r="C300" s="3">
-        <v>-4.48789785035828</v>
+        <v>-4.8974996366109025</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.2">
@@ -7032,7 +7033,7 @@
         <v>37103</v>
       </c>
       <c r="C301" s="3">
-        <v>-13.422232080824914</v>
+        <v>-13.94743492330549</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.2">
@@ -7044,7 +7045,7 @@
         <v>37071</v>
       </c>
       <c r="C302" s="3">
-        <v>0.1703505961593299</v>
+        <v>-2.8939356883051048</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.2">
@@ -7056,7 +7057,7 @@
         <v>37042</v>
       </c>
       <c r="C303" s="3">
-        <v>4.4863022748378611</v>
+        <v>1.142632978191771</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.2">
@@ -7068,7 +7069,7 @@
         <v>37011</v>
       </c>
       <c r="C304" s="3">
-        <v>0.3033451266698961</v>
+        <v>-3.2902630011441891</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.2">
@@ -7080,7 +7081,7 @@
         <v>36980</v>
       </c>
       <c r="C305" s="3">
-        <v>7.8397594912157142</v>
+        <v>11.51642783535134</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.2">
@@ -7092,7 +7093,7 @@
         <v>36950</v>
       </c>
       <c r="C306" s="3">
-        <v>-5.1522894491979665</v>
+        <v>-6.1185427738265403</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.2">
@@ -7104,7 +7105,7 @@
         <v>36910</v>
       </c>
       <c r="C307" s="3">
-        <v>-0.37960392133598031</v>
+        <v>-0.1974225033038679</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
@@ -7116,7 +7117,7 @@
         <v>36889</v>
       </c>
       <c r="C308" s="3">
-        <v>0.13831652752107626</v>
+        <v>-1.5992359410798351</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.2">
@@ -7128,7 +7129,7 @@
         <v>36860</v>
       </c>
       <c r="C309" s="3">
-        <v>5.5741969431296834</v>
+        <v>5.6146386006895588</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
@@ -7140,7 +7141,7 @@
         <v>36830</v>
       </c>
       <c r="C310" s="3">
-        <v>2.6765283135819384</v>
+        <v>1.0957061740741736</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.2">
@@ -7152,7 +7153,7 @@
         <v>36798</v>
       </c>
       <c r="C311" s="3">
-        <v>-5.4936698464624234</v>
+        <v>-6.2707418079635646</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.2">
@@ -7164,7 +7165,7 @@
         <v>36769</v>
       </c>
       <c r="C312" s="3">
-        <v>-0.11563898694316732</v>
+        <v>-1.3857839756851398</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.2">
@@ -7176,7 +7177,7 @@
         <v>36738</v>
       </c>
       <c r="C313" s="3">
-        <v>4.949572274553371</v>
+        <v>1.3135020082083892</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.2">
@@ -7188,7 +7189,7 @@
         <v>36707</v>
       </c>
       <c r="C314" s="3">
-        <v>1.770970898691715</v>
+        <v>4.0386116767585856</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.2">
@@ -7200,7 +7201,7 @@
         <v>36677</v>
       </c>
       <c r="C315" s="3">
-        <v>3.1711775882321325</v>
+        <v>-0.85444261045404257</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.2">
@@ -7212,7 +7213,7 @@
         <v>36644</v>
       </c>
       <c r="C316" s="3">
-        <v>2.0050826979960856</v>
+        <v>3.3284770932634267</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.2">
@@ -7224,7 +7225,7 @@
         <v>36616</v>
       </c>
       <c r="C317" s="3">
-        <v>4.9952233144248792</v>
+        <v>1.073756446017593</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.2">
@@ -7236,7 +7237,7 @@
         <v>36585</v>
       </c>
       <c r="C318" s="3">
-        <v>11.699110812594405</v>
+        <v>13.454004104334395</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
@@ -7248,7 +7249,7 @@
         <v>36553</v>
       </c>
       <c r="C319" s="3">
-        <v>12.323976642421242</v>
+        <v>17.295541863251994</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.2">
@@ -7260,7 +7261,7 @@
         <v>36524</v>
       </c>
       <c r="C320" s="3">
-        <v>-4.7661523945049851</v>
+        <v>-4.6510976425183763</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
@@ -7272,7 +7273,7 @@
         <v>36494</v>
       </c>
       <c r="C321" s="3">
-        <v>-4.6252632824281932</v>
+        <v>-5.5591305839701954</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.2">
@@ -7284,7 +7285,7 @@
         <v>36462</v>
       </c>
       <c r="C322" s="3">
-        <v>-4.2107923718184503</v>
+        <v>-5.6915630124012235</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.2">
@@ -7296,7 +7297,7 @@
         <v>36433</v>
       </c>
       <c r="C323" s="3">
-        <v>-3.4671160507302456</v>
+        <v>-4.4860874503123043</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.2">
@@ -7308,7 +7309,7 @@
         <v>36403</v>
       </c>
       <c r="C324" s="3">
-        <v>1.6021015836184427</v>
+        <v>2.6905920493998536</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.2">
@@ -7320,7 +7321,7 @@
         <v>36371</v>
       </c>
       <c r="C325" s="3">
-        <v>-5.207028651117418</v>
+        <v>-13.979387484918481</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.2">
@@ -7332,7 +7333,7 @@
         <v>36341</v>
       </c>
       <c r="C326" s="3">
-        <v>32.056098289255445</v>
+        <v>43.800415124017398</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.2">
@@ -7344,7 +7345,7 @@
         <v>36311</v>
       </c>
       <c r="C327" s="3">
-        <v>14.1310718717633</v>
+        <v>17.07163054836316</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.2">
@@ -7356,7 +7357,7 @@
         <v>36280</v>
       </c>
       <c r="C328" s="3">
-        <v>-3.2059817590544326</v>
+        <v>-2.7399296834362041</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.2">
@@ -7368,7 +7369,7 @@
         <v>36250</v>
       </c>
       <c r="C329" s="3">
-        <v>6.2350069306394973</v>
+        <v>4.2410626792000805</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
@@ -7380,7 +7381,7 @@
         <v>36200</v>
       </c>
       <c r="C330" s="3">
-        <v>-3.9294140250098475</v>
+        <v>-5.6531413227119192</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.2">
@@ -7392,7 +7393,7 @@
         <v>36189</v>
       </c>
       <c r="C331" s="3">
-        <v>-1.0488357896572764</v>
+        <v>-0.98066772747724684</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
@@ -7404,7 +7405,7 @@
         <v>36160</v>
       </c>
       <c r="C332" s="3">
-        <v>-8.0740442049450856</v>
+        <v>-7.8528203098174547</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.2">
@@ -7416,7 +7417,7 @@
         <v>36129</v>
       </c>
       <c r="C333" s="3">
-        <v>2.4727350991854191</v>
+        <v>2.8377041068777809</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.2">
@@ -7428,7 +7429,7 @@
         <v>36098</v>
       </c>
       <c r="C334" s="3">
-        <v>-2.0580965744519175</v>
+        <v>-5.2090351017185954</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.2">
@@ -7440,7 +7441,7 @@
         <v>36068</v>
       </c>
       <c r="C335" s="3">
-        <v>8.0569593896140148</v>
+        <v>0.85624406964588395</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.2">
@@ -7452,7 +7453,7 @@
         <v>36038</v>
       </c>
       <c r="C336" s="3">
-        <v>-12.658029840863417</v>
+        <v>-13.047738985391321</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.2">
@@ -7464,7 +7465,7 @@
         <v>36007</v>
       </c>
       <c r="C337" s="3">
-        <v>-1.6639013382596435</v>
+        <v>0.18361620093210185</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.2">
@@ -7476,7 +7477,7 @@
         <v>35976</v>
       </c>
       <c r="C338" s="3">
-        <v>-5.1023025695752349</v>
+        <v>-10.703039110667845</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.2">
@@ -7488,7 +7489,7 @@
         <v>35944</v>
       </c>
       <c r="C339" s="3">
-        <v>5.0435893313324875</v>
+        <v>9.8566068206484836E-2</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.2">
@@ -7500,7 +7501,7 @@
         <v>35915</v>
       </c>
       <c r="C340" s="3">
-        <v>8.0797029161330247</v>
+        <v>2.8957575993241003</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
@@ -7512,7 +7513,7 @@
         <v>35885</v>
       </c>
       <c r="C341" s="3">
-        <v>3.0240441596976586</v>
+        <v>-0.45089133357163469</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.2">
@@ -7524,7 +7525,7 @@
         <v>35853</v>
       </c>
       <c r="C342" s="3">
-        <v>-1.3396701155356183</v>
+        <v>-2.0068499530884187</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
@@ -7536,7 +7537,7 @@
         <v>35818</v>
       </c>
       <c r="C343" s="3">
-        <v>2.4127754580429484</v>
+        <v>-0.46740093537538385</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.2">
@@ -7548,7 +7549,7 @@
         <v>35795</v>
       </c>
       <c r="C344" s="3">
-        <v>4.779980835851716</v>
+        <v>-1.9596616322579474</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.2">
@@ -7560,7 +7561,7 @@
         <v>35762</v>
       </c>
       <c r="C345" s="3">
-        <v>-3.453510822243111</v>
+        <v>-5.6335453091372001</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.2">
@@ -7572,7 +7573,7 @@
         <v>35734</v>
       </c>
       <c r="C346" s="3">
-        <v>7.5643599363212299</v>
+        <v>15.484814791647782</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.2">
@@ -7584,7 +7585,7 @@
         <v>35703</v>
       </c>
       <c r="C347" s="3">
-        <v>-10.128953109746908</v>
+        <v>-10.956104425476864</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.2">
@@ -7596,7 +7597,7 @@
         <v>35671</v>
       </c>
       <c r="C348" s="3">
-        <v>2.6311188811188879</v>
+        <v>-2.9753018777031404</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.2">
@@ -7608,7 +7609,7 @@
         <v>35642</v>
       </c>
       <c r="C349" s="3">
-        <v>-4.8399068362724229</v>
+        <v>-10.780828921531393</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.2">
@@ -7620,7 +7621,7 @@
         <v>35608</v>
       </c>
       <c r="C350" s="3">
-        <v>-2.7163467897932003</v>
+        <v>4.8974186682851029</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.2">
@@ -7632,7 +7633,7 @@
         <v>35580</v>
       </c>
       <c r="C351" s="3">
-        <v>-7.7895661270429573</v>
+        <v>-7.0342751503960299</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
@@ -7644,7 +7645,7 @@
         <v>35550</v>
       </c>
       <c r="C352" s="3">
-        <v>12.889179397335383</v>
+        <v>14.691542451720331</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.2">
@@ -7656,7 +7657,7 @@
         <v>35520</v>
       </c>
       <c r="C353" s="3">
-        <v>18.682019046923259</v>
+        <v>20.536383240192624</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
@@ -7668,7 +7669,7 @@
         <v>35489</v>
       </c>
       <c r="C354" s="3">
-        <v>7.8291398114729072</v>
+        <v>1.9679899319944294</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.2">
@@ -7680,7 +7681,7 @@
         <v>35461</v>
       </c>
       <c r="C355" s="3">
-        <v>5.204259894571317</v>
+        <v>14.884654186332291</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.2">
@@ -7692,7 +7693,7 @@
         <v>35430</v>
       </c>
       <c r="C356" s="3">
-        <v>-11.22313148690106</v>
+        <v>-21.108318642222624</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.2">
@@ -7704,7 +7705,7 @@
         <v>35398</v>
       </c>
       <c r="C357" s="3">
-        <v>5.7577991420175723</v>
+        <v>13.561417914582851</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.2">
@@ -7716,7 +7717,7 @@
         <v>35369</v>
       </c>
       <c r="C358" s="3">
-        <v>11.557065760543672</v>
+        <v>29.932714335124434</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.2">
@@ -7728,7 +7729,7 @@
         <v>35335</v>
       </c>
       <c r="C359" s="3">
-        <v>8.0977803239260293</v>
+        <v>1.9208361234597904</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.2">
@@ -7740,7 +7741,7 @@
         <v>35307</v>
       </c>
       <c r="C360" s="3">
-        <v>-1.5245411117879248</v>
+        <v>4.7969960665536604</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.2">
@@ -7752,7 +7753,7 @@
         <v>35277</v>
       </c>
       <c r="C361" s="3">
-        <v>2.2662079375717292</v>
+        <v>25.67483630214522</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.2">
@@ -7764,7 +7765,7 @@
         <v>35244</v>
       </c>
       <c r="C362" s="3">
-        <v>24.951604132680806</v>
+        <v>18.655525232455751</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
@@ -7776,7 +7777,7 @@
         <v>35216</v>
       </c>
       <c r="C363" s="3">
-        <v>-5.5067825474191086</v>
+        <v>13.755391533489792</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.2">
@@ -7788,7 +7789,7 @@
         <v>35185</v>
       </c>
       <c r="C364" s="3">
-        <v>22.424917773504195</v>
+        <v>50.298026620427372</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
@@ -7800,7 +7801,7 @@
         <v>35153</v>
       </c>
       <c r="C365" s="3">
-        <v>0.62393749773934637</v>
+        <v>0.37380220127962716</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.2">
@@ -7812,7 +7813,7 @@
         <v>35111</v>
       </c>
       <c r="C366" s="3">
-        <v>2.9012747743556444</v>
+        <v>5.4792948784812667</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.2">
@@ -7824,7 +7825,7 @@
         <v>35095</v>
       </c>
       <c r="C367" s="3">
-        <v>-3.230744295773369</v>
+        <v>-2.9410275879524161</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.2">
@@ -7836,7 +7837,7 @@
         <v>35062</v>
       </c>
       <c r="C368" s="3">
-        <v>-13.390211186324363</v>
+        <v>-9.0620339170303321</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.2">
@@ -7848,7 +7849,7 @@
         <v>35033</v>
       </c>
       <c r="C369" s="3">
-        <v>-10.620085875202145</v>
+        <v>-5.8549227288880346</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.2">
@@ -7860,7 +7861,7 @@
         <v>35003</v>
       </c>
       <c r="C370" s="3">
-        <v>-0.70733496670956075</v>
+        <v>-0.96398159593462651</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.2">
@@ -7872,7 +7873,7 @@
         <v>34971</v>
       </c>
       <c r="C371" s="3">
-        <v>-0.19893074723362769</v>
+        <v>-0.585414142103724</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.2">
@@ -7884,7 +7885,7 @@
         <v>34942</v>
       </c>
       <c r="C372" s="3">
-        <v>4.0715980159585996</v>
+        <v>8.1952985060846029</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.2">
@@ -7896,7 +7897,7 @@
         <v>34911</v>
       </c>
       <c r="C373" s="3">
-        <v>10.303212915094019</v>
+        <v>3.0778894472361706</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.2">
@@ -7908,7 +7909,7 @@
         <v>34880</v>
       </c>
       <c r="C374" s="3">
-        <v>-9.9827268704229759</v>
+        <v>-7.0307384664389794</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.2">
@@ -7920,7 +7921,7 @@
         <v>34850</v>
       </c>
       <c r="C375" s="3">
-        <v>20.792164571586234</v>
+        <v>3.8558379739390913</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
@@ -7932,7 +7933,7 @@
         <v>34817</v>
       </c>
       <c r="C376" s="3">
-        <v>-10.355221665739201</v>
+        <v>-11.192537764103893</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.2">
@@ -7944,7 +7945,7 @@
         <v>34789</v>
       </c>
       <c r="C377" s="3">
-        <v>17.78028620325529</v>
+        <v>4.3471966755228575</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.2">
@@ -7956,7 +7957,7 @@
         <v>34758</v>
       </c>
       <c r="C378" s="3">
-        <v>-2.369398673989942</v>
+        <v>1.5276877188431959</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.2">
@@ -7968,7 +7969,7 @@
         <v>34726</v>
       </c>
       <c r="C379" s="3">
-        <v>-13.163134579468094</v>
+        <v>-9.000432713111195</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.2">
@@ -7980,7 +7981,7 @@
         <v>34698</v>
       </c>
       <c r="C380" s="3">
-        <v>-5.2253543790868884</v>
+        <v>-6.9257412329840502</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.2">
@@ -7992,7 +7993,7 @@
         <v>34668</v>
       </c>
       <c r="C381" s="3">
-        <v>4.368072307551385</v>
+        <v>-1.5464140496582623</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.2">
@@ -8004,7 +8005,7 @@
         <v>34638</v>
       </c>
       <c r="C382" s="3">
-        <v>-17.211653921506663</v>
+        <v>-19.383935836336164</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.2">
@@ -8016,7 +8017,7 @@
         <v>34607</v>
       </c>
       <c r="C383" s="3">
-        <v>0.7410897329784838</v>
+        <v>13.420478441144091</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.2">
@@ -8028,7 +8029,7 @@
         <v>34577</v>
       </c>
       <c r="C384" s="3">
-        <v>135.18507426928608</v>
+        <v>56.315431539032225</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.2">
@@ -8040,7 +8041,7 @@
         <v>34544</v>
       </c>
       <c r="C385" s="3">
-        <v>-28.845703083381281</v>
+        <v>-15.118862280686407</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.2">
@@ -8052,7 +8053,7 @@
         <v>34515</v>
       </c>
       <c r="C386" s="3">
-        <v>-15.634775105166643</v>
+        <v>-14.090137204514374</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
@@ -8064,7 +8065,7 @@
         <v>34485</v>
       </c>
       <c r="C387" s="3">
-        <v>-6.1259619279060313</v>
+        <v>-1.8981136804239962</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.2">
@@ -8076,7 +8077,7 @@
         <v>34453</v>
       </c>
       <c r="C388" s="3">
-        <v>-15.884507282173587</v>
+        <v>-13.070697620771632</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.2">
@@ -8088,7 +8089,7 @@
         <v>34424</v>
       </c>
       <c r="C389" s="3">
-        <v>-8.6279799735401674</v>
+        <v>-16.793828009618405</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.2">
@@ -8100,7 +8101,7 @@
         <v>34393</v>
       </c>
       <c r="C390" s="3">
-        <v>9.4774423888344117E-2</v>
+        <v>1.7181068284984446</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.2">
@@ -8112,7 +8113,7 @@
         <v>34365</v>
       </c>
       <c r="C391" s="3">
-        <v>-7.6217318301750936</v>
+        <v>-17.142690237172975</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.2">
@@ -8124,7 +8125,7 @@
         <v>34334</v>
       </c>
       <c r="C392" s="3">
-        <v>-15.344237661559701</v>
+        <v>-2.7738578425161697</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.2">
@@ -8136,7 +8137,7 @@
         <v>34303</v>
       </c>
       <c r="C393" s="3">
-        <v>20.877003509977655</v>
+        <v>7.8836355409335201</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.2">
@@ -8148,7 +8149,7 @@
         <v>34271</v>
       </c>
       <c r="C394" s="3">
-        <v>-8.474957035506069</v>
+        <v>-4.7144050516936158</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.2">
@@ -8160,7 +8161,7 @@
         <v>34242</v>
       </c>
       <c r="C395" s="3">
-        <v>-0.60401036084315463</v>
+        <v>-4.4505190341116325</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.2">
@@ -8172,7 +8173,7 @@
         <v>34212</v>
       </c>
       <c r="C396" s="3">
-        <v>1.6582110388504878</v>
+        <v>11.549434663143487</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.2">
@@ -8184,7 +8185,7 @@
         <v>34180</v>
       </c>
       <c r="C397" s="3">
-        <v>-12.509805868626177</v>
+        <v>-10.656151365592038</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
@@ -8196,7 +8197,7 @@
         <v>34150</v>
       </c>
       <c r="C398" s="3">
-        <v>7.6506178646256418</v>
+        <v>-6.8569220534515747</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.2">
@@ -8208,7 +8209,7 @@
         <v>34120</v>
       </c>
       <c r="C399" s="3">
-        <v>-31.152946025110761</v>
+        <v>-13.278197514742619</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.2">
@@ -8220,7 +8221,7 @@
         <v>34089</v>
       </c>
       <c r="C400" s="3">
-        <v>46.750764113142736</v>
+        <v>-0.49158293141557952</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.2">
@@ -8232,7 +8233,7 @@
         <v>34059</v>
       </c>
       <c r="C401" s="3">
-        <v>-30.896050392572473</v>
+        <v>-8.6837644399799139</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.2">
@@ -8240,7 +8241,7 @@
         <v>34026</v>
       </c>
       <c r="C402" s="3">
-        <v>11.798277818570192</v>
+        <v>21.997081812646236</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.2">
@@ -8248,7 +8249,7 @@
         <v>33998</v>
       </c>
       <c r="C403" s="3">
-        <v>53.574494803880121</v>
+        <v>13.050650064725055</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.2">
@@ -8256,7 +8257,7 @@
         <v>33969</v>
       </c>
       <c r="C404" s="3">
-        <v>7.6994203698592223</v>
+        <v>11.466240704189335</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.2">
@@ -8264,7 +8265,7 @@
         <v>33938</v>
       </c>
       <c r="C405" s="3">
-        <v>42.84869393790045</v>
+        <v>-5.639318582337971</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.2">
@@ -8272,7 +8273,7 @@
         <v>33907</v>
       </c>
       <c r="C406" s="3">
-        <v>-27.77508827884726</v>
+        <v>-13.829920814923513</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.2">
@@ -8280,7 +8281,7 @@
         <v>33877</v>
       </c>
       <c r="C407" s="3">
-        <v>-14.691413509541206</v>
+        <v>-0.6645852091786919</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.2">
@@ -8288,7 +8289,7 @@
         <v>33847</v>
       </c>
       <c r="C408" s="3">
-        <v>-21.747602345851512</v>
+        <v>-9.0815339308306431</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
@@ -8296,7 +8297,7 @@
         <v>33816</v>
       </c>
       <c r="C409" s="3">
-        <v>-11.679077225295719</v>
+        <v>7.2174388825983371</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.2">
@@ -8304,7 +8305,7 @@
         <v>33785</v>
       </c>
       <c r="C410" s="3">
-        <v>-3.5247143053834473</v>
+        <v>-4.8802790176554423</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.2">
@@ -8312,7 +8313,7 @@
         <v>33753</v>
       </c>
       <c r="C411" s="3">
-        <v>177.22618887242353</v>
+        <v>38.547550374554326</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.2">
@@ -8320,7 +8321,7 @@
         <v>33724</v>
       </c>
       <c r="C412" s="3">
-        <v>16.824047843877878</v>
+        <v>58.006171374317582</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.2">
@@ -8328,7 +8329,7 @@
         <v>33694</v>
       </c>
       <c r="C413" s="3">
-        <v>4.5467010365820126</v>
+        <v>27.135011165429425</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.2">
@@ -8336,7 +8337,7 @@
         <v>33662</v>
       </c>
       <c r="C414" s="3">
-        <v>16.415528029625847</v>
+        <v>-1.0559840756407035</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.2">
@@ -8344,7 +8345,7 @@
         <v>33634</v>
       </c>
       <c r="C415" s="3">
-        <v>6.9991460290350194</v>
+        <v>4.273690546613107</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.2">
@@ -8352,7 +8353,7 @@
         <v>33603</v>
       </c>
       <c r="C416" s="3">
-        <v>12.769645608628654</v>
+        <v>7.0871304734385632</v>
       </c>
     </row>
     <row r="417" spans="2:3" x14ac:dyDescent="0.2">
@@ -8360,7 +8361,7 @@
         <v>33571</v>
       </c>
       <c r="C417" s="3">
-        <v>18.755718206770378</v>
+        <v>15.387081468562847</v>
       </c>
     </row>
     <row r="418" spans="2:3" x14ac:dyDescent="0.2">
@@ -8368,7 +8369,7 @@
         <v>33542</v>
       </c>
       <c r="C418" s="3">
-        <v>20.826884810966174</v>
+        <v>88.46005123495577</v>
       </c>
     </row>
     <row r="419" spans="2:3" x14ac:dyDescent="0.2">
@@ -8376,7 +8377,7 @@
         <v>33511</v>
       </c>
       <c r="C419" s="3">
-        <v>1.3955052401501966</v>
+        <v>-4.6084330405514518</v>
       </c>
     </row>
     <row r="420" spans="2:3" x14ac:dyDescent="0.2">
@@ -8384,7 +8385,7 @@
         <v>33480</v>
       </c>
       <c r="C420" s="3">
-        <v>24.082058414464534</v>
+        <v>-25.007779813976004</v>
       </c>
     </row>
     <row r="421" spans="2:3" x14ac:dyDescent="0.2">
@@ -8392,7 +8393,7 @@
         <v>33450</v>
       </c>
       <c r="C421" s="3">
-        <v>4.5362023844140786</v>
+        <v>-16.341967862773178</v>
       </c>
     </row>
     <row r="422" spans="2:3" x14ac:dyDescent="0.2">
@@ -8400,7 +8401,7 @@
         <v>33417</v>
       </c>
       <c r="C422" s="3">
-        <v>19.794478794740055</v>
+        <v>-12.240908802437023</v>
       </c>
     </row>
     <row r="423" spans="2:3" x14ac:dyDescent="0.2">
@@ -8408,7 +8409,7 @@
         <v>33389</v>
       </c>
       <c r="C423" s="3">
-        <v>0.78111286642092992</v>
+        <v>-10.571182092669529</v>
       </c>
     </row>
     <row r="424" spans="2:3" x14ac:dyDescent="0.2">
@@ -8416,40 +8417,32 @@
         <v>33358</v>
       </c>
       <c r="C424" s="3">
-        <v>-5.2000998419169608</v>
+        <v>-10.836496128738416</v>
       </c>
     </row>
     <row r="425" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B425" s="2">
         <v>33326</v>
       </c>
-      <c r="C425" s="3">
-        <v>-9.6383730546575457</v>
-      </c>
+      <c r="C425" s="3"/>
     </row>
     <row r="426" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B426" s="2">
         <v>33297</v>
       </c>
-      <c r="C426" s="3">
-        <v>2.3390013079941374</v>
-      </c>
+      <c r="C426" s="3"/>
     </row>
     <row r="427" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B427" s="2">
         <v>33269</v>
       </c>
-      <c r="C427" s="3">
-        <v>1.8493848444479211</v>
-      </c>
+      <c r="C427" s="3"/>
     </row>
     <row r="428" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B428" s="2">
         <v>33238</v>
       </c>
-      <c r="C428" s="3">
-        <v>27.61</v>
-      </c>
+      <c r="C428" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/docs/deepreview/【2】每月必用/月度收益-20260323145627.xlsx
+++ b/docs/deepreview/【2】每月必用/月度收益-20260323145627.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C63A01-B0A3-4563-A224-FFF276A928E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9841D4EB-BC26-4ED3-B9F3-7F236058C6AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="月度收益" sheetId="1" r:id="rId1"/>
@@ -168,8 +168,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>399001.SZ</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>000905.SH</t>
   </si>
 </sst>
 </file>
@@ -1150,7 +1149,7 @@
       </c>
       <c r="O1" s="10">
         <f>data!B5</f>
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="P1" s="8"/>
       <c r="Q1" s="7"/>
@@ -1191,7 +1190,7 @@
       </c>
       <c r="F4" s="18" t="str">
         <f>[1]!s_info_name(D4)</f>
-        <v>深证成指</v>
+        <v>中证500</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>22</v>
@@ -1274,15 +1273,15 @@
       </c>
       <c r="D8" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C8,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.0341482603637466E-2</v>
+        <v>0.121215873790391</v>
       </c>
       <c r="E8" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C8,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.035773535524088E-2</v>
+        <v>3.43981006772065E-2</v>
       </c>
       <c r="F8" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C8,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.9308118651993609E-2</v>
+        <v>-0.14063777671623301</v>
       </c>
       <c r="G8" s="12" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C8,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
@@ -1330,51 +1329,51 @@
       </c>
       <c r="D9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.4825199189143055E-2</v>
+        <v>-2.3820393701947995E-2</v>
       </c>
       <c r="E9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.481787314015695E-2</v>
+        <v>4.8400606353891318E-2</v>
       </c>
       <c r="F9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.0074977289647125E-2</v>
+        <v>-3.5814782810561496E-4</v>
       </c>
       <c r="G9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.754866768393585E-2</v>
+        <v>-3.8572207341422637E-2</v>
       </c>
       <c r="H9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.422298371743369E-2</v>
+        <v>6.9688601291564289E-3</v>
       </c>
       <c r="I9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.2277580985608854E-2</v>
+        <v>4.3080970771612215E-2</v>
       </c>
       <c r="J9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.2044181548268842E-2</v>
+        <v>5.2567240057101339E-2</v>
       </c>
       <c r="K9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.15317144951776229</v>
+        <v>0.13131277440665334</v>
       </c>
       <c r="L9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.5402374280261188E-2</v>
+        <v>5.2304067938325982E-2</v>
       </c>
       <c r="M9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.0963456935093485E-2</v>
+        <v>-1.0976963854090194E-2</v>
       </c>
       <c r="N9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.9460663793646868E-2</v>
+        <v>-4.0847425095209659E-2</v>
       </c>
       <c r="O9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.1661940366236827E-2</v>
+        <v>6.1725177114208218E-2</v>
       </c>
       <c r="Q9" s="9"/>
     </row>
@@ -1386,51 +1385,51 @@
       </c>
       <c r="D10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.13773099900002006</v>
+        <v>-0.1348716782759275</v>
       </c>
       <c r="E10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.13607935715816866</v>
+        <v>0.13834705605278774</v>
       </c>
       <c r="F10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.5462118192435312E-3</v>
+        <v>-1.1339825786033542E-2</v>
       </c>
       <c r="G10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.9814362369642957E-2</v>
+        <v>2.931804274148897E-2</v>
       </c>
       <c r="H10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.3234213762426847E-2</v>
+        <v>-2.4370035175158455E-2</v>
       </c>
       <c r="I10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.5067849054147411E-2</v>
+        <v>-6.8900032651160292E-2</v>
       </c>
       <c r="J10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.0692181738983675E-2</v>
+        <v>-1.1404124928276693E-2</v>
       </c>
       <c r="K10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.6333773710481418E-2</v>
+        <v>-5.0609551348661859E-2</v>
       </c>
       <c r="L10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.26127870933686648</v>
+        <v>0.23799857145148207</v>
       </c>
       <c r="M10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.8369059387963773E-3</v>
+        <v>2.7523494236766588E-2</v>
       </c>
       <c r="N10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.9356602800544298E-3</v>
+        <v>-8.3628997481635103E-3</v>
       </c>
       <c r="O10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.8574530667462841E-2</v>
+        <v>-2.1566545854847963E-2</v>
       </c>
       <c r="Q10" s="9"/>
     </row>
@@ -1442,51 +1441,51 @@
       </c>
       <c r="D11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.9440799942919202E-2</v>
+        <v>7.2416318011787162E-2</v>
       </c>
       <c r="E11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.8120348750580773E-2</v>
+        <v>1.0873520269034875E-2</v>
       </c>
       <c r="F11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.8710782750638337E-3</v>
+        <v>-2.7867561000685104E-3</v>
       </c>
       <c r="G11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.3064843093288609E-2</v>
+        <v>-1.5548426679673155E-2</v>
       </c>
       <c r="H11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.8049469875036992E-2</v>
+        <v>-3.0994141055947444E-2</v>
       </c>
       <c r="I11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.1561927865715091E-2</v>
+        <v>-8.1141543966857244E-3</v>
       </c>
       <c r="J11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.4267861977762752E-2</v>
+        <v>1.4922126924447054E-2</v>
       </c>
       <c r="K11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.8464536194953629E-2</v>
+        <v>-5.7298089821676064E-2</v>
       </c>
       <c r="L11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.9629130148077221E-2</v>
+        <v>-8.4727869736312966E-3</v>
       </c>
       <c r="M11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.4306180481728723E-2</v>
+        <v>-2.8560495076790704E-2</v>
       </c>
       <c r="N11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.3877831203754187E-2</v>
+        <v>3.041095278360384E-3</v>
       </c>
       <c r="O11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.079033216213988E-2</v>
+        <v>-2.0887384540274057E-2</v>
       </c>
       <c r="Q11" s="9"/>
     </row>
@@ -1498,51 +1497,51 @@
       </c>
       <c r="D12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.10293153784343978</v>
+        <v>-0.10583364757986334</v>
       </c>
       <c r="E12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>9.5795891732417537E-3</v>
+        <v>4.1452299434848072E-2</v>
       </c>
       <c r="F12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-9.9398440807372701E-2</v>
+        <v>-7.7093746886996106E-2</v>
       </c>
       <c r="G12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-9.0509653688320521E-2</v>
+        <v>-0.11020760618456936</v>
       </c>
       <c r="H12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.592736664706476E-2</v>
+        <v>7.0778629926771419E-2</v>
       </c>
       <c r="I12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.11872208704158617</v>
+        <v>7.0996291500170505E-2</v>
       </c>
       <c r="J12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.8796056576028146E-2</v>
+        <v>-2.478485772204353E-2</v>
       </c>
       <c r="K12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.677593041467675E-2</v>
+        <v>-2.1983855266437535E-2</v>
       </c>
       <c r="L12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.7778977368145661E-2</v>
+        <v>-7.1751276916825146E-2</v>
       </c>
       <c r="M12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.5400950650939289E-2</v>
+        <v>1.6283229923842901E-2</v>
       </c>
       <c r="N12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.8428678839623336E-2</v>
+        <v>6.0105701870826644E-2</v>
       </c>
       <c r="O12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.3279582437844057E-3</v>
+        <v>-4.7380223976151277E-2</v>
       </c>
       <c r="Q12" s="9"/>
     </row>
@@ -1554,51 +1553,51 @@
       </c>
       <c r="D13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.4277457749886988E-2</v>
+        <v>-3.2947104504112978E-3</v>
       </c>
       <c r="E13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.1221792915779414E-2</v>
+        <v>2.8703760591619609E-3</v>
       </c>
       <c r="F13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.0234585409741239E-2</v>
+        <v>-1.7328297429892725E-2</v>
       </c>
       <c r="G13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.7892700063107752E-2</v>
+        <v>3.7037963840983901E-2</v>
       </c>
       <c r="H13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.8633327024997444E-2</v>
+        <v>3.7510649377882066E-2</v>
       </c>
       <c r="I13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.1024282437704036E-2</v>
+        <v>1.176885282021356E-2</v>
       </c>
       <c r="J13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.5409935746196561E-2</v>
+        <v>-6.0026440828244709E-3</v>
       </c>
       <c r="K13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.0006626173552857E-2</v>
+        <v>7.2115119199398947E-2</v>
       </c>
       <c r="L13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.3517995451517439E-3</v>
+        <v>-2.091344614529389E-2</v>
       </c>
       <c r="M13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>9.9496242672285629E-3</v>
+        <v>-1.1417916721638721E-2</v>
       </c>
       <c r="N13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.3828336971509101E-2</v>
+        <v>3.2788326981938232E-2</v>
       </c>
       <c r="O13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.1640988094515663E-3</v>
+        <v>1.4704370554241342E-2</v>
       </c>
       <c r="Q13" s="9"/>
     </row>
@@ -1610,51 +1609,51 @@
       </c>
       <c r="D14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.4076639739082584E-2</v>
+        <v>2.0897106879784522E-2</v>
       </c>
       <c r="E14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.7979150533463004E-2</v>
+        <v>1.3676485839007713E-2</v>
       </c>
       <c r="F14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-9.2750278290932187E-2</v>
+        <v>-7.5181529978126105E-2</v>
       </c>
       <c r="G14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.623485959027132E-2</v>
+        <v>6.1967467556081957E-2</v>
       </c>
       <c r="H14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.2661163450887756E-3</v>
+        <v>9.8024238402223407E-3</v>
       </c>
       <c r="I14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.1159744592919514</v>
+        <v>8.4729424080093541E-2</v>
       </c>
       <c r="J14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.13721549480206829</v>
+        <v>0.12196494096155931</v>
       </c>
       <c r="K14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.8243317184737435E-3</v>
+        <v>1.3490571015906339E-2</v>
       </c>
       <c r="L14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.1837884382173192E-2</v>
+        <v>-7.1370379347436286E-2</v>
       </c>
       <c r="M14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.5501005113474084E-2</v>
+        <v>-1.3084237564946477E-2</v>
       </c>
       <c r="N14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.2750824777448395E-2</v>
+        <v>3.4273823970274453E-2</v>
       </c>
       <c r="O14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.8563725153767177E-2</v>
+        <v>7.3044151743091312E-3</v>
       </c>
       <c r="Q14" s="9"/>
     </row>
@@ -1666,51 +1665,51 @@
       </c>
       <c r="D15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.307088047633866E-2</v>
+        <v>2.0243585690460364E-3</v>
       </c>
       <c r="E15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.20760350353866674</v>
+        <v>0.20323780785509027</v>
       </c>
       <c r="F15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>9.6871613194907891E-2</v>
+        <v>0.10394716819699588</v>
       </c>
       <c r="G15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.3451346697111575E-2</v>
+        <v>-4.3278836263841214E-2</v>
       </c>
       <c r="H15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.7713298994248281E-2</v>
+        <v>-7.4527560687020045E-2</v>
       </c>
       <c r="I15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.8648173165088497E-2</v>
+        <v>7.8337329159474667E-3</v>
       </c>
       <c r="J15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.6157783235449585E-2</v>
+        <v>-9.5499430176444466E-3</v>
       </c>
       <c r="K15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.1881970314481265E-3</v>
+        <v>-3.4077724295732414E-3</v>
       </c>
       <c r="L15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.601813319110585E-3</v>
+        <v>1.113456805636126E-2</v>
       </c>
       <c r="M15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.001758753024041E-2</v>
+        <v>-4.7533011678229098E-3</v>
       </c>
       <c r="N15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.5185764230928358E-3</v>
+        <v>-4.5706512528304044E-3</v>
       </c>
       <c r="O15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.8561532259786357E-2</v>
+        <v>7.6144034077955114E-2</v>
       </c>
       <c r="Q15" s="9"/>
     </row>
@@ -1722,51 +1721,51 @@
       </c>
       <c r="D16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.0799016344442469E-2</v>
+        <v>-9.8354124923147879E-3</v>
       </c>
       <c r="E16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.9655502543263768E-2</v>
+        <v>-2.6766063135022167E-2</v>
       </c>
       <c r="F16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.6869235138945466E-3</v>
+        <v>1.5117211630039318E-2</v>
       </c>
       <c r="G16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.0069397271966028E-2</v>
+        <v>-4.1498849451968356E-2</v>
       </c>
       <c r="H16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.7835720231160765E-3</v>
+        <v>-1.8172547010709916E-2</v>
       </c>
       <c r="I16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.8993610845817694E-2</v>
+        <v>-9.3268341127094367E-2</v>
       </c>
       <c r="J16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.1397178641631598E-2</v>
+        <v>-5.5670778382994612E-3</v>
       </c>
       <c r="K16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.7713046109850303E-2</v>
+        <v>-7.2058840137848357E-2</v>
       </c>
       <c r="L16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.6050476868998462E-3</v>
+        <v>-2.9274176747116076E-3</v>
       </c>
       <c r="M16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.10930238534662395</v>
+        <v>-0.11002015173238167</v>
       </c>
       <c r="N16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.6583417595123171E-2</v>
+        <v>2.4364666567646909E-2</v>
       </c>
       <c r="O16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.7533808639995465E-2</v>
+        <v>-4.7665394209741807E-2</v>
       </c>
       <c r="Q16" s="9"/>
     </row>
@@ -1778,51 +1777,51 @@
       </c>
       <c r="D17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.2291107895865294E-2</v>
+        <v>-6.3732257560221717E-3</v>
       </c>
       <c r="E17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.3753772961884199E-2</v>
+        <v>3.6515863112494884E-2</v>
       </c>
       <c r="F17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.597089970323486E-3</v>
+        <v>-7.6457027757731444E-3</v>
       </c>
       <c r="G17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.8609191530145841E-2</v>
+        <v>-2.9646350902866714E-2</v>
       </c>
       <c r="H17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.6132901705594911E-2</v>
+        <v>-6.2422213344584081E-2</v>
       </c>
       <c r="I17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.7387211861919871E-2</v>
+        <v>5.3922695957259847E-2</v>
       </c>
       <c r="J17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.3329830259419815E-3</v>
+        <v>2.6041177581096253E-2</v>
       </c>
       <c r="K17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.9661960482983307E-2</v>
+        <v>2.7377816616207307E-2</v>
       </c>
       <c r="L17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.5011666742259964E-2</v>
+        <v>2.0529220495361766E-2</v>
       </c>
       <c r="M17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.5293405139346969E-2</v>
+        <v>-6.5200080681376837E-3</v>
       </c>
       <c r="N17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.7256763491866352E-2</v>
+        <v>-4.5240107878329446E-2</v>
       </c>
       <c r="O17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.8039686411813811E-3</v>
+        <v>-2.0117280955567196E-3</v>
       </c>
       <c r="Q17" s="9"/>
     </row>
@@ -1834,51 +1833,51 @@
       </c>
       <c r="D18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.25635327270904051</v>
+        <v>-0.28204926717276069</v>
       </c>
       <c r="E18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.4066155288205779E-2</v>
+        <v>-2.1702135409072953E-2</v>
       </c>
       <c r="F18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.14927481175312152</v>
+        <v>0.15052613398424142</v>
       </c>
       <c r="G18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.0015965959690361E-2</v>
+        <v>-2.7651876020031607E-2</v>
       </c>
       <c r="H18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.8136297038093829E-3</v>
+        <v>-6.3939518784601468E-3</v>
       </c>
       <c r="I18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.2486333080510299E-2</v>
+        <v>2.9621985853667487E-2</v>
       </c>
       <c r="J18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.5305825275574669E-2</v>
+        <v>1.2966192388956355E-2</v>
       </c>
       <c r="K18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.1477583236643634E-2</v>
+        <v>3.7291958140237114E-2</v>
       </c>
       <c r="L18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.7689181181227753E-2</v>
+        <v>-1.6493818985058528E-2</v>
       </c>
       <c r="M18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.2938349065258814E-2</v>
+        <v>1.961417841756119E-2</v>
       </c>
       <c r="N18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.8763103140568402E-2</v>
+        <v>2.067072938064074E-2</v>
       </c>
       <c r="O18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.58300458410055E-2</v>
+        <v>-4.8887435477185652E-2</v>
       </c>
       <c r="Q18" s="9"/>
     </row>
@@ -1890,51 +1889,51 @@
       </c>
       <c r="D19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.2353576481593853E-2</v>
+        <v>5.8243595278649307E-2</v>
       </c>
       <c r="E19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.4435176859843892E-2</v>
+        <v>6.8481027310390186E-2</v>
       </c>
       <c r="F19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.11932452003302707</v>
+        <v>0.20514224312752294</v>
       </c>
       <c r="G19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.12597966181645526</v>
+        <v>0.16773080876821855</v>
       </c>
       <c r="H19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.6499705775968661E-2</v>
+        <v>0.17676857182089534</v>
       </c>
       <c r="I19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.10946794772418755</v>
+        <v>-0.10643536645748963</v>
       </c>
       <c r="J19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.13695883620862515</v>
+        <v>-0.13237780439797342</v>
       </c>
       <c r="K19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.1474909921842561</v>
+        <v>-0.14827735016657306</v>
       </c>
       <c r="L19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.3171327431380089E-2</v>
+        <v>-6.9527968181788524E-2</v>
       </c>
       <c r="M19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.15596335694440966</v>
+        <v>0.15697027924528451</v>
       </c>
       <c r="N19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.2595169551910006E-2</v>
+        <v>4.5649900085682926E-2</v>
       </c>
       <c r="O19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.2088424044246295E-2</v>
+        <v>2.8250396023496993E-2</v>
       </c>
       <c r="Q19" s="9"/>
     </row>
@@ -1946,51 +1945,51 @@
       </c>
       <c r="D20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.7614914351371791E-2</v>
+        <v>1.4708432486414624E-2</v>
       </c>
       <c r="E20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.7296842815855094E-2</v>
+        <v>2.3295575042672434E-2</v>
       </c>
       <c r="F20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.3940917128534411E-2</v>
+        <v>-3.4053173484737798E-2</v>
       </c>
       <c r="G20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.714759892722495E-2</v>
+        <v>-1.9363443019411841E-2</v>
       </c>
       <c r="H20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.1062465010278686E-3</v>
+        <v>1.6745924905142262E-2</v>
       </c>
       <c r="I20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.9266124169345931E-3</v>
+        <v>2.4982777252288813E-2</v>
       </c>
       <c r="J20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.3563804978024306E-2</v>
+        <v>8.4624256956159272E-2</v>
       </c>
       <c r="K20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.4478741551208318E-2</v>
+        <v>4.0129714391085702E-2</v>
       </c>
       <c r="L20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.0432810432328372E-2</v>
+        <v>0.11026498239902205</v>
       </c>
       <c r="M20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.7977695509573399E-2</v>
+        <v>1.4299287710488828E-2</v>
       </c>
       <c r="N20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>9.4414251486698131E-2</v>
+        <v>5.1911232436282928E-2</v>
       </c>
       <c r="O20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.22354435185871213</v>
+        <v>1.4765120631609507E-2</v>
       </c>
       <c r="Q20" s="9"/>
     </row>
@@ -2002,51 +2001,51 @@
       </c>
       <c r="D21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.0460589850209745E-2</v>
+        <v>6.2205955077445196E-2</v>
       </c>
       <c r="E21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.7137867316971986E-3</v>
+        <v>3.6946659393879422E-2</v>
       </c>
       <c r="F21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.7962141739052138E-2</v>
+        <v>-4.4596764202861398E-2</v>
       </c>
       <c r="G21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.2315877949134588E-2</v>
+        <v>-2.3067138342202531E-2</v>
       </c>
       <c r="H21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.5186726259770289E-2</v>
+        <v>0.14058340157837557</v>
       </c>
       <c r="I21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.16888006187979657</v>
+        <v>-0.15756460580992793</v>
       </c>
       <c r="J21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>9.2183135255909932E-3</v>
+        <v>6.018736839372818E-2</v>
       </c>
       <c r="K21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.6286247346561513E-2</v>
+        <v>6.8033367699066982E-2</v>
       </c>
       <c r="L21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.8048000355014544E-2</v>
+        <v>5.6969587472994965E-2</v>
       </c>
       <c r="M21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.2404640798611206E-3</v>
+        <v>-4.1071106276367564E-2</v>
       </c>
       <c r="N21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.1629356952917336E-2</v>
+        <v>6.2618391961503761E-2</v>
       </c>
       <c r="O21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.9261302871441703E-2</v>
+        <v>-2.9720125998921043E-2</v>
       </c>
       <c r="Q21" s="9"/>
     </row>
@@ -2058,51 +2057,51 @@
       </c>
       <c r="D22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.3148440331093108E-2</v>
+        <v>8.4851267687551246E-3</v>
       </c>
       <c r="E22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.0742083025703071E-2</v>
+        <v>0.12191553543579058</v>
       </c>
       <c r="F22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.4106706766737687E-2</v>
+        <v>-7.5561991091256053E-2</v>
       </c>
       <c r="G22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.1839485446845148E-2</v>
+        <v>7.2517542442525951E-2</v>
       </c>
       <c r="H22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.8292234887199461E-3</v>
+        <v>2.4273884623801756E-2</v>
       </c>
       <c r="I22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.3215371432572054E-2</v>
+        <v>-7.5295323707178619E-2</v>
       </c>
       <c r="J22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.6429292833070616E-2</v>
+        <v>-8.9823147165125614E-2</v>
       </c>
       <c r="K22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-9.3631639972695191E-2</v>
+        <v>-6.2332393852605472E-3</v>
       </c>
       <c r="L22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.7024155662517728E-2</v>
+        <v>1.9191591017677867E-2</v>
       </c>
       <c r="M22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.4129244808778205E-2</v>
+        <v>-9.8929542039507545E-3</v>
       </c>
       <c r="N22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.6890040799093664E-2</v>
+        <v>-0.11094136322214897</v>
       </c>
       <c r="O22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.15351062493143641</v>
+        <v>0.16304483665551395</v>
       </c>
       <c r="Q22" s="9"/>
     </row>
@@ -2114,51 +2113,51 @@
       </c>
       <c r="D23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.7232898333610542E-2</v>
+        <v>-6.6006632749382566E-2</v>
       </c>
       <c r="E23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.5679442659764895E-2</v>
+        <v>0.10504504582659191</v>
       </c>
       <c r="F23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.6315497811072119E-2</v>
+        <v>-1.8606894949136477E-2</v>
       </c>
       <c r="G23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.9892698350484461E-2</v>
+        <v>-3.2704570552527623E-2</v>
       </c>
       <c r="H23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.2615160686790056E-2</v>
+        <v>-8.1166193150688959E-2</v>
       </c>
       <c r="I23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.8215568933114508E-2</v>
+        <v>3.0388751733690711E-2</v>
       </c>
       <c r="J23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-9.9499369619066025E-3</v>
+        <v>1.069763013470082E-2</v>
       </c>
       <c r="K23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.9451695969484961E-2</v>
+        <v>-4.273300031112804E-2</v>
       </c>
       <c r="L23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-9.696414497203365E-2</v>
+        <v>-0.12948991747729044</v>
       </c>
       <c r="M23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.8322180372304153E-2</v>
+        <v>3.6956275986380627E-2</v>
       </c>
       <c r="N23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.5139167278572727E-2</v>
+        <v>-4.4862155513804458E-2</v>
       </c>
       <c r="O23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.9906967483495128E-2</v>
+        <v>-0.14481031387387555</v>
       </c>
       <c r="Q23" s="9"/>
     </row>
@@ -2170,51 +2169,51 @@
       </c>
       <c r="D24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.11407076073889211</v>
+        <v>-2.4659913427441671E-2</v>
       </c>
       <c r="E24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.4672156783390964E-2</v>
+        <v>5.9438368655405194E-2</v>
       </c>
       <c r="F24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.6391091495261438E-3</v>
+        <v>2.621243233877868E-2</v>
       </c>
       <c r="G24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.10659322013550121</v>
+        <v>-6.6750529892095734E-2</v>
       </c>
       <c r="H24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.5855303323966514E-2</v>
+        <v>-7.5318996792064996E-2</v>
       </c>
       <c r="I24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.0088501038888649E-2</v>
+        <v>-0.10717860306736915</v>
       </c>
       <c r="J24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.14897394112690865</v>
+        <v>0.14372251985556428</v>
       </c>
       <c r="K24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.1307394310762033E-2</v>
+        <v>9.5000393688575505E-2</v>
       </c>
       <c r="L24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.1450063913773567E-2</v>
+        <v>1.5539662026078593E-2</v>
       </c>
       <c r="M24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.16555660121778337</v>
+        <v>8.4728699385594908E-2</v>
       </c>
       <c r="N24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.7124994277051773E-2</v>
+        <v>1.0955016841090792E-2</v>
       </c>
       <c r="O24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>9.9109229615910177E-3</v>
+        <v>-3.4076161127008509E-2</v>
       </c>
       <c r="Q24" s="9"/>
     </row>
@@ -2226,51 +2225,51 @@
       </c>
       <c r="D25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.1677887315930064E-2</v>
+        <v>0.15398778921468281</v>
       </c>
       <c r="E25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.4528446370157648E-2</v>
+        <v>7.9919770589281347E-2</v>
       </c>
       <c r="F25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.18055858772804112</v>
+        <v>0.20570520933623349</v>
       </c>
       <c r="G25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.795654909349901E-2</v>
+        <v>5.9053342886791427E-2</v>
       </c>
       <c r="H25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.5814569530848521E-2</v>
+        <v>6.1736099567852865E-2</v>
       </c>
       <c r="I25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.14205197118460666</v>
+        <v>5.3563777257207512E-2</v>
       </c>
       <c r="J25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.18191214349648299</v>
+        <v>0.13797355531719346</v>
       </c>
       <c r="K25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.22571111480757644</v>
+        <v>-0.16560343370537578</v>
       </c>
       <c r="L25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.8739443282694426E-2</v>
+        <v>3.7408820081287431E-2</v>
       </c>
       <c r="M25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>9.7290076325660557E-2</v>
+        <v>0.125582871138612</v>
       </c>
       <c r="N25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>9.6738662140093634E-2</v>
+        <v>0.15091244494384726</v>
       </c>
       <c r="O25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.5807858558900545E-2</v>
+        <v>1.8143257437357674E-2</v>
       </c>
       <c r="Q25" s="9"/>
     </row>
@@ -2282,51 +2281,51 @@
       </c>
       <c r="D26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.10411566328008137</v>
+        <v>-5.7439531829857844E-2</v>
       </c>
       <c r="E26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.1331579402069645E-3</v>
+        <v>8.4530756966729292E-2</v>
       </c>
       <c r="F26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.15936322329986885</v>
+        <v>-0.20039457317546983</v>
       </c>
       <c r="G26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.524168520879865E-2</v>
+        <v>-3.4845842014708861E-2</v>
       </c>
       <c r="H26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.10786052602447194</v>
+        <v>-3.7801760514124649E-2</v>
       </c>
       <c r="I26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.22222853941915666</v>
+        <v>-0.25080073095573019</v>
       </c>
       <c r="J26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.0624091190720719E-2</v>
+        <v>7.2324641150706137E-2</v>
       </c>
       <c r="K26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.15480868995750319</v>
+        <v>-0.23533574151279146</v>
       </c>
       <c r="L26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.5592383240690706E-2</v>
+        <v>-7.4185209682214981E-2</v>
       </c>
       <c r="M26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.22752729132936012</v>
+        <v>-0.26871663449595773</v>
       </c>
       <c r="N26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.14028735150905192</v>
+        <v>0.17888864561446649</v>
       </c>
       <c r="O26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.5981777012375029E-2</v>
+        <v>5.3209698878601053E-2</v>
       </c>
       <c r="Q26" s="9"/>
     </row>
@@ -2338,51 +2337,51 @@
       </c>
       <c r="D27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.14830425540973335</v>
+        <v>0.241430910247453</v>
       </c>
       <c r="E27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.3290227170717186E-2</v>
+        <v>0.17296353384283195</v>
       </c>
       <c r="F27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.3373019313285317E-2</v>
+        <v>0.16412396415722408</v>
       </c>
       <c r="G27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.27098246280148564</v>
+        <v>0.33410923342756682</v>
       </c>
       <c r="H27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.19127264588369353</v>
+        <v>9.3268700452315834E-2</v>
       </c>
       <c r="I27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.0730221995471596E-2</v>
+        <v>-0.15987113678044873</v>
       </c>
       <c r="J27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.21146325944496325</v>
+        <v>0.22816934719588922</v>
       </c>
       <c r="K27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.17583065880451046</v>
+        <v>0.11219315902682926</v>
       </c>
       <c r="L27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.5529981880707791E-2</v>
+        <v>3.7980364404377687E-2</v>
       </c>
       <c r="M27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.5336439795088603E-2</v>
+        <v>-0.10493779076057554</v>
       </c>
       <c r="N27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.19934801602874999</v>
+        <v>-9.3897542142810556E-2</v>
       </c>
       <c r="O27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.13192282373741637</v>
+        <v>0.20002051937795742</v>
       </c>
       <c r="Q27" s="9"/>
     </row>
@@ -2394,51 +2393,51 @@
       </c>
       <c r="D28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.13225779190756293</v>
+        <v>0.11353619390534696</v>
       </c>
       <c r="E28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.3707373084990611E-2</v>
+        <v>7.2448258328834392E-3</v>
       </c>
       <c r="F28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.9157456742046746E-2</v>
+        <v>3.6823927208347262E-2</v>
       </c>
       <c r="G28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>9.4332094565003466E-2</v>
+        <v>0.14139850897424733</v>
       </c>
       <c r="H28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.11537886830011136</v>
+        <v>0.22830027547002918</v>
       </c>
       <c r="I28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.2278164858886562E-3</v>
+        <v>5.9659909350995077E-2</v>
       </c>
       <c r="J28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.2469383309733968E-2</v>
+        <v>-4.1016961699063437E-2</v>
       </c>
       <c r="K28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.8764316925021154E-2</v>
+        <v>3.8494250002105268E-2</v>
       </c>
       <c r="L28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.5402177494753939E-2</v>
+        <v>4.7910669639840586E-2</v>
       </c>
       <c r="M28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.8225578426815758E-2</v>
+        <v>-5.9091967193771744E-3</v>
       </c>
       <c r="N28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.22609788540658804</v>
+        <v>5.3304956607870047E-2</v>
       </c>
       <c r="O28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.17295656692832792</v>
+        <v>6.3018223739635504E-2</v>
       </c>
       <c r="Q28" s="9"/>
     </row>
@@ -2450,51 +2449,51 @@
       </c>
       <c r="D29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.1998357005709224E-3</v>
+        <v>-7.7346999999999944E-2</v>
       </c>
       <c r="E29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.10863100906128566</v>
+        <v>0.1064257093403478</v>
       </c>
       <c r="F29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.1003732468328027E-2</v>
+        <v>-0.12223085339918714</v>
       </c>
       <c r="G29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.3143501506142101E-3</v>
+        <v>-5.4077369128235804E-2</v>
       </c>
       <c r="H29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.11246274557508663</v>
+        <v>-5.9861186322499371E-2</v>
       </c>
       <c r="I29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.4789068210891876E-2</v>
+        <v>-6.7388488991958484E-3</v>
       </c>
       <c r="J29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.6134561250330552E-2</v>
+        <v>-5.8972687371604771E-2</v>
       </c>
       <c r="K29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.1769500466135572E-2</v>
+        <v>0.13468532876850259</v>
       </c>
       <c r="L29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.6039679599570644E-2</v>
+        <v>2.8831841276377279E-2</v>
       </c>
       <c r="M29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.2951415189715605E-2</v>
+        <v>-4.6980537291735909E-2</v>
       </c>
       <c r="N29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.4670937673253484E-3</v>
+        <v>1.0148927363367033E-3</v>
       </c>
       <c r="O29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.9770517328782589E-2</v>
+        <v>3.6927064496684814E-2</v>
       </c>
       <c r="Q29" s="9"/>
     </row>
@@ -2504,53 +2503,53 @@
         <f t="shared" si="0"/>
         <v>2004年</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.812841902226463E-2</v>
-      </c>
-      <c r="E30" s="5">
+        <v/>
+      </c>
+      <c r="E30" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.4629043961463175E-2</v>
-      </c>
-      <c r="F30" s="5">
+        <v/>
+      </c>
+      <c r="F30" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.5772431974342211E-2</v>
-      </c>
-      <c r="G30" s="5">
+        <v/>
+      </c>
+      <c r="G30" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.11008824073437806</v>
-      </c>
-      <c r="H30" s="5">
+        <v/>
+      </c>
+      <c r="H30" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-9.8309821655172547E-3</v>
-      </c>
-      <c r="I30" s="5">
+        <v/>
+      </c>
+      <c r="I30" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.4356538150203719E-2</v>
-      </c>
-      <c r="J30" s="5">
+        <v/>
+      </c>
+      <c r="J30" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.2955874047956293E-3</v>
-      </c>
-      <c r="K30" s="5">
+        <v/>
+      </c>
+      <c r="K30" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.2764507198396742E-2</v>
-      </c>
-      <c r="L30" s="5">
+        <v/>
+      </c>
+      <c r="L30" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.7575004912160428E-2</v>
-      </c>
-      <c r="M30" s="5">
+        <v/>
+      </c>
+      <c r="M30" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.8781138604573577E-2</v>
-      </c>
-      <c r="N30" s="5">
+        <v/>
+      </c>
+      <c r="N30" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.0024736129299345E-3</v>
+        <v/>
       </c>
       <c r="O30" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.911182716703788E-2</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="9"/>
     </row>
@@ -2560,53 +2559,53 @@
         <f t="shared" si="0"/>
         <v>2003年</v>
       </c>
-      <c r="D31" s="5">
+      <c r="D31" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.10579458558330002</v>
-      </c>
-      <c r="E31" s="5">
+        <v/>
+      </c>
+      <c r="E31" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.9736374216337005E-3</v>
-      </c>
-      <c r="F31" s="5">
+        <v/>
+      </c>
+      <c r="F31" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.4594204382317288E-2</v>
-      </c>
-      <c r="G31" s="5">
+        <v/>
+      </c>
+      <c r="G31" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.1225732697714577E-2</v>
-      </c>
-      <c r="H31" s="5">
+        <v/>
+      </c>
+      <c r="H31" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.4503320397674822E-2</v>
-      </c>
-      <c r="I31" s="5">
+        <v/>
+      </c>
+      <c r="I31" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.9597201922201433E-2</v>
-      </c>
-      <c r="J31" s="5">
+        <v/>
+      </c>
+      <c r="J31" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.90284038703712E-2</v>
-      </c>
-      <c r="K31" s="5">
+        <v/>
+      </c>
+      <c r="K31" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.798557023256266E-2</v>
-      </c>
-      <c r="L31" s="5">
+        <v/>
+      </c>
+      <c r="L31" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.3062731528903712E-2</v>
-      </c>
-      <c r="M31" s="5">
+        <v/>
+      </c>
+      <c r="M31" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.6808151117518451E-2</v>
-      </c>
-      <c r="N31" s="5">
+        <v/>
+      </c>
+      <c r="N31" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.1761677546988221E-2</v>
-      </c>
-      <c r="O31" s="5">
+        <v/>
+      </c>
+      <c r="O31" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.4828933465404415E-2</v>
+        <v/>
       </c>
       <c r="Q31" s="9"/>
     </row>
@@ -2616,53 +2615,53 @@
         <f t="shared" si="0"/>
         <v>2002年</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.10312737546547102</v>
-      </c>
-      <c r="E32" s="5">
+        <v/>
+      </c>
+      <c r="E32" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.5688150690465585E-2</v>
-      </c>
-      <c r="F32" s="5">
+        <v/>
+      </c>
+      <c r="F32" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.76680893483723E-2</v>
-      </c>
-      <c r="G32" s="5">
+        <v/>
+      </c>
+      <c r="G32" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.5066952329941161E-2</v>
-      </c>
-      <c r="H32" s="5">
+        <v/>
+      </c>
+      <c r="H32" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.6531938305680716E-2</v>
-      </c>
-      <c r="I32" s="5">
+        <v/>
+      </c>
+      <c r="I32" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.16935358269556033</v>
-      </c>
-      <c r="J32" s="5">
+        <v/>
+      </c>
+      <c r="J32" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.1005787130898641E-2</v>
-      </c>
-      <c r="K32" s="5">
+        <v/>
+      </c>
+      <c r="K32" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>9.1434866751445298E-3</v>
-      </c>
-      <c r="L32" s="5">
+        <v/>
+      </c>
+      <c r="L32" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.6132037454140304E-2</v>
-      </c>
-      <c r="M32" s="5">
+        <v/>
+      </c>
+      <c r="M32" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.4040301782469666E-2</v>
-      </c>
-      <c r="N32" s="5">
+        <v/>
+      </c>
+      <c r="N32" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.8029974467950645E-2</v>
-      </c>
-      <c r="O32" s="5">
+        <v/>
+      </c>
+      <c r="O32" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.5266547472231038E-2</v>
+        <v/>
       </c>
       <c r="Q32" s="9"/>
     </row>
@@ -2672,53 +2671,53 @@
         <f t="shared" si="0"/>
         <v>2001年</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.974225033038679E-3</v>
-      </c>
-      <c r="E33" s="5">
+        <v/>
+      </c>
+      <c r="E33" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.1185427738265401E-2</v>
-      </c>
-      <c r="F33" s="5">
+        <v/>
+      </c>
+      <c r="F33" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.11516427835351341</v>
-      </c>
-      <c r="G33" s="5">
+        <v/>
+      </c>
+      <c r="G33" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.2902630011441891E-2</v>
-      </c>
-      <c r="H33" s="5">
+        <v/>
+      </c>
+      <c r="H33" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.142632978191771E-2</v>
-      </c>
-      <c r="I33" s="5">
+        <v/>
+      </c>
+      <c r="I33" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.8939356883051048E-2</v>
-      </c>
-      <c r="J33" s="5">
+        <v/>
+      </c>
+      <c r="J33" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.13947434923305491</v>
-      </c>
-      <c r="K33" s="5">
+        <v/>
+      </c>
+      <c r="K33" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.8974996366109025E-2</v>
-      </c>
-      <c r="L33" s="5">
+        <v/>
+      </c>
+      <c r="L33" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-9.3671863261679325E-2</v>
-      </c>
-      <c r="M33" s="5">
+        <v/>
+      </c>
+      <c r="M33" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.7177600578055618E-2</v>
-      </c>
-      <c r="N33" s="5">
+        <v/>
+      </c>
+      <c r="N33" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.1876803097139241E-2</v>
-      </c>
-      <c r="O33" s="5">
+        <v/>
+      </c>
+      <c r="O33" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.3529105070591158E-2</v>
+        <v/>
       </c>
       <c r="Q33" s="9"/>
     </row>
@@ -2728,53 +2727,53 @@
         <f t="shared" si="0"/>
         <v>2000年</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D34" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.17295541863251995</v>
-      </c>
-      <c r="E34" s="5">
+        <v/>
+      </c>
+      <c r="E34" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.13454004104334394</v>
-      </c>
-      <c r="F34" s="5">
+        <v/>
+      </c>
+      <c r="F34" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.073756446017593E-2</v>
-      </c>
-      <c r="G34" s="5">
+        <v/>
+      </c>
+      <c r="G34" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.3284770932634267E-2</v>
-      </c>
-      <c r="H34" s="5">
+        <v/>
+      </c>
+      <c r="H34" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.5444261045404257E-3</v>
-      </c>
-      <c r="I34" s="5">
+        <v/>
+      </c>
+      <c r="I34" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.0386116767585856E-2</v>
-      </c>
-      <c r="J34" s="5">
+        <v/>
+      </c>
+      <c r="J34" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.3135020082083892E-2</v>
-      </c>
-      <c r="K34" s="5">
+        <v/>
+      </c>
+      <c r="K34" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.3857839756851398E-2</v>
-      </c>
-      <c r="L34" s="5">
+        <v/>
+      </c>
+      <c r="L34" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.2707418079635646E-2</v>
-      </c>
-      <c r="M34" s="5">
+        <v/>
+      </c>
+      <c r="M34" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.0957061740741736E-2</v>
-      </c>
-      <c r="N34" s="5">
+        <v/>
+      </c>
+      <c r="N34" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.6146386006895588E-2</v>
-      </c>
-      <c r="O34" s="5">
+        <v/>
+      </c>
+      <c r="O34" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.5992359410798351E-2</v>
+        <v/>
       </c>
       <c r="Q34" s="9"/>
     </row>
@@ -2784,53 +2783,53 @@
         <f t="shared" si="0"/>
         <v>1999年</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D35" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-9.8066772747724684E-3</v>
-      </c>
-      <c r="E35" s="5">
+        <v/>
+      </c>
+      <c r="E35" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.6531413227119194E-2</v>
-      </c>
-      <c r="F35" s="5">
+        <v/>
+      </c>
+      <c r="F35" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.2410626792000805E-2</v>
-      </c>
-      <c r="G35" s="5">
+        <v/>
+      </c>
+      <c r="G35" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.7399296834362041E-2</v>
-      </c>
-      <c r="H35" s="5">
+        <v/>
+      </c>
+      <c r="H35" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.17071630548363159</v>
-      </c>
-      <c r="I35" s="5">
+        <v/>
+      </c>
+      <c r="I35" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.438004151240174</v>
-      </c>
-      <c r="J35" s="5">
+        <v/>
+      </c>
+      <c r="J35" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.13979387484918482</v>
-      </c>
-      <c r="K35" s="5">
+        <v/>
+      </c>
+      <c r="K35" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.6905920493998536E-2</v>
-      </c>
-      <c r="L35" s="5">
+        <v/>
+      </c>
+      <c r="L35" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.4860874503123045E-2</v>
-      </c>
-      <c r="M35" s="5">
+        <v/>
+      </c>
+      <c r="M35" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.6915630124012233E-2</v>
-      </c>
-      <c r="N35" s="5">
+        <v/>
+      </c>
+      <c r="N35" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.5591305839701954E-2</v>
-      </c>
-      <c r="O35" s="5">
+        <v/>
+      </c>
+      <c r="O35" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.6510976425183766E-2</v>
+        <v/>
       </c>
       <c r="Q35" s="9"/>
     </row>
@@ -2840,53 +2839,53 @@
         <f t="shared" si="0"/>
         <v>1998年</v>
       </c>
-      <c r="D36" s="5">
+      <c r="D36" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.6740093537538385E-3</v>
-      </c>
-      <c r="E36" s="5">
+        <v/>
+      </c>
+      <c r="E36" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.0068499530884187E-2</v>
-      </c>
-      <c r="F36" s="5">
+        <v/>
+      </c>
+      <c r="F36" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.5089133357163469E-3</v>
-      </c>
-      <c r="G36" s="5">
+        <v/>
+      </c>
+      <c r="G36" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.8957575993241003E-2</v>
-      </c>
-      <c r="H36" s="5">
+        <v/>
+      </c>
+      <c r="H36" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>9.8566068206484836E-4</v>
-      </c>
-      <c r="I36" s="5">
+        <v/>
+      </c>
+      <c r="I36" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.10703039110667845</v>
-      </c>
-      <c r="J36" s="5">
+        <v/>
+      </c>
+      <c r="J36" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.8361620093210185E-3</v>
-      </c>
-      <c r="K36" s="5">
+        <v/>
+      </c>
+      <c r="K36" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.13047738985391322</v>
-      </c>
-      <c r="L36" s="5">
+        <v/>
+      </c>
+      <c r="L36" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.5624406964588395E-3</v>
-      </c>
-      <c r="M36" s="5">
+        <v/>
+      </c>
+      <c r="M36" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.2090351017185954E-2</v>
-      </c>
-      <c r="N36" s="5">
+        <v/>
+      </c>
+      <c r="N36" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.8377041068777809E-2</v>
-      </c>
-      <c r="O36" s="5">
+        <v/>
+      </c>
+      <c r="O36" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.8528203098174543E-2</v>
+        <v/>
       </c>
       <c r="Q36" s="9"/>
     </row>
@@ -2896,53 +2895,53 @@
         <f t="shared" si="0"/>
         <v>1997年</v>
       </c>
-      <c r="D37" s="5">
+      <c r="D37" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.14884654186332291</v>
-      </c>
-      <c r="E37" s="5">
+        <v/>
+      </c>
+      <c r="E37" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.9679899319944294E-2</v>
-      </c>
-      <c r="F37" s="5">
+        <v/>
+      </c>
+      <c r="F37" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.20536383240192624</v>
-      </c>
-      <c r="G37" s="5">
+        <v/>
+      </c>
+      <c r="G37" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.1469154245172033</v>
-      </c>
-      <c r="H37" s="5">
+        <v/>
+      </c>
+      <c r="H37" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.0342751503960299E-2</v>
-      </c>
-      <c r="I37" s="5">
+        <v/>
+      </c>
+      <c r="I37" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.8974186682851029E-2</v>
-      </c>
-      <c r="J37" s="5">
+        <v/>
+      </c>
+      <c r="J37" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.10780828921531393</v>
-      </c>
-      <c r="K37" s="5">
+        <v/>
+      </c>
+      <c r="K37" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.9753018777031404E-2</v>
-      </c>
-      <c r="L37" s="5">
+        <v/>
+      </c>
+      <c r="L37" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.10956104425476865</v>
-      </c>
-      <c r="M37" s="5">
+        <v/>
+      </c>
+      <c r="M37" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.15484814791647783</v>
-      </c>
-      <c r="N37" s="5">
+        <v/>
+      </c>
+      <c r="N37" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.6335453091372001E-2</v>
-      </c>
-      <c r="O37" s="5">
+        <v/>
+      </c>
+      <c r="O37" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.9596616322579474E-2</v>
+        <v/>
       </c>
       <c r="Q37" s="9"/>
     </row>
@@ -2952,53 +2951,53 @@
         <f t="shared" si="0"/>
         <v>1996年</v>
       </c>
-      <c r="D38" s="5">
+      <c r="D38" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.9410275879524161E-2</v>
-      </c>
-      <c r="E38" s="5">
+        <v/>
+      </c>
+      <c r="E38" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.4792948784812667E-2</v>
-      </c>
-      <c r="F38" s="5">
+        <v/>
+      </c>
+      <c r="F38" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.7380220127962716E-3</v>
-      </c>
-      <c r="G38" s="5">
+        <v/>
+      </c>
+      <c r="G38" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.50298026620427372</v>
-      </c>
-      <c r="H38" s="5">
+        <v/>
+      </c>
+      <c r="H38" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.13755391533489791</v>
-      </c>
-      <c r="I38" s="5">
+        <v/>
+      </c>
+      <c r="I38" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.18655525232455752</v>
-      </c>
-      <c r="J38" s="5">
+        <v/>
+      </c>
+      <c r="J38" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.25674836302145221</v>
-      </c>
-      <c r="K38" s="5">
+        <v/>
+      </c>
+      <c r="K38" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.7969960665536604E-2</v>
-      </c>
-      <c r="L38" s="5">
+        <v/>
+      </c>
+      <c r="L38" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.9208361234597904E-2</v>
-      </c>
-      <c r="M38" s="5">
+        <v/>
+      </c>
+      <c r="M38" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.29932714335124433</v>
-      </c>
-      <c r="N38" s="5">
+        <v/>
+      </c>
+      <c r="N38" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.13561417914582852</v>
-      </c>
-      <c r="O38" s="5">
+        <v/>
+      </c>
+      <c r="O38" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.21108318642222623</v>
+        <v/>
       </c>
       <c r="Q38" s="9"/>
     </row>
@@ -3008,53 +3007,53 @@
         <f t="shared" si="0"/>
         <v>1995年</v>
       </c>
-      <c r="D39" s="5">
+      <c r="D39" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-9.000432713111195E-2</v>
-      </c>
-      <c r="E39" s="5">
+        <v/>
+      </c>
+      <c r="E39" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.5276877188431959E-2</v>
-      </c>
-      <c r="F39" s="5">
+        <v/>
+      </c>
+      <c r="F39" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.3471966755228575E-2</v>
-      </c>
-      <c r="G39" s="5">
+        <v/>
+      </c>
+      <c r="G39" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.11192537764103892</v>
-      </c>
-      <c r="H39" s="5">
+        <v/>
+      </c>
+      <c r="H39" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.8558379739390913E-2</v>
-      </c>
-      <c r="I39" s="5">
+        <v/>
+      </c>
+      <c r="I39" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.0307384664389794E-2</v>
-      </c>
-      <c r="J39" s="5">
+        <v/>
+      </c>
+      <c r="J39" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.0778894472361706E-2</v>
-      </c>
-      <c r="K39" s="5">
+        <v/>
+      </c>
+      <c r="K39" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.1952985060846029E-2</v>
-      </c>
-      <c r="L39" s="5">
+        <v/>
+      </c>
+      <c r="L39" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.85414142103724E-3</v>
-      </c>
-      <c r="M39" s="5">
+        <v/>
+      </c>
+      <c r="M39" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-9.6398159593462651E-3</v>
-      </c>
-      <c r="N39" s="5">
+        <v/>
+      </c>
+      <c r="N39" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.8549227288880346E-2</v>
-      </c>
-      <c r="O39" s="5">
+        <v/>
+      </c>
+      <c r="O39" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-9.0620339170303321E-2</v>
+        <v/>
       </c>
       <c r="Q39" s="9"/>
     </row>
@@ -3064,53 +3063,53 @@
         <f t="shared" si="0"/>
         <v>1994年</v>
       </c>
-      <c r="D40" s="5">
+      <c r="D40" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.17142690237172975</v>
-      </c>
-      <c r="E40" s="5">
+        <v/>
+      </c>
+      <c r="E40" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.7181068284984446E-2</v>
-      </c>
-      <c r="F40" s="5">
+        <v/>
+      </c>
+      <c r="F40" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.16793828009618406</v>
-      </c>
-      <c r="G40" s="5">
+        <v/>
+      </c>
+      <c r="G40" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.13070697620771632</v>
-      </c>
-      <c r="H40" s="5">
+        <v/>
+      </c>
+      <c r="H40" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.8981136804239962E-2</v>
-      </c>
-      <c r="I40" s="5">
+        <v/>
+      </c>
+      <c r="I40" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.14090137204514375</v>
-      </c>
-      <c r="J40" s="5">
+        <v/>
+      </c>
+      <c r="J40" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.15118862280686407</v>
-      </c>
-      <c r="K40" s="5">
+        <v/>
+      </c>
+      <c r="K40" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.56315431539032224</v>
-      </c>
-      <c r="L40" s="5">
+        <v/>
+      </c>
+      <c r="L40" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.1342047844114409</v>
-      </c>
-      <c r="M40" s="5">
+        <v/>
+      </c>
+      <c r="M40" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.19383935836336164</v>
-      </c>
-      <c r="N40" s="5">
+        <v/>
+      </c>
+      <c r="N40" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.5464140496582623E-2</v>
-      </c>
-      <c r="O40" s="5">
+        <v/>
+      </c>
+      <c r="O40" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.9257412329840506E-2</v>
+        <v/>
       </c>
       <c r="Q40" s="9"/>
     </row>
@@ -3128,45 +3127,45 @@
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
         <v/>
       </c>
-      <c r="F41" s="5">
+      <c r="F41" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.6837644399799144E-2</v>
-      </c>
-      <c r="G41" s="5">
+        <v/>
+      </c>
+      <c r="G41" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.9158293141557952E-3</v>
-      </c>
-      <c r="H41" s="5">
+        <v/>
+      </c>
+      <c r="H41" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.13278197514742618</v>
-      </c>
-      <c r="I41" s="5">
+        <v/>
+      </c>
+      <c r="I41" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.8569220534515751E-2</v>
-      </c>
-      <c r="J41" s="5">
+        <v/>
+      </c>
+      <c r="J41" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.10656151365592038</v>
-      </c>
-      <c r="K41" s="5">
+        <v/>
+      </c>
+      <c r="K41" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.11549434663143486</v>
-      </c>
-      <c r="L41" s="5">
+        <v/>
+      </c>
+      <c r="L41" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.4505190341116323E-2</v>
-      </c>
-      <c r="M41" s="5">
+        <v/>
+      </c>
+      <c r="M41" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.714405051693616E-2</v>
-      </c>
-      <c r="N41" s="5">
+        <v/>
+      </c>
+      <c r="N41" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.8836355409335201E-2</v>
-      </c>
-      <c r="O41" s="5">
+        <v/>
+      </c>
+      <c r="O41" s="5" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.7738578425161697E-2</v>
+        <v/>
       </c>
       <c r="Q41" s="9"/>
     </row>
@@ -3446,13 +3445,13 @@
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C1" s="1" t="str">
         <f>[1]!s_info_name(C2)</f>
-        <v>深证成指</v>
+        <v>中证500</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C2" s="1" t="str">
         <f>IF(月度收益!D5="",月度收益!D4,月度收益!D5)</f>
-        <v>399001.SZ</v>
+        <v>000905.SH</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -3477,11 +3476,11 @@
         <v>2026/03</v>
       </c>
       <c r="B5" s="2">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="C5" s="3">
         <f>[1]!WSD(C2,C4:C4,"-"&amp;月度收益!I4&amp;LEFT(月度收益!L4,1),"","Per="&amp;LEFT(月度收益!L4,1),"TradingCalendar=SSE","Sort=D","rptType=1","ShowParams=Y","cols=1;rows=424")</f>
-        <v>-7.9308118651993613</v>
+        <v>-14.063777671623301</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -3493,7 +3492,7 @@
         <v>46080</v>
       </c>
       <c r="C6" s="3">
-        <v>2.035773535524088</v>
+        <v>3.43981006772065</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -3505,7 +3504,7 @@
         <v>46052</v>
       </c>
       <c r="C7" s="3">
-        <v>5.0341482603637466</v>
+        <v>12.1215873790391</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -3517,7 +3516,7 @@
         <v>46022</v>
       </c>
       <c r="C8" s="3">
-        <v>4.1661940366236827</v>
+        <v>6.1725177114208218</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -3529,7 +3528,7 @@
         <v>45989</v>
       </c>
       <c r="C9" s="3">
-        <v>-2.9460663793646868</v>
+        <v>-4.0847425095209662</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -3541,7 +3540,7 @@
         <v>45961</v>
       </c>
       <c r="C10" s="3">
-        <v>-1.0963456935093485</v>
+        <v>-1.0976963854090194</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -3553,7 +3552,7 @@
         <v>45930</v>
       </c>
       <c r="C11" s="3">
-        <v>6.5402374280261188</v>
+        <v>5.2304067938325982</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -3565,7 +3564,7 @@
         <v>45898</v>
       </c>
       <c r="C12" s="3">
-        <v>15.317144951776228</v>
+        <v>13.131277440665334</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -3577,7 +3576,7 @@
         <v>45869</v>
       </c>
       <c r="C13" s="3">
-        <v>5.2044181548268842</v>
+        <v>5.2567240057101339</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -3589,7 +3588,7 @@
         <v>45838</v>
       </c>
       <c r="C14" s="3">
-        <v>4.2277580985608854</v>
+        <v>4.3080970771612215</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -3601,7 +3600,7 @@
         <v>45807</v>
       </c>
       <c r="C15" s="3">
-        <v>1.422298371743369</v>
+        <v>0.69688601291564289</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -3613,7 +3612,7 @@
         <v>45777</v>
       </c>
       <c r="C16" s="3">
-        <v>-5.754866768393585</v>
+        <v>-3.8572207341422637</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -3625,7 +3624,7 @@
         <v>45747</v>
       </c>
       <c r="C17" s="3">
-        <v>-1.0074977289647125</v>
+        <v>-3.5814782810561496E-2</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -3637,7 +3636,7 @@
         <v>45716</v>
       </c>
       <c r="C18" s="3">
-        <v>4.481787314015695</v>
+        <v>4.8400606353891318</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -3649,7 +3648,7 @@
         <v>45684</v>
       </c>
       <c r="C19" s="3">
-        <v>-2.4825199189143055</v>
+        <v>-2.3820393701947995</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -3661,7 +3660,7 @@
         <v>45657</v>
       </c>
       <c r="C20" s="3">
-        <v>-1.8574530667462841</v>
+        <v>-2.1566545854847963</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -3673,7 +3672,7 @@
         <v>45625</v>
       </c>
       <c r="C21" s="3">
-        <v>0.19356602800544298</v>
+        <v>-0.83628997481635103</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -3685,7 +3684,7 @@
         <v>45596</v>
       </c>
       <c r="C22" s="3">
-        <v>0.58369059387963773</v>
+        <v>2.7523494236766588</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -3697,7 +3696,7 @@
         <v>45565</v>
       </c>
       <c r="C23" s="3">
-        <v>26.127870933686648</v>
+        <v>23.799857145148206</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -3709,7 +3708,7 @@
         <v>45534</v>
       </c>
       <c r="C24" s="3">
-        <v>-4.6333773710481418</v>
+        <v>-5.0609551348661856</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -3721,7 +3720,7 @@
         <v>45504</v>
       </c>
       <c r="C25" s="3">
-        <v>-1.0692181738983675</v>
+        <v>-1.1404124928276693</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -3733,7 +3732,7 @@
         <v>45471</v>
       </c>
       <c r="C26" s="3">
-        <v>-5.5067849054147411</v>
+        <v>-6.8900032651160288</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -3745,7 +3744,7 @@
         <v>45443</v>
       </c>
       <c r="C27" s="3">
-        <v>-2.3234213762426847</v>
+        <v>-2.4370035175158455</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -3757,7 +3756,7 @@
         <v>45412</v>
       </c>
       <c r="C28" s="3">
-        <v>1.9814362369642957</v>
+        <v>2.931804274148897</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -3769,7 +3768,7 @@
         <v>45380</v>
       </c>
       <c r="C29" s="3">
-        <v>0.75462118192435312</v>
+        <v>-1.1339825786033542</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -3781,7 +3780,7 @@
         <v>45351</v>
       </c>
       <c r="C30" s="3">
-        <v>13.607935715816865</v>
+        <v>13.834705605278774</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -3793,7 +3792,7 @@
         <v>45322</v>
       </c>
       <c r="C31" s="3">
-        <v>-13.773099900002006</v>
+        <v>-13.487167827592749</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -3805,7 +3804,7 @@
         <v>45289</v>
       </c>
       <c r="C32" s="3">
-        <v>-2.079033216213988</v>
+        <v>-2.0887384540274057</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -3817,7 +3816,7 @@
         <v>45260</v>
       </c>
       <c r="C33" s="3">
-        <v>-1.3877831203754187</v>
+        <v>0.3041095278360384</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -3829,7 +3828,7 @@
         <v>45230</v>
       </c>
       <c r="C34" s="3">
-        <v>-2.4306180481728723</v>
+        <v>-2.8560495076790704</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -3841,7 +3840,7 @@
         <v>45197</v>
       </c>
       <c r="C35" s="3">
-        <v>-2.9629130148077221</v>
+        <v>-0.84727869736312966</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -3853,7 +3852,7 @@
         <v>45169</v>
       </c>
       <c r="C36" s="3">
-        <v>-6.8464536194953629</v>
+        <v>-5.7298089821676061</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -3865,7 +3864,7 @@
         <v>45138</v>
       </c>
       <c r="C37" s="3">
-        <v>1.4267861977762752</v>
+        <v>1.4922126924447054</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -3877,7 +3876,7 @@
         <v>45107</v>
       </c>
       <c r="C38" s="3">
-        <v>2.1561927865715091</v>
+        <v>-0.81141543966857244</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
@@ -3889,7 +3888,7 @@
         <v>45077</v>
       </c>
       <c r="C39" s="3">
-        <v>-4.8049469875036994</v>
+        <v>-3.0994141055947444</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
@@ -3901,7 +3900,7 @@
         <v>45044</v>
       </c>
       <c r="C40" s="3">
-        <v>-3.3064843093288609</v>
+        <v>-1.5548426679673155</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
@@ -3913,7 +3912,7 @@
         <v>45016</v>
       </c>
       <c r="C41" s="3">
-        <v>-0.48710782750638337</v>
+        <v>-0.27867561000685104</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
@@ -3925,7 +3924,7 @@
         <v>44985</v>
       </c>
       <c r="C42" s="3">
-        <v>-1.8120348750580773</v>
+        <v>1.0873520269034875</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
@@ -3937,7 +3936,7 @@
         <v>44957</v>
       </c>
       <c r="C43" s="3">
-        <v>8.9440799942919202</v>
+        <v>7.2416318011787162</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -3949,7 +3948,7 @@
         <v>44925</v>
       </c>
       <c r="C44" s="3">
-        <v>-0.83279582437844057</v>
+        <v>-4.7380223976151274</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
@@ -3961,7 +3960,7 @@
         <v>44895</v>
       </c>
       <c r="C45" s="3">
-        <v>6.8428678839623336</v>
+        <v>6.0105701870826644</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
@@ -3973,7 +3972,7 @@
         <v>44865</v>
       </c>
       <c r="C46" s="3">
-        <v>-3.5400950650939289</v>
+        <v>1.6283229923842901</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
@@ -3985,7 +3984,7 @@
         <v>44834</v>
       </c>
       <c r="C47" s="3">
-        <v>-8.7778977368145661</v>
+        <v>-7.1751276916825146</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
@@ -3997,7 +3996,7 @@
         <v>44804</v>
       </c>
       <c r="C48" s="3">
-        <v>-3.677593041467675</v>
+        <v>-2.1983855266437535</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
@@ -4009,7 +4008,7 @@
         <v>44771</v>
       </c>
       <c r="C49" s="3">
-        <v>-4.8796056576028146</v>
+        <v>-2.478485772204353</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
@@ -4021,7 +4020,7 @@
         <v>44742</v>
       </c>
       <c r="C50" s="3">
-        <v>11.872208704158616</v>
+        <v>7.0996291500170505</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -4033,7 +4032,7 @@
         <v>44712</v>
       </c>
       <c r="C51" s="3">
-        <v>4.592736664706476</v>
+        <v>7.0778629926771419</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
@@ -4045,7 +4044,7 @@
         <v>44680</v>
       </c>
       <c r="C52" s="3">
-        <v>-9.0509653688320526</v>
+        <v>-11.020760618456936</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
@@ -4057,7 +4056,7 @@
         <v>44651</v>
       </c>
       <c r="C53" s="3">
-        <v>-9.9398440807372701</v>
+        <v>-7.7093746886996106</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
@@ -4069,7 +4068,7 @@
         <v>44620</v>
       </c>
       <c r="C54" s="3">
-        <v>0.95795891732417537</v>
+        <v>4.1452299434848072</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
@@ -4081,7 +4080,7 @@
         <v>44589</v>
       </c>
       <c r="C55" s="3">
-        <v>-10.293153784343978</v>
+        <v>-10.583364757986335</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
@@ -4093,7 +4092,7 @@
         <v>44561</v>
       </c>
       <c r="C56" s="3">
-        <v>0.41640988094515663</v>
+        <v>1.4704370554241342</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
@@ -4105,7 +4104,7 @@
         <v>44530</v>
       </c>
       <c r="C57" s="3">
-        <v>2.3828336971509101</v>
+        <v>3.2788326981938232</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
@@ -4117,7 +4116,7 @@
         <v>44498</v>
       </c>
       <c r="C58" s="3">
-        <v>0.99496242672285629</v>
+        <v>-1.1417916721638721</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
@@ -4129,7 +4128,7 @@
         <v>44469</v>
       </c>
       <c r="C59" s="3">
-        <v>-0.13517995451517439</v>
+        <v>-2.091344614529389</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
@@ -4141,7 +4140,7 @@
         <v>44439</v>
       </c>
       <c r="C60" s="3">
-        <v>-1.0006626173552857</v>
+        <v>7.2115119199398947</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
@@ -4153,7 +4152,7 @@
         <v>44407</v>
       </c>
       <c r="C61" s="3">
-        <v>-4.5409935746196561</v>
+        <v>-0.60026440828244709</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
@@ -4165,7 +4164,7 @@
         <v>44377</v>
       </c>
       <c r="C62" s="3">
-        <v>1.1024282437704036</v>
+        <v>1.176885282021356</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
@@ -4177,7 +4176,7 @@
         <v>44347</v>
       </c>
       <c r="C63" s="3">
-        <v>3.8633327024997444</v>
+        <v>3.7510649377882066</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
@@ -4189,7 +4188,7 @@
         <v>44316</v>
       </c>
       <c r="C64" s="3">
-        <v>4.7892700063107752</v>
+        <v>3.7037963840983901</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
@@ -4201,7 +4200,7 @@
         <v>44286</v>
       </c>
       <c r="C65" s="3">
-        <v>-5.0234585409741239</v>
+        <v>-1.7328297429892725</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
@@ -4213,7 +4212,7 @@
         <v>44253</v>
       </c>
       <c r="C66" s="3">
-        <v>-2.1221792915779414</v>
+        <v>0.28703760591619609</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
@@ -4225,7 +4224,7 @@
         <v>44225</v>
       </c>
       <c r="C67" s="3">
-        <v>2.4277457749886988</v>
+        <v>-0.32947104504112978</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
@@ -4237,7 +4236,7 @@
         <v>44196</v>
       </c>
       <c r="C68" s="3">
-        <v>5.8563725153767177</v>
+        <v>0.73044151743091312</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
@@ -4249,7 +4248,7 @@
         <v>44165</v>
       </c>
       <c r="C69" s="3">
-        <v>3.2750824777448395</v>
+        <v>3.4273823970274453</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
@@ -4261,7 +4260,7 @@
         <v>44134</v>
       </c>
       <c r="C70" s="3">
-        <v>2.5501005113474084</v>
+        <v>-1.3084237564946477</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
@@ -4273,7 +4272,7 @@
         <v>44104</v>
       </c>
       <c r="C71" s="3">
-        <v>-6.1837884382173192</v>
+        <v>-7.1370379347436286</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
@@ -4285,7 +4284,7 @@
         <v>44074</v>
       </c>
       <c r="C72" s="3">
-        <v>0.88243317184737435</v>
+        <v>1.3490571015906339</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
@@ -4297,7 +4296,7 @@
         <v>44043</v>
       </c>
       <c r="C73" s="3">
-        <v>13.721549480206829</v>
+        <v>12.196494096155931</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
@@ -4309,7 +4308,7 @@
         <v>44012</v>
       </c>
       <c r="C74" s="3">
-        <v>11.597445929195139</v>
+        <v>8.4729424080093541</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
@@ -4321,7 +4320,7 @@
         <v>43980</v>
       </c>
       <c r="C75" s="3">
-        <v>0.22661163450887756</v>
+        <v>0.98024238402223407</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
@@ -4333,7 +4332,7 @@
         <v>43951</v>
       </c>
       <c r="C76" s="3">
-        <v>7.623485959027132</v>
+        <v>6.1967467556081957</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
@@ -4345,7 +4344,7 @@
         <v>43921</v>
       </c>
       <c r="C77" s="3">
-        <v>-9.2750278290932187</v>
+        <v>-7.51815299781261</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
@@ -4357,7 +4356,7 @@
         <v>43889</v>
       </c>
       <c r="C78" s="3">
-        <v>2.7979150533463004</v>
+        <v>1.3676485839007713</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
@@ -4369,7 +4368,7 @@
         <v>43853</v>
       </c>
       <c r="C79" s="3">
-        <v>2.4076639739082584</v>
+        <v>2.0897106879784522</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
@@ -4381,7 +4380,7 @@
         <v>43830</v>
       </c>
       <c r="C80" s="3">
-        <v>8.8561532259786357</v>
+        <v>7.6144034077955114</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
@@ -4393,7 +4392,7 @@
         <v>43798</v>
       </c>
       <c r="C81" s="3">
-        <v>-0.55185764230928358</v>
+        <v>-0.45706512528304044</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
@@ -4405,7 +4404,7 @@
         <v>43769</v>
       </c>
       <c r="C82" s="3">
-        <v>2.001758753024041</v>
+        <v>-0.47533011678229098</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
@@ -4417,7 +4416,7 @@
         <v>43738</v>
       </c>
       <c r="C83" s="3">
-        <v>0.8601813319110585</v>
+        <v>1.113456805636126</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
@@ -4429,7 +4428,7 @@
         <v>43707</v>
       </c>
       <c r="C84" s="3">
-        <v>0.41881970314481265</v>
+        <v>-0.34077724295732414</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
@@ -4441,7 +4440,7 @@
         <v>43677</v>
       </c>
       <c r="C85" s="3">
-        <v>1.6157783235449585</v>
+        <v>-0.95499430176444466</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
@@ -4453,7 +4452,7 @@
         <v>43644</v>
       </c>
       <c r="C86" s="3">
-        <v>2.8648173165088497</v>
+        <v>0.78337329159474667</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
@@ -4465,7 +4464,7 @@
         <v>43616</v>
       </c>
       <c r="C87" s="3">
-        <v>-7.7713298994248277</v>
+        <v>-7.4527560687020049</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
@@ -4477,7 +4476,7 @@
         <v>43585</v>
       </c>
       <c r="C88" s="3">
-        <v>-2.3451346697111575</v>
+        <v>-4.3278836263841214</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
@@ -4489,7 +4488,7 @@
         <v>43553</v>
       </c>
       <c r="C89" s="3">
-        <v>9.6871613194907891</v>
+        <v>10.394716819699589</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
@@ -4501,7 +4500,7 @@
         <v>43524</v>
       </c>
       <c r="C90" s="3">
-        <v>20.760350353866674</v>
+        <v>20.323780785509026</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
@@ -4513,7 +4512,7 @@
         <v>43496</v>
       </c>
       <c r="C91" s="3">
-        <v>3.307088047633866</v>
+        <v>0.20243585690460364</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
@@ -4525,7 +4524,7 @@
         <v>43462</v>
       </c>
       <c r="C92" s="3">
-        <v>-5.7533808639995465</v>
+        <v>-4.7665394209741807</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
@@ -4537,7 +4536,7 @@
         <v>43434</v>
       </c>
       <c r="C93" s="3">
-        <v>2.6583417595123171</v>
+        <v>2.4364666567646909</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
@@ -4549,7 +4548,7 @@
         <v>43404</v>
       </c>
       <c r="C94" s="3">
-        <v>-10.930238534662395</v>
+        <v>-11.002015173238167</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.2">
@@ -4561,7 +4560,7 @@
         <v>43371</v>
       </c>
       <c r="C95" s="3">
-        <v>-0.76050476868998462</v>
+        <v>-0.29274176747116076</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.2">
@@ -4573,7 +4572,7 @@
         <v>43343</v>
       </c>
       <c r="C96" s="3">
-        <v>-7.7713046109850303</v>
+        <v>-7.2058840137848357</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.2">
@@ -4585,7 +4584,7 @@
         <v>43312</v>
       </c>
       <c r="C97" s="3">
-        <v>-2.1397178641631598</v>
+        <v>-0.55670778382994612</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
@@ -4597,7 +4596,7 @@
         <v>43280</v>
       </c>
       <c r="C98" s="3">
-        <v>-8.8993610845817699</v>
+        <v>-9.3268341127094363</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
@@ -4609,7 +4608,7 @@
         <v>43251</v>
       </c>
       <c r="C99" s="3">
-        <v>-0.27835720231160765</v>
+        <v>-1.8172547010709916</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
@@ -4621,7 +4620,7 @@
         <v>43217</v>
       </c>
       <c r="C100" s="3">
-        <v>-5.0069397271966025</v>
+        <v>-4.1498849451968356</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
@@ -4633,7 +4632,7 @@
         <v>43189</v>
       </c>
       <c r="C101" s="3">
-        <v>0.36869235138945466</v>
+        <v>1.5117211630039318</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.2">
@@ -4645,7 +4644,7 @@
         <v>43159</v>
       </c>
       <c r="C102" s="3">
-        <v>-2.9655502543263768</v>
+        <v>-2.6766063135022167</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.2">
@@ -4657,7 +4656,7 @@
         <v>43131</v>
       </c>
       <c r="C103" s="3">
-        <v>1.0799016344442469</v>
+        <v>-0.98354124923147879</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.2">
@@ -4669,7 +4668,7 @@
         <v>43098</v>
       </c>
       <c r="C104" s="3">
-        <v>0.88039686411813811</v>
+        <v>-0.20117280955567196</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
@@ -4681,7 +4680,7 @@
         <v>43069</v>
       </c>
       <c r="C105" s="3">
-        <v>-3.7256763491866352</v>
+        <v>-4.5240107878329443</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
@@ -4693,7 +4692,7 @@
         <v>43039</v>
       </c>
       <c r="C106" s="3">
-        <v>2.5293405139346969</v>
+        <v>-0.65200080681376837</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
@@ -4705,7 +4704,7 @@
         <v>43007</v>
       </c>
       <c r="C107" s="3">
-        <v>2.5011666742259964</v>
+        <v>2.0529220495361766</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.2">
@@ -4717,7 +4716,7 @@
         <v>42978</v>
       </c>
       <c r="C108" s="3">
-        <v>2.9661960482983307</v>
+        <v>2.7377816616207307</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
@@ -4729,7 +4728,7 @@
         <v>42947</v>
       </c>
       <c r="C109" s="3">
-        <v>-0.23329830259419815</v>
+        <v>2.6041177581096253</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
@@ -4741,7 +4740,7 @@
         <v>42916</v>
       </c>
       <c r="C110" s="3">
-        <v>6.7387211861919871</v>
+        <v>5.3922695957259847</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
@@ -4753,7 +4752,7 @@
         <v>42886</v>
       </c>
       <c r="C111" s="3">
-        <v>-3.6132901705594911</v>
+        <v>-6.2422213344584083</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
@@ -4765,7 +4764,7 @@
         <v>42853</v>
       </c>
       <c r="C112" s="3">
-        <v>-1.8609191530145841</v>
+        <v>-2.9646350902866714</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.2">
@@ -4777,7 +4776,7 @@
         <v>42825</v>
       </c>
       <c r="C113" s="3">
-        <v>0.3597089970323486</v>
+        <v>-0.76457027757731444</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.2">
@@ -4789,7 +4788,7 @@
         <v>42794</v>
       </c>
       <c r="C114" s="3">
-        <v>3.3753772961884199</v>
+        <v>3.6515863112494884</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.2">
@@ -4801,7 +4800,7 @@
         <v>42761</v>
       </c>
       <c r="C115" s="3">
-        <v>-1.2291107895865294</v>
+        <v>-0.63732257560221717</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.2">
@@ -4813,7 +4812,7 @@
         <v>42734</v>
       </c>
       <c r="C116" s="3">
-        <v>-7.58300458410055</v>
+        <v>-4.8887435477185655</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.2">
@@ -4825,7 +4824,7 @@
         <v>42704</v>
       </c>
       <c r="C117" s="3">
-        <v>2.8763103140568402</v>
+        <v>2.067072938064074</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.2">
@@ -4837,7 +4836,7 @@
         <v>42674</v>
       </c>
       <c r="C118" s="3">
-        <v>1.2938349065258814</v>
+        <v>1.961417841756119</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.2">
@@ -4849,7 +4848,7 @@
         <v>42643</v>
       </c>
       <c r="C119" s="3">
-        <v>-1.7689181181227753</v>
+        <v>-1.6493818985058528</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
@@ -4861,7 +4860,7 @@
         <v>42613</v>
       </c>
       <c r="C120" s="3">
-        <v>4.1477583236643634</v>
+        <v>3.7291958140237114</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
@@ -4873,7 +4872,7 @@
         <v>42580</v>
       </c>
       <c r="C121" s="3">
-        <v>-1.5305825275574669</v>
+        <v>1.2966192388956355</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
@@ -4885,7 +4884,7 @@
         <v>42551</v>
       </c>
       <c r="C122" s="3">
-        <v>3.2486333080510299</v>
+        <v>2.9621985853667487</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
@@ -4897,7 +4896,7 @@
         <v>42521</v>
       </c>
       <c r="C123" s="3">
-        <v>0.18136297038093829</v>
+        <v>-0.63939518784601468</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.2">
@@ -4909,7 +4908,7 @@
         <v>42489</v>
       </c>
       <c r="C124" s="3">
-        <v>-3.0015965959690361</v>
+        <v>-2.7651876020031607</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.2">
@@ -4921,7 +4920,7 @@
         <v>42460</v>
       </c>
       <c r="C125" s="3">
-        <v>14.927481175312153</v>
+        <v>15.052613398424143</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.2">
@@ -4933,7 +4932,7 @@
         <v>42429</v>
       </c>
       <c r="C126" s="3">
-        <v>-3.4066155288205779</v>
+        <v>-2.1702135409072953</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.2">
@@ -4945,7 +4944,7 @@
         <v>42398</v>
       </c>
       <c r="C127" s="3">
-        <v>-25.63532727090405</v>
+        <v>-28.20492671727607</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.2">
@@ -4957,7 +4956,7 @@
         <v>42369</v>
       </c>
       <c r="C128" s="3">
-        <v>5.2088424044246295</v>
+        <v>2.8250396023496993</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.2">
@@ -4969,7 +4968,7 @@
         <v>42338</v>
       </c>
       <c r="C129" s="3">
-        <v>4.2595169551910006</v>
+        <v>4.5649900085682926</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.2">
@@ -4981,7 +4980,7 @@
         <v>42307</v>
       </c>
       <c r="C130" s="3">
-        <v>15.596335694440967</v>
+        <v>15.697027924528451</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
@@ -4993,7 +4992,7 @@
         <v>42277</v>
       </c>
       <c r="C131" s="3">
-        <v>-5.3171327431380089</v>
+        <v>-6.952796818178852</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
@@ -5005,7 +5004,7 @@
         <v>42247</v>
       </c>
       <c r="C132" s="3">
-        <v>-14.749099218425609</v>
+        <v>-14.827735016657307</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
@@ -5017,7 +5016,7 @@
         <v>42216</v>
       </c>
       <c r="C133" s="3">
-        <v>-13.695883620862514</v>
+        <v>-13.237780439797342</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
@@ -5029,7 +5028,7 @@
         <v>42185</v>
       </c>
       <c r="C134" s="3">
-        <v>-10.946794772418755</v>
+        <v>-10.643536645748963</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.2">
@@ -5041,7 +5040,7 @@
         <v>42153</v>
       </c>
       <c r="C135" s="3">
-        <v>8.6499705775968661</v>
+        <v>17.676857182089535</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.2">
@@ -5053,7 +5052,7 @@
         <v>42124</v>
       </c>
       <c r="C136" s="3">
-        <v>12.597966181645525</v>
+        <v>16.773080876821854</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.2">
@@ -5065,7 +5064,7 @@
         <v>42094</v>
       </c>
       <c r="C137" s="3">
-        <v>11.932452003302707</v>
+        <v>20.514224312752294</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.2">
@@ -5077,7 +5076,7 @@
         <v>42062</v>
       </c>
       <c r="C138" s="3">
-        <v>5.4435176859843892</v>
+        <v>6.8481027310390186</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.2">
@@ -5089,7 +5088,7 @@
         <v>42034</v>
       </c>
       <c r="C139" s="3">
-        <v>1.2353576481593853</v>
+        <v>5.8243595278649307</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.2">
@@ -5101,7 +5100,7 @@
         <v>42004</v>
       </c>
       <c r="C140" s="3">
-        <v>22.354435185871214</v>
+        <v>1.4765120631609507</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.2">
@@ -5113,7 +5112,7 @@
         <v>41971</v>
       </c>
       <c r="C141" s="3">
-        <v>9.4414251486698131</v>
+        <v>5.1911232436282928</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
@@ -5125,7 +5124,7 @@
         <v>41943</v>
       </c>
       <c r="C142" s="3">
-        <v>1.7977695509573399</v>
+        <v>1.4299287710488828</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
@@ -5137,7 +5136,7 @@
         <v>41912</v>
       </c>
       <c r="C143" s="3">
-        <v>3.0432810432328372</v>
+        <v>11.026498239902205</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.2">
@@ -5149,7 +5148,7 @@
         <v>41880</v>
       </c>
       <c r="C144" s="3">
-        <v>-1.4478741551208318</v>
+        <v>4.0129714391085702</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
@@ -5161,7 +5160,7 @@
         <v>41851</v>
       </c>
       <c r="C145" s="3">
-        <v>8.3563804978024301</v>
+        <v>8.4624256956159272</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.2">
@@ -5173,7 +5172,7 @@
         <v>41820</v>
       </c>
       <c r="C146" s="3">
-        <v>-0.29266124169345931</v>
+        <v>2.4982777252288813</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.2">
@@ -5185,7 +5184,7 @@
         <v>41789</v>
       </c>
       <c r="C147" s="3">
-        <v>0.71062465010278686</v>
+        <v>1.6745924905142262</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.2">
@@ -5197,7 +5196,7 @@
         <v>41759</v>
       </c>
       <c r="C148" s="3">
-        <v>1.714759892722495</v>
+        <v>-1.9363443019411841</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.2">
@@ -5209,7 +5208,7 @@
         <v>41729</v>
       </c>
       <c r="C149" s="3">
-        <v>-2.3940917128534411</v>
+        <v>-3.4053173484737798</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.2">
@@ -5221,7 +5220,7 @@
         <v>41698</v>
       </c>
       <c r="C150" s="3">
-        <v>-2.7296842815855094</v>
+        <v>2.3295575042672434</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.2">
@@ -5233,7 +5232,7 @@
         <v>41669</v>
       </c>
       <c r="C151" s="3">
-        <v>-6.7614914351371791</v>
+        <v>1.4708432486414624</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.2">
@@ -5245,7 +5244,7 @@
         <v>41639</v>
       </c>
       <c r="C152" s="3">
-        <v>-4.9261302871441703</v>
+        <v>-2.9720125998921043</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
@@ -5257,7 +5256,7 @@
         <v>41607</v>
       </c>
       <c r="C153" s="3">
-        <v>1.1629356952917336</v>
+        <v>6.2618391961503761</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
@@ -5269,7 +5268,7 @@
         <v>41578</v>
       </c>
       <c r="C154" s="3">
-        <v>-0.82404640798611206</v>
+        <v>-4.1071106276367564</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.2">
@@ -5281,7 +5280,7 @@
         <v>41547</v>
       </c>
       <c r="C155" s="3">
-        <v>3.8048000355014544</v>
+        <v>5.6969587472994965</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
@@ -5293,7 +5292,7 @@
         <v>41516</v>
       </c>
       <c r="C156" s="3">
-        <v>5.6286247346561513</v>
+        <v>6.8033367699066982</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.2">
@@ -5305,7 +5304,7 @@
         <v>41486</v>
       </c>
       <c r="C157" s="3">
-        <v>0.92183135255909932</v>
+        <v>6.018736839372818</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.2">
@@ -5317,7 +5316,7 @@
         <v>41453</v>
       </c>
       <c r="C158" s="3">
-        <v>-16.888006187979656</v>
+        <v>-15.756460580992792</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.2">
@@ -5329,7 +5328,7 @@
         <v>41425</v>
       </c>
       <c r="C159" s="3">
-        <v>6.5186726259770289</v>
+        <v>14.058340157837556</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.2">
@@ -5341,7 +5340,7 @@
         <v>41390</v>
       </c>
       <c r="C160" s="3">
-        <v>-2.2315877949134588</v>
+        <v>-2.3067138342202531</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.2">
@@ -5353,7 +5352,7 @@
         <v>41362</v>
       </c>
       <c r="C161" s="3">
-        <v>-7.7962141739052138</v>
+        <v>-4.4596764202861401</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.2">
@@ -5365,7 +5364,7 @@
         <v>41333</v>
       </c>
       <c r="C162" s="3">
-        <v>-0.27137867316971986</v>
+        <v>3.6946659393879422</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.2">
@@ -5377,7 +5376,7 @@
         <v>41305</v>
       </c>
       <c r="C163" s="3">
-        <v>6.0460589850209745</v>
+        <v>6.2205955077445196</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
@@ -5389,7 +5388,7 @@
         <v>41274</v>
       </c>
       <c r="C164" s="3">
-        <v>15.35106249314364</v>
+        <v>16.304483665551395</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
@@ -5401,7 +5400,7 @@
         <v>41243</v>
       </c>
       <c r="C165" s="3">
-        <v>-6.6890040799093669</v>
+        <v>-11.094136322214897</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.2">
@@ -5413,7 +5412,7 @@
         <v>41213</v>
       </c>
       <c r="C166" s="3">
-        <v>-2.4129244808778205</v>
+        <v>-0.98929542039507545</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
@@ -5425,7 +5424,7 @@
         <v>41180</v>
       </c>
       <c r="C167" s="3">
-        <v>5.7024155662517728</v>
+        <v>1.9191591017677867</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.2">
@@ -5437,7 +5436,7 @@
         <v>41152</v>
       </c>
       <c r="C168" s="3">
-        <v>-9.3631639972695186</v>
+        <v>-0.62332393852605472</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.2">
@@ -5449,7 +5448,7 @@
         <v>41121</v>
       </c>
       <c r="C169" s="3">
-        <v>-4.6429292833070619</v>
+        <v>-8.9823147165125619</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.2">
@@ -5461,7 +5460,7 @@
         <v>41089</v>
       </c>
       <c r="C170" s="3">
-        <v>-6.3215371432572054</v>
+        <v>-7.5295323707178614</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.2">
@@ -5473,7 +5472,7 @@
         <v>41060</v>
       </c>
       <c r="C171" s="3">
-        <v>-0.38292234887199461</v>
+        <v>2.4273884623801756</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.2">
@@ -5485,7 +5484,7 @@
         <v>41026</v>
       </c>
       <c r="C172" s="3">
-        <v>8.1839485446845153</v>
+        <v>7.2517542442525951</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.2">
@@ -5497,7 +5496,7 @@
         <v>40998</v>
       </c>
       <c r="C173" s="3">
-        <v>-6.4106706766737691</v>
+        <v>-7.5561991091256058</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.2">
@@ -5509,7 +5508,7 @@
         <v>40968</v>
       </c>
       <c r="C174" s="3">
-        <v>8.0742083025703071</v>
+        <v>12.191553543579058</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
@@ -5521,7 +5520,7 @@
         <v>40939</v>
       </c>
       <c r="C175" s="3">
-        <v>4.3148440331093108</v>
+        <v>0.84851267687551246</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
@@ -5533,7 +5532,7 @@
         <v>40907</v>
       </c>
       <c r="C176" s="3">
-        <v>-7.9906967483495128</v>
+        <v>-14.481031387387555</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.2">
@@ -5545,7 +5544,7 @@
         <v>40877</v>
       </c>
       <c r="C177" s="3">
-        <v>-7.5139167278572732</v>
+        <v>-4.4862155513804458</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
@@ -5557,7 +5556,7 @@
         <v>40847</v>
       </c>
       <c r="C178" s="3">
-        <v>1.8322180372304153</v>
+        <v>3.6956275986380627</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.2">
@@ -5569,7 +5568,7 @@
         <v>40816</v>
       </c>
       <c r="C179" s="3">
-        <v>-9.6964144972033655</v>
+        <v>-12.948991747729044</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.2">
@@ -5581,7 +5580,7 @@
         <v>40786</v>
       </c>
       <c r="C180" s="3">
-        <v>-4.9451695969484959</v>
+        <v>-4.2733000311128038</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.2">
@@ -5593,7 +5592,7 @@
         <v>40753</v>
       </c>
       <c r="C181" s="3">
-        <v>-0.99499369619066025</v>
+        <v>1.069763013470082</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.2">
@@ -5605,7 +5604,7 @@
         <v>40724</v>
       </c>
       <c r="C182" s="3">
-        <v>3.8215568933114508</v>
+        <v>3.0388751733690711</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.2">
@@ -5617,7 +5616,7 @@
         <v>40694</v>
       </c>
       <c r="C183" s="3">
-        <v>-5.2615160686790059</v>
+        <v>-8.1166193150688954</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.2">
@@ -5629,7 +5628,7 @@
         <v>40662</v>
       </c>
       <c r="C184" s="3">
-        <v>-1.9892698350484461</v>
+        <v>-3.2704570552527623</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.2">
@@ -5641,7 +5640,7 @@
         <v>40633</v>
       </c>
       <c r="C185" s="3">
-        <v>-2.6315497811072119</v>
+        <v>-1.8606894949136477</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.2">
@@ -5653,7 +5652,7 @@
         <v>40602</v>
       </c>
       <c r="C186" s="3">
-        <v>7.5679442659764895</v>
+        <v>10.504504582659191</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
@@ -5665,7 +5664,7 @@
         <v>40574</v>
       </c>
       <c r="C187" s="3">
-        <v>-3.7232898333610542</v>
+        <v>-6.6006632749382561</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.2">
@@ -5677,7 +5676,7 @@
         <v>40543</v>
       </c>
       <c r="C188" s="3">
-        <v>0.99109229615910177</v>
+        <v>-3.4076161127008509</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
@@ -5689,7 +5688,7 @@
         <v>40512</v>
       </c>
       <c r="C189" s="3">
-        <v>-7.7124994277051773</v>
+        <v>1.0955016841090792</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.2">
@@ -5701,7 +5700,7 @@
         <v>40480</v>
       </c>
       <c r="C190" s="3">
-        <v>16.555660121778338</v>
+        <v>8.4728699385594908</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.2">
@@ -5713,7 +5712,7 @@
         <v>40451</v>
       </c>
       <c r="C191" s="3">
-        <v>1.1450063913773567</v>
+        <v>1.5539662026078593</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.2">
@@ -5725,7 +5724,7 @@
         <v>40421</v>
       </c>
       <c r="C192" s="3">
-        <v>5.1307394310762033</v>
+        <v>9.50003936885755</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.2">
@@ -5737,7 +5736,7 @@
         <v>40389</v>
       </c>
       <c r="C193" s="3">
-        <v>14.897394112690865</v>
+        <v>14.372251985556428</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.2">
@@ -5749,7 +5748,7 @@
         <v>40359</v>
       </c>
       <c r="C194" s="3">
-        <v>-8.0088501038888644</v>
+        <v>-10.717860306736915</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.2">
@@ -5761,7 +5760,7 @@
         <v>40329</v>
       </c>
       <c r="C195" s="3">
-        <v>-8.585530332396651</v>
+        <v>-7.5318996792065001</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.2">
@@ -5773,7 +5772,7 @@
         <v>40298</v>
       </c>
       <c r="C196" s="3">
-        <v>-10.659322013550121</v>
+        <v>-6.6750529892095738</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.2">
@@ -5785,7 +5784,7 @@
         <v>40268</v>
       </c>
       <c r="C197" s="3">
-        <v>0.46391091495261438</v>
+        <v>2.621243233877868</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
@@ -5797,7 +5796,7 @@
         <v>40235</v>
       </c>
       <c r="C198" s="3">
-        <v>2.4672156783390964</v>
+        <v>5.9438368655405194</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.2">
@@ -5809,7 +5808,7 @@
         <v>40207</v>
       </c>
       <c r="C199" s="3">
-        <v>-11.407076073889211</v>
+        <v>-2.4659913427441671</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
@@ -5821,7 +5820,7 @@
         <v>40178</v>
       </c>
       <c r="C200" s="3">
-        <v>1.5807858558900545</v>
+        <v>1.8143257437357674</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.2">
@@ -5833,7 +5832,7 @@
         <v>40147</v>
       </c>
       <c r="C201" s="3">
-        <v>9.6738662140093634</v>
+        <v>15.091244494384725</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.2">
@@ -5845,7 +5844,7 @@
         <v>40116</v>
       </c>
       <c r="C202" s="3">
-        <v>9.7290076325660557</v>
+        <v>12.5582871138612</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.2">
@@ -5857,7 +5856,7 @@
         <v>40086</v>
       </c>
       <c r="C203" s="3">
-        <v>5.8739443282694426</v>
+        <v>3.7408820081287431</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.2">
@@ -5869,7 +5868,7 @@
         <v>40056</v>
       </c>
       <c r="C204" s="3">
-        <v>-22.571111480757644</v>
+        <v>-16.560343370537577</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.2">
@@ -5881,7 +5880,7 @@
         <v>40025</v>
       </c>
       <c r="C205" s="3">
-        <v>18.191214349648298</v>
+        <v>13.797355531719347</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.2">
@@ -5893,7 +5892,7 @@
         <v>39994</v>
       </c>
       <c r="C206" s="3">
-        <v>14.205197118460667</v>
+        <v>5.3563777257207512</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.2">
@@ -5905,7 +5904,7 @@
         <v>39960</v>
       </c>
       <c r="C207" s="3">
-        <v>6.5814569530848521</v>
+        <v>6.1736099567852865</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.2">
@@ -5917,7 +5916,7 @@
         <v>39933</v>
       </c>
       <c r="C208" s="3">
-        <v>5.795654909349901</v>
+        <v>5.9053342886791427</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
@@ -5929,7 +5928,7 @@
         <v>39903</v>
       </c>
       <c r="C209" s="3">
-        <v>18.055858772804111</v>
+        <v>20.570520933623349</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.2">
@@ -5941,7 +5940,7 @@
         <v>39871</v>
       </c>
       <c r="C210" s="3">
-        <v>8.4528446370157653</v>
+        <v>7.9919770589281347</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
@@ -5953,7 +5952,7 @@
         <v>39836</v>
       </c>
       <c r="C211" s="3">
-        <v>8.1677887315930064</v>
+        <v>15.398778921468281</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.2">
@@ -5965,7 +5964,7 @@
         <v>39813</v>
       </c>
       <c r="C212" s="3">
-        <v>-2.5981777012375029</v>
+        <v>5.3209698878601053</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.2">
@@ -5977,7 +5976,7 @@
         <v>39780</v>
       </c>
       <c r="C213" s="3">
-        <v>14.028735150905192</v>
+        <v>17.888864561446649</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.2">
@@ -5989,7 +5988,7 @@
         <v>39752</v>
       </c>
       <c r="C214" s="3">
-        <v>-22.752729132936011</v>
+        <v>-26.871663449595772</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.2">
@@ -6001,7 +6000,7 @@
         <v>39717</v>
       </c>
       <c r="C215" s="3">
-        <v>-5.5592383240690708</v>
+        <v>-7.4185209682214985</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.2">
@@ -6013,7 +6012,7 @@
         <v>39689</v>
       </c>
       <c r="C216" s="3">
-        <v>-15.480868995750319</v>
+        <v>-23.533574151279147</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.2">
@@ -6025,7 +6024,7 @@
         <v>39660</v>
       </c>
       <c r="C217" s="3">
-        <v>1.0624091190720719</v>
+        <v>7.2324641150706137</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.2">
@@ -6037,7 +6036,7 @@
         <v>39629</v>
       </c>
       <c r="C218" s="3">
-        <v>-22.222853941915666</v>
+        <v>-25.08007309557302</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.2">
@@ -6049,7 +6048,7 @@
         <v>39598</v>
       </c>
       <c r="C219" s="3">
-        <v>-10.786052602447194</v>
+        <v>-3.7801760514124649</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
@@ -6061,7 +6060,7 @@
         <v>39568</v>
       </c>
       <c r="C220" s="3">
-        <v>1.524168520879865</v>
+        <v>-3.4845842014708861</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.2">
@@ -6073,7 +6072,7 @@
         <v>39538</v>
       </c>
       <c r="C221" s="3">
-        <v>-15.936322329986885</v>
+        <v>-20.039457317546983</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
@@ -6085,7 +6084,7 @@
         <v>39507</v>
       </c>
       <c r="C222" s="3">
-        <v>-0.21331579402069645</v>
+        <v>8.4530756966729292</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.2">
@@ -6097,7 +6096,7 @@
         <v>39478</v>
       </c>
       <c r="C223" s="3">
-        <v>-10.411566328008137</v>
+        <v>-5.7439531829857842</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.2">
@@ -6109,7 +6108,7 @@
         <v>39444</v>
       </c>
       <c r="C224" s="3">
-        <v>13.192282373741637</v>
+        <v>20.002051937795741</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.2">
@@ -6121,7 +6120,7 @@
         <v>39416</v>
       </c>
       <c r="C225" s="3">
-        <v>-19.934801602874998</v>
+        <v>-9.3897542142810551</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.2">
@@ -6133,7 +6132,7 @@
         <v>39386</v>
       </c>
       <c r="C226" s="3">
-        <v>3.5336439795088603</v>
+        <v>-10.493779076057553</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.2">
@@ -6145,7 +6144,7 @@
         <v>39353</v>
       </c>
       <c r="C227" s="3">
-        <v>5.5529981880707791</v>
+        <v>3.7980364404377687</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.2">
@@ -6157,7 +6156,7 @@
         <v>39325</v>
       </c>
       <c r="C228" s="3">
-        <v>17.583065880451045</v>
+        <v>11.219315902682926</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.2">
@@ -6169,7 +6168,7 @@
         <v>39294</v>
       </c>
       <c r="C229" s="3">
-        <v>21.146325944496326</v>
+        <v>22.816934719588922</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.2">
@@ -6181,7 +6180,7 @@
         <v>39262</v>
       </c>
       <c r="C230" s="3">
-        <v>-3.0730221995471596</v>
+        <v>-15.987113678044873</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
@@ -6193,7 +6192,7 @@
         <v>39233</v>
       </c>
       <c r="C231" s="3">
-        <v>19.127264588369354</v>
+        <v>9.3268700452315834</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.2">
@@ -6205,7 +6204,7 @@
         <v>39202</v>
       </c>
       <c r="C232" s="3">
-        <v>27.098246280148565</v>
+        <v>33.410923342756682</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
@@ -6217,7 +6216,7 @@
         <v>39171</v>
       </c>
       <c r="C233" s="3">
-        <v>6.3373019313285317</v>
+        <v>16.412396415722409</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.2">
@@ -6229,7 +6228,7 @@
         <v>39141</v>
       </c>
       <c r="C234" s="3">
-        <v>5.3290227170717186</v>
+        <v>17.296353384283194</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.2">
@@ -6241,7 +6240,7 @@
         <v>39113</v>
       </c>
       <c r="C235" s="3">
-        <v>14.830425540973335</v>
+        <v>24.143091024745299</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.2">
@@ -6253,7 +6252,7 @@
         <v>39080</v>
       </c>
       <c r="C236" s="3">
-        <v>17.295656692832793</v>
+        <v>6.3018223739635504</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.2">
@@ -6265,7 +6264,7 @@
         <v>39051</v>
       </c>
       <c r="C237" s="3">
-        <v>22.609788540658805</v>
+        <v>5.3304956607870047</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.2">
@@ -6277,7 +6276,7 @@
         <v>39021</v>
       </c>
       <c r="C238" s="3">
-        <v>6.8225578426815758</v>
+        <v>-0.59091967193771744</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.2">
@@ -6289,7 +6288,7 @@
         <v>38989</v>
       </c>
       <c r="C239" s="3">
-        <v>3.5402177494753939</v>
+        <v>4.7910669639840586</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.2">
@@ -6301,7 +6300,7 @@
         <v>38960</v>
       </c>
       <c r="C240" s="3">
-        <v>5.8764316925021154</v>
+        <v>3.8494250002105268</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.2">
@@ -6313,7 +6312,7 @@
         <v>38929</v>
       </c>
       <c r="C241" s="3">
-        <v>-8.2469383309733963</v>
+        <v>-4.1016961699063437</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
@@ -6325,7 +6324,7 @@
         <v>38898</v>
       </c>
       <c r="C242" s="3">
-        <v>0.22278164858886562</v>
+        <v>5.9659909350995077</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.2">
@@ -6337,7 +6336,7 @@
         <v>38868</v>
       </c>
       <c r="C243" s="3">
-        <v>11.537886830011136</v>
+        <v>22.830027547002917</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
@@ -6349,7 +6348,7 @@
         <v>38835</v>
       </c>
       <c r="C244" s="3">
-        <v>9.4332094565003466</v>
+        <v>14.139850897424733</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.2">
@@ -6361,7 +6360,7 @@
         <v>38807</v>
       </c>
       <c r="C245" s="3">
-        <v>4.9157456742046746</v>
+        <v>3.6823927208347262</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.2">
@@ -6373,7 +6372,7 @@
         <v>38776</v>
       </c>
       <c r="C246" s="3">
-        <v>3.3707373084990611</v>
+        <v>0.72448258328834392</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.2">
@@ -6385,7 +6384,7 @@
         <v>38742</v>
       </c>
       <c r="C247" s="3">
-        <v>13.225779190756292</v>
+        <v>11.353619390534696</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.2">
@@ -6397,7 +6396,7 @@
         <v>38716</v>
       </c>
       <c r="C248" s="3">
-        <v>6.9770517328782589</v>
+        <v>3.6927064496684814</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.2">
@@ -6409,7 +6408,7 @@
         <v>38686</v>
       </c>
       <c r="C249" s="3">
-        <v>0.54670937673253484</v>
+        <v>0.10148927363367033</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.2">
@@ -6421,7 +6420,7 @@
         <v>38656</v>
       </c>
       <c r="C250" s="3">
-        <v>-8.29514151897156</v>
+        <v>-4.6980537291735907</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.2">
@@ -6433,7 +6432,7 @@
         <v>38625</v>
       </c>
       <c r="C251" s="3">
-        <v>-1.6039679599570644</v>
+        <v>2.8831841276377279</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.2">
@@ -6445,7 +6444,7 @@
         <v>38595</v>
       </c>
       <c r="C252" s="3">
-        <v>2.1769500466135572</v>
+        <v>13.468532876850258</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
@@ -6457,7 +6456,7 @@
         <v>38562</v>
       </c>
       <c r="C253" s="3">
-        <v>4.6134561250330552</v>
+        <v>-5.8972687371604771</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.2">
@@ -6469,7 +6468,7 @@
         <v>38533</v>
       </c>
       <c r="C254" s="3">
-        <v>-1.4789068210891876</v>
+        <v>-0.67388488991958484</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
@@ -6481,7 +6480,7 @@
         <v>38503</v>
       </c>
       <c r="C255" s="3">
-        <v>-11.246274557508663</v>
+        <v>-5.9861186322499371</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.2">
@@ -6493,7 +6492,7 @@
         <v>38471</v>
       </c>
       <c r="C256" s="3">
-        <v>-0.43143501506142101</v>
+        <v>-5.4077369128235802</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.2">
@@ -6505,7 +6504,7 @@
         <v>38442</v>
       </c>
       <c r="C257" s="3">
-        <v>-6.1003732468328025</v>
+        <v>-12.223085339918715</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.2">
@@ -6517,7 +6516,7 @@
         <v>38411</v>
       </c>
       <c r="C258" s="3">
-        <v>10.863100906128565</v>
+        <v>10.642570934034779</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.2">
@@ -6529,7 +6528,7 @@
         <v>38383</v>
       </c>
       <c r="C259" s="3">
-        <v>-0.71998357005709224</v>
+        <v>-7.7346999999999948</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.2">
@@ -6541,1884 +6540,1556 @@
         <v>38352</v>
       </c>
       <c r="C260" s="3">
-        <v>-4.911182716703788</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A261" t="str">
         <f t="shared" si="3"/>
-        <v>2004/11</v>
+        <v/>
       </c>
       <c r="B261" s="2">
         <v>38321</v>
       </c>
-      <c r="C261" s="3">
-        <v>0.30024736129299345</v>
-      </c>
+      <c r="C261" s="3"/>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A262" t="str">
         <f t="shared" ref="A262:A325" si="4">IF(C262="","",TEXT(B262,"YYYY/MM"))</f>
-        <v>2004/10</v>
+        <v/>
       </c>
       <c r="B262" s="2">
         <v>38289</v>
       </c>
-      <c r="C262" s="3">
-        <v>-6.8781138604573577</v>
-      </c>
+      <c r="C262" s="3"/>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A263" t="str">
         <f t="shared" si="4"/>
-        <v>2004/09</v>
+        <v/>
       </c>
       <c r="B263" s="2">
         <v>38260</v>
       </c>
-      <c r="C263" s="3">
-        <v>8.7575004912160423</v>
-      </c>
+      <c r="C263" s="3"/>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A264" t="str">
         <f t="shared" si="4"/>
-        <v>2004/08</v>
+        <v/>
       </c>
       <c r="B264" s="2">
         <v>38230</v>
       </c>
-      <c r="C264" s="3">
-        <v>-3.2764507198396742</v>
-      </c>
+      <c r="C264" s="3"/>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A265" t="str">
         <f t="shared" si="4"/>
-        <v>2004/07</v>
+        <v/>
       </c>
       <c r="B265" s="2">
         <v>38198</v>
       </c>
-      <c r="C265" s="3">
-        <v>0.22955874047956293</v>
-      </c>
+      <c r="C265" s="3"/>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" t="str">
         <f t="shared" si="4"/>
-        <v>2004/06</v>
+        <v/>
       </c>
       <c r="B266" s="2">
         <v>38168</v>
       </c>
-      <c r="C266" s="3">
-        <v>-8.4356538150203715</v>
-      </c>
+      <c r="C266" s="3"/>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A267" t="str">
         <f t="shared" si="4"/>
-        <v>2004/05</v>
+        <v/>
       </c>
       <c r="B267" s="2">
         <v>38138</v>
       </c>
-      <c r="C267" s="3">
-        <v>-0.98309821655172547</v>
-      </c>
+      <c r="C267" s="3"/>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A268" t="str">
         <f t="shared" si="4"/>
-        <v>2004/04</v>
+        <v/>
       </c>
       <c r="B268" s="2">
         <v>38107</v>
       </c>
-      <c r="C268" s="3">
-        <v>-11.008824073437806</v>
-      </c>
+      <c r="C268" s="3"/>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A269" t="str">
         <f t="shared" si="4"/>
-        <v>2004/03</v>
+        <v/>
       </c>
       <c r="B269" s="2">
         <v>38077</v>
       </c>
-      <c r="C269" s="3">
-        <v>3.5772431974342211</v>
-      </c>
+      <c r="C269" s="3"/>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A270" t="str">
         <f t="shared" si="4"/>
-        <v>2004/02</v>
+        <v/>
       </c>
       <c r="B270" s="2">
         <v>38044</v>
       </c>
-      <c r="C270" s="3">
-        <v>5.4629043961463175</v>
-      </c>
+      <c r="C270" s="3"/>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A271" t="str">
         <f t="shared" si="4"/>
-        <v>2004/01</v>
+        <v/>
       </c>
       <c r="B271" s="2">
         <v>38016</v>
       </c>
-      <c r="C271" s="3">
-        <v>6.812841902226463</v>
-      </c>
+      <c r="C271" s="3"/>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A272" t="str">
         <f t="shared" si="4"/>
-        <v>2003/12</v>
+        <v/>
       </c>
       <c r="B272" s="2">
         <v>37986</v>
       </c>
-      <c r="C272" s="3">
-        <v>6.4828933465404415</v>
-      </c>
+      <c r="C272" s="3"/>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A273" t="str">
         <f t="shared" si="4"/>
-        <v>2003/11</v>
+        <v/>
       </c>
       <c r="B273" s="2">
         <v>37953</v>
       </c>
-      <c r="C273" s="3">
-        <v>3.1761677546988221</v>
-      </c>
+      <c r="C273" s="3"/>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A274" t="str">
         <f t="shared" si="4"/>
-        <v>2003/10</v>
+        <v/>
       </c>
       <c r="B274" s="2">
         <v>37925</v>
       </c>
-      <c r="C274" s="3">
-        <v>3.6808151117518451</v>
-      </c>
+      <c r="C274" s="3"/>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A275" t="str">
         <f t="shared" si="4"/>
-        <v>2003/09</v>
+        <v/>
       </c>
       <c r="B275" s="2">
         <v>37894</v>
       </c>
-      <c r="C275" s="3">
-        <v>-4.3062731528903715</v>
-      </c>
+      <c r="C275" s="3"/>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A276" t="str">
         <f t="shared" si="4"/>
-        <v>2003/08</v>
+        <v/>
       </c>
       <c r="B276" s="2">
         <v>37862</v>
       </c>
-      <c r="C276" s="3">
-        <v>-3.798557023256266</v>
-      </c>
+      <c r="C276" s="3"/>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" t="str">
         <f t="shared" si="4"/>
-        <v>2003/07</v>
+        <v/>
       </c>
       <c r="B277" s="2">
         <v>37833</v>
       </c>
-      <c r="C277" s="3">
-        <v>2.90284038703712</v>
-      </c>
+      <c r="C277" s="3"/>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A278" t="str">
         <f t="shared" si="4"/>
-        <v>2003/06</v>
+        <v/>
       </c>
       <c r="B278" s="2">
         <v>37802</v>
       </c>
-      <c r="C278" s="3">
-        <v>-7.9597201922201428</v>
-      </c>
+      <c r="C278" s="3"/>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A279" t="str">
         <f t="shared" si="4"/>
-        <v>2003/05</v>
+        <v/>
       </c>
       <c r="B279" s="2">
         <v>37771</v>
       </c>
-      <c r="C279" s="3">
-        <v>7.4503320397674822</v>
-      </c>
+      <c r="C279" s="3"/>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A280" t="str">
         <f t="shared" si="4"/>
-        <v>2003/04</v>
+        <v/>
       </c>
       <c r="B280" s="2">
         <v>37741</v>
       </c>
-      <c r="C280" s="3">
-        <v>5.1225732697714577</v>
-      </c>
+      <c r="C280" s="3"/>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A281" t="str">
         <f t="shared" si="4"/>
-        <v>2003/03</v>
+        <v/>
       </c>
       <c r="B281" s="2">
         <v>37711</v>
       </c>
-      <c r="C281" s="3">
-        <v>1.4594204382317288</v>
-      </c>
+      <c r="C281" s="3"/>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A282" t="str">
         <f t="shared" si="4"/>
-        <v>2003/02</v>
+        <v/>
       </c>
       <c r="B282" s="2">
         <v>37680</v>
       </c>
-      <c r="C282" s="3">
-        <v>0.19736374216337005</v>
-      </c>
+      <c r="C282" s="3"/>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A283" t="str">
         <f t="shared" si="4"/>
-        <v>2003/01</v>
+        <v/>
       </c>
       <c r="B283" s="2">
         <v>37650</v>
       </c>
-      <c r="C283" s="3">
-        <v>10.579458558330002</v>
-      </c>
+      <c r="C283" s="3"/>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A284" t="str">
         <f t="shared" si="4"/>
-        <v>2002/12</v>
+        <v/>
       </c>
       <c r="B284" s="2">
         <v>37621</v>
       </c>
-      <c r="C284" s="3">
-        <v>-5.5266547472231036</v>
-      </c>
+      <c r="C284" s="3"/>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A285" t="str">
         <f t="shared" si="4"/>
-        <v>2002/11</v>
+        <v/>
       </c>
       <c r="B285" s="2">
         <v>37589</v>
       </c>
-      <c r="C285" s="3">
-        <v>-3.8029974467950645</v>
-      </c>
+      <c r="C285" s="3"/>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A286" t="str">
         <f t="shared" si="4"/>
-        <v>2002/10</v>
+        <v/>
       </c>
       <c r="B286" s="2">
         <v>37560</v>
       </c>
-      <c r="C286" s="3">
-        <v>-6.4040301782469662</v>
-      </c>
+      <c r="C286" s="3"/>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A287" t="str">
         <f t="shared" si="4"/>
-        <v>2002/09</v>
+        <v/>
       </c>
       <c r="B287" s="2">
         <v>37526</v>
       </c>
-      <c r="C287" s="3">
-        <v>-5.6132037454140304</v>
-      </c>
+      <c r="C287" s="3"/>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" t="str">
         <f t="shared" si="4"/>
-        <v>2002/08</v>
+        <v/>
       </c>
       <c r="B288" s="2">
         <v>37498</v>
       </c>
-      <c r="C288" s="3">
-        <v>0.91434866751445298</v>
-      </c>
+      <c r="C288" s="3"/>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A289" t="str">
         <f t="shared" si="4"/>
-        <v>2002/07</v>
+        <v/>
       </c>
       <c r="B289" s="2">
         <v>37468</v>
       </c>
-      <c r="C289" s="3">
-        <v>-4.1005787130898641</v>
-      </c>
+      <c r="C289" s="3"/>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A290" t="str">
         <f t="shared" si="4"/>
-        <v>2002/06</v>
+        <v/>
       </c>
       <c r="B290" s="2">
         <v>37435</v>
       </c>
-      <c r="C290" s="3">
-        <v>16.935358269556033</v>
-      </c>
+      <c r="C290" s="3"/>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A291" t="str">
         <f t="shared" si="4"/>
-        <v>2002/05</v>
+        <v/>
       </c>
       <c r="B291" s="2">
         <v>37407</v>
       </c>
-      <c r="C291" s="3">
-        <v>-6.6531938305680711</v>
-      </c>
+      <c r="C291" s="3"/>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A292" t="str">
         <f t="shared" si="4"/>
-        <v>2002/04</v>
+        <v/>
       </c>
       <c r="B292" s="2">
         <v>37376</v>
       </c>
-      <c r="C292" s="3">
-        <v>2.5066952329941161</v>
-      </c>
+      <c r="C292" s="3"/>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A293" t="str">
         <f t="shared" si="4"/>
-        <v>2002/03</v>
+        <v/>
       </c>
       <c r="B293" s="2">
         <v>37344</v>
       </c>
-      <c r="C293" s="3">
-        <v>4.76680893483723</v>
-      </c>
+      <c r="C293" s="3"/>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A294" t="str">
         <f t="shared" si="4"/>
-        <v>2002/02</v>
+        <v/>
       </c>
       <c r="B294" s="2">
         <v>37315</v>
       </c>
-      <c r="C294" s="3">
-        <v>1.5688150690465585</v>
-      </c>
+      <c r="C294" s="3"/>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A295" t="str">
         <f t="shared" si="4"/>
-        <v>2002/01</v>
+        <v/>
       </c>
       <c r="B295" s="2">
         <v>37287</v>
       </c>
-      <c r="C295" s="3">
-        <v>-10.312737546547101</v>
-      </c>
+      <c r="C295" s="3"/>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A296" t="str">
         <f t="shared" si="4"/>
-        <v>2001/12</v>
+        <v/>
       </c>
       <c r="B296" s="2">
         <v>37256</v>
       </c>
-      <c r="C296" s="3">
-        <v>-5.3529105070591161</v>
-      </c>
+      <c r="C296" s="3"/>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A297" t="str">
         <f t="shared" si="4"/>
-        <v>2001/11</v>
+        <v/>
       </c>
       <c r="B297" s="2">
         <v>37225</v>
       </c>
-      <c r="C297" s="3">
-        <v>2.1876803097139241</v>
-      </c>
+      <c r="C297" s="3"/>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A298" t="str">
         <f t="shared" si="4"/>
-        <v>2001/10</v>
+        <v/>
       </c>
       <c r="B298" s="2">
         <v>37195</v>
       </c>
-      <c r="C298" s="3">
-        <v>-1.7177600578055618</v>
-      </c>
+      <c r="C298" s="3"/>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" t="str">
         <f t="shared" si="4"/>
-        <v>2001/09</v>
+        <v/>
       </c>
       <c r="B299" s="2">
         <v>37162</v>
       </c>
-      <c r="C299" s="3">
-        <v>-9.367186326167932</v>
-      </c>
+      <c r="C299" s="3"/>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A300" t="str">
         <f t="shared" si="4"/>
-        <v>2001/08</v>
+        <v/>
       </c>
       <c r="B300" s="2">
         <v>37134</v>
       </c>
-      <c r="C300" s="3">
-        <v>-4.8974996366109025</v>
-      </c>
+      <c r="C300" s="3"/>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A301" t="str">
         <f t="shared" si="4"/>
-        <v>2001/07</v>
+        <v/>
       </c>
       <c r="B301" s="2">
         <v>37103</v>
       </c>
-      <c r="C301" s="3">
-        <v>-13.94743492330549</v>
-      </c>
+      <c r="C301" s="3"/>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A302" t="str">
         <f t="shared" si="4"/>
-        <v>2001/06</v>
+        <v/>
       </c>
       <c r="B302" s="2">
         <v>37071</v>
       </c>
-      <c r="C302" s="3">
-        <v>-2.8939356883051048</v>
-      </c>
+      <c r="C302" s="3"/>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A303" t="str">
         <f t="shared" si="4"/>
-        <v>2001/05</v>
+        <v/>
       </c>
       <c r="B303" s="2">
         <v>37042</v>
       </c>
-      <c r="C303" s="3">
-        <v>1.142632978191771</v>
-      </c>
+      <c r="C303" s="3"/>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A304" t="str">
         <f t="shared" si="4"/>
-        <v>2001/04</v>
+        <v/>
       </c>
       <c r="B304" s="2">
         <v>37011</v>
       </c>
-      <c r="C304" s="3">
-        <v>-3.2902630011441891</v>
-      </c>
+      <c r="C304" s="3"/>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A305" t="str">
         <f t="shared" si="4"/>
-        <v>2001/03</v>
+        <v/>
       </c>
       <c r="B305" s="2">
         <v>36980</v>
       </c>
-      <c r="C305" s="3">
-        <v>11.51642783535134</v>
-      </c>
+      <c r="C305" s="3"/>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A306" t="str">
         <f t="shared" si="4"/>
-        <v>2001/02</v>
+        <v/>
       </c>
       <c r="B306" s="2">
         <v>36950</v>
       </c>
-      <c r="C306" s="3">
-        <v>-6.1185427738265403</v>
-      </c>
+      <c r="C306" s="3"/>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A307" t="str">
         <f t="shared" si="4"/>
-        <v>2001/01</v>
+        <v/>
       </c>
       <c r="B307" s="2">
         <v>36910</v>
       </c>
-      <c r="C307" s="3">
-        <v>-0.1974225033038679</v>
-      </c>
+      <c r="C307" s="3"/>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A308" t="str">
         <f t="shared" si="4"/>
-        <v>2000/12</v>
+        <v/>
       </c>
       <c r="B308" s="2">
         <v>36889</v>
       </c>
-      <c r="C308" s="3">
-        <v>-1.5992359410798351</v>
-      </c>
+      <c r="C308" s="3"/>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A309" t="str">
         <f t="shared" si="4"/>
-        <v>2000/11</v>
+        <v/>
       </c>
       <c r="B309" s="2">
         <v>36860</v>
       </c>
-      <c r="C309" s="3">
-        <v>5.6146386006895588</v>
-      </c>
+      <c r="C309" s="3"/>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" t="str">
         <f t="shared" si="4"/>
-        <v>2000/10</v>
+        <v/>
       </c>
       <c r="B310" s="2">
         <v>36830</v>
       </c>
-      <c r="C310" s="3">
-        <v>1.0957061740741736</v>
-      </c>
+      <c r="C310" s="3"/>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A311" t="str">
         <f t="shared" si="4"/>
-        <v>2000/09</v>
+        <v/>
       </c>
       <c r="B311" s="2">
         <v>36798</v>
       </c>
-      <c r="C311" s="3">
-        <v>-6.2707418079635646</v>
-      </c>
+      <c r="C311" s="3"/>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A312" t="str">
         <f t="shared" si="4"/>
-        <v>2000/08</v>
+        <v/>
       </c>
       <c r="B312" s="2">
         <v>36769</v>
       </c>
-      <c r="C312" s="3">
-        <v>-1.3857839756851398</v>
-      </c>
+      <c r="C312" s="3"/>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A313" t="str">
         <f t="shared" si="4"/>
-        <v>2000/07</v>
+        <v/>
       </c>
       <c r="B313" s="2">
         <v>36738</v>
       </c>
-      <c r="C313" s="3">
-        <v>1.3135020082083892</v>
-      </c>
+      <c r="C313" s="3"/>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A314" t="str">
         <f t="shared" si="4"/>
-        <v>2000/06</v>
+        <v/>
       </c>
       <c r="B314" s="2">
         <v>36707</v>
       </c>
-      <c r="C314" s="3">
-        <v>4.0386116767585856</v>
-      </c>
+      <c r="C314" s="3"/>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A315" t="str">
         <f t="shared" si="4"/>
-        <v>2000/05</v>
+        <v/>
       </c>
       <c r="B315" s="2">
         <v>36677</v>
       </c>
-      <c r="C315" s="3">
-        <v>-0.85444261045404257</v>
-      </c>
+      <c r="C315" s="3"/>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A316" t="str">
         <f t="shared" si="4"/>
-        <v>2000/04</v>
+        <v/>
       </c>
       <c r="B316" s="2">
         <v>36644</v>
       </c>
-      <c r="C316" s="3">
-        <v>3.3284770932634267</v>
-      </c>
+      <c r="C316" s="3"/>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A317" t="str">
         <f t="shared" si="4"/>
-        <v>2000/03</v>
+        <v/>
       </c>
       <c r="B317" s="2">
         <v>36616</v>
       </c>
-      <c r="C317" s="3">
-        <v>1.073756446017593</v>
-      </c>
+      <c r="C317" s="3"/>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A318" t="str">
         <f t="shared" si="4"/>
-        <v>2000/02</v>
+        <v/>
       </c>
       <c r="B318" s="2">
         <v>36585</v>
       </c>
-      <c r="C318" s="3">
-        <v>13.454004104334395</v>
-      </c>
+      <c r="C318" s="3"/>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A319" t="str">
         <f t="shared" si="4"/>
-        <v>2000/01</v>
+        <v/>
       </c>
       <c r="B319" s="2">
         <v>36553</v>
       </c>
-      <c r="C319" s="3">
-        <v>17.295541863251994</v>
-      </c>
+      <c r="C319" s="3"/>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A320" t="str">
         <f t="shared" si="4"/>
-        <v>1999/12</v>
+        <v/>
       </c>
       <c r="B320" s="2">
         <v>36524</v>
       </c>
-      <c r="C320" s="3">
-        <v>-4.6510976425183763</v>
-      </c>
+      <c r="C320" s="3"/>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" t="str">
         <f t="shared" si="4"/>
-        <v>1999/11</v>
+        <v/>
       </c>
       <c r="B321" s="2">
         <v>36494</v>
       </c>
-      <c r="C321" s="3">
-        <v>-5.5591305839701954</v>
-      </c>
+      <c r="C321" s="3"/>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A322" t="str">
         <f t="shared" si="4"/>
-        <v>1999/10</v>
+        <v/>
       </c>
       <c r="B322" s="2">
         <v>36462</v>
       </c>
-      <c r="C322" s="3">
-        <v>-5.6915630124012235</v>
-      </c>
+      <c r="C322" s="3"/>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A323" t="str">
         <f t="shared" si="4"/>
-        <v>1999/09</v>
+        <v/>
       </c>
       <c r="B323" s="2">
         <v>36433</v>
       </c>
-      <c r="C323" s="3">
-        <v>-4.4860874503123043</v>
-      </c>
+      <c r="C323" s="3"/>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A324" t="str">
         <f t="shared" si="4"/>
-        <v>1999/08</v>
+        <v/>
       </c>
       <c r="B324" s="2">
         <v>36403</v>
       </c>
-      <c r="C324" s="3">
-        <v>2.6905920493998536</v>
-      </c>
+      <c r="C324" s="3"/>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A325" t="str">
         <f t="shared" si="4"/>
-        <v>1999/07</v>
+        <v/>
       </c>
       <c r="B325" s="2">
         <v>36371</v>
       </c>
-      <c r="C325" s="3">
-        <v>-13.979387484918481</v>
-      </c>
+      <c r="C325" s="3"/>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A326" t="str">
         <f t="shared" ref="A326:A389" si="5">IF(C326="","",TEXT(B326,"YYYY/MM"))</f>
-        <v>1999/06</v>
+        <v/>
       </c>
       <c r="B326" s="2">
         <v>36341</v>
       </c>
-      <c r="C326" s="3">
-        <v>43.800415124017398</v>
-      </c>
+      <c r="C326" s="3"/>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A327" t="str">
         <f t="shared" si="5"/>
-        <v>1999/05</v>
+        <v/>
       </c>
       <c r="B327" s="2">
         <v>36311</v>
       </c>
-      <c r="C327" s="3">
-        <v>17.07163054836316</v>
-      </c>
+      <c r="C327" s="3"/>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A328" t="str">
         <f t="shared" si="5"/>
-        <v>1999/04</v>
+        <v/>
       </c>
       <c r="B328" s="2">
         <v>36280</v>
       </c>
-      <c r="C328" s="3">
-        <v>-2.7399296834362041</v>
-      </c>
+      <c r="C328" s="3"/>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A329" t="str">
         <f t="shared" si="5"/>
-        <v>1999/03</v>
+        <v/>
       </c>
       <c r="B329" s="2">
         <v>36250</v>
       </c>
-      <c r="C329" s="3">
-        <v>4.2410626792000805</v>
-      </c>
+      <c r="C329" s="3"/>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A330" t="str">
         <f t="shared" si="5"/>
-        <v>1999/02</v>
+        <v/>
       </c>
       <c r="B330" s="2">
         <v>36200</v>
       </c>
-      <c r="C330" s="3">
-        <v>-5.6531413227119192</v>
-      </c>
+      <c r="C330" s="3"/>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A331" t="str">
         <f t="shared" si="5"/>
-        <v>1999/01</v>
+        <v/>
       </c>
       <c r="B331" s="2">
         <v>36189</v>
       </c>
-      <c r="C331" s="3">
-        <v>-0.98066772747724684</v>
-      </c>
+      <c r="C331" s="3"/>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" t="str">
         <f t="shared" si="5"/>
-        <v>1998/12</v>
+        <v/>
       </c>
       <c r="B332" s="2">
         <v>36160</v>
       </c>
-      <c r="C332" s="3">
-        <v>-7.8528203098174547</v>
-      </c>
+      <c r="C332" s="3"/>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A333" t="str">
         <f t="shared" si="5"/>
-        <v>1998/11</v>
+        <v/>
       </c>
       <c r="B333" s="2">
         <v>36129</v>
       </c>
-      <c r="C333" s="3">
-        <v>2.8377041068777809</v>
-      </c>
+      <c r="C333" s="3"/>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A334" t="str">
         <f t="shared" si="5"/>
-        <v>1998/10</v>
+        <v/>
       </c>
       <c r="B334" s="2">
         <v>36098</v>
       </c>
-      <c r="C334" s="3">
-        <v>-5.2090351017185954</v>
-      </c>
+      <c r="C334" s="3"/>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A335" t="str">
         <f t="shared" si="5"/>
-        <v>1998/09</v>
+        <v/>
       </c>
       <c r="B335" s="2">
         <v>36068</v>
       </c>
-      <c r="C335" s="3">
-        <v>0.85624406964588395</v>
-      </c>
+      <c r="C335" s="3"/>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A336" t="str">
         <f t="shared" si="5"/>
-        <v>1998/08</v>
+        <v/>
       </c>
       <c r="B336" s="2">
         <v>36038</v>
       </c>
-      <c r="C336" s="3">
-        <v>-13.047738985391321</v>
-      </c>
+      <c r="C336" s="3"/>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A337" t="str">
         <f t="shared" si="5"/>
-        <v>1998/07</v>
+        <v/>
       </c>
       <c r="B337" s="2">
         <v>36007</v>
       </c>
-      <c r="C337" s="3">
-        <v>0.18361620093210185</v>
-      </c>
+      <c r="C337" s="3"/>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A338" t="str">
         <f t="shared" si="5"/>
-        <v>1998/06</v>
+        <v/>
       </c>
       <c r="B338" s="2">
         <v>35976</v>
       </c>
-      <c r="C338" s="3">
-        <v>-10.703039110667845</v>
-      </c>
+      <c r="C338" s="3"/>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A339" t="str">
         <f t="shared" si="5"/>
-        <v>1998/05</v>
+        <v/>
       </c>
       <c r="B339" s="2">
         <v>35944</v>
       </c>
-      <c r="C339" s="3">
-        <v>9.8566068206484836E-2</v>
-      </c>
+      <c r="C339" s="3"/>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A340" t="str">
         <f t="shared" si="5"/>
-        <v>1998/04</v>
+        <v/>
       </c>
       <c r="B340" s="2">
         <v>35915</v>
       </c>
-      <c r="C340" s="3">
-        <v>2.8957575993241003</v>
-      </c>
+      <c r="C340" s="3"/>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A341" t="str">
         <f t="shared" si="5"/>
-        <v>1998/03</v>
+        <v/>
       </c>
       <c r="B341" s="2">
         <v>35885</v>
       </c>
-      <c r="C341" s="3">
-        <v>-0.45089133357163469</v>
-      </c>
+      <c r="C341" s="3"/>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A342" t="str">
         <f t="shared" si="5"/>
-        <v>1998/02</v>
+        <v/>
       </c>
       <c r="B342" s="2">
         <v>35853</v>
       </c>
-      <c r="C342" s="3">
-        <v>-2.0068499530884187</v>
-      </c>
+      <c r="C342" s="3"/>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" t="str">
         <f t="shared" si="5"/>
-        <v>1998/01</v>
+        <v/>
       </c>
       <c r="B343" s="2">
         <v>35818</v>
       </c>
-      <c r="C343" s="3">
-        <v>-0.46740093537538385</v>
-      </c>
+      <c r="C343" s="3"/>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A344" t="str">
         <f t="shared" si="5"/>
-        <v>1997/12</v>
+        <v/>
       </c>
       <c r="B344" s="2">
         <v>35795</v>
       </c>
-      <c r="C344" s="3">
-        <v>-1.9596616322579474</v>
-      </c>
+      <c r="C344" s="3"/>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A345" t="str">
         <f t="shared" si="5"/>
-        <v>1997/11</v>
+        <v/>
       </c>
       <c r="B345" s="2">
         <v>35762</v>
       </c>
-      <c r="C345" s="3">
-        <v>-5.6335453091372001</v>
-      </c>
+      <c r="C345" s="3"/>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A346" t="str">
         <f t="shared" si="5"/>
-        <v>1997/10</v>
+        <v/>
       </c>
       <c r="B346" s="2">
         <v>35734</v>
       </c>
-      <c r="C346" s="3">
-        <v>15.484814791647782</v>
-      </c>
+      <c r="C346" s="3"/>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A347" t="str">
         <f t="shared" si="5"/>
-        <v>1997/09</v>
+        <v/>
       </c>
       <c r="B347" s="2">
         <v>35703</v>
       </c>
-      <c r="C347" s="3">
-        <v>-10.956104425476864</v>
-      </c>
+      <c r="C347" s="3"/>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A348" t="str">
         <f t="shared" si="5"/>
-        <v>1997/08</v>
+        <v/>
       </c>
       <c r="B348" s="2">
         <v>35671</v>
       </c>
-      <c r="C348" s="3">
-        <v>-2.9753018777031404</v>
-      </c>
+      <c r="C348" s="3"/>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A349" t="str">
         <f t="shared" si="5"/>
-        <v>1997/07</v>
+        <v/>
       </c>
       <c r="B349" s="2">
         <v>35642</v>
       </c>
-      <c r="C349" s="3">
-        <v>-10.780828921531393</v>
-      </c>
+      <c r="C349" s="3"/>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A350" t="str">
         <f t="shared" si="5"/>
-        <v>1997/06</v>
+        <v/>
       </c>
       <c r="B350" s="2">
         <v>35608</v>
       </c>
-      <c r="C350" s="3">
-        <v>4.8974186682851029</v>
-      </c>
+      <c r="C350" s="3"/>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A351" t="str">
         <f t="shared" si="5"/>
-        <v>1997/05</v>
+        <v/>
       </c>
       <c r="B351" s="2">
         <v>35580</v>
       </c>
-      <c r="C351" s="3">
-        <v>-7.0342751503960299</v>
-      </c>
+      <c r="C351" s="3"/>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A352" t="str">
         <f t="shared" si="5"/>
-        <v>1997/04</v>
+        <v/>
       </c>
       <c r="B352" s="2">
         <v>35550</v>
       </c>
-      <c r="C352" s="3">
-        <v>14.691542451720331</v>
-      </c>
+      <c r="C352" s="3"/>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A353" t="str">
         <f t="shared" si="5"/>
-        <v>1997/03</v>
+        <v/>
       </c>
       <c r="B353" s="2">
         <v>35520</v>
       </c>
-      <c r="C353" s="3">
-        <v>20.536383240192624</v>
-      </c>
+      <c r="C353" s="3"/>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" t="str">
         <f t="shared" si="5"/>
-        <v>1997/02</v>
+        <v/>
       </c>
       <c r="B354" s="2">
         <v>35489</v>
       </c>
-      <c r="C354" s="3">
-        <v>1.9679899319944294</v>
-      </c>
+      <c r="C354" s="3"/>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A355" t="str">
         <f t="shared" si="5"/>
-        <v>1997/01</v>
+        <v/>
       </c>
       <c r="B355" s="2">
         <v>35461</v>
       </c>
-      <c r="C355" s="3">
-        <v>14.884654186332291</v>
-      </c>
+      <c r="C355" s="3"/>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A356" t="str">
         <f t="shared" si="5"/>
-        <v>1996/12</v>
+        <v/>
       </c>
       <c r="B356" s="2">
         <v>35430</v>
       </c>
-      <c r="C356" s="3">
-        <v>-21.108318642222624</v>
-      </c>
+      <c r="C356" s="3"/>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A357" t="str">
         <f t="shared" si="5"/>
-        <v>1996/11</v>
+        <v/>
       </c>
       <c r="B357" s="2">
         <v>35398</v>
       </c>
-      <c r="C357" s="3">
-        <v>13.561417914582851</v>
-      </c>
+      <c r="C357" s="3"/>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A358" t="str">
         <f t="shared" si="5"/>
-        <v>1996/10</v>
+        <v/>
       </c>
       <c r="B358" s="2">
         <v>35369</v>
       </c>
-      <c r="C358" s="3">
-        <v>29.932714335124434</v>
-      </c>
+      <c r="C358" s="3"/>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A359" t="str">
         <f t="shared" si="5"/>
-        <v>1996/09</v>
+        <v/>
       </c>
       <c r="B359" s="2">
         <v>35335</v>
       </c>
-      <c r="C359" s="3">
-        <v>1.9208361234597904</v>
-      </c>
+      <c r="C359" s="3"/>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A360" t="str">
         <f t="shared" si="5"/>
-        <v>1996/08</v>
+        <v/>
       </c>
       <c r="B360" s="2">
         <v>35307</v>
       </c>
-      <c r="C360" s="3">
-        <v>4.7969960665536604</v>
-      </c>
+      <c r="C360" s="3"/>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A361" t="str">
         <f t="shared" si="5"/>
-        <v>1996/07</v>
+        <v/>
       </c>
       <c r="B361" s="2">
         <v>35277</v>
       </c>
-      <c r="C361" s="3">
-        <v>25.67483630214522</v>
-      </c>
+      <c r="C361" s="3"/>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A362" t="str">
         <f t="shared" si="5"/>
-        <v>1996/06</v>
+        <v/>
       </c>
       <c r="B362" s="2">
         <v>35244</v>
       </c>
-      <c r="C362" s="3">
-        <v>18.655525232455751</v>
-      </c>
+      <c r="C362" s="3"/>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A363" t="str">
         <f t="shared" si="5"/>
-        <v>1996/05</v>
+        <v/>
       </c>
       <c r="B363" s="2">
         <v>35216</v>
       </c>
-      <c r="C363" s="3">
-        <v>13.755391533489792</v>
-      </c>
+      <c r="C363" s="3"/>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A364" t="str">
         <f t="shared" si="5"/>
-        <v>1996/04</v>
+        <v/>
       </c>
       <c r="B364" s="2">
         <v>35185</v>
       </c>
-      <c r="C364" s="3">
-        <v>50.298026620427372</v>
-      </c>
+      <c r="C364" s="3"/>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" t="str">
         <f t="shared" si="5"/>
-        <v>1996/03</v>
+        <v/>
       </c>
       <c r="B365" s="2">
         <v>35153</v>
       </c>
-      <c r="C365" s="3">
-        <v>0.37380220127962716</v>
-      </c>
+      <c r="C365" s="3"/>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A366" t="str">
         <f t="shared" si="5"/>
-        <v>1996/02</v>
+        <v/>
       </c>
       <c r="B366" s="2">
         <v>35111</v>
       </c>
-      <c r="C366" s="3">
-        <v>5.4792948784812667</v>
-      </c>
+      <c r="C366" s="3"/>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A367" t="str">
         <f t="shared" si="5"/>
-        <v>1996/01</v>
+        <v/>
       </c>
       <c r="B367" s="2">
         <v>35095</v>
       </c>
-      <c r="C367" s="3">
-        <v>-2.9410275879524161</v>
-      </c>
+      <c r="C367" s="3"/>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A368" t="str">
         <f t="shared" si="5"/>
-        <v>1995/12</v>
+        <v/>
       </c>
       <c r="B368" s="2">
         <v>35062</v>
       </c>
-      <c r="C368" s="3">
-        <v>-9.0620339170303321</v>
-      </c>
+      <c r="C368" s="3"/>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A369" t="str">
         <f t="shared" si="5"/>
-        <v>1995/11</v>
+        <v/>
       </c>
       <c r="B369" s="2">
         <v>35033</v>
       </c>
-      <c r="C369" s="3">
-        <v>-5.8549227288880346</v>
-      </c>
+      <c r="C369" s="3"/>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A370" t="str">
         <f t="shared" si="5"/>
-        <v>1995/10</v>
+        <v/>
       </c>
       <c r="B370" s="2">
         <v>35003</v>
       </c>
-      <c r="C370" s="3">
-        <v>-0.96398159593462651</v>
-      </c>
+      <c r="C370" s="3"/>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A371" t="str">
         <f t="shared" si="5"/>
-        <v>1995/09</v>
+        <v/>
       </c>
       <c r="B371" s="2">
         <v>34971</v>
       </c>
-      <c r="C371" s="3">
-        <v>-0.585414142103724</v>
-      </c>
+      <c r="C371" s="3"/>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A372" t="str">
         <f t="shared" si="5"/>
-        <v>1995/08</v>
+        <v/>
       </c>
       <c r="B372" s="2">
         <v>34942</v>
       </c>
-      <c r="C372" s="3">
-        <v>8.1952985060846029</v>
-      </c>
+      <c r="C372" s="3"/>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A373" t="str">
         <f t="shared" si="5"/>
-        <v>1995/07</v>
+        <v/>
       </c>
       <c r="B373" s="2">
         <v>34911</v>
       </c>
-      <c r="C373" s="3">
-        <v>3.0778894472361706</v>
-      </c>
+      <c r="C373" s="3"/>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A374" t="str">
         <f t="shared" si="5"/>
-        <v>1995/06</v>
+        <v/>
       </c>
       <c r="B374" s="2">
         <v>34880</v>
       </c>
-      <c r="C374" s="3">
-        <v>-7.0307384664389794</v>
-      </c>
+      <c r="C374" s="3"/>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A375" t="str">
         <f t="shared" si="5"/>
-        <v>1995/05</v>
+        <v/>
       </c>
       <c r="B375" s="2">
         <v>34850</v>
       </c>
-      <c r="C375" s="3">
-        <v>3.8558379739390913</v>
-      </c>
+      <c r="C375" s="3"/>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" t="str">
         <f t="shared" si="5"/>
-        <v>1995/04</v>
+        <v/>
       </c>
       <c r="B376" s="2">
         <v>34817</v>
       </c>
-      <c r="C376" s="3">
-        <v>-11.192537764103893</v>
-      </c>
+      <c r="C376" s="3"/>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A377" t="str">
         <f t="shared" si="5"/>
-        <v>1995/03</v>
+        <v/>
       </c>
       <c r="B377" s="2">
         <v>34789</v>
       </c>
-      <c r="C377" s="3">
-        <v>4.3471966755228575</v>
-      </c>
+      <c r="C377" s="3"/>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A378" t="str">
         <f t="shared" si="5"/>
-        <v>1995/02</v>
+        <v/>
       </c>
       <c r="B378" s="2">
         <v>34758</v>
       </c>
-      <c r="C378" s="3">
-        <v>1.5276877188431959</v>
-      </c>
+      <c r="C378" s="3"/>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A379" t="str">
         <f t="shared" si="5"/>
-        <v>1995/01</v>
+        <v/>
       </c>
       <c r="B379" s="2">
         <v>34726</v>
       </c>
-      <c r="C379" s="3">
-        <v>-9.000432713111195</v>
-      </c>
+      <c r="C379" s="3"/>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A380" t="str">
         <f t="shared" si="5"/>
-        <v>1994/12</v>
+        <v/>
       </c>
       <c r="B380" s="2">
         <v>34698</v>
       </c>
-      <c r="C380" s="3">
-        <v>-6.9257412329840502</v>
-      </c>
+      <c r="C380" s="3"/>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A381" t="str">
         <f t="shared" si="5"/>
-        <v>1994/11</v>
+        <v/>
       </c>
       <c r="B381" s="2">
         <v>34668</v>
       </c>
-      <c r="C381" s="3">
-        <v>-1.5464140496582623</v>
-      </c>
+      <c r="C381" s="3"/>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A382" t="str">
         <f t="shared" si="5"/>
-        <v>1994/10</v>
+        <v/>
       </c>
       <c r="B382" s="2">
         <v>34638</v>
       </c>
-      <c r="C382" s="3">
-        <v>-19.383935836336164</v>
-      </c>
+      <c r="C382" s="3"/>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A383" t="str">
         <f t="shared" si="5"/>
-        <v>1994/09</v>
+        <v/>
       </c>
       <c r="B383" s="2">
         <v>34607</v>
       </c>
-      <c r="C383" s="3">
-        <v>13.420478441144091</v>
-      </c>
+      <c r="C383" s="3"/>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A384" t="str">
         <f t="shared" si="5"/>
-        <v>1994/08</v>
+        <v/>
       </c>
       <c r="B384" s="2">
         <v>34577</v>
       </c>
-      <c r="C384" s="3">
-        <v>56.315431539032225</v>
-      </c>
+      <c r="C384" s="3"/>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A385" t="str">
         <f t="shared" si="5"/>
-        <v>1994/07</v>
+        <v/>
       </c>
       <c r="B385" s="2">
         <v>34544</v>
       </c>
-      <c r="C385" s="3">
-        <v>-15.118862280686407</v>
-      </c>
+      <c r="C385" s="3"/>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A386" t="str">
         <f t="shared" si="5"/>
-        <v>1994/06</v>
+        <v/>
       </c>
       <c r="B386" s="2">
         <v>34515</v>
       </c>
-      <c r="C386" s="3">
-        <v>-14.090137204514374</v>
-      </c>
+      <c r="C386" s="3"/>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" t="str">
         <f t="shared" si="5"/>
-        <v>1994/05</v>
+        <v/>
       </c>
       <c r="B387" s="2">
         <v>34485</v>
       </c>
-      <c r="C387" s="3">
-        <v>-1.8981136804239962</v>
-      </c>
+      <c r="C387" s="3"/>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A388" t="str">
         <f t="shared" si="5"/>
-        <v>1994/04</v>
+        <v/>
       </c>
       <c r="B388" s="2">
         <v>34453</v>
       </c>
-      <c r="C388" s="3">
-        <v>-13.070697620771632</v>
-      </c>
+      <c r="C388" s="3"/>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A389" t="str">
         <f t="shared" si="5"/>
-        <v>1994/03</v>
+        <v/>
       </c>
       <c r="B389" s="2">
         <v>34424</v>
       </c>
-      <c r="C389" s="3">
-        <v>-16.793828009618405</v>
-      </c>
+      <c r="C389" s="3"/>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A390" t="str">
         <f t="shared" ref="A390:A401" si="6">IF(C390="","",TEXT(B390,"YYYY/MM"))</f>
-        <v>1994/02</v>
+        <v/>
       </c>
       <c r="B390" s="2">
         <v>34393</v>
       </c>
-      <c r="C390" s="3">
-        <v>1.7181068284984446</v>
-      </c>
+      <c r="C390" s="3"/>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A391" t="str">
         <f t="shared" si="6"/>
-        <v>1994/01</v>
+        <v/>
       </c>
       <c r="B391" s="2">
         <v>34365</v>
       </c>
-      <c r="C391" s="3">
-        <v>-17.142690237172975</v>
-      </c>
+      <c r="C391" s="3"/>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A392" t="str">
         <f t="shared" si="6"/>
-        <v>1993/12</v>
+        <v/>
       </c>
       <c r="B392" s="2">
         <v>34334</v>
       </c>
-      <c r="C392" s="3">
-        <v>-2.7738578425161697</v>
-      </c>
+      <c r="C392" s="3"/>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A393" t="str">
         <f t="shared" si="6"/>
-        <v>1993/11</v>
+        <v/>
       </c>
       <c r="B393" s="2">
         <v>34303</v>
       </c>
-      <c r="C393" s="3">
-        <v>7.8836355409335201</v>
-      </c>
+      <c r="C393" s="3"/>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A394" t="str">
         <f t="shared" si="6"/>
-        <v>1993/10</v>
+        <v/>
       </c>
       <c r="B394" s="2">
         <v>34271</v>
       </c>
-      <c r="C394" s="3">
-        <v>-4.7144050516936158</v>
-      </c>
+      <c r="C394" s="3"/>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A395" t="str">
         <f t="shared" si="6"/>
-        <v>1993/09</v>
+        <v/>
       </c>
       <c r="B395" s="2">
         <v>34242</v>
       </c>
-      <c r="C395" s="3">
-        <v>-4.4505190341116325</v>
-      </c>
+      <c r="C395" s="3"/>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A396" t="str">
         <f t="shared" si="6"/>
-        <v>1993/08</v>
+        <v/>
       </c>
       <c r="B396" s="2">
         <v>34212</v>
       </c>
-      <c r="C396" s="3">
-        <v>11.549434663143487</v>
-      </c>
+      <c r="C396" s="3"/>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A397" t="str">
         <f t="shared" si="6"/>
-        <v>1993/07</v>
+        <v/>
       </c>
       <c r="B397" s="2">
         <v>34180</v>
       </c>
-      <c r="C397" s="3">
-        <v>-10.656151365592038</v>
-      </c>
+      <c r="C397" s="3"/>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" t="str">
         <f t="shared" si="6"/>
-        <v>1993/06</v>
+        <v/>
       </c>
       <c r="B398" s="2">
         <v>34150</v>
       </c>
-      <c r="C398" s="3">
-        <v>-6.8569220534515747</v>
-      </c>
+      <c r="C398" s="3"/>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A399" t="str">
         <f t="shared" si="6"/>
-        <v>1993/05</v>
+        <v/>
       </c>
       <c r="B399" s="2">
         <v>34120</v>
       </c>
-      <c r="C399" s="3">
-        <v>-13.278197514742619</v>
-      </c>
+      <c r="C399" s="3"/>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A400" t="str">
         <f t="shared" si="6"/>
-        <v>1993/04</v>
+        <v/>
       </c>
       <c r="B400" s="2">
         <v>34089</v>
       </c>
-      <c r="C400" s="3">
-        <v>-0.49158293141557952</v>
-      </c>
+      <c r="C400" s="3"/>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A401" t="str">
         <f t="shared" si="6"/>
-        <v>1993/03</v>
+        <v/>
       </c>
       <c r="B401" s="2">
         <v>34059</v>
       </c>
-      <c r="C401" s="3">
-        <v>-8.6837644399799139</v>
-      </c>
+      <c r="C401" s="3"/>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B402" s="2">
         <v>34026</v>
       </c>
-      <c r="C402" s="3">
-        <v>21.997081812646236</v>
-      </c>
+      <c r="C402" s="3"/>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B403" s="2">
         <v>33998</v>
       </c>
-      <c r="C403" s="3">
-        <v>13.050650064725055</v>
-      </c>
+      <c r="C403" s="3"/>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B404" s="2">
         <v>33969</v>
       </c>
-      <c r="C404" s="3">
-        <v>11.466240704189335</v>
-      </c>
+      <c r="C404" s="3"/>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B405" s="2">
         <v>33938</v>
       </c>
-      <c r="C405" s="3">
-        <v>-5.639318582337971</v>
-      </c>
+      <c r="C405" s="3"/>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B406" s="2">
         <v>33907</v>
       </c>
-      <c r="C406" s="3">
-        <v>-13.829920814923513</v>
-      </c>
+      <c r="C406" s="3"/>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B407" s="2">
         <v>33877</v>
       </c>
-      <c r="C407" s="3">
-        <v>-0.6645852091786919</v>
-      </c>
+      <c r="C407" s="3"/>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B408" s="2">
         <v>33847</v>
       </c>
-      <c r="C408" s="3">
-        <v>-9.0815339308306431</v>
-      </c>
+      <c r="C408" s="3"/>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B409" s="2">
         <v>33816</v>
       </c>
-      <c r="C409" s="3">
-        <v>7.2174388825983371</v>
-      </c>
+      <c r="C409" s="3"/>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B410" s="2">
         <v>33785</v>
       </c>
-      <c r="C410" s="3">
-        <v>-4.8802790176554423</v>
-      </c>
+      <c r="C410" s="3"/>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B411" s="2">
         <v>33753</v>
       </c>
-      <c r="C411" s="3">
-        <v>38.547550374554326</v>
-      </c>
+      <c r="C411" s="3"/>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B412" s="2">
         <v>33724</v>
       </c>
-      <c r="C412" s="3">
-        <v>58.006171374317582</v>
-      </c>
+      <c r="C412" s="3"/>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B413" s="2">
         <v>33694</v>
       </c>
-      <c r="C413" s="3">
-        <v>27.135011165429425</v>
-      </c>
+      <c r="C413" s="3"/>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B414" s="2">
         <v>33662</v>
       </c>
-      <c r="C414" s="3">
-        <v>-1.0559840756407035</v>
-      </c>
+      <c r="C414" s="3"/>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B415" s="2">
         <v>33634</v>
       </c>
-      <c r="C415" s="3">
-        <v>4.273690546613107</v>
-      </c>
+      <c r="C415" s="3"/>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B416" s="2">
         <v>33603</v>
       </c>
-      <c r="C416" s="3">
-        <v>7.0871304734385632</v>
-      </c>
+      <c r="C416" s="3"/>
     </row>
     <row r="417" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B417" s="2">
         <v>33571</v>
       </c>
-      <c r="C417" s="3">
-        <v>15.387081468562847</v>
-      </c>
+      <c r="C417" s="3"/>
     </row>
     <row r="418" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B418" s="2">
         <v>33542</v>
       </c>
-      <c r="C418" s="3">
-        <v>88.46005123495577</v>
-      </c>
+      <c r="C418" s="3"/>
     </row>
     <row r="419" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B419" s="2">
         <v>33511</v>
       </c>
-      <c r="C419" s="3">
-        <v>-4.6084330405514518</v>
-      </c>
+      <c r="C419" s="3"/>
     </row>
     <row r="420" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B420" s="2">
         <v>33480</v>
       </c>
-      <c r="C420" s="3">
-        <v>-25.007779813976004</v>
-      </c>
+      <c r="C420" s="3"/>
     </row>
     <row r="421" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B421" s="2">
         <v>33450</v>
       </c>
-      <c r="C421" s="3">
-        <v>-16.341967862773178</v>
-      </c>
+      <c r="C421" s="3"/>
     </row>
     <row r="422" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B422" s="2">
         <v>33417</v>
       </c>
-      <c r="C422" s="3">
-        <v>-12.240908802437023</v>
-      </c>
+      <c r="C422" s="3"/>
     </row>
     <row r="423" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B423" s="2">
         <v>33389</v>
       </c>
-      <c r="C423" s="3">
-        <v>-10.571182092669529</v>
-      </c>
+      <c r="C423" s="3"/>
     </row>
     <row r="424" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B424" s="2">
         <v>33358</v>
       </c>
-      <c r="C424" s="3">
-        <v>-10.836496128738416</v>
-      </c>
+      <c r="C424" s="3"/>
     </row>
     <row r="425" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B425" s="2">

--- a/docs/deepreview/【2】每月必用/月度收益-20260323145627.xlsx
+++ b/docs/deepreview/【2】每月必用/月度收益-20260323145627.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9841D4EB-BC26-4ED3-B9F3-7F236058C6AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7B4E60E-FD43-42E5-AFE7-D2B8168C7118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -168,7 +168,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>000905.SH</t>
+    <t>SPX.GI</t>
   </si>
 </sst>
 </file>
@@ -1190,13 +1190,13 @@
       </c>
       <c r="F4" s="18" t="str">
         <f>[1]!s_info_name(D4)</f>
-        <v>中证500</v>
+        <v>标普500</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="6">
-        <v>640</v>
+        <v>1000</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>20</v>
@@ -1273,15 +1273,15 @@
       </c>
       <c r="D8" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C8,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.121215873790391</v>
+        <v>1.3662990285588927E-2</v>
       </c>
       <c r="E8" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C8,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.43981006772065E-2</v>
+        <v>-8.6683585457909551E-3</v>
       </c>
       <c r="F8" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C8,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.14063777671623301</v>
+        <v>-4.3303561044821241E-2</v>
       </c>
       <c r="G8" s="12" t="str">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C8,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
@@ -1329,51 +1329,51 @@
       </c>
       <c r="D9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.3820393701947995E-2</v>
+        <v>2.7016320305765618E-2</v>
       </c>
       <c r="E9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.8400606353891318E-2</v>
+        <v>-1.4242127760312417E-2</v>
       </c>
       <c r="F9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.5814782810561496E-4</v>
+        <v>-5.7544714081786852E-2</v>
       </c>
       <c r="G9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.8572207341422637E-2</v>
+        <v>-7.6249365182604611E-3</v>
       </c>
       <c r="H9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.9688601291564289E-3</v>
+        <v>6.1523847830692979E-2</v>
       </c>
       <c r="I9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.3080970771612215E-2</v>
+        <v>4.960679602617879E-2</v>
       </c>
       <c r="J9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.2567240057101339E-2</v>
+        <v>2.1666572655702376E-2</v>
       </c>
       <c r="K9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.13131277440665334</v>
+        <v>1.9066503244002941E-2</v>
       </c>
       <c r="L9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.2304067938325982E-2</v>
+        <v>3.5323655704259549E-2</v>
       </c>
       <c r="M9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.0976963854090194E-2</v>
+        <v>2.2686836730727133E-2</v>
       </c>
       <c r="N9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.0847425095209659E-2</v>
+        <v>1.299669600304032E-3</v>
       </c>
       <c r="O9" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C9,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.1725177114208218E-2</v>
+        <v>-5.2415722380638741E-4</v>
       </c>
       <c r="Q9" s="9"/>
     </row>
@@ -1385,51 +1385,51 @@
       </c>
       <c r="D10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.1348716782759275</v>
+        <v>1.5895744712075555E-2</v>
       </c>
       <c r="E10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.13834705605278774</v>
+        <v>5.1720615397315317E-2</v>
       </c>
       <c r="F10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.1339825786033542E-2</v>
+        <v>3.1018764704381807E-2</v>
       </c>
       <c r="G10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.931804274148897E-2</v>
+        <v>-4.1615042774082574E-2</v>
       </c>
       <c r="H10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.4370035175158455E-2</v>
+        <v>4.8021224499522619E-2</v>
       </c>
       <c r="I10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.8900032651160292E-2</v>
+        <v>3.4669759034089864E-2</v>
       </c>
       <c r="J10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.1404124928276693E-2</v>
+        <v>1.1321349038912354E-2</v>
       </c>
       <c r="K10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.0609551348661859E-2</v>
+        <v>2.2834688445031892E-2</v>
       </c>
       <c r="L10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.23799857145148207</v>
+        <v>2.0196869910062976E-2</v>
       </c>
       <c r="M10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.7523494236766588E-2</v>
+        <v>-9.8967805528175079E-3</v>
       </c>
       <c r="N10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.3628997481635103E-3</v>
+        <v>5.7301352215863854E-2</v>
       </c>
       <c r="O10" s="12">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C10,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.1566545854847963E-2</v>
+        <v>-2.4990136563014964E-2</v>
       </c>
       <c r="Q10" s="9"/>
     </row>
@@ -1441,51 +1441,51 @@
       </c>
       <c r="D11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.2416318011787162E-2</v>
+        <v>6.1752832400052027E-2</v>
       </c>
       <c r="E11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.0873520269034875E-2</v>
+        <v>-2.6112446646715304E-2</v>
       </c>
       <c r="F11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.7867561000685104E-3</v>
+        <v>3.5051572358727023E-2</v>
       </c>
       <c r="G11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.5548426679673155E-2</v>
+        <v>1.464236088297044E-2</v>
       </c>
       <c r="H11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.0994141055947444E-2</v>
+        <v>2.4823239348792381E-3</v>
       </c>
       <c r="I11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.1141543966857244E-3</v>
+        <v>6.4727512841431301E-2</v>
       </c>
       <c r="J11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.4922126924447054E-2</v>
+        <v>3.1138913980379268E-2</v>
       </c>
       <c r="K11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.7298089821676064E-2</v>
+        <v>-1.771643248143373E-2</v>
       </c>
       <c r="L11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.4727869736312966E-3</v>
+        <v>-4.871929116215501E-2</v>
       </c>
       <c r="M11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.8560495076790704E-2</v>
+        <v>-2.1979687736850106E-2</v>
       </c>
       <c r="N11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.041095278360384E-3</v>
+        <v>8.9179264628737709E-2</v>
       </c>
       <c r="O11" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C11,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.0887384540274057E-2</v>
+        <v>4.4229169403213753E-2</v>
       </c>
       <c r="Q11" s="9"/>
     </row>
@@ -1497,51 +1497,51 @@
       </c>
       <c r="D12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.10583364757986334</v>
+        <v>-5.2585089106999765E-2</v>
       </c>
       <c r="E12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.1452299434848072E-2</v>
+        <v>-3.1360520866782648E-2</v>
       </c>
       <c r="F12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.7093746886996106E-2</v>
+        <v>3.5773238773280092E-2</v>
       </c>
       <c r="G12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.11020760618456936</v>
+        <v>-8.7956719149039339E-2</v>
       </c>
       <c r="H12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.0778629926771419E-2</v>
+        <v>5.3243883608722342E-5</v>
       </c>
       <c r="I12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.0996291500170505E-2</v>
+        <v>-8.3919993223866451E-2</v>
       </c>
       <c r="J12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.478485772204353E-2</v>
+        <v>9.1116347632205899E-2</v>
       </c>
       <c r="K12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.1983855266437535E-2</v>
+        <v>-4.2440119216810457E-2</v>
       </c>
       <c r="L12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.1751276916825146E-2</v>
+        <v>-9.3395701643489315E-2</v>
       </c>
       <c r="M12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.6283229923842901E-2</v>
+        <v>7.9863454576893256E-2</v>
       </c>
       <c r="N12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.0105701870826644E-2</v>
+        <v>5.3752860293699856E-2</v>
       </c>
       <c r="O12" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C12,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.7380223976151277E-2</v>
+        <v>-5.8971449299161094E-2</v>
       </c>
       <c r="Q12" s="9"/>
     </row>
@@ -1553,51 +1553,51 @@
       </c>
       <c r="D13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.2947104504112978E-3</v>
+        <v>-1.1136640158463607E-2</v>
       </c>
       <c r="E13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.8703760591619609E-3</v>
+        <v>2.6091474971999817E-2</v>
       </c>
       <c r="F13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.7328297429892725E-2</v>
+        <v>4.2438634008107767E-2</v>
       </c>
       <c r="G13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.7037963840983901E-2</v>
+        <v>5.242531255584737E-2</v>
       </c>
       <c r="H13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.7510649377882066E-2</v>
+        <v>5.4865025818131574E-3</v>
       </c>
       <c r="I13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.176885282021356E-2</v>
+        <v>2.221397632316946E-2</v>
       </c>
       <c r="J13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.0026440828244709E-3</v>
+        <v>2.274810936591054E-2</v>
       </c>
       <c r="K13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.2115119199398947E-2</v>
+        <v>2.8990321391681118E-2</v>
       </c>
       <c r="L13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.091344614529389E-2</v>
+        <v>-4.7569140421166341E-2</v>
       </c>
       <c r="M13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.1417916721638721E-2</v>
+        <v>6.9143873301234615E-2</v>
       </c>
       <c r="N13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.2788326981938232E-2</v>
+        <v>-8.3337314184714906E-3</v>
       </c>
       <c r="O13" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C13,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.4704370554241342E-2</v>
+        <v>4.3612874972629889E-2</v>
       </c>
       <c r="Q13" s="9"/>
     </row>
@@ -1609,51 +1609,51 @@
       </c>
       <c r="D14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.0897106879784522E-2</v>
+        <v>-1.6280898111292741E-3</v>
       </c>
       <c r="E14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.3676485839007713E-2</v>
+        <v>-8.4110469009648123E-2</v>
       </c>
       <c r="F14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.5181529978126105E-2</v>
+        <v>-0.12511932083595656</v>
       </c>
       <c r="G14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.1967467556081957E-2</v>
+        <v>0.12684410293315374</v>
       </c>
       <c r="H14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>9.8024238402223407E-3</v>
+        <v>4.528177501261843E-2</v>
       </c>
       <c r="I14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.4729424080093541E-2</v>
+        <v>1.8388403283502663E-2</v>
       </c>
       <c r="J14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.12196494096155931</v>
+        <v>5.5101296975444303E-2</v>
       </c>
       <c r="K14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.3490571015906339E-2</v>
+        <v>7.0064687324219221E-2</v>
       </c>
       <c r="L14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.1370379347436286E-2</v>
+        <v>-3.9227954095494399E-2</v>
       </c>
       <c r="M14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.3084237564946477E-2</v>
+        <v>-2.7665774606006499E-2</v>
       </c>
       <c r="N14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.4273823970274453E-2</v>
+        <v>0.10754565805086314</v>
       </c>
       <c r="O14" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C14,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.3044151743091312E-3</v>
+        <v>3.712140665943231E-2</v>
       </c>
       <c r="Q14" s="9"/>
     </row>
@@ -1665,51 +1665,51 @@
       </c>
       <c r="D15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.0243585690460364E-3</v>
+        <v>7.8684404731036883E-2</v>
       </c>
       <c r="E15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.20323780785509027</v>
+        <v>2.9728930143116061E-2</v>
       </c>
       <c r="F15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.10394716819699588</v>
+        <v>1.7924287751078349E-2</v>
       </c>
       <c r="G15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.3278836263841214E-2</v>
+        <v>3.9313434942139347E-2</v>
       </c>
       <c r="H15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.4527560687020045E-2</v>
+        <v>-6.5777726481161536E-2</v>
       </c>
       <c r="I15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.8337329159474667E-3</v>
+        <v>6.8930183208214979E-2</v>
       </c>
       <c r="J15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-9.5499430176444466E-3</v>
+        <v>1.3128195366039375E-2</v>
       </c>
       <c r="K15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.4077724295732414E-3</v>
+        <v>-1.8091652742267761E-2</v>
       </c>
       <c r="L15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.113456805636126E-2</v>
+        <v>1.7181167690656807E-2</v>
       </c>
       <c r="M15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.7533011678229098E-3</v>
+        <v>2.0431747482144935E-2</v>
       </c>
       <c r="N15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.5706512528304044E-3</v>
+        <v>3.404706409091518E-2</v>
       </c>
       <c r="O15" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C15,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.6144034077955114E-2</v>
+        <v>2.8589803182446305E-2</v>
       </c>
       <c r="Q15" s="9"/>
     </row>
@@ -1721,51 +1721,51 @@
       </c>
       <c r="D16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-9.8354124923147879E-3</v>
+        <v>5.6178724645703726E-2</v>
       </c>
       <c r="E16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.6766063135022167E-2</v>
+        <v>-3.8947379604151844E-2</v>
       </c>
       <c r="F16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.5117211630039318E-2</v>
+        <v>-2.6884513768364315E-2</v>
       </c>
       <c r="G16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.1498849451968356E-2</v>
+        <v>2.718801001185378E-3</v>
       </c>
       <c r="H16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.8172547010709916E-2</v>
+        <v>2.1608353316591389E-2</v>
       </c>
       <c r="I16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-9.3268341127094367E-2</v>
+        <v>4.8424002040461378E-3</v>
       </c>
       <c r="J16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.5670778382994612E-3</v>
+        <v>3.6021586465418753E-2</v>
       </c>
       <c r="K16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.2058840137848357E-2</v>
+        <v>3.0263218631604083E-2</v>
       </c>
       <c r="L16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.9274176747116076E-3</v>
+        <v>4.2943009181395375E-3</v>
       </c>
       <c r="M16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.11002015173238167</v>
+        <v>-6.9403358979814644E-2</v>
       </c>
       <c r="N16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.4364666567646909E-2</v>
+        <v>1.785938179914015E-2</v>
       </c>
       <c r="O16" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C16,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.7665394209741807E-2</v>
+        <v>-9.1776955767217339E-2</v>
       </c>
       <c r="Q16" s="9"/>
     </row>
@@ -1777,51 +1777,51 @@
       </c>
       <c r="D17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.3732257560221717E-3</v>
+        <v>1.7884341374735824E-2</v>
       </c>
       <c r="E17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.6515863112494884E-2</v>
+        <v>3.7198260541408734E-2</v>
       </c>
       <c r="F17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.6457027757731444E-3</v>
+        <v>-3.8923017041514463E-4</v>
       </c>
       <c r="G17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.9646350902866714E-2</v>
+        <v>9.0912169025529899E-3</v>
       </c>
       <c r="H17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.2422213344584081E-2</v>
+        <v>1.1576210049492719E-2</v>
       </c>
       <c r="I17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.3922695957259847E-2</v>
+        <v>4.8138319927024664E-3</v>
       </c>
       <c r="J17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.6041177581096253E-2</v>
+        <v>1.9348768883515444E-2</v>
       </c>
       <c r="K17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.7377816616207307E-2</v>
+        <v>5.4649232886694321E-4</v>
       </c>
       <c r="L17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.0529220495361766E-2</v>
+        <v>1.9302894827342154E-2</v>
       </c>
       <c r="M17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.5200080681376837E-3</v>
+        <v>2.2188174774546043E-2</v>
       </c>
       <c r="N17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.5240107878329446E-2</v>
+        <v>2.8082601368405458E-2</v>
       </c>
       <c r="O17" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C17,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.0117280955567196E-3</v>
+        <v>9.8316198188534987E-3</v>
       </c>
       <c r="Q17" s="9"/>
     </row>
@@ -1833,51 +1833,51 @@
       </c>
       <c r="D18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.28204926717276069</v>
+        <v>-5.0735344481736222E-2</v>
       </c>
       <c r="E18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.1702135409072953E-2</v>
+        <v>-4.1283552550199776E-3</v>
       </c>
       <c r="F18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.15052613398424142</v>
+        <v>6.5991108718941094E-2</v>
       </c>
       <c r="G18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.7651876020031607E-2</v>
+        <v>2.69936982337593E-3</v>
       </c>
       <c r="H18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.3939518784601468E-3</v>
+        <v>1.5329492083474561E-2</v>
       </c>
       <c r="I18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.9621985853667487E-2</v>
+        <v>9.0607355409733081E-4</v>
       </c>
       <c r="J18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.2966192388956355E-2</v>
+        <v>3.5609807228685897E-2</v>
       </c>
       <c r="K18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.7291958140237114E-2</v>
+        <v>-1.2191755612808164E-3</v>
       </c>
       <c r="L18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.6493818985058528E-2</v>
+        <v>-1.2344825997834263E-3</v>
       </c>
       <c r="M18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.961417841756119E-2</v>
+        <v>-1.9425625037472249E-2</v>
       </c>
       <c r="N18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.067072938064074E-2</v>
+        <v>3.4174446769983158E-2</v>
       </c>
       <c r="O18" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C18,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.8887435477185652E-2</v>
+        <v>1.8200754044233047E-2</v>
       </c>
       <c r="Q18" s="9"/>
     </row>
@@ -1889,51 +1889,51 @@
       </c>
       <c r="D19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.8243595278649307E-2</v>
+        <v>-3.1040847054252363E-2</v>
       </c>
       <c r="E19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.8481027310390186E-2</v>
+        <v>5.4892505726845675E-2</v>
       </c>
       <c r="F19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.20514224312752294</v>
+        <v>-1.7396056070325572E-2</v>
       </c>
       <c r="G19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.16773080876821855</v>
+        <v>8.5207627098153882E-3</v>
       </c>
       <c r="H19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.17676857182089534</v>
+        <v>1.0491438545008114E-2</v>
       </c>
       <c r="I19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.10643536645748963</v>
+        <v>-2.10117728564716E-2</v>
       </c>
       <c r="J19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.13237780439797342</v>
+        <v>1.9742039930008559E-2</v>
       </c>
       <c r="K19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.14827735016657306</v>
+        <v>-6.258080462392579E-2</v>
       </c>
       <c r="L19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.9527968181788524E-2</v>
+        <v>-2.6442819620927094E-2</v>
       </c>
       <c r="M19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.15697027924528451</v>
+        <v>8.2983078389400333E-2</v>
       </c>
       <c r="N19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.5649900085682926E-2</v>
+        <v>5.0496306555847248E-4</v>
       </c>
       <c r="O19" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C19,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.8250396023496993E-2</v>
+        <v>-1.7530198374358763E-2</v>
       </c>
       <c r="Q19" s="9"/>
     </row>
@@ -1945,51 +1945,51 @@
       </c>
       <c r="D20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.4708432486414624E-2</v>
+        <v>-3.5582895107013734E-2</v>
       </c>
       <c r="E20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.3295575042672434E-2</v>
+        <v>4.3117037568930705E-2</v>
       </c>
       <c r="F20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.4053173484737798E-2</v>
+        <v>6.9321573583585039E-3</v>
       </c>
       <c r="G20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.9363443019411841E-2</v>
+        <v>6.2007968638175814E-3</v>
       </c>
       <c r="H20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.6745924905142262E-2</v>
+        <v>2.1030282120013677E-2</v>
       </c>
       <c r="I20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.4982777252288813E-2</v>
+        <v>1.9058313448431896E-2</v>
       </c>
       <c r="J20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.4624256956159272E-2</v>
+        <v>-1.5079863077291922E-2</v>
       </c>
       <c r="K20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.0129714391085702E-2</v>
+        <v>3.7655321727690261E-2</v>
       </c>
       <c r="L20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.11026498239902205</v>
+        <v>-1.5513859147336717E-2</v>
       </c>
       <c r="M20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.4299287710488828E-2</v>
+        <v>2.3201456175308888E-2</v>
       </c>
       <c r="N20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.1911232436282928E-2</v>
+        <v>2.4533584400783015E-2</v>
       </c>
       <c r="O20" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C20,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.4765120631609507E-2</v>
+        <v>-4.1885120625277938E-3</v>
       </c>
       <c r="Q20" s="9"/>
     </row>
@@ -2001,51 +2001,51 @@
       </c>
       <c r="D21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.2205955077445196E-2</v>
+        <v>5.0428063581991145E-2</v>
       </c>
       <c r="E21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.6946659393879422E-2</v>
+        <v>1.1060603026480154E-2</v>
       </c>
       <c r="F21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.4596764202861398E-2</v>
+        <v>3.5987799403174314E-2</v>
       </c>
       <c r="G21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.3067138342202531E-2</v>
+        <v>1.8085763992887971E-2</v>
       </c>
       <c r="H21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.14058340157837557</v>
+        <v>2.0762783477406455E-2</v>
       </c>
       <c r="I21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.15756460580992793</v>
+        <v>-1.499932545960736E-2</v>
       </c>
       <c r="J21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.018736839372818E-2</v>
+        <v>4.9462111213487203E-2</v>
       </c>
       <c r="K21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.8033367699066982E-2</v>
+        <v>-3.1298013323604601E-2</v>
       </c>
       <c r="L21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.6969587472994965E-2</v>
+        <v>2.9749474883188354E-2</v>
       </c>
       <c r="M21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.1071106276367564E-2</v>
+        <v>4.4595759864410889E-2</v>
       </c>
       <c r="N21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.2618391961503761E-2</v>
+        <v>2.804946087194149E-2</v>
       </c>
       <c r="O21" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C21,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.9720125998921043E-2</v>
+        <v>2.3562833299184183E-2</v>
       </c>
       <c r="Q21" s="9"/>
     </row>
@@ -2057,51 +2057,51 @@
       </c>
       <c r="D22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.4851267687551246E-3</v>
+        <v>4.3583015267175673E-2</v>
       </c>
       <c r="E22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.12191553543579058</v>
+        <v>4.0589449943234213E-2</v>
       </c>
       <c r="F22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.5561991091256053E-2</v>
+        <v>3.1332376545017748E-2</v>
       </c>
       <c r="G22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.2517542442525951E-2</v>
+        <v>-7.497497284287169E-3</v>
       </c>
       <c r="H22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.4273884623801756E-2</v>
+        <v>-6.2650671359386623E-2</v>
       </c>
       <c r="I22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.5295323707178619E-2</v>
+        <v>3.9554921279372435E-2</v>
       </c>
       <c r="J22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.9823147165125614E-2</v>
+        <v>1.2597639043871345E-2</v>
       </c>
       <c r="K22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.2332393852605472E-3</v>
+        <v>1.9763361656468303E-2</v>
       </c>
       <c r="L22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.9191591017677867E-2</v>
+        <v>2.4236090375236552E-2</v>
       </c>
       <c r="M22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-9.8929542039507545E-3</v>
+        <v>-1.9789403541407791E-2</v>
       </c>
       <c r="N22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.11094136322214897</v>
+        <v>2.8467029231815655E-3</v>
       </c>
       <c r="O22" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C22,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.16304483665551395</v>
+        <v>7.0683105254980561E-3</v>
       </c>
       <c r="Q22" s="9"/>
     </row>
@@ -2113,51 +2113,51 @@
       </c>
       <c r="D23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.6006632749382566E-2</v>
+        <v>2.2645590152984729E-2</v>
       </c>
       <c r="E23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.10504504582659191</v>
+        <v>3.1956582589494076E-2</v>
       </c>
       <c r="F23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-1.8606894949136477E-2</v>
+        <v>-1.0473018791158362E-3</v>
       </c>
       <c r="G23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.2704570552527623E-2</v>
+        <v>2.8495357625034856E-2</v>
       </c>
       <c r="H23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-8.1166193150688959E-2</v>
+        <v>-1.350092768460176E-2</v>
       </c>
       <c r="I23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.0388751733690711E-2</v>
+        <v>-1.8257508177222714E-2</v>
       </c>
       <c r="J23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.069763013470082E-2</v>
+        <v>-2.1474436636782279E-2</v>
       </c>
       <c r="K23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.273300031112804E-2</v>
+        <v>-5.6791097904478782E-2</v>
       </c>
       <c r="L23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.12948991747729044</v>
+        <v>-7.1762012979021961E-2</v>
       </c>
       <c r="M23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.6956275986380627E-2</v>
+        <v>0.10772303830584562</v>
       </c>
       <c r="N23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.4862155513804458E-2</v>
+        <v>-5.0586451767333784E-3</v>
       </c>
       <c r="O23" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C23,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.14481031387387555</v>
+        <v>8.5327516520175006E-3</v>
       </c>
       <c r="Q23" s="9"/>
     </row>
@@ -2169,51 +2169,51 @@
       </c>
       <c r="D24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-2.4659913427441671E-2</v>
+        <v>-3.6974262397991176E-2</v>
       </c>
       <c r="E24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.9438368655405194E-2</v>
+        <v>2.8513693463827261E-2</v>
       </c>
       <c r="F24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.621243233877868E-2</v>
+        <v>5.8796367554255768E-2</v>
       </c>
       <c r="G24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.6750529892095734E-2</v>
+        <v>1.4759327193589966E-2</v>
       </c>
       <c r="H24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.5318996792064996E-2</v>
+        <v>-8.1975916203894883E-2</v>
       </c>
       <c r="I24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.10717860306736915</v>
+        <v>-5.3882376699314394E-2</v>
       </c>
       <c r="J24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.14372251985556428</v>
+        <v>6.8777832756061308E-2</v>
       </c>
       <c r="K24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>9.5000393688575505E-2</v>
+        <v>-4.7449164851125596E-2</v>
       </c>
       <c r="L24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.5539662026078593E-2</v>
+        <v>8.7551104037814742E-2</v>
       </c>
       <c r="M24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.4728699385594908E-2</v>
+        <v>3.6855941114616098E-2</v>
       </c>
       <c r="N24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.0955016841090792E-2</v>
+        <v>-2.2902827780877377E-3</v>
       </c>
       <c r="O24" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C24,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.4076161127008509E-2</v>
+        <v>6.5300072000338938E-2</v>
       </c>
       <c r="Q24" s="9"/>
     </row>
@@ -2225,51 +2225,51 @@
       </c>
       <c r="D25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.15398778921468281</v>
+        <v>-8.5657348463880401E-2</v>
       </c>
       <c r="E25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.9919770589281347E-2</v>
+        <v>-0.10993122487528451</v>
       </c>
       <c r="F25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.20570520933623349</v>
+        <v>8.5404508291501605E-2</v>
       </c>
       <c r="G25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.9053342886791427E-2</v>
+        <v>9.3925075513554793E-2</v>
       </c>
       <c r="H25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.1736099567852865E-2</v>
+        <v>5.3081426656431674E-2</v>
       </c>
       <c r="I25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.3563777257207512E-2</v>
+        <v>1.9583523728705643E-4</v>
       </c>
       <c r="J25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.13797355531719346</v>
+        <v>7.4141756950789617E-2</v>
       </c>
       <c r="K25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.16560343370537578</v>
+        <v>3.3560173370599911E-2</v>
       </c>
       <c r="L25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.7408820081287431E-2</v>
+        <v>3.5723383825517763E-2</v>
       </c>
       <c r="M25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.125582871138612</v>
+        <v>-1.9761985847807084E-2</v>
       </c>
       <c r="N25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.15091244494384726</v>
+        <v>5.7363996950366314E-2</v>
       </c>
       <c r="O25" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C25,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.8143257437357674E-2</v>
+        <v>1.7770597738287375E-2</v>
       </c>
       <c r="Q25" s="9"/>
     </row>
@@ -2281,51 +2281,51 @@
       </c>
       <c r="D26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.7439531829857844E-2</v>
+        <v>-6.1163474897164116E-2</v>
       </c>
       <c r="E26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>8.4530756966729292E-2</v>
+        <v>-3.4761162090602316E-2</v>
       </c>
       <c r="F26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.20039457317546983</v>
+        <v>-5.9595830546433914E-3</v>
       </c>
       <c r="G26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.4845842014708861E-2</v>
+        <v>4.7546684811370588E-2</v>
       </c>
       <c r="H26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-3.7801760514124649E-2</v>
+        <v>1.0674153248796614E-2</v>
       </c>
       <c r="I26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.25080073095573019</v>
+        <v>-8.5962381639269392E-2</v>
       </c>
       <c r="J26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.2324641150706137E-2</v>
+        <v>-9.8593749999998925E-3</v>
       </c>
       <c r="K26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.23533574151279146</v>
+        <v>1.2190503242910378E-2</v>
       </c>
       <c r="L26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.4185209682214981E-2</v>
+        <v>-9.0791453271283018E-2</v>
       </c>
       <c r="M26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.26871663449595773</v>
+        <v>-0.16942453444905514</v>
       </c>
       <c r="N26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.17888864561446649</v>
+        <v>-7.4849032258064496E-2</v>
       </c>
       <c r="O26" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C26,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.3209698878601053E-2</v>
+        <v>7.8215656520574939E-3</v>
       </c>
       <c r="Q26" s="9"/>
     </row>
@@ -2337,51 +2337,51 @@
       </c>
       <c r="D27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.241430910247453</v>
+        <v>1.4059084819854739E-2</v>
       </c>
       <c r="E27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.17296353384283195</v>
+        <v>-2.1846145288686225E-2</v>
       </c>
       <c r="F27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.16412396415722408</v>
+        <v>9.9799547916576969E-3</v>
       </c>
       <c r="G27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.33410923342756682</v>
+        <v>4.3290683107413797E-2</v>
       </c>
       <c r="H27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>9.3268700452315834E-2</v>
+        <v>3.2549228600146973E-2</v>
       </c>
       <c r="I27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.15987113678044873</v>
+        <v>-1.7816309730697366E-2</v>
       </c>
       <c r="J27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.22816934719588922</v>
+        <v>-3.1981907074200899E-2</v>
       </c>
       <c r="K27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.11219315902682926</v>
+        <v>1.2863592323073991E-2</v>
       </c>
       <c r="L27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.7980364404377687E-2</v>
+        <v>3.579400131615551E-2</v>
       </c>
       <c r="M27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.10493779076057554</v>
+        <v>1.4822335025380884E-2</v>
       </c>
       <c r="N27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-9.3897542142810556E-2</v>
+        <v>-4.4043423821141348E-2</v>
       </c>
       <c r="O27" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C27,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.20002051937795742</v>
+        <v>-8.628488866683881E-3</v>
       </c>
       <c r="Q27" s="9"/>
     </row>
@@ -2393,51 +2393,51 @@
       </c>
       <c r="D28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.11353619390534696</v>
+        <v>2.5466838635253009E-2</v>
       </c>
       <c r="E28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>7.2448258328834392E-3</v>
+        <v>4.5309668145754323E-4</v>
       </c>
       <c r="F28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.6823927208347262E-2</v>
+        <v>1.1064607311854768E-2</v>
       </c>
       <c r="G28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.14139850897424733</v>
+        <v>1.2186928013716125E-2</v>
       </c>
       <c r="H28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.22830027547002918</v>
+        <v>-3.091690129023883E-2</v>
       </c>
       <c r="I28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.9659909350995077E-2</v>
+        <v>8.6608035651192239E-5</v>
       </c>
       <c r="J28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.1016961699063437E-2</v>
+        <v>5.0858132577547011E-3</v>
       </c>
       <c r="K28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.8494250002105268E-2</v>
+        <v>2.1274262528785837E-2</v>
       </c>
       <c r="L28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>4.7910669639840586E-2</v>
+        <v>2.4566274485741779E-2</v>
       </c>
       <c r="M28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.9091967193771744E-3</v>
+        <v>3.1508028596025195E-2</v>
       </c>
       <c r="N28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>5.3304956607870047E-2</v>
+        <v>1.6466609576614388E-2</v>
       </c>
       <c r="O28" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C28,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>6.3018223739635504E-2</v>
+        <v>1.2615751483260995E-2</v>
       </c>
       <c r="Q28" s="9"/>
     </row>
@@ -2449,51 +2449,51 @@
       </c>
       <c r="D29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-7.7346999999999944E-2</v>
+        <v>-2.5290448214403627E-2</v>
       </c>
       <c r="E29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.1064257093403478</v>
+        <v>1.8903383646414307E-2</v>
       </c>
       <c r="F29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-0.12223085339918714</v>
+        <v>-1.9117647058823573E-2</v>
       </c>
       <c r="G29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.4077369128235804E-2</v>
+        <v>-2.010858977291019E-2</v>
       </c>
       <c r="H29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.9861186322499371E-2</v>
+        <v>2.9952024895189666E-2</v>
       </c>
       <c r="I29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-6.7388488991958484E-3</v>
+        <v>-1.4267729752415192E-4</v>
       </c>
       <c r="J29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-5.8972687371604771E-2</v>
+        <v>3.5968203604375137E-2</v>
       </c>
       <c r="K29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0.13468532876850259</v>
+        <v>-1.1222025960556881E-2</v>
       </c>
       <c r="L29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>2.8831841276377279E-2</v>
+        <v>6.9489400408087043E-3</v>
       </c>
       <c r="M29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>-4.6980537291735909E-2</v>
+        <v>-1.7740741042146402E-2</v>
       </c>
       <c r="N29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>1.0148927363367033E-3</v>
+        <v>3.518612107604735E-2</v>
       </c>
       <c r="O29" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C29,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>3.6927064496684814E-2</v>
+        <v>-9.5239619681797283E-4</v>
       </c>
       <c r="Q29" s="9"/>
     </row>
@@ -2503,53 +2503,53 @@
         <f t="shared" si="0"/>
         <v>2004年</v>
       </c>
-      <c r="D30" s="5" t="str">
+      <c r="D30" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="E30" s="5" t="str">
+        <v>1.7276422764227695E-2</v>
+      </c>
+      <c r="E30" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="F30" s="5" t="str">
+        <v>1.2209029908144986E-2</v>
+      </c>
+      <c r="F30" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="G30" s="5" t="str">
+        <v>-1.6358935839432598E-2</v>
+      </c>
+      <c r="G30" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="H30" s="5" t="str">
+        <v>-1.6790829419024988E-2</v>
+      </c>
+      <c r="H30" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="I30" s="5" t="str">
+        <v>1.2083446220536587E-2</v>
+      </c>
+      <c r="I30" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="J30" s="5" t="str">
+        <v>1.7989078059749364E-2</v>
+      </c>
+      <c r="J30" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="K30" s="5" t="str">
+        <v>-3.4290522772693732E-2</v>
+      </c>
+      <c r="K30" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="L30" s="5" t="str">
+        <v>2.2873325345822426E-3</v>
+      </c>
+      <c r="L30" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="M30" s="5" t="str">
+        <v>9.3639063971600045E-3</v>
+      </c>
+      <c r="M30" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="N30" s="5" t="str">
+        <v>1.4014247519245071E-2</v>
+      </c>
+      <c r="N30" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
+        <v>3.8594938948858459E-2</v>
       </c>
       <c r="O30" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C30,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v>0</v>
+        <v>3.2458128162750732E-2</v>
       </c>
       <c r="Q30" s="9"/>
     </row>
@@ -2559,53 +2559,53 @@
         <f t="shared" si="0"/>
         <v>2003年</v>
       </c>
-      <c r="D31" s="5" t="str">
+      <c r="D31" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="E31" s="5" t="str">
+        <v>-2.7414698461048825E-2</v>
+      </c>
+      <c r="E31" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="F31" s="5" t="str">
+        <v>-1.7003622764987791E-2</v>
+      </c>
+      <c r="F31" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="G31" s="5" t="str">
+        <v>8.3576056589194092E-3</v>
+      </c>
+      <c r="G31" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="5" t="str">
+        <v>8.1044117993822162E-2</v>
+      </c>
+      <c r="H31" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="I31" s="5" t="str">
+        <v>5.0898660733760925E-2</v>
+      </c>
+      <c r="I31" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="J31" s="5" t="str">
+        <v>1.1322242862628284E-2</v>
+      </c>
+      <c r="J31" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="K31" s="5" t="str">
+        <v>1.6223704463827593E-2</v>
+      </c>
+      <c r="K31" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="L31" s="5" t="str">
+        <v>1.7873191222950391E-2</v>
+      </c>
+      <c r="L31" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="M31" s="5" t="str">
+        <v>-1.1944325949147294E-2</v>
+      </c>
+      <c r="M31" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="N31" s="5" t="str">
+        <v>5.4961494824141255E-2</v>
+      </c>
+      <c r="N31" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="O31" s="5" t="str">
+        <v>7.1285131006653124E-3</v>
+      </c>
+      <c r="O31" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C31,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
+        <v>5.0765450765450693E-2</v>
       </c>
       <c r="Q31" s="9"/>
     </row>
@@ -2615,53 +2615,53 @@
         <f t="shared" si="0"/>
         <v>2002年</v>
       </c>
-      <c r="D32" s="5" t="str">
+      <c r="D32" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="E32" s="5" t="str">
+        <v>-1.5573827607832103E-2</v>
+      </c>
+      <c r="E32" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="F32" s="5" t="str">
+        <v>-2.0766236064413413E-2</v>
+      </c>
+      <c r="F32" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="G32" s="5" t="str">
+        <v>3.6738861330225081E-2</v>
+      </c>
+      <c r="G32" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="H32" s="5" t="str">
+        <v>-6.1417652236815723E-2</v>
+      </c>
+      <c r="H32" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="I32" s="5" t="str">
+        <v>-9.0814545184414452E-3</v>
+      </c>
+      <c r="I32" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="J32" s="5" t="str">
+        <v>-7.2464718781041104E-2</v>
+      </c>
+      <c r="J32" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="K32" s="5" t="str">
+        <v>-7.8994958628423539E-2</v>
+      </c>
+      <c r="K32" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="L32" s="5" t="str">
+        <v>4.8814198898663452E-3</v>
+      </c>
+      <c r="L32" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="M32" s="5" t="str">
+        <v>-0.11002434311788412</v>
+      </c>
+      <c r="M32" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="N32" s="5" t="str">
+        <v>8.644882739672255E-2</v>
+      </c>
+      <c r="N32" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="O32" s="5" t="str">
+        <v>5.7069635115606809E-2</v>
+      </c>
+      <c r="O32" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C32,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
+        <v>-6.0332582157618608E-2</v>
       </c>
       <c r="Q32" s="9"/>
     </row>
@@ -2671,53 +2671,53 @@
         <f t="shared" si="0"/>
         <v>2001年</v>
       </c>
-      <c r="D33" s="5" t="str">
+      <c r="D33" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="E33" s="5" t="str">
+        <v>3.4636592238010078E-2</v>
+      </c>
+      <c r="E33" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="F33" s="5" t="str">
+        <v>-9.2290686012547418E-2</v>
+      </c>
+      <c r="F33" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="G33" s="5" t="str">
+        <v>-6.4204719583205727E-2</v>
+      </c>
+      <c r="G33" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="5" t="str">
+        <v>7.6814354537071416E-2</v>
+      </c>
+      <c r="H33" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="I33" s="5" t="str">
+        <v>5.0901989659533076E-3</v>
+      </c>
+      <c r="I33" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="J33" s="5" t="str">
+        <v>-2.5003583316080213E-2</v>
+      </c>
+      <c r="J33" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="K33" s="5" t="str">
+        <v>-1.0772447362833004E-2</v>
+      </c>
+      <c r="K33" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="L33" s="5" t="str">
+        <v>-6.4108385690579084E-2</v>
+      </c>
+      <c r="L33" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="M33" s="5" t="str">
+        <v>-8.1723389615201314E-2</v>
+      </c>
+      <c r="M33" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="N33" s="5" t="str">
+        <v>1.8099025880454089E-2</v>
+      </c>
+      <c r="N33" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="O33" s="5" t="str">
+        <v>7.5175979920360847E-2</v>
+      </c>
+      <c r="O33" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C33,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
+        <v>7.5738294791345417E-3</v>
       </c>
       <c r="Q33" s="9"/>
     </row>
@@ -2727,53 +2727,53 @@
         <f t="shared" si="0"/>
         <v>2000年</v>
       </c>
-      <c r="D34" s="5" t="str">
+      <c r="D34" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="E34" s="5" t="str">
+        <v>-5.0903522205206657E-2</v>
+      </c>
+      <c r="E34" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="F34" s="5" t="str">
+        <v>-2.0108142219927405E-2</v>
+      </c>
+      <c r="F34" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="G34" s="5" t="str">
+        <v>9.6719895786068655E-2</v>
+      </c>
+      <c r="G34" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="H34" s="5" t="str">
+        <v>-3.0795820042973876E-2</v>
+      </c>
+      <c r="H34" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="I34" s="5" t="str">
+        <v>-2.1914997624670529E-2</v>
+      </c>
+      <c r="I34" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="J34" s="5" t="str">
+        <v>2.3933549204561366E-2</v>
+      </c>
+      <c r="J34" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="K34" s="5" t="str">
+        <v>-1.6341262202667406E-2</v>
+      </c>
+      <c r="K34" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="L34" s="5" t="str">
+        <v>6.069903482594019E-2</v>
+      </c>
+      <c r="L34" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="M34" s="5" t="str">
+        <v>-5.3482947656950157E-2</v>
+      </c>
+      <c r="M34" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="N34" s="5" t="str">
+        <v>-4.9494956526581202E-3</v>
+      </c>
+      <c r="N34" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="O34" s="5" t="str">
+        <v>-8.0068560235063688E-2</v>
+      </c>
+      <c r="O34" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C34,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
+        <v>4.0533860603064742E-3</v>
       </c>
       <c r="Q34" s="9"/>
     </row>
@@ -2783,53 +2783,53 @@
         <f t="shared" si="0"/>
         <v>1999年</v>
       </c>
-      <c r="D35" s="5" t="str">
+      <c r="D35" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="E35" s="5" t="str">
+        <v>4.1009412396378231E-2</v>
+      </c>
+      <c r="E35" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="F35" s="5" t="str">
+        <v>-3.2282516957894525E-2</v>
+      </c>
+      <c r="F35" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="G35" s="5" t="str">
+        <v>3.8794182487705164E-2</v>
+      </c>
+      <c r="G35" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="5" t="str">
+        <v>3.7943981902563095E-2</v>
+      </c>
+      <c r="H35" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="I35" s="5" t="str">
+        <v>-2.4970415973876281E-2</v>
+      </c>
+      <c r="I35" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="J35" s="5" t="str">
+        <v>5.4438333435752551E-2</v>
+      </c>
+      <c r="J35" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="K35" s="5" t="str">
+        <v>-3.2046098593293548E-2</v>
+      </c>
+      <c r="K35" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="L35" s="5" t="str">
+        <v>-6.2541393220543195E-3</v>
+      </c>
+      <c r="L35" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="M35" s="5" t="str">
+        <v>-2.855173771783015E-2</v>
+      </c>
+      <c r="M35" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="N35" s="5" t="str">
+        <v>6.2539467221741418E-2</v>
+      </c>
+      <c r="N35" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="O35" s="5" t="str">
+        <v>1.906187405075821E-2</v>
+      </c>
+      <c r="O35" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C35,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
+        <v>5.7843920772404189E-2</v>
       </c>
       <c r="Q35" s="9"/>
     </row>
@@ -2839,53 +2839,53 @@
         <f t="shared" si="0"/>
         <v>1998年</v>
       </c>
-      <c r="D36" s="5" t="str">
+      <c r="D36" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="E36" s="5" t="str">
+        <v>1.0150139628824384E-2</v>
+      </c>
+      <c r="E36" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="F36" s="5" t="str">
+        <v>7.0449259395274799E-2</v>
+      </c>
+      <c r="F36" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="G36" s="5" t="str">
+        <v>4.994568014180345E-2</v>
+      </c>
+      <c r="G36" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="5" t="str">
+        <v>9.0764692534603952E-3</v>
+      </c>
+      <c r="H36" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="I36" s="5" t="str">
+        <v>-1.8826174949404195E-2</v>
+      </c>
+      <c r="I36" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="J36" s="5" t="str">
+        <v>3.9438220788031053E-2</v>
+      </c>
+      <c r="J36" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="K36" s="5" t="str">
+        <v>-1.1615395470260248E-2</v>
+      </c>
+      <c r="K36" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="L36" s="5" t="str">
+        <v>-0.14579671089616042</v>
+      </c>
+      <c r="L36" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="M36" s="5" t="str">
+        <v>6.2395537355841579E-2</v>
+      </c>
+      <c r="M36" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="N36" s="5" t="str">
+        <v>8.0294195730622242E-2</v>
+      </c>
+      <c r="N36" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="O36" s="5" t="str">
+        <v>5.9126034204993294E-2</v>
+      </c>
+      <c r="O36" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C36,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
+        <v>5.6375308302467175E-2</v>
       </c>
       <c r="Q36" s="9"/>
     </row>
@@ -2895,53 +2895,53 @@
         <f t="shared" si="0"/>
         <v>1997年</v>
       </c>
-      <c r="D37" s="5" t="str">
+      <c r="D37" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="E37" s="5" t="str">
+        <v>6.1317061317061272E-2</v>
+      </c>
+      <c r="E37" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="F37" s="5" t="str">
+        <v>5.9275465554087248E-3</v>
+      </c>
+      <c r="F37" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="G37" s="5" t="str">
+        <v>-4.2613995599504406E-2</v>
+      </c>
+      <c r="G37" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="5" t="str">
+        <v>5.8405536770921529E-2</v>
+      </c>
+      <c r="H37" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="I37" s="5" t="str">
+        <v>5.8576883719769324E-2</v>
+      </c>
+      <c r="I37" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="J37" s="5" t="str">
+        <v>4.345263356438922E-2</v>
+      </c>
+      <c r="J37" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="K37" s="5" t="str">
+        <v>7.8123234742526471E-2</v>
+      </c>
+      <c r="K37" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="L37" s="5" t="str">
+        <v>-5.7445849794087733E-2</v>
+      </c>
+      <c r="L37" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="M37" s="5" t="str">
+        <v>5.3153523741759079E-2</v>
+      </c>
+      <c r="M37" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="N37" s="5" t="str">
+        <v>-3.4477662359597927E-2</v>
+      </c>
+      <c r="N37" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="O37" s="5" t="str">
+        <v>4.4586822942861426E-2</v>
+      </c>
+      <c r="O37" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C37,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
+        <v>1.5731630730583923E-2</v>
       </c>
       <c r="Q37" s="9"/>
     </row>
@@ -2951,53 +2951,53 @@
         <f t="shared" si="0"/>
         <v>1996年</v>
       </c>
-      <c r="D38" s="5" t="str">
+      <c r="D38" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="E38" s="5" t="str">
+        <v>3.2617342879872835E-2</v>
+      </c>
+      <c r="E38" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="F38" s="5" t="str">
+        <v>6.9337442218797563E-3</v>
+      </c>
+      <c r="F38" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="G38" s="5" t="str">
+        <v>7.9165560638947419E-3</v>
+      </c>
+      <c r="G38" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="H38" s="5" t="str">
+        <v>1.343144848954303E-2</v>
+      </c>
+      <c r="H38" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="I38" s="5" t="str">
+        <v>2.2853386734335235E-2</v>
+      </c>
+      <c r="I38" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="J38" s="5" t="str">
+        <v>2.2566953610712037E-3</v>
+      </c>
+      <c r="J38" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="K38" s="5" t="str">
+        <v>-4.5748027973696266E-2</v>
+      </c>
+      <c r="K38" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="L38" s="5" t="str">
+        <v>1.8813969841393829E-2</v>
+      </c>
+      <c r="L38" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="M38" s="5" t="str">
+        <v>5.4172610009355804E-2</v>
+      </c>
+      <c r="M38" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="N38" s="5" t="str">
+        <v>2.6130857982569866E-2</v>
+      </c>
+      <c r="N38" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="O38" s="5" t="str">
+        <v>7.3376153813433209E-2</v>
+      </c>
+      <c r="O38" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C38,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
+        <v>-2.1505376344086002E-2</v>
       </c>
       <c r="Q38" s="9"/>
     </row>
@@ -3007,53 +3007,53 @@
         <f t="shared" si="0"/>
         <v>1995年</v>
       </c>
-      <c r="D39" s="5" t="str">
+      <c r="D39" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="E39" s="5" t="str">
+        <v>2.4277658022514137E-2</v>
+      </c>
+      <c r="E39" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="F39" s="5" t="str">
+        <v>3.6074146507376392E-2</v>
+      </c>
+      <c r="F39" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="G39" s="5" t="str">
+        <v>2.7329243521615032E-2</v>
+      </c>
+      <c r="G39" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="H39" s="5" t="str">
+        <v>2.7960296379141658E-2</v>
+      </c>
+      <c r="H39" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="I39" s="5" t="str">
+        <v>3.6311709506323897E-2</v>
+      </c>
+      <c r="I39" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="J39" s="5" t="str">
+        <v>2.1278590176228018E-2</v>
+      </c>
+      <c r="J39" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="K39" s="5" t="str">
+        <v>3.1776044056906816E-2</v>
+      </c>
+      <c r="K39" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="L39" s="5" t="str">
+        <v>-3.2025050706319114E-4</v>
+      </c>
+      <c r="L39" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="M39" s="5" t="str">
+        <v>4.0097529721648595E-2</v>
+      </c>
+      <c r="M39" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="N39" s="5" t="str">
+        <v>-4.9793809140842304E-3</v>
+      </c>
+      <c r="N39" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="O39" s="5" t="str">
+        <v>4.1049011177987982E-2</v>
+      </c>
+      <c r="O39" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C39,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
+        <v>1.7443877298181087E-2</v>
       </c>
       <c r="Q39" s="9"/>
     </row>
@@ -3063,53 +3063,53 @@
         <f t="shared" si="0"/>
         <v>1994年</v>
       </c>
-      <c r="D40" s="5" t="str">
+      <c r="D40" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(D$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="E40" s="5" t="str">
+        <v>3.2500803944688572E-2</v>
+      </c>
+      <c r="E40" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="F40" s="5" t="str">
+        <v>-3.0045057203961778E-2</v>
+      </c>
+      <c r="F40" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="G40" s="5" t="str">
+        <v>-4.574645716487568E-2</v>
+      </c>
+      <c r="G40" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="5" t="str">
+        <v>1.1530609955807014E-2</v>
+      </c>
+      <c r="H40" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="I40" s="5" t="str">
+        <v>1.239715242509587E-2</v>
+      </c>
+      <c r="I40" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="J40" s="5" t="str">
+        <v>-2.6790799561883905E-2</v>
+      </c>
+      <c r="J40" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="K40" s="5" t="str">
+        <v>3.1489859769959772E-2</v>
+      </c>
+      <c r="K40" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="L40" s="5" t="str">
+        <v>3.7598743071618701E-2</v>
+      </c>
+      <c r="L40" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="M40" s="5" t="str">
+        <v>-2.6919598729731486E-2</v>
+      </c>
+      <c r="M40" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="N40" s="5" t="str">
+        <v>2.0877909615509394E-2</v>
+      </c>
+      <c r="N40" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="O40" s="5" t="str">
+        <v>-3.9504604636392604E-2</v>
+      </c>
+      <c r="O40" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C40,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
+        <v>1.229914699464385E-2</v>
       </c>
       <c r="Q40" s="9"/>
     </row>
@@ -3127,45 +3127,45 @@
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(E$7,2),data!$A:$C,3,0)/100,"")</f>
         <v/>
       </c>
-      <c r="F41" s="5" t="str">
+      <c r="F41" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(F$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="G41" s="5" t="str">
+        <v>1.8697279985565585E-2</v>
+      </c>
+      <c r="G41" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(G$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="5" t="str">
+        <v>-2.5416786591980878E-2</v>
+      </c>
+      <c r="H41" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(H$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="I41" s="5" t="str">
+        <v>2.2717462913741882E-2</v>
+      </c>
+      <c r="I41" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(I$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="J41" s="5" t="str">
+        <v>7.5523667784715975E-4</v>
+      </c>
+      <c r="J41" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(J$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="K41" s="5" t="str">
+        <v>-5.327059241337917E-3</v>
+      </c>
+      <c r="K41" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(K$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="L41" s="5" t="str">
+        <v>3.4431972865016869E-2</v>
+      </c>
+      <c r="L41" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(L$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="M41" s="5" t="str">
+        <v>-9.9879195789109865E-3</v>
+      </c>
+      <c r="M41" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(M$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="N41" s="5" t="str">
+        <v>1.9392935741834316E-2</v>
+      </c>
+      <c r="N41" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(N$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
-      </c>
-      <c r="O41" s="5" t="str">
+        <v>-1.2910672680247037E-2</v>
+      </c>
+      <c r="O41" s="5">
         <f>_xlfn.IFNA(VLOOKUP(LEFT($C41,4)&amp;"/"&amp;LEFT(O$7,2),data!$A:$C,3,0)/100,"")</f>
-        <v/>
+        <v>1.0091166980662036E-2</v>
       </c>
       <c r="Q41" s="9"/>
     </row>
@@ -3445,13 +3445,13 @@
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C1" s="1" t="str">
         <f>[1]!s_info_name(C2)</f>
-        <v>中证500</v>
+        <v>标普500</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C2" s="1" t="str">
         <f>IF(月度收益!D5="",月度收益!D4,月度收益!D5)</f>
-        <v>000905.SH</v>
+        <v>SPX.GI</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="C5" s="3">
         <f>[1]!WSD(C2,C4:C4,"-"&amp;月度收益!I4&amp;LEFT(月度收益!L4,1),"","Per="&amp;LEFT(月度收益!L4,1),"TradingCalendar=SSE","Sort=D","rptType=1","ShowParams=Y","cols=1;rows=424")</f>
-        <v>-14.063777671623301</v>
+        <v>-4.3303561044821244</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -3492,7 +3492,7 @@
         <v>46080</v>
       </c>
       <c r="C6" s="3">
-        <v>3.43981006772065</v>
+        <v>-0.86683585457909551</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -3504,7 +3504,7 @@
         <v>46052</v>
       </c>
       <c r="C7" s="3">
-        <v>12.1215873790391</v>
+        <v>1.3662990285588927</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -3516,7 +3516,7 @@
         <v>46022</v>
       </c>
       <c r="C8" s="3">
-        <v>6.1725177114208218</v>
+        <v>-5.2415722380638741E-2</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -3528,7 +3528,7 @@
         <v>45989</v>
       </c>
       <c r="C9" s="3">
-        <v>-4.0847425095209662</v>
+        <v>0.1299669600304032</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -3540,7 +3540,7 @@
         <v>45961</v>
       </c>
       <c r="C10" s="3">
-        <v>-1.0976963854090194</v>
+        <v>2.2686836730727133</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -3552,7 +3552,7 @@
         <v>45930</v>
       </c>
       <c r="C11" s="3">
-        <v>5.2304067938325982</v>
+        <v>3.5323655704259549</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -3564,7 +3564,7 @@
         <v>45898</v>
       </c>
       <c r="C12" s="3">
-        <v>13.131277440665334</v>
+        <v>1.9066503244002941</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
@@ -3576,7 +3576,7 @@
         <v>45869</v>
       </c>
       <c r="C13" s="3">
-        <v>5.2567240057101339</v>
+        <v>2.1666572655702376</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
@@ -3588,7 +3588,7 @@
         <v>45838</v>
       </c>
       <c r="C14" s="3">
-        <v>4.3080970771612215</v>
+        <v>4.960679602617879</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -3600,7 +3600,7 @@
         <v>45807</v>
       </c>
       <c r="C15" s="3">
-        <v>0.69688601291564289</v>
+        <v>6.1523847830692979</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -3612,7 +3612,7 @@
         <v>45777</v>
       </c>
       <c r="C16" s="3">
-        <v>-3.8572207341422637</v>
+        <v>-0.76249365182604611</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
@@ -3624,7 +3624,7 @@
         <v>45747</v>
       </c>
       <c r="C17" s="3">
-        <v>-3.5814782810561496E-2</v>
+        <v>-5.7544714081786852</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
@@ -3636,7 +3636,7 @@
         <v>45716</v>
       </c>
       <c r="C18" s="3">
-        <v>4.8400606353891318</v>
+        <v>-1.4242127760312417</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
@@ -3648,7 +3648,7 @@
         <v>45684</v>
       </c>
       <c r="C19" s="3">
-        <v>-2.3820393701947995</v>
+        <v>2.7016320305765618</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
@@ -3660,7 +3660,7 @@
         <v>45657</v>
       </c>
       <c r="C20" s="3">
-        <v>-2.1566545854847963</v>
+        <v>-2.4990136563014964</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
@@ -3672,7 +3672,7 @@
         <v>45625</v>
       </c>
       <c r="C21" s="3">
-        <v>-0.83628997481635103</v>
+        <v>5.7301352215863854</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
@@ -3684,7 +3684,7 @@
         <v>45596</v>
       </c>
       <c r="C22" s="3">
-        <v>2.7523494236766588</v>
+        <v>-0.98967805528175079</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
@@ -3696,7 +3696,7 @@
         <v>45565</v>
       </c>
       <c r="C23" s="3">
-        <v>23.799857145148206</v>
+        <v>2.0196869910062976</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
@@ -3708,7 +3708,7 @@
         <v>45534</v>
       </c>
       <c r="C24" s="3">
-        <v>-5.0609551348661856</v>
+        <v>2.2834688445031892</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
@@ -3720,7 +3720,7 @@
         <v>45504</v>
       </c>
       <c r="C25" s="3">
-        <v>-1.1404124928276693</v>
+        <v>1.1321349038912354</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
@@ -3732,7 +3732,7 @@
         <v>45471</v>
       </c>
       <c r="C26" s="3">
-        <v>-6.8900032651160288</v>
+        <v>3.4669759034089864</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
@@ -3744,7 +3744,7 @@
         <v>45443</v>
       </c>
       <c r="C27" s="3">
-        <v>-2.4370035175158455</v>
+        <v>4.8021224499522619</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
@@ -3756,7 +3756,7 @@
         <v>45412</v>
       </c>
       <c r="C28" s="3">
-        <v>2.931804274148897</v>
+        <v>-4.1615042774082571</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
@@ -3768,7 +3768,7 @@
         <v>45380</v>
       </c>
       <c r="C29" s="3">
-        <v>-1.1339825786033542</v>
+        <v>3.1018764704381807</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
@@ -3780,7 +3780,7 @@
         <v>45351</v>
       </c>
       <c r="C30" s="3">
-        <v>13.834705605278774</v>
+        <v>5.1720615397315317</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
@@ -3792,7 +3792,7 @@
         <v>45322</v>
       </c>
       <c r="C31" s="3">
-        <v>-13.487167827592749</v>
+        <v>1.5895744712075555</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
@@ -3804,7 +3804,7 @@
         <v>45289</v>
       </c>
       <c r="C32" s="3">
-        <v>-2.0887384540274057</v>
+        <v>4.4229169403213753</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
@@ -3816,7 +3816,7 @@
         <v>45260</v>
       </c>
       <c r="C33" s="3">
-        <v>0.3041095278360384</v>
+        <v>8.9179264628737709</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
@@ -3828,7 +3828,7 @@
         <v>45230</v>
       </c>
       <c r="C34" s="3">
-        <v>-2.8560495076790704</v>
+        <v>-2.1979687736850106</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
@@ -3840,7 +3840,7 @@
         <v>45197</v>
       </c>
       <c r="C35" s="3">
-        <v>-0.84727869736312966</v>
+        <v>-4.871929116215501</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
@@ -3852,7 +3852,7 @@
         <v>45169</v>
       </c>
       <c r="C36" s="3">
-        <v>-5.7298089821676061</v>
+        <v>-1.771643248143373</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
@@ -3864,7 +3864,7 @@
         <v>45138</v>
       </c>
       <c r="C37" s="3">
-        <v>1.4922126924447054</v>
+        <v>3.1138913980379268</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
@@ -3876,7 +3876,7 @@
         <v>45107</v>
       </c>
       <c r="C38" s="3">
-        <v>-0.81141543966857244</v>
+        <v>6.4727512841431301</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
@@ -3888,7 +3888,7 @@
         <v>45077</v>
       </c>
       <c r="C39" s="3">
-        <v>-3.0994141055947444</v>
+        <v>0.24823239348792381</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
@@ -3900,7 +3900,7 @@
         <v>45044</v>
       </c>
       <c r="C40" s="3">
-        <v>-1.5548426679673155</v>
+        <v>1.464236088297044</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
@@ -3912,7 +3912,7 @@
         <v>45016</v>
       </c>
       <c r="C41" s="3">
-        <v>-0.27867561000685104</v>
+        <v>3.5051572358727023</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
@@ -3924,7 +3924,7 @@
         <v>44985</v>
       </c>
       <c r="C42" s="3">
-        <v>1.0873520269034875</v>
+        <v>-2.6112446646715304</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
@@ -3936,7 +3936,7 @@
         <v>44957</v>
       </c>
       <c r="C43" s="3">
-        <v>7.2416318011787162</v>
+        <v>6.1752832400052027</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
@@ -3948,7 +3948,7 @@
         <v>44925</v>
       </c>
       <c r="C44" s="3">
-        <v>-4.7380223976151274</v>
+        <v>-5.8971449299161094</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
@@ -3960,7 +3960,7 @@
         <v>44895</v>
       </c>
       <c r="C45" s="3">
-        <v>6.0105701870826644</v>
+        <v>5.3752860293699856</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
@@ -3972,7 +3972,7 @@
         <v>44865</v>
       </c>
       <c r="C46" s="3">
-        <v>1.6283229923842901</v>
+        <v>7.9863454576893256</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.2">
@@ -3984,7 +3984,7 @@
         <v>44834</v>
       </c>
       <c r="C47" s="3">
-        <v>-7.1751276916825146</v>
+        <v>-9.3395701643489311</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.2">
@@ -3996,7 +3996,7 @@
         <v>44804</v>
       </c>
       <c r="C48" s="3">
-        <v>-2.1983855266437535</v>
+        <v>-4.2440119216810457</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.2">
@@ -4008,7 +4008,7 @@
         <v>44771</v>
       </c>
       <c r="C49" s="3">
-        <v>-2.478485772204353</v>
+        <v>9.1116347632205894</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
@@ -4020,7 +4020,7 @@
         <v>44742</v>
       </c>
       <c r="C50" s="3">
-        <v>7.0996291500170505</v>
+        <v>-8.3919993223866456</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
@@ -4032,7 +4032,7 @@
         <v>44712</v>
       </c>
       <c r="C51" s="3">
-        <v>7.0778629926771419</v>
+        <v>5.3243883608722342E-3</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.2">
@@ -4044,7 +4044,7 @@
         <v>44680</v>
       </c>
       <c r="C52" s="3">
-        <v>-11.020760618456936</v>
+        <v>-8.7956719149039344</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.2">
@@ -4056,7 +4056,7 @@
         <v>44651</v>
       </c>
       <c r="C53" s="3">
-        <v>-7.7093746886996106</v>
+        <v>3.5773238773280092</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.2">
@@ -4068,7 +4068,7 @@
         <v>44620</v>
       </c>
       <c r="C54" s="3">
-        <v>4.1452299434848072</v>
+        <v>-3.1360520866782648</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.2">
@@ -4080,7 +4080,7 @@
         <v>44589</v>
       </c>
       <c r="C55" s="3">
-        <v>-10.583364757986335</v>
+        <v>-5.2585089106999767</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.2">
@@ -4092,7 +4092,7 @@
         <v>44561</v>
       </c>
       <c r="C56" s="3">
-        <v>1.4704370554241342</v>
+        <v>4.3612874972629889</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
@@ -4104,7 +4104,7 @@
         <v>44530</v>
       </c>
       <c r="C57" s="3">
-        <v>3.2788326981938232</v>
+        <v>-0.83337314184714906</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.2">
@@ -4116,7 +4116,7 @@
         <v>44498</v>
       </c>
       <c r="C58" s="3">
-        <v>-1.1417916721638721</v>
+        <v>6.9143873301234615</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.2">
@@ -4128,7 +4128,7 @@
         <v>44469</v>
       </c>
       <c r="C59" s="3">
-        <v>-2.091344614529389</v>
+        <v>-4.7569140421166338</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.2">
@@ -4140,7 +4140,7 @@
         <v>44439</v>
       </c>
       <c r="C60" s="3">
-        <v>7.2115119199398947</v>
+        <v>2.8990321391681118</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.2">
@@ -4152,7 +4152,7 @@
         <v>44407</v>
       </c>
       <c r="C61" s="3">
-        <v>-0.60026440828244709</v>
+        <v>2.274810936591054</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.2">
@@ -4164,7 +4164,7 @@
         <v>44377</v>
       </c>
       <c r="C62" s="3">
-        <v>1.176885282021356</v>
+        <v>2.221397632316946</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.2">
@@ -4176,7 +4176,7 @@
         <v>44347</v>
       </c>
       <c r="C63" s="3">
-        <v>3.7510649377882066</v>
+        <v>0.54865025818131574</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
@@ -4188,7 +4188,7 @@
         <v>44316</v>
       </c>
       <c r="C64" s="3">
-        <v>3.7037963840983901</v>
+        <v>5.242531255584737</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
@@ -4200,7 +4200,7 @@
         <v>44286</v>
       </c>
       <c r="C65" s="3">
-        <v>-1.7328297429892725</v>
+        <v>4.2438634008107767</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
@@ -4212,7 +4212,7 @@
         <v>44253</v>
       </c>
       <c r="C66" s="3">
-        <v>0.28703760591619609</v>
+        <v>2.6091474971999817</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
@@ -4224,7 +4224,7 @@
         <v>44225</v>
       </c>
       <c r="C67" s="3">
-        <v>-0.32947104504112978</v>
+        <v>-1.1136640158463607</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
@@ -4236,7 +4236,7 @@
         <v>44196</v>
       </c>
       <c r="C68" s="3">
-        <v>0.73044151743091312</v>
+        <v>3.712140665943231</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
@@ -4248,7 +4248,7 @@
         <v>44165</v>
       </c>
       <c r="C69" s="3">
-        <v>3.4273823970274453</v>
+        <v>10.754565805086314</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
@@ -4260,7 +4260,7 @@
         <v>44134</v>
       </c>
       <c r="C70" s="3">
-        <v>-1.3084237564946477</v>
+        <v>-2.7665774606006499</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
@@ -4272,7 +4272,7 @@
         <v>44104</v>
       </c>
       <c r="C71" s="3">
-        <v>-7.1370379347436286</v>
+        <v>-3.9227954095494399</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
@@ -4284,7 +4284,7 @@
         <v>44074</v>
       </c>
       <c r="C72" s="3">
-        <v>1.3490571015906339</v>
+        <v>7.0064687324219221</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
@@ -4296,7 +4296,7 @@
         <v>44043</v>
       </c>
       <c r="C73" s="3">
-        <v>12.196494096155931</v>
+        <v>5.5101296975444303</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
@@ -4308,7 +4308,7 @@
         <v>44012</v>
       </c>
       <c r="C74" s="3">
-        <v>8.4729424080093541</v>
+        <v>1.8388403283502663</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
@@ -4320,7 +4320,7 @@
         <v>43980</v>
       </c>
       <c r="C75" s="3">
-        <v>0.98024238402223407</v>
+        <v>4.528177501261843</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
@@ -4332,7 +4332,7 @@
         <v>43951</v>
       </c>
       <c r="C76" s="3">
-        <v>6.1967467556081957</v>
+        <v>12.684410293315374</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
@@ -4344,7 +4344,7 @@
         <v>43921</v>
       </c>
       <c r="C77" s="3">
-        <v>-7.51815299781261</v>
+        <v>-12.511932083595656</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
@@ -4356,7 +4356,7 @@
         <v>43889</v>
       </c>
       <c r="C78" s="3">
-        <v>1.3676485839007713</v>
+        <v>-8.4110469009648128</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
@@ -4368,7 +4368,7 @@
         <v>43853</v>
       </c>
       <c r="C79" s="3">
-        <v>2.0897106879784522</v>
+        <v>-0.16280898111292741</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
@@ -4380,7 +4380,7 @@
         <v>43830</v>
       </c>
       <c r="C80" s="3">
-        <v>7.6144034077955114</v>
+        <v>2.8589803182446305</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
@@ -4392,7 +4392,7 @@
         <v>43798</v>
       </c>
       <c r="C81" s="3">
-        <v>-0.45706512528304044</v>
+        <v>3.404706409091518</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.2">
@@ -4404,7 +4404,7 @@
         <v>43769</v>
       </c>
       <c r="C82" s="3">
-        <v>-0.47533011678229098</v>
+        <v>2.0431747482144935</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.2">
@@ -4416,7 +4416,7 @@
         <v>43738</v>
       </c>
       <c r="C83" s="3">
-        <v>1.113456805636126</v>
+        <v>1.7181167690656807</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.2">
@@ -4428,7 +4428,7 @@
         <v>43707</v>
       </c>
       <c r="C84" s="3">
-        <v>-0.34077724295732414</v>
+        <v>-1.8091652742267761</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.2">
@@ -4440,7 +4440,7 @@
         <v>43677</v>
       </c>
       <c r="C85" s="3">
-        <v>-0.95499430176444466</v>
+        <v>1.3128195366039375</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.2">
@@ -4452,7 +4452,7 @@
         <v>43644</v>
       </c>
       <c r="C86" s="3">
-        <v>0.78337329159474667</v>
+        <v>6.8930183208214979</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.2">
@@ -4464,7 +4464,7 @@
         <v>43616</v>
       </c>
       <c r="C87" s="3">
-        <v>-7.4527560687020049</v>
+        <v>-6.577772648116154</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.2">
@@ -4476,7 +4476,7 @@
         <v>43585</v>
       </c>
       <c r="C88" s="3">
-        <v>-4.3278836263841214</v>
+        <v>3.9313434942139347</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.2">
@@ -4488,7 +4488,7 @@
         <v>43553</v>
       </c>
       <c r="C89" s="3">
-        <v>10.394716819699589</v>
+        <v>1.7924287751078349</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
@@ -4500,7 +4500,7 @@
         <v>43524</v>
       </c>
       <c r="C90" s="3">
-        <v>20.323780785509026</v>
+        <v>2.9728930143116061</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.2">
@@ -4512,7 +4512,7 @@
         <v>43496</v>
       </c>
       <c r="C91" s="3">
-        <v>0.20243585690460364</v>
+        <v>7.8684404731036883</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.2">
@@ -4524,7 +4524,7 @@
         <v>43462</v>
       </c>
       <c r="C92" s="3">
-        <v>-4.7665394209741807</v>
+        <v>-9.1776955767217334</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.2">
@@ -4536,7 +4536,7 @@
         <v>43434</v>
       </c>
       <c r="C93" s="3">
-        <v>2.4364666567646909</v>
+        <v>1.785938179914015</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
@@ -4548,7 +4548,7 @@
         <v>43404</v>
       </c>
       <c r="C94" s="3">
-        <v>-11.002015173238167</v>
+        <v>-6.9403358979814644</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.2">
@@ -4560,7 +4560,7 @@
         <v>43371</v>
       </c>
       <c r="C95" s="3">
-        <v>-0.29274176747116076</v>
+        <v>0.42943009181395375</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.2">
@@ -4572,7 +4572,7 @@
         <v>43343</v>
       </c>
       <c r="C96" s="3">
-        <v>-7.2058840137848357</v>
+        <v>3.0263218631604083</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.2">
@@ -4584,7 +4584,7 @@
         <v>43312</v>
       </c>
       <c r="C97" s="3">
-        <v>-0.55670778382994612</v>
+        <v>3.6021586465418753</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.2">
@@ -4596,7 +4596,7 @@
         <v>43280</v>
       </c>
       <c r="C98" s="3">
-        <v>-9.3268341127094363</v>
+        <v>0.48424002040461378</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.2">
@@ -4608,7 +4608,7 @@
         <v>43251</v>
       </c>
       <c r="C99" s="3">
-        <v>-1.8172547010709916</v>
+        <v>2.1608353316591389</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.2">
@@ -4620,7 +4620,7 @@
         <v>43217</v>
       </c>
       <c r="C100" s="3">
-        <v>-4.1498849451968356</v>
+        <v>0.2718801001185378</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
@@ -4632,7 +4632,7 @@
         <v>43189</v>
       </c>
       <c r="C101" s="3">
-        <v>1.5117211630039318</v>
+        <v>-2.6884513768364315</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.2">
@@ -4644,7 +4644,7 @@
         <v>43159</v>
       </c>
       <c r="C102" s="3">
-        <v>-2.6766063135022167</v>
+        <v>-3.8947379604151844</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.2">
@@ -4656,7 +4656,7 @@
         <v>43131</v>
       </c>
       <c r="C103" s="3">
-        <v>-0.98354124923147879</v>
+        <v>5.6178724645703726</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.2">
@@ -4668,7 +4668,7 @@
         <v>43098</v>
       </c>
       <c r="C104" s="3">
-        <v>-0.20117280955567196</v>
+        <v>0.98316198188534987</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.2">
@@ -4680,7 +4680,7 @@
         <v>43069</v>
       </c>
       <c r="C105" s="3">
-        <v>-4.5240107878329443</v>
+        <v>2.8082601368405458</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.2">
@@ -4692,7 +4692,7 @@
         <v>43039</v>
       </c>
       <c r="C106" s="3">
-        <v>-0.65200080681376837</v>
+        <v>2.2188174774546043</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.2">
@@ -4704,7 +4704,7 @@
         <v>43007</v>
       </c>
       <c r="C107" s="3">
-        <v>2.0529220495361766</v>
+        <v>1.9302894827342154</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.2">
@@ -4716,7 +4716,7 @@
         <v>42978</v>
       </c>
       <c r="C108" s="3">
-        <v>2.7377816616207307</v>
+        <v>5.4649232886694321E-2</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.2">
@@ -4728,7 +4728,7 @@
         <v>42947</v>
       </c>
       <c r="C109" s="3">
-        <v>2.6041177581096253</v>
+        <v>1.9348768883515444</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.2">
@@ -4740,7 +4740,7 @@
         <v>42916</v>
       </c>
       <c r="C110" s="3">
-        <v>5.3922695957259847</v>
+        <v>0.48138319927024664</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.2">
@@ -4752,7 +4752,7 @@
         <v>42886</v>
       </c>
       <c r="C111" s="3">
-        <v>-6.2422213344584083</v>
+        <v>1.1576210049492719</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
@@ -4764,7 +4764,7 @@
         <v>42853</v>
       </c>
       <c r="C112" s="3">
-        <v>-2.9646350902866714</v>
+        <v>0.90912169025529899</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.2">
@@ -4776,7 +4776,7 @@
         <v>42825</v>
       </c>
       <c r="C113" s="3">
-        <v>-0.76457027757731444</v>
+        <v>-3.8923017041514463E-2</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.2">
@@ -4788,7 +4788,7 @@
         <v>42794</v>
       </c>
       <c r="C114" s="3">
-        <v>3.6515863112494884</v>
+        <v>3.7198260541408734</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.2">
@@ -4800,7 +4800,7 @@
         <v>42761</v>
       </c>
       <c r="C115" s="3">
-        <v>-0.63732257560221717</v>
+        <v>1.7884341374735824</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.2">
@@ -4812,7 +4812,7 @@
         <v>42734</v>
       </c>
       <c r="C116" s="3">
-        <v>-4.8887435477185655</v>
+        <v>1.8200754044233047</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.2">
@@ -4824,7 +4824,7 @@
         <v>42704</v>
       </c>
       <c r="C117" s="3">
-        <v>2.067072938064074</v>
+        <v>3.4174446769983158</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.2">
@@ -4836,7 +4836,7 @@
         <v>42674</v>
       </c>
       <c r="C118" s="3">
-        <v>1.961417841756119</v>
+        <v>-1.9425625037472249</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.2">
@@ -4848,7 +4848,7 @@
         <v>42643</v>
       </c>
       <c r="C119" s="3">
-        <v>-1.6493818985058528</v>
+        <v>-0.12344825997834263</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.2">
@@ -4860,7 +4860,7 @@
         <v>42613</v>
       </c>
       <c r="C120" s="3">
-        <v>3.7291958140237114</v>
+        <v>-0.12191755612808164</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.2">
@@ -4872,7 +4872,7 @@
         <v>42580</v>
       </c>
       <c r="C121" s="3">
-        <v>1.2966192388956355</v>
+        <v>3.5609807228685897</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.2">
@@ -4884,7 +4884,7 @@
         <v>42551</v>
       </c>
       <c r="C122" s="3">
-        <v>2.9621985853667487</v>
+        <v>9.0607355409733081E-2</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
@@ -4896,7 +4896,7 @@
         <v>42521</v>
       </c>
       <c r="C123" s="3">
-        <v>-0.63939518784601468</v>
+        <v>1.5329492083474561</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.2">
@@ -4908,7 +4908,7 @@
         <v>42489</v>
       </c>
       <c r="C124" s="3">
-        <v>-2.7651876020031607</v>
+        <v>0.269936982337593</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.2">
@@ -4920,7 +4920,7 @@
         <v>42460</v>
       </c>
       <c r="C125" s="3">
-        <v>15.052613398424143</v>
+        <v>6.5991108718941094</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.2">
@@ -4932,7 +4932,7 @@
         <v>42429</v>
       </c>
       <c r="C126" s="3">
-        <v>-2.1702135409072953</v>
+        <v>-0.41283552550199776</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.2">
@@ -4944,7 +4944,7 @@
         <v>42398</v>
       </c>
       <c r="C127" s="3">
-        <v>-28.20492671727607</v>
+        <v>-5.0735344481736222</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.2">
@@ -4956,7 +4956,7 @@
         <v>42369</v>
       </c>
       <c r="C128" s="3">
-        <v>2.8250396023496993</v>
+        <v>-1.7530198374358763</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.2">
@@ -4968,7 +4968,7 @@
         <v>42338</v>
       </c>
       <c r="C129" s="3">
-        <v>4.5649900085682926</v>
+        <v>5.0496306555847248E-2</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.2">
@@ -4980,7 +4980,7 @@
         <v>42307</v>
       </c>
       <c r="C130" s="3">
-        <v>15.697027924528451</v>
+        <v>8.2983078389400333</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.2">
@@ -4992,7 +4992,7 @@
         <v>42277</v>
       </c>
       <c r="C131" s="3">
-        <v>-6.952796818178852</v>
+        <v>-2.6442819620927094</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
@@ -5004,7 +5004,7 @@
         <v>42247</v>
       </c>
       <c r="C132" s="3">
-        <v>-14.827735016657307</v>
+        <v>-6.258080462392579</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.2">
@@ -5016,7 +5016,7 @@
         <v>42216</v>
       </c>
       <c r="C133" s="3">
-        <v>-13.237780439797342</v>
+        <v>1.9742039930008559</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
@@ -5028,7 +5028,7 @@
         <v>42185</v>
       </c>
       <c r="C134" s="3">
-        <v>-10.643536645748963</v>
+        <v>-2.10117728564716</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.2">
@@ -5040,7 +5040,7 @@
         <v>42153</v>
       </c>
       <c r="C135" s="3">
-        <v>17.676857182089535</v>
+        <v>1.0491438545008114</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.2">
@@ -5052,7 +5052,7 @@
         <v>42124</v>
       </c>
       <c r="C136" s="3">
-        <v>16.773080876821854</v>
+        <v>0.85207627098153882</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.2">
@@ -5064,7 +5064,7 @@
         <v>42094</v>
       </c>
       <c r="C137" s="3">
-        <v>20.514224312752294</v>
+        <v>-1.7396056070325572</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.2">
@@ -5076,7 +5076,7 @@
         <v>42062</v>
       </c>
       <c r="C138" s="3">
-        <v>6.8481027310390186</v>
+        <v>5.4892505726845675</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.2">
@@ -5088,7 +5088,7 @@
         <v>42034</v>
       </c>
       <c r="C139" s="3">
-        <v>5.8243595278649307</v>
+        <v>-3.1040847054252363</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.2">
@@ -5100,7 +5100,7 @@
         <v>42004</v>
       </c>
       <c r="C140" s="3">
-        <v>1.4765120631609507</v>
+        <v>-0.41885120625277938</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.2">
@@ -5112,7 +5112,7 @@
         <v>41971</v>
       </c>
       <c r="C141" s="3">
-        <v>5.1911232436282928</v>
+        <v>2.4533584400783015</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.2">
@@ -5124,7 +5124,7 @@
         <v>41943</v>
       </c>
       <c r="C142" s="3">
-        <v>1.4299287710488828</v>
+        <v>2.3201456175308888</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.2">
@@ -5136,7 +5136,7 @@
         <v>41912</v>
       </c>
       <c r="C143" s="3">
-        <v>11.026498239902205</v>
+        <v>-1.5513859147336717</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.2">
@@ -5148,7 +5148,7 @@
         <v>41880</v>
       </c>
       <c r="C144" s="3">
-        <v>4.0129714391085702</v>
+        <v>3.7655321727690261</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
@@ -5160,7 +5160,7 @@
         <v>41851</v>
       </c>
       <c r="C145" s="3">
-        <v>8.4624256956159272</v>
+        <v>-1.5079863077291922</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.2">
@@ -5172,7 +5172,7 @@
         <v>41820</v>
       </c>
       <c r="C146" s="3">
-        <v>2.4982777252288813</v>
+        <v>1.9058313448431896</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.2">
@@ -5184,7 +5184,7 @@
         <v>41789</v>
       </c>
       <c r="C147" s="3">
-        <v>1.6745924905142262</v>
+        <v>2.1030282120013677</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.2">
@@ -5196,7 +5196,7 @@
         <v>41759</v>
       </c>
       <c r="C148" s="3">
-        <v>-1.9363443019411841</v>
+        <v>0.62007968638175814</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.2">
@@ -5208,7 +5208,7 @@
         <v>41729</v>
       </c>
       <c r="C149" s="3">
-        <v>-3.4053173484737798</v>
+        <v>0.69321573583585039</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.2">
@@ -5220,7 +5220,7 @@
         <v>41698</v>
       </c>
       <c r="C150" s="3">
-        <v>2.3295575042672434</v>
+        <v>4.3117037568930705</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.2">
@@ -5232,7 +5232,7 @@
         <v>41669</v>
       </c>
       <c r="C151" s="3">
-        <v>1.4708432486414624</v>
+        <v>-3.5582895107013734</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.2">
@@ -5244,7 +5244,7 @@
         <v>41639</v>
       </c>
       <c r="C152" s="3">
-        <v>-2.9720125998921043</v>
+        <v>2.3562833299184183</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.2">
@@ -5256,7 +5256,7 @@
         <v>41607</v>
       </c>
       <c r="C153" s="3">
-        <v>6.2618391961503761</v>
+        <v>2.804946087194149</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.2">
@@ -5268,7 +5268,7 @@
         <v>41578</v>
       </c>
       <c r="C154" s="3">
-        <v>-4.1071106276367564</v>
+        <v>4.4595759864410889</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.2">
@@ -5280,7 +5280,7 @@
         <v>41547</v>
       </c>
       <c r="C155" s="3">
-        <v>5.6969587472994965</v>
+        <v>2.9749474883188354</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
@@ -5292,7 +5292,7 @@
         <v>41516</v>
       </c>
       <c r="C156" s="3">
-        <v>6.8033367699066982</v>
+        <v>-3.1298013323604601</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.2">
@@ -5304,7 +5304,7 @@
         <v>41486</v>
       </c>
       <c r="C157" s="3">
-        <v>6.018736839372818</v>
+        <v>4.9462111213487203</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.2">
@@ -5316,7 +5316,7 @@
         <v>41453</v>
       </c>
       <c r="C158" s="3">
-        <v>-15.756460580992792</v>
+        <v>-1.499932545960736</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.2">
@@ -5328,7 +5328,7 @@
         <v>41425</v>
       </c>
       <c r="C159" s="3">
-        <v>14.058340157837556</v>
+        <v>2.0762783477406455</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.2">
@@ -5340,7 +5340,7 @@
         <v>41390</v>
       </c>
       <c r="C160" s="3">
-        <v>-2.3067138342202531</v>
+        <v>1.8085763992887971</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.2">
@@ -5352,7 +5352,7 @@
         <v>41362</v>
       </c>
       <c r="C161" s="3">
-        <v>-4.4596764202861401</v>
+        <v>3.5987799403174314</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.2">
@@ -5364,7 +5364,7 @@
         <v>41333</v>
       </c>
       <c r="C162" s="3">
-        <v>3.6946659393879422</v>
+        <v>1.1060603026480154</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.2">
@@ -5376,7 +5376,7 @@
         <v>41305</v>
       </c>
       <c r="C163" s="3">
-        <v>6.2205955077445196</v>
+        <v>5.0428063581991145</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
@@ -5388,7 +5388,7 @@
         <v>41274</v>
       </c>
       <c r="C164" s="3">
-        <v>16.304483665551395</v>
+        <v>0.70683105254980561</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
@@ -5400,7 +5400,7 @@
         <v>41243</v>
       </c>
       <c r="C165" s="3">
-        <v>-11.094136322214897</v>
+        <v>0.28467029231815655</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.2">
@@ -5412,7 +5412,7 @@
         <v>41213</v>
       </c>
       <c r="C166" s="3">
-        <v>-0.98929542039507545</v>
+        <v>-1.9789403541407791</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
@@ -5424,7 +5424,7 @@
         <v>41180</v>
       </c>
       <c r="C167" s="3">
-        <v>1.9191591017677867</v>
+        <v>2.4236090375236552</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.2">
@@ -5436,7 +5436,7 @@
         <v>41152</v>
       </c>
       <c r="C168" s="3">
-        <v>-0.62332393852605472</v>
+        <v>1.9763361656468303</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.2">
@@ -5448,7 +5448,7 @@
         <v>41121</v>
       </c>
       <c r="C169" s="3">
-        <v>-8.9823147165125619</v>
+        <v>1.2597639043871345</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.2">
@@ -5460,7 +5460,7 @@
         <v>41089</v>
       </c>
       <c r="C170" s="3">
-        <v>-7.5295323707178614</v>
+        <v>3.9554921279372435</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.2">
@@ -5472,7 +5472,7 @@
         <v>41060</v>
       </c>
       <c r="C171" s="3">
-        <v>2.4273884623801756</v>
+        <v>-6.2650671359386623</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.2">
@@ -5484,7 +5484,7 @@
         <v>41026</v>
       </c>
       <c r="C172" s="3">
-        <v>7.2517542442525951</v>
+        <v>-0.7497497284287169</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.2">
@@ -5496,7 +5496,7 @@
         <v>40998</v>
       </c>
       <c r="C173" s="3">
-        <v>-7.5561991091256058</v>
+        <v>3.1332376545017748</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.2">
@@ -5508,7 +5508,7 @@
         <v>40968</v>
       </c>
       <c r="C174" s="3">
-        <v>12.191553543579058</v>
+        <v>4.0589449943234213</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
@@ -5520,7 +5520,7 @@
         <v>40939</v>
       </c>
       <c r="C175" s="3">
-        <v>0.84851267687551246</v>
+        <v>4.3583015267175673</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
@@ -5532,7 +5532,7 @@
         <v>40907</v>
       </c>
       <c r="C176" s="3">
-        <v>-14.481031387387555</v>
+        <v>0.85327516520175006</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.2">
@@ -5544,7 +5544,7 @@
         <v>40877</v>
       </c>
       <c r="C177" s="3">
-        <v>-4.4862155513804458</v>
+        <v>-0.50586451767333784</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
@@ -5556,7 +5556,7 @@
         <v>40847</v>
       </c>
       <c r="C178" s="3">
-        <v>3.6956275986380627</v>
+        <v>10.772303830584562</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.2">
@@ -5568,7 +5568,7 @@
         <v>40816</v>
       </c>
       <c r="C179" s="3">
-        <v>-12.948991747729044</v>
+        <v>-7.1762012979021961</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.2">
@@ -5580,7 +5580,7 @@
         <v>40786</v>
       </c>
       <c r="C180" s="3">
-        <v>-4.2733000311128038</v>
+        <v>-5.6791097904478782</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.2">
@@ -5592,7 +5592,7 @@
         <v>40753</v>
       </c>
       <c r="C181" s="3">
-        <v>1.069763013470082</v>
+        <v>-2.1474436636782279</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.2">
@@ -5604,7 +5604,7 @@
         <v>40724</v>
       </c>
       <c r="C182" s="3">
-        <v>3.0388751733690711</v>
+        <v>-1.8257508177222714</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.2">
@@ -5616,7 +5616,7 @@
         <v>40694</v>
       </c>
       <c r="C183" s="3">
-        <v>-8.1166193150688954</v>
+        <v>-1.350092768460176</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.2">
@@ -5628,7 +5628,7 @@
         <v>40662</v>
       </c>
       <c r="C184" s="3">
-        <v>-3.2704570552527623</v>
+        <v>2.8495357625034856</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.2">
@@ -5640,7 +5640,7 @@
         <v>40633</v>
       </c>
       <c r="C185" s="3">
-        <v>-1.8606894949136477</v>
+        <v>-0.10473018791158362</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.2">
@@ -5652,7 +5652,7 @@
         <v>40602</v>
       </c>
       <c r="C186" s="3">
-        <v>10.504504582659191</v>
+        <v>3.1956582589494076</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.2">
@@ -5664,7 +5664,7 @@
         <v>40574</v>
       </c>
       <c r="C187" s="3">
-        <v>-6.6006632749382561</v>
+        <v>2.2645590152984729</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.2">
@@ -5676,7 +5676,7 @@
         <v>40543</v>
       </c>
       <c r="C188" s="3">
-        <v>-3.4076161127008509</v>
+        <v>6.5300072000338938</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
@@ -5688,7 +5688,7 @@
         <v>40512</v>
       </c>
       <c r="C189" s="3">
-        <v>1.0955016841090792</v>
+        <v>-0.22902827780877377</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.2">
@@ -5700,7 +5700,7 @@
         <v>40480</v>
       </c>
       <c r="C190" s="3">
-        <v>8.4728699385594908</v>
+        <v>3.6855941114616098</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.2">
@@ -5712,7 +5712,7 @@
         <v>40451</v>
       </c>
       <c r="C191" s="3">
-        <v>1.5539662026078593</v>
+        <v>8.7551104037814742</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.2">
@@ -5724,7 +5724,7 @@
         <v>40421</v>
       </c>
       <c r="C192" s="3">
-        <v>9.50003936885755</v>
+        <v>-4.7449164851125598</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.2">
@@ -5736,7 +5736,7 @@
         <v>40389</v>
       </c>
       <c r="C193" s="3">
-        <v>14.372251985556428</v>
+        <v>6.8777832756061308</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.2">
@@ -5748,7 +5748,7 @@
         <v>40359</v>
       </c>
       <c r="C194" s="3">
-        <v>-10.717860306736915</v>
+        <v>-5.3882376699314394</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.2">
@@ -5760,7 +5760,7 @@
         <v>40329</v>
       </c>
       <c r="C195" s="3">
-        <v>-7.5318996792065001</v>
+        <v>-8.1975916203894883</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.2">
@@ -5772,7 +5772,7 @@
         <v>40298</v>
       </c>
       <c r="C196" s="3">
-        <v>-6.6750529892095738</v>
+        <v>1.4759327193589966</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.2">
@@ -5784,7 +5784,7 @@
         <v>40268</v>
       </c>
       <c r="C197" s="3">
-        <v>2.621243233877868</v>
+        <v>5.8796367554255768</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.2">
@@ -5796,7 +5796,7 @@
         <v>40235</v>
       </c>
       <c r="C198" s="3">
-        <v>5.9438368655405194</v>
+        <v>2.8513693463827261</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.2">
@@ -5808,7 +5808,7 @@
         <v>40207</v>
       </c>
       <c r="C199" s="3">
-        <v>-2.4659913427441671</v>
+        <v>-3.6974262397991176</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
@@ -5820,7 +5820,7 @@
         <v>40178</v>
       </c>
       <c r="C200" s="3">
-        <v>1.8143257437357674</v>
+        <v>1.7770597738287375</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.2">
@@ -5832,7 +5832,7 @@
         <v>40147</v>
       </c>
       <c r="C201" s="3">
-        <v>15.091244494384725</v>
+        <v>5.7363996950366314</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.2">
@@ -5844,7 +5844,7 @@
         <v>40116</v>
       </c>
       <c r="C202" s="3">
-        <v>12.5582871138612</v>
+        <v>-1.9761985847807084</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.2">
@@ -5856,7 +5856,7 @@
         <v>40086</v>
       </c>
       <c r="C203" s="3">
-        <v>3.7408820081287431</v>
+        <v>3.5723383825517763</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.2">
@@ -5868,7 +5868,7 @@
         <v>40056</v>
       </c>
       <c r="C204" s="3">
-        <v>-16.560343370537577</v>
+        <v>3.3560173370599911</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.2">
@@ -5880,7 +5880,7 @@
         <v>40025</v>
       </c>
       <c r="C205" s="3">
-        <v>13.797355531719347</v>
+        <v>7.4141756950789617</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.2">
@@ -5892,7 +5892,7 @@
         <v>39994</v>
       </c>
       <c r="C206" s="3">
-        <v>5.3563777257207512</v>
+        <v>1.9583523728705643E-2</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.2">
@@ -5904,7 +5904,7 @@
         <v>39960</v>
       </c>
       <c r="C207" s="3">
-        <v>6.1736099567852865</v>
+        <v>5.3081426656431674</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.2">
@@ -5916,7 +5916,7 @@
         <v>39933</v>
       </c>
       <c r="C208" s="3">
-        <v>5.9053342886791427</v>
+        <v>9.3925075513554788</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.2">
@@ -5928,7 +5928,7 @@
         <v>39903</v>
       </c>
       <c r="C209" s="3">
-        <v>20.570520933623349</v>
+        <v>8.54045082915016</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.2">
@@ -5940,7 +5940,7 @@
         <v>39871</v>
       </c>
       <c r="C210" s="3">
-        <v>7.9919770589281347</v>
+        <v>-10.993122487528451</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
@@ -5952,7 +5952,7 @@
         <v>39836</v>
       </c>
       <c r="C211" s="3">
-        <v>15.398778921468281</v>
+        <v>-8.5657348463880396</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.2">
@@ -5964,7 +5964,7 @@
         <v>39813</v>
       </c>
       <c r="C212" s="3">
-        <v>5.3209698878601053</v>
+        <v>0.78215656520574939</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.2">
@@ -5976,7 +5976,7 @@
         <v>39780</v>
       </c>
       <c r="C213" s="3">
-        <v>17.888864561446649</v>
+        <v>-7.4849032258064501</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.2">
@@ -5988,7 +5988,7 @@
         <v>39752</v>
       </c>
       <c r="C214" s="3">
-        <v>-26.871663449595772</v>
+        <v>-16.942453444905514</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.2">
@@ -6000,7 +6000,7 @@
         <v>39717</v>
       </c>
       <c r="C215" s="3">
-        <v>-7.4185209682214985</v>
+        <v>-9.0791453271283018</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.2">
@@ -6012,7 +6012,7 @@
         <v>39689</v>
       </c>
       <c r="C216" s="3">
-        <v>-23.533574151279147</v>
+        <v>1.2190503242910378</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.2">
@@ -6024,7 +6024,7 @@
         <v>39660</v>
       </c>
       <c r="C217" s="3">
-        <v>7.2324641150706137</v>
+        <v>-0.98593749999998925</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.2">
@@ -6036,7 +6036,7 @@
         <v>39629</v>
       </c>
       <c r="C218" s="3">
-        <v>-25.08007309557302</v>
+        <v>-8.5962381639269392</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.2">
@@ -6048,7 +6048,7 @@
         <v>39598</v>
       </c>
       <c r="C219" s="3">
-        <v>-3.7801760514124649</v>
+        <v>1.0674153248796614</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.2">
@@ -6060,7 +6060,7 @@
         <v>39568</v>
       </c>
       <c r="C220" s="3">
-        <v>-3.4845842014708861</v>
+        <v>4.7546684811370588</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.2">
@@ -6072,7 +6072,7 @@
         <v>39538</v>
       </c>
       <c r="C221" s="3">
-        <v>-20.039457317546983</v>
+        <v>-0.59595830546433914</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
@@ -6084,7 +6084,7 @@
         <v>39507</v>
       </c>
       <c r="C222" s="3">
-        <v>8.4530756966729292</v>
+        <v>-3.4761162090602316</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.2">
@@ -6096,7 +6096,7 @@
         <v>39478</v>
       </c>
       <c r="C223" s="3">
-        <v>-5.7439531829857842</v>
+        <v>-6.1163474897164116</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.2">
@@ -6108,7 +6108,7 @@
         <v>39444</v>
       </c>
       <c r="C224" s="3">
-        <v>20.002051937795741</v>
+        <v>-0.8628488866683881</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.2">
@@ -6120,7 +6120,7 @@
         <v>39416</v>
       </c>
       <c r="C225" s="3">
-        <v>-9.3897542142810551</v>
+        <v>-4.4043423821141348</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.2">
@@ -6132,7 +6132,7 @@
         <v>39386</v>
       </c>
       <c r="C226" s="3">
-        <v>-10.493779076057553</v>
+        <v>1.4822335025380884</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.2">
@@ -6144,7 +6144,7 @@
         <v>39353</v>
       </c>
       <c r="C227" s="3">
-        <v>3.7980364404377687</v>
+        <v>3.579400131615551</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.2">
@@ -6156,7 +6156,7 @@
         <v>39325</v>
       </c>
       <c r="C228" s="3">
-        <v>11.219315902682926</v>
+        <v>1.2863592323073991</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.2">
@@ -6168,7 +6168,7 @@
         <v>39294</v>
       </c>
       <c r="C229" s="3">
-        <v>22.816934719588922</v>
+        <v>-3.1981907074200899</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.2">
@@ -6180,7 +6180,7 @@
         <v>39262</v>
       </c>
       <c r="C230" s="3">
-        <v>-15.987113678044873</v>
+        <v>-1.7816309730697366</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.2">
@@ -6192,7 +6192,7 @@
         <v>39233</v>
       </c>
       <c r="C231" s="3">
-        <v>9.3268700452315834</v>
+        <v>3.2549228600146973</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.2">
@@ -6204,7 +6204,7 @@
         <v>39202</v>
       </c>
       <c r="C232" s="3">
-        <v>33.410923342756682</v>
+        <v>4.3290683107413797</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
@@ -6216,7 +6216,7 @@
         <v>39171</v>
       </c>
       <c r="C233" s="3">
-        <v>16.412396415722409</v>
+        <v>0.99799547916576969</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.2">
@@ -6228,7 +6228,7 @@
         <v>39141</v>
       </c>
       <c r="C234" s="3">
-        <v>17.296353384283194</v>
+        <v>-2.1846145288686225</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.2">
@@ -6240,7 +6240,7 @@
         <v>39113</v>
       </c>
       <c r="C235" s="3">
-        <v>24.143091024745299</v>
+        <v>1.4059084819854739</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.2">
@@ -6252,7 +6252,7 @@
         <v>39080</v>
       </c>
       <c r="C236" s="3">
-        <v>6.3018223739635504</v>
+        <v>1.2615751483260995</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.2">
@@ -6264,7 +6264,7 @@
         <v>39051</v>
       </c>
       <c r="C237" s="3">
-        <v>5.3304956607870047</v>
+        <v>1.6466609576614388</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.2">
@@ -6276,7 +6276,7 @@
         <v>39021</v>
       </c>
       <c r="C238" s="3">
-        <v>-0.59091967193771744</v>
+        <v>3.1508028596025195</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.2">
@@ -6288,7 +6288,7 @@
         <v>38989</v>
       </c>
       <c r="C239" s="3">
-        <v>4.7910669639840586</v>
+        <v>2.4566274485741779</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.2">
@@ -6300,7 +6300,7 @@
         <v>38960</v>
       </c>
       <c r="C240" s="3">
-        <v>3.8494250002105268</v>
+        <v>2.1274262528785837</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.2">
@@ -6312,7 +6312,7 @@
         <v>38929</v>
       </c>
       <c r="C241" s="3">
-        <v>-4.1016961699063437</v>
+        <v>0.50858132577547011</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.2">
@@ -6324,7 +6324,7 @@
         <v>38898</v>
       </c>
       <c r="C242" s="3">
-        <v>5.9659909350995077</v>
+        <v>8.6608035651192239E-3</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.2">
@@ -6336,7 +6336,7 @@
         <v>38868</v>
       </c>
       <c r="C243" s="3">
-        <v>22.830027547002917</v>
+        <v>-3.091690129023883</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
@@ -6348,7 +6348,7 @@
         <v>38835</v>
       </c>
       <c r="C244" s="3">
-        <v>14.139850897424733</v>
+        <v>1.2186928013716125</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.2">
@@ -6360,7 +6360,7 @@
         <v>38807</v>
       </c>
       <c r="C245" s="3">
-        <v>3.6823927208347262</v>
+        <v>1.1064607311854768</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.2">
@@ -6372,7 +6372,7 @@
         <v>38776</v>
       </c>
       <c r="C246" s="3">
-        <v>0.72448258328834392</v>
+        <v>4.5309668145754323E-2</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.2">
@@ -6384,7 +6384,7 @@
         <v>38742</v>
       </c>
       <c r="C247" s="3">
-        <v>11.353619390534696</v>
+        <v>2.5466838635253009</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.2">
@@ -6396,7 +6396,7 @@
         <v>38716</v>
       </c>
       <c r="C248" s="3">
-        <v>3.6927064496684814</v>
+        <v>-9.5239619681797283E-2</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.2">
@@ -6408,7 +6408,7 @@
         <v>38686</v>
       </c>
       <c r="C249" s="3">
-        <v>0.10148927363367033</v>
+        <v>3.518612107604735</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.2">
@@ -6420,7 +6420,7 @@
         <v>38656</v>
       </c>
       <c r="C250" s="3">
-        <v>-4.6980537291735907</v>
+        <v>-1.7740741042146402</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.2">
@@ -6432,7 +6432,7 @@
         <v>38625</v>
       </c>
       <c r="C251" s="3">
-        <v>2.8831841276377279</v>
+        <v>0.69489400408087043</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.2">
@@ -6444,7 +6444,7 @@
         <v>38595</v>
       </c>
       <c r="C252" s="3">
-        <v>13.468532876850258</v>
+        <v>-1.1222025960556881</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.2">
@@ -6456,7 +6456,7 @@
         <v>38562</v>
       </c>
       <c r="C253" s="3">
-        <v>-5.8972687371604771</v>
+        <v>3.5968203604375137</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.2">
@@ -6468,7 +6468,7 @@
         <v>38533</v>
       </c>
       <c r="C254" s="3">
-        <v>-0.67388488991958484</v>
+        <v>-1.4267729752415192E-2</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
@@ -6480,7 +6480,7 @@
         <v>38503</v>
       </c>
       <c r="C255" s="3">
-        <v>-5.9861186322499371</v>
+        <v>2.9952024895189666</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.2">
@@ -6492,7 +6492,7 @@
         <v>38471</v>
       </c>
       <c r="C256" s="3">
-        <v>-5.4077369128235802</v>
+        <v>-2.010858977291019</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.2">
@@ -6504,7 +6504,7 @@
         <v>38442</v>
       </c>
       <c r="C257" s="3">
-        <v>-12.223085339918715</v>
+        <v>-1.9117647058823573</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.2">
@@ -6516,7 +6516,7 @@
         <v>38411</v>
       </c>
       <c r="C258" s="3">
-        <v>10.642570934034779</v>
+        <v>1.8903383646414307</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.2">
@@ -6528,7 +6528,7 @@
         <v>38383</v>
       </c>
       <c r="C259" s="3">
-        <v>-7.7346999999999948</v>
+        <v>-2.5290448214403627</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.2">
@@ -6540,1580 +6540,1916 @@
         <v>38352</v>
       </c>
       <c r="C260" s="3">
-        <v>0</v>
+        <v>3.2458128162750732</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A261" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>2004/11</v>
       </c>
       <c r="B261" s="2">
         <v>38321</v>
       </c>
-      <c r="C261" s="3"/>
+      <c r="C261" s="3">
+        <v>3.8594938948858459</v>
+      </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A262" t="str">
         <f t="shared" ref="A262:A325" si="4">IF(C262="","",TEXT(B262,"YYYY/MM"))</f>
-        <v/>
+        <v>2004/10</v>
       </c>
       <c r="B262" s="2">
         <v>38289</v>
       </c>
-      <c r="C262" s="3"/>
+      <c r="C262" s="3">
+        <v>1.4014247519245071</v>
+      </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A263" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2004/09</v>
       </c>
       <c r="B263" s="2">
         <v>38260</v>
       </c>
-      <c r="C263" s="3"/>
+      <c r="C263" s="3">
+        <v>0.93639063971600045</v>
+      </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A264" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2004/08</v>
       </c>
       <c r="B264" s="2">
         <v>38230</v>
       </c>
-      <c r="C264" s="3"/>
+      <c r="C264" s="3">
+        <v>0.22873325345822426</v>
+      </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A265" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2004/07</v>
       </c>
       <c r="B265" s="2">
         <v>38198</v>
       </c>
-      <c r="C265" s="3"/>
+      <c r="C265" s="3">
+        <v>-3.4290522772693732</v>
+      </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2004/06</v>
       </c>
       <c r="B266" s="2">
         <v>38168</v>
       </c>
-      <c r="C266" s="3"/>
+      <c r="C266" s="3">
+        <v>1.7989078059749364</v>
+      </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A267" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2004/05</v>
       </c>
       <c r="B267" s="2">
         <v>38138</v>
       </c>
-      <c r="C267" s="3"/>
+      <c r="C267" s="3">
+        <v>1.2083446220536587</v>
+      </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A268" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2004/04</v>
       </c>
       <c r="B268" s="2">
         <v>38107</v>
       </c>
-      <c r="C268" s="3"/>
+      <c r="C268" s="3">
+        <v>-1.6790829419024988</v>
+      </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A269" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2004/03</v>
       </c>
       <c r="B269" s="2">
         <v>38077</v>
       </c>
-      <c r="C269" s="3"/>
+      <c r="C269" s="3">
+        <v>-1.6358935839432598</v>
+      </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A270" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2004/02</v>
       </c>
       <c r="B270" s="2">
         <v>38044</v>
       </c>
-      <c r="C270" s="3"/>
+      <c r="C270" s="3">
+        <v>1.2209029908144986</v>
+      </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A271" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2004/01</v>
       </c>
       <c r="B271" s="2">
         <v>38016</v>
       </c>
-      <c r="C271" s="3"/>
+      <c r="C271" s="3">
+        <v>1.7276422764227695</v>
+      </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A272" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2003/12</v>
       </c>
       <c r="B272" s="2">
         <v>37986</v>
       </c>
-      <c r="C272" s="3"/>
+      <c r="C272" s="3">
+        <v>5.0765450765450693</v>
+      </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A273" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2003/11</v>
       </c>
       <c r="B273" s="2">
         <v>37953</v>
       </c>
-      <c r="C273" s="3"/>
+      <c r="C273" s="3">
+        <v>0.71285131006653124</v>
+      </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A274" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2003/10</v>
       </c>
       <c r="B274" s="2">
         <v>37925</v>
       </c>
-      <c r="C274" s="3"/>
+      <c r="C274" s="3">
+        <v>5.4961494824141255</v>
+      </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A275" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2003/09</v>
       </c>
       <c r="B275" s="2">
         <v>37894</v>
       </c>
-      <c r="C275" s="3"/>
+      <c r="C275" s="3">
+        <v>-1.1944325949147294</v>
+      </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A276" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2003/08</v>
       </c>
       <c r="B276" s="2">
         <v>37862</v>
       </c>
-      <c r="C276" s="3"/>
+      <c r="C276" s="3">
+        <v>1.7873191222950391</v>
+      </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2003/07</v>
       </c>
       <c r="B277" s="2">
         <v>37833</v>
       </c>
-      <c r="C277" s="3"/>
+      <c r="C277" s="3">
+        <v>1.6223704463827593</v>
+      </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A278" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2003/06</v>
       </c>
       <c r="B278" s="2">
         <v>37802</v>
       </c>
-      <c r="C278" s="3"/>
+      <c r="C278" s="3">
+        <v>1.1322242862628284</v>
+      </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A279" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2003/05</v>
       </c>
       <c r="B279" s="2">
         <v>37771</v>
       </c>
-      <c r="C279" s="3"/>
+      <c r="C279" s="3">
+        <v>5.0898660733760925</v>
+      </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A280" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2003/04</v>
       </c>
       <c r="B280" s="2">
         <v>37741</v>
       </c>
-      <c r="C280" s="3"/>
+      <c r="C280" s="3">
+        <v>8.1044117993822162</v>
+      </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A281" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2003/03</v>
       </c>
       <c r="B281" s="2">
         <v>37711</v>
       </c>
-      <c r="C281" s="3"/>
+      <c r="C281" s="3">
+        <v>0.83576056589194092</v>
+      </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A282" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2003/02</v>
       </c>
       <c r="B282" s="2">
         <v>37680</v>
       </c>
-      <c r="C282" s="3"/>
+      <c r="C282" s="3">
+        <v>-1.7003622764987791</v>
+      </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A283" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2003/01</v>
       </c>
       <c r="B283" s="2">
         <v>37650</v>
       </c>
-      <c r="C283" s="3"/>
+      <c r="C283" s="3">
+        <v>-2.7414698461048825</v>
+      </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A284" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2002/12</v>
       </c>
       <c r="B284" s="2">
         <v>37621</v>
       </c>
-      <c r="C284" s="3"/>
+      <c r="C284" s="3">
+        <v>-6.0332582157618608</v>
+      </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A285" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2002/11</v>
       </c>
       <c r="B285" s="2">
         <v>37589</v>
       </c>
-      <c r="C285" s="3"/>
+      <c r="C285" s="3">
+        <v>5.7069635115606809</v>
+      </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A286" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2002/10</v>
       </c>
       <c r="B286" s="2">
         <v>37560</v>
       </c>
-      <c r="C286" s="3"/>
+      <c r="C286" s="3">
+        <v>8.644882739672255</v>
+      </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A287" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2002/09</v>
       </c>
       <c r="B287" s="2">
         <v>37526</v>
       </c>
-      <c r="C287" s="3"/>
+      <c r="C287" s="3">
+        <v>-11.002434311788411</v>
+      </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2002/08</v>
       </c>
       <c r="B288" s="2">
         <v>37498</v>
       </c>
-      <c r="C288" s="3"/>
+      <c r="C288" s="3">
+        <v>0.48814198898663452</v>
+      </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A289" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2002/07</v>
       </c>
       <c r="B289" s="2">
         <v>37468</v>
       </c>
-      <c r="C289" s="3"/>
+      <c r="C289" s="3">
+        <v>-7.8994958628423539</v>
+      </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A290" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2002/06</v>
       </c>
       <c r="B290" s="2">
         <v>37435</v>
       </c>
-      <c r="C290" s="3"/>
+      <c r="C290" s="3">
+        <v>-7.24647187810411</v>
+      </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A291" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2002/05</v>
       </c>
       <c r="B291" s="2">
         <v>37407</v>
       </c>
-      <c r="C291" s="3"/>
+      <c r="C291" s="3">
+        <v>-0.90814545184414452</v>
+      </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A292" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2002/04</v>
       </c>
       <c r="B292" s="2">
         <v>37376</v>
       </c>
-      <c r="C292" s="3"/>
+      <c r="C292" s="3">
+        <v>-6.1417652236815723</v>
+      </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A293" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2002/03</v>
       </c>
       <c r="B293" s="2">
         <v>37344</v>
       </c>
-      <c r="C293" s="3"/>
+      <c r="C293" s="3">
+        <v>3.6738861330225081</v>
+      </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A294" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2002/02</v>
       </c>
       <c r="B294" s="2">
         <v>37315</v>
       </c>
-      <c r="C294" s="3"/>
+      <c r="C294" s="3">
+        <v>-2.0766236064413413</v>
+      </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A295" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2002/01</v>
       </c>
       <c r="B295" s="2">
         <v>37287</v>
       </c>
-      <c r="C295" s="3"/>
+      <c r="C295" s="3">
+        <v>-1.5573827607832103</v>
+      </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A296" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2001/12</v>
       </c>
       <c r="B296" s="2">
         <v>37256</v>
       </c>
-      <c r="C296" s="3"/>
+      <c r="C296" s="3">
+        <v>0.75738294791345417</v>
+      </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A297" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2001/11</v>
       </c>
       <c r="B297" s="2">
         <v>37225</v>
       </c>
-      <c r="C297" s="3"/>
+      <c r="C297" s="3">
+        <v>7.5175979920360847</v>
+      </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A298" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2001/10</v>
       </c>
       <c r="B298" s="2">
         <v>37195</v>
       </c>
-      <c r="C298" s="3"/>
+      <c r="C298" s="3">
+        <v>1.8099025880454089</v>
+      </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2001/09</v>
       </c>
       <c r="B299" s="2">
         <v>37162</v>
       </c>
-      <c r="C299" s="3"/>
+      <c r="C299" s="3">
+        <v>-8.172338961520131</v>
+      </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A300" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2001/08</v>
       </c>
       <c r="B300" s="2">
         <v>37134</v>
       </c>
-      <c r="C300" s="3"/>
+      <c r="C300" s="3">
+        <v>-6.4108385690579084</v>
+      </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A301" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2001/07</v>
       </c>
       <c r="B301" s="2">
         <v>37103</v>
       </c>
-      <c r="C301" s="3"/>
+      <c r="C301" s="3">
+        <v>-1.0772447362833004</v>
+      </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A302" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2001/06</v>
       </c>
       <c r="B302" s="2">
         <v>37071</v>
       </c>
-      <c r="C302" s="3"/>
+      <c r="C302" s="3">
+        <v>-2.5003583316080213</v>
+      </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A303" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2001/05</v>
       </c>
       <c r="B303" s="2">
         <v>37042</v>
       </c>
-      <c r="C303" s="3"/>
+      <c r="C303" s="3">
+        <v>0.50901989659533076</v>
+      </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A304" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2001/04</v>
       </c>
       <c r="B304" s="2">
         <v>37011</v>
       </c>
-      <c r="C304" s="3"/>
+      <c r="C304" s="3">
+        <v>7.6814354537071416</v>
+      </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A305" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2001/03</v>
       </c>
       <c r="B305" s="2">
         <v>36980</v>
       </c>
-      <c r="C305" s="3"/>
+      <c r="C305" s="3">
+        <v>-6.4204719583205723</v>
+      </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A306" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2001/02</v>
       </c>
       <c r="B306" s="2">
         <v>36950</v>
       </c>
-      <c r="C306" s="3"/>
+      <c r="C306" s="3">
+        <v>-9.2290686012547418</v>
+      </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A307" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2001/01</v>
       </c>
       <c r="B307" s="2">
         <v>36910</v>
       </c>
-      <c r="C307" s="3"/>
+      <c r="C307" s="3">
+        <v>3.4636592238010078</v>
+      </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A308" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2000/12</v>
       </c>
       <c r="B308" s="2">
         <v>36889</v>
       </c>
-      <c r="C308" s="3"/>
+      <c r="C308" s="3">
+        <v>0.40533860603064742</v>
+      </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A309" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2000/11</v>
       </c>
       <c r="B309" s="2">
         <v>36860</v>
       </c>
-      <c r="C309" s="3"/>
+      <c r="C309" s="3">
+        <v>-8.0068560235063693</v>
+      </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2000/10</v>
       </c>
       <c r="B310" s="2">
         <v>36830</v>
       </c>
-      <c r="C310" s="3"/>
+      <c r="C310" s="3">
+        <v>-0.49494956526581202</v>
+      </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A311" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2000/09</v>
       </c>
       <c r="B311" s="2">
         <v>36798</v>
       </c>
-      <c r="C311" s="3"/>
+      <c r="C311" s="3">
+        <v>-5.3482947656950159</v>
+      </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A312" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2000/08</v>
       </c>
       <c r="B312" s="2">
         <v>36769</v>
       </c>
-      <c r="C312" s="3"/>
+      <c r="C312" s="3">
+        <v>6.069903482594019</v>
+      </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A313" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2000/07</v>
       </c>
       <c r="B313" s="2">
         <v>36738</v>
       </c>
-      <c r="C313" s="3"/>
+      <c r="C313" s="3">
+        <v>-1.6341262202667406</v>
+      </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A314" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2000/06</v>
       </c>
       <c r="B314" s="2">
         <v>36707</v>
       </c>
-      <c r="C314" s="3"/>
+      <c r="C314" s="3">
+        <v>2.3933549204561366</v>
+      </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A315" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2000/05</v>
       </c>
       <c r="B315" s="2">
         <v>36677</v>
       </c>
-      <c r="C315" s="3"/>
+      <c r="C315" s="3">
+        <v>-2.1914997624670529</v>
+      </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A316" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2000/04</v>
       </c>
       <c r="B316" s="2">
         <v>36644</v>
       </c>
-      <c r="C316" s="3"/>
+      <c r="C316" s="3">
+        <v>-3.0795820042973876</v>
+      </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A317" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2000/03</v>
       </c>
       <c r="B317" s="2">
         <v>36616</v>
       </c>
-      <c r="C317" s="3"/>
+      <c r="C317" s="3">
+        <v>9.6719895786068655</v>
+      </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A318" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2000/02</v>
       </c>
       <c r="B318" s="2">
         <v>36585</v>
       </c>
-      <c r="C318" s="3"/>
+      <c r="C318" s="3">
+        <v>-2.0108142219927405</v>
+      </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A319" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2000/01</v>
       </c>
       <c r="B319" s="2">
         <v>36553</v>
       </c>
-      <c r="C319" s="3"/>
+      <c r="C319" s="3">
+        <v>-5.0903522205206659</v>
+      </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A320" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1999/12</v>
       </c>
       <c r="B320" s="2">
         <v>36524</v>
       </c>
-      <c r="C320" s="3"/>
+      <c r="C320" s="3">
+        <v>5.7843920772404189</v>
+      </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1999/11</v>
       </c>
       <c r="B321" s="2">
         <v>36494</v>
       </c>
-      <c r="C321" s="3"/>
+      <c r="C321" s="3">
+        <v>1.906187405075821</v>
+      </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A322" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1999/10</v>
       </c>
       <c r="B322" s="2">
         <v>36462</v>
       </c>
-      <c r="C322" s="3"/>
+      <c r="C322" s="3">
+        <v>6.2539467221741418</v>
+      </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A323" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1999/09</v>
       </c>
       <c r="B323" s="2">
         <v>36433</v>
       </c>
-      <c r="C323" s="3"/>
+      <c r="C323" s="3">
+        <v>-2.855173771783015</v>
+      </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A324" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1999/08</v>
       </c>
       <c r="B324" s="2">
         <v>36403</v>
       </c>
-      <c r="C324" s="3"/>
+      <c r="C324" s="3">
+        <v>-0.62541393220543195</v>
+      </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A325" t="str">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1999/07</v>
       </c>
       <c r="B325" s="2">
         <v>36371</v>
       </c>
-      <c r="C325" s="3"/>
+      <c r="C325" s="3">
+        <v>-3.2046098593293548</v>
+      </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A326" t="str">
         <f t="shared" ref="A326:A389" si="5">IF(C326="","",TEXT(B326,"YYYY/MM"))</f>
-        <v/>
+        <v>1999/06</v>
       </c>
       <c r="B326" s="2">
         <v>36341</v>
       </c>
-      <c r="C326" s="3"/>
+      <c r="C326" s="3">
+        <v>5.4438333435752551</v>
+      </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A327" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1999/05</v>
       </c>
       <c r="B327" s="2">
         <v>36311</v>
       </c>
-      <c r="C327" s="3"/>
+      <c r="C327" s="3">
+        <v>-2.4970415973876281</v>
+      </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A328" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1999/04</v>
       </c>
       <c r="B328" s="2">
         <v>36280</v>
       </c>
-      <c r="C328" s="3"/>
+      <c r="C328" s="3">
+        <v>3.7943981902563095</v>
+      </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A329" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1999/03</v>
       </c>
       <c r="B329" s="2">
         <v>36250</v>
       </c>
-      <c r="C329" s="3"/>
+      <c r="C329" s="3">
+        <v>3.8794182487705164</v>
+      </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A330" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1999/02</v>
       </c>
       <c r="B330" s="2">
         <v>36200</v>
       </c>
-      <c r="C330" s="3"/>
+      <c r="C330" s="3">
+        <v>-3.2282516957894525</v>
+      </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A331" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1999/01</v>
       </c>
       <c r="B331" s="2">
         <v>36189</v>
       </c>
-      <c r="C331" s="3"/>
+      <c r="C331" s="3">
+        <v>4.1009412396378231</v>
+      </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1998/12</v>
       </c>
       <c r="B332" s="2">
         <v>36160</v>
       </c>
-      <c r="C332" s="3"/>
+      <c r="C332" s="3">
+        <v>5.6375308302467175</v>
+      </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A333" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1998/11</v>
       </c>
       <c r="B333" s="2">
         <v>36129</v>
       </c>
-      <c r="C333" s="3"/>
+      <c r="C333" s="3">
+        <v>5.9126034204993294</v>
+      </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A334" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1998/10</v>
       </c>
       <c r="B334" s="2">
         <v>36098</v>
       </c>
-      <c r="C334" s="3"/>
+      <c r="C334" s="3">
+        <v>8.0294195730622242</v>
+      </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A335" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1998/09</v>
       </c>
       <c r="B335" s="2">
         <v>36068</v>
       </c>
-      <c r="C335" s="3"/>
+      <c r="C335" s="3">
+        <v>6.2395537355841579</v>
+      </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A336" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1998/08</v>
       </c>
       <c r="B336" s="2">
         <v>36038</v>
       </c>
-      <c r="C336" s="3"/>
+      <c r="C336" s="3">
+        <v>-14.579671089616042</v>
+      </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A337" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1998/07</v>
       </c>
       <c r="B337" s="2">
         <v>36007</v>
       </c>
-      <c r="C337" s="3"/>
+      <c r="C337" s="3">
+        <v>-1.1615395470260248</v>
+      </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A338" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1998/06</v>
       </c>
       <c r="B338" s="2">
         <v>35976</v>
       </c>
-      <c r="C338" s="3"/>
+      <c r="C338" s="3">
+        <v>3.9438220788031053</v>
+      </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A339" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1998/05</v>
       </c>
       <c r="B339" s="2">
         <v>35944</v>
       </c>
-      <c r="C339" s="3"/>
+      <c r="C339" s="3">
+        <v>-1.8826174949404195</v>
+      </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A340" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1998/04</v>
       </c>
       <c r="B340" s="2">
         <v>35915</v>
       </c>
-      <c r="C340" s="3"/>
+      <c r="C340" s="3">
+        <v>0.90764692534603952</v>
+      </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A341" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1998/03</v>
       </c>
       <c r="B341" s="2">
         <v>35885</v>
       </c>
-      <c r="C341" s="3"/>
+      <c r="C341" s="3">
+        <v>4.994568014180345</v>
+      </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A342" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1998/02</v>
       </c>
       <c r="B342" s="2">
         <v>35853</v>
       </c>
-      <c r="C342" s="3"/>
+      <c r="C342" s="3">
+        <v>7.0449259395274799</v>
+      </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1998/01</v>
       </c>
       <c r="B343" s="2">
         <v>35818</v>
       </c>
-      <c r="C343" s="3"/>
+      <c r="C343" s="3">
+        <v>1.0150139628824384</v>
+      </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A344" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1997/12</v>
       </c>
       <c r="B344" s="2">
         <v>35795</v>
       </c>
-      <c r="C344" s="3"/>
+      <c r="C344" s="3">
+        <v>1.5731630730583923</v>
+      </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A345" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1997/11</v>
       </c>
       <c r="B345" s="2">
         <v>35762</v>
       </c>
-      <c r="C345" s="3"/>
+      <c r="C345" s="3">
+        <v>4.4586822942861426</v>
+      </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A346" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1997/10</v>
       </c>
       <c r="B346" s="2">
         <v>35734</v>
       </c>
-      <c r="C346" s="3"/>
+      <c r="C346" s="3">
+        <v>-3.4477662359597927</v>
+      </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A347" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1997/09</v>
       </c>
       <c r="B347" s="2">
         <v>35703</v>
       </c>
-      <c r="C347" s="3"/>
+      <c r="C347" s="3">
+        <v>5.3153523741759079</v>
+      </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A348" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1997/08</v>
       </c>
       <c r="B348" s="2">
         <v>35671</v>
       </c>
-      <c r="C348" s="3"/>
+      <c r="C348" s="3">
+        <v>-5.7445849794087733</v>
+      </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A349" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1997/07</v>
       </c>
       <c r="B349" s="2">
         <v>35642</v>
       </c>
-      <c r="C349" s="3"/>
+      <c r="C349" s="3">
+        <v>7.8123234742526471</v>
+      </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A350" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1997/06</v>
       </c>
       <c r="B350" s="2">
         <v>35608</v>
       </c>
-      <c r="C350" s="3"/>
+      <c r="C350" s="3">
+        <v>4.345263356438922</v>
+      </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A351" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1997/05</v>
       </c>
       <c r="B351" s="2">
         <v>35580</v>
       </c>
-      <c r="C351" s="3"/>
+      <c r="C351" s="3">
+        <v>5.8576883719769324</v>
+      </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A352" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1997/04</v>
       </c>
       <c r="B352" s="2">
         <v>35550</v>
       </c>
-      <c r="C352" s="3"/>
+      <c r="C352" s="3">
+        <v>5.8405536770921529</v>
+      </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A353" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1997/03</v>
       </c>
       <c r="B353" s="2">
         <v>35520</v>
       </c>
-      <c r="C353" s="3"/>
+      <c r="C353" s="3">
+        <v>-4.2613995599504406</v>
+      </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1997/02</v>
       </c>
       <c r="B354" s="2">
         <v>35489</v>
       </c>
-      <c r="C354" s="3"/>
+      <c r="C354" s="3">
+        <v>0.59275465554087248</v>
+      </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A355" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1997/01</v>
       </c>
       <c r="B355" s="2">
         <v>35461</v>
       </c>
-      <c r="C355" s="3"/>
+      <c r="C355" s="3">
+        <v>6.1317061317061272</v>
+      </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A356" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1996/12</v>
       </c>
       <c r="B356" s="2">
         <v>35430</v>
       </c>
-      <c r="C356" s="3"/>
+      <c r="C356" s="3">
+        <v>-2.1505376344086002</v>
+      </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A357" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1996/11</v>
       </c>
       <c r="B357" s="2">
         <v>35398</v>
       </c>
-      <c r="C357" s="3"/>
+      <c r="C357" s="3">
+        <v>7.3376153813433209</v>
+      </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A358" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1996/10</v>
       </c>
       <c r="B358" s="2">
         <v>35369</v>
       </c>
-      <c r="C358" s="3"/>
+      <c r="C358" s="3">
+        <v>2.6130857982569866</v>
+      </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A359" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1996/09</v>
       </c>
       <c r="B359" s="2">
         <v>35335</v>
       </c>
-      <c r="C359" s="3"/>
+      <c r="C359" s="3">
+        <v>5.4172610009355804</v>
+      </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A360" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1996/08</v>
       </c>
       <c r="B360" s="2">
         <v>35307</v>
       </c>
-      <c r="C360" s="3"/>
+      <c r="C360" s="3">
+        <v>1.8813969841393829</v>
+      </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A361" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1996/07</v>
       </c>
       <c r="B361" s="2">
         <v>35277</v>
       </c>
-      <c r="C361" s="3"/>
+      <c r="C361" s="3">
+        <v>-4.5748027973696264</v>
+      </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A362" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1996/06</v>
       </c>
       <c r="B362" s="2">
         <v>35244</v>
       </c>
-      <c r="C362" s="3"/>
+      <c r="C362" s="3">
+        <v>0.22566953610712037</v>
+      </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A363" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1996/05</v>
       </c>
       <c r="B363" s="2">
         <v>35216</v>
       </c>
-      <c r="C363" s="3"/>
+      <c r="C363" s="3">
+        <v>2.2853386734335235</v>
+      </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A364" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1996/04</v>
       </c>
       <c r="B364" s="2">
         <v>35185</v>
       </c>
-      <c r="C364" s="3"/>
+      <c r="C364" s="3">
+        <v>1.343144848954303</v>
+      </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1996/03</v>
       </c>
       <c r="B365" s="2">
         <v>35153</v>
       </c>
-      <c r="C365" s="3"/>
+      <c r="C365" s="3">
+        <v>0.79165560638947419</v>
+      </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A366" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1996/02</v>
       </c>
       <c r="B366" s="2">
         <v>35111</v>
       </c>
-      <c r="C366" s="3"/>
+      <c r="C366" s="3">
+        <v>0.69337442218797563</v>
+      </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A367" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1996/01</v>
       </c>
       <c r="B367" s="2">
         <v>35095</v>
       </c>
-      <c r="C367" s="3"/>
+      <c r="C367" s="3">
+        <v>3.2617342879872835</v>
+      </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A368" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1995/12</v>
       </c>
       <c r="B368" s="2">
         <v>35062</v>
       </c>
-      <c r="C368" s="3"/>
+      <c r="C368" s="3">
+        <v>1.7443877298181087</v>
+      </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A369" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1995/11</v>
       </c>
       <c r="B369" s="2">
         <v>35033</v>
       </c>
-      <c r="C369" s="3"/>
+      <c r="C369" s="3">
+        <v>4.1049011177987982</v>
+      </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A370" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1995/10</v>
       </c>
       <c r="B370" s="2">
         <v>35003</v>
       </c>
-      <c r="C370" s="3"/>
+      <c r="C370" s="3">
+        <v>-0.49793809140842304</v>
+      </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A371" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1995/09</v>
       </c>
       <c r="B371" s="2">
         <v>34971</v>
       </c>
-      <c r="C371" s="3"/>
+      <c r="C371" s="3">
+        <v>4.0097529721648595</v>
+      </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A372" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1995/08</v>
       </c>
       <c r="B372" s="2">
         <v>34942</v>
       </c>
-      <c r="C372" s="3"/>
+      <c r="C372" s="3">
+        <v>-3.2025050706319114E-2</v>
+      </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A373" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1995/07</v>
       </c>
       <c r="B373" s="2">
         <v>34911</v>
       </c>
-      <c r="C373" s="3"/>
+      <c r="C373" s="3">
+        <v>3.1776044056906816</v>
+      </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A374" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1995/06</v>
       </c>
       <c r="B374" s="2">
         <v>34880</v>
       </c>
-      <c r="C374" s="3"/>
+      <c r="C374" s="3">
+        <v>2.1278590176228018</v>
+      </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A375" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1995/05</v>
       </c>
       <c r="B375" s="2">
         <v>34850</v>
       </c>
-      <c r="C375" s="3"/>
+      <c r="C375" s="3">
+        <v>3.6311709506323897</v>
+      </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1995/04</v>
       </c>
       <c r="B376" s="2">
         <v>34817</v>
       </c>
-      <c r="C376" s="3"/>
+      <c r="C376" s="3">
+        <v>2.7960296379141658</v>
+      </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A377" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1995/03</v>
       </c>
       <c r="B377" s="2">
         <v>34789</v>
       </c>
-      <c r="C377" s="3"/>
+      <c r="C377" s="3">
+        <v>2.7329243521615032</v>
+      </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A378" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1995/02</v>
       </c>
       <c r="B378" s="2">
         <v>34758</v>
       </c>
-      <c r="C378" s="3"/>
+      <c r="C378" s="3">
+        <v>3.6074146507376392</v>
+      </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A379" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1995/01</v>
       </c>
       <c r="B379" s="2">
         <v>34726</v>
       </c>
-      <c r="C379" s="3"/>
+      <c r="C379" s="3">
+        <v>2.4277658022514137</v>
+      </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A380" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1994/12</v>
       </c>
       <c r="B380" s="2">
         <v>34698</v>
       </c>
-      <c r="C380" s="3"/>
+      <c r="C380" s="3">
+        <v>1.229914699464385</v>
+      </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A381" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1994/11</v>
       </c>
       <c r="B381" s="2">
         <v>34668</v>
       </c>
-      <c r="C381" s="3"/>
+      <c r="C381" s="3">
+        <v>-3.9504604636392604</v>
+      </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A382" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1994/10</v>
       </c>
       <c r="B382" s="2">
         <v>34638</v>
       </c>
-      <c r="C382" s="3"/>
+      <c r="C382" s="3">
+        <v>2.0877909615509394</v>
+      </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A383" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1994/09</v>
       </c>
       <c r="B383" s="2">
         <v>34607</v>
       </c>
-      <c r="C383" s="3"/>
+      <c r="C383" s="3">
+        <v>-2.6919598729731486</v>
+      </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A384" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1994/08</v>
       </c>
       <c r="B384" s="2">
         <v>34577</v>
       </c>
-      <c r="C384" s="3"/>
+      <c r="C384" s="3">
+        <v>3.7598743071618701</v>
+      </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A385" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1994/07</v>
       </c>
       <c r="B385" s="2">
         <v>34544</v>
       </c>
-      <c r="C385" s="3"/>
+      <c r="C385" s="3">
+        <v>3.1489859769959772</v>
+      </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A386" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1994/06</v>
       </c>
       <c r="B386" s="2">
         <v>34515</v>
       </c>
-      <c r="C386" s="3"/>
+      <c r="C386" s="3">
+        <v>-2.6790799561883905</v>
+      </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1994/05</v>
       </c>
       <c r="B387" s="2">
         <v>34485</v>
       </c>
-      <c r="C387" s="3"/>
+      <c r="C387" s="3">
+        <v>1.239715242509587</v>
+      </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A388" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1994/04</v>
       </c>
       <c r="B388" s="2">
         <v>34453</v>
       </c>
-      <c r="C388" s="3"/>
+      <c r="C388" s="3">
+        <v>1.1530609955807014</v>
+      </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A389" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1994/03</v>
       </c>
       <c r="B389" s="2">
         <v>34424</v>
       </c>
-      <c r="C389" s="3"/>
+      <c r="C389" s="3">
+        <v>-4.5746457164875682</v>
+      </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A390" t="str">
         <f t="shared" ref="A390:A401" si="6">IF(C390="","",TEXT(B390,"YYYY/MM"))</f>
-        <v/>
+        <v>1994/02</v>
       </c>
       <c r="B390" s="2">
         <v>34393</v>
       </c>
-      <c r="C390" s="3"/>
+      <c r="C390" s="3">
+        <v>-3.0045057203961778</v>
+      </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A391" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1994/01</v>
       </c>
       <c r="B391" s="2">
         <v>34365</v>
       </c>
-      <c r="C391" s="3"/>
+      <c r="C391" s="3">
+        <v>3.2500803944688572</v>
+      </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A392" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1993/12</v>
       </c>
       <c r="B392" s="2">
         <v>34334</v>
       </c>
-      <c r="C392" s="3"/>
+      <c r="C392" s="3">
+        <v>1.0091166980662036</v>
+      </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A393" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1993/11</v>
       </c>
       <c r="B393" s="2">
         <v>34303</v>
       </c>
-      <c r="C393" s="3"/>
+      <c r="C393" s="3">
+        <v>-1.2910672680247037</v>
+      </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A394" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1993/10</v>
       </c>
       <c r="B394" s="2">
         <v>34271</v>
       </c>
-      <c r="C394" s="3"/>
+      <c r="C394" s="3">
+        <v>1.9392935741834316</v>
+      </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A395" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1993/09</v>
       </c>
       <c r="B395" s="2">
         <v>34242</v>
       </c>
-      <c r="C395" s="3"/>
+      <c r="C395" s="3">
+        <v>-0.99879195789109865</v>
+      </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A396" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1993/08</v>
       </c>
       <c r="B396" s="2">
         <v>34212</v>
       </c>
-      <c r="C396" s="3"/>
+      <c r="C396" s="3">
+        <v>3.4431972865016869</v>
+      </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A397" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1993/07</v>
       </c>
       <c r="B397" s="2">
         <v>34180</v>
       </c>
-      <c r="C397" s="3"/>
+      <c r="C397" s="3">
+        <v>-0.5327059241337917</v>
+      </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1993/06</v>
       </c>
       <c r="B398" s="2">
         <v>34150</v>
       </c>
-      <c r="C398" s="3"/>
+      <c r="C398" s="3">
+        <v>7.5523667784715975E-2</v>
+      </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A399" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1993/05</v>
       </c>
       <c r="B399" s="2">
         <v>34120</v>
       </c>
-      <c r="C399" s="3"/>
+      <c r="C399" s="3">
+        <v>2.2717462913741882</v>
+      </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A400" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1993/04</v>
       </c>
       <c r="B400" s="2">
         <v>34089</v>
       </c>
-      <c r="C400" s="3"/>
+      <c r="C400" s="3">
+        <v>-2.5416786591980878</v>
+      </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A401" t="str">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1993/03</v>
       </c>
       <c r="B401" s="2">
         <v>34059</v>
       </c>
-      <c r="C401" s="3"/>
+      <c r="C401" s="3">
+        <v>1.8697279985565585</v>
+      </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B402" s="2">
         <v>34026</v>
       </c>
-      <c r="C402" s="3"/>
+      <c r="C402" s="3">
+        <v>1.0483613656046442</v>
+      </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B403" s="2">
         <v>33998</v>
       </c>
-      <c r="C403" s="3"/>
+      <c r="C403" s="3">
+        <v>0.70459709439765206</v>
+      </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B404" s="2">
         <v>33969</v>
       </c>
-      <c r="C404" s="3"/>
+      <c r="C404" s="3">
+        <v>1.0107801089602297</v>
+      </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B405" s="2">
         <v>33938</v>
       </c>
-      <c r="C405" s="3"/>
+      <c r="C405" s="3">
+        <v>3.026177510270367</v>
+      </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B406" s="2">
         <v>33907</v>
       </c>
-      <c r="C406" s="3"/>
+      <c r="C406" s="3">
+        <v>0.21062709430348381</v>
+      </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B407" s="2">
         <v>33877</v>
       </c>
-      <c r="C407" s="3"/>
+      <c r="C407" s="3">
+        <v>0.91056203656740831</v>
+      </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B408" s="2">
         <v>33847</v>
       </c>
-      <c r="C408" s="3"/>
+      <c r="C408" s="3">
+        <v>-2.3997548384055101</v>
+      </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B409" s="2">
         <v>33816</v>
       </c>
-      <c r="C409" s="3"/>
+      <c r="C409" s="3">
+        <v>3.9373744303425218</v>
+      </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B410" s="2">
         <v>33785</v>
       </c>
-      <c r="C410" s="3"/>
+      <c r="C410" s="3">
+        <v>-1.7358853978572397</v>
+      </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B411" s="2">
         <v>33753</v>
       </c>
-      <c r="C411" s="3"/>
+      <c r="C411" s="3">
+        <v>9.6397156283889451E-2</v>
+      </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B412" s="2">
         <v>33724</v>
       </c>
-      <c r="C412" s="3"/>
+      <c r="C412" s="3">
+        <v>2.7892689935346437</v>
+      </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B413" s="2">
         <v>33694</v>
       </c>
-      <c r="C413" s="3"/>
+      <c r="C413" s="3">
+        <v>-2.1831839108311102</v>
+      </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B414" s="2">
         <v>33662</v>
       </c>
-      <c r="C414" s="3"/>
+      <c r="C414" s="3">
+        <v>0.9564813229286262</v>
+      </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B415" s="2">
         <v>33634</v>
       </c>
-      <c r="C415" s="3"/>
+      <c r="C415" s="3">
+        <v>-1.9899781821669071</v>
+      </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B416" s="2">
         <v>33603</v>
       </c>
-      <c r="C416" s="3"/>
+      <c r="C416" s="3">
+        <v>11.158786845050894</v>
+      </c>
     </row>
     <row r="417" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B417" s="2">
         <v>33571</v>
       </c>
-      <c r="C417" s="3"/>
+      <c r="C417" s="3">
+        <v>-4.3928043622279862</v>
+      </c>
     </row>
     <row r="418" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B418" s="2">
         <v>33542</v>
       </c>
-      <c r="C418" s="3"/>
+      <c r="C418" s="3">
+        <v>1.1859949466302089</v>
+      </c>
     </row>
     <row r="419" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B419" s="2">
         <v>33511</v>
       </c>
-      <c r="C419" s="3"/>
+      <c r="C419" s="3">
+        <v>-1.9143716966340429</v>
+      </c>
     </row>
     <row r="420" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B420" s="2">
         <v>33480</v>
       </c>
-      <c r="C420" s="3"/>
+      <c r="C420" s="3">
+        <v>1.9648797091359249</v>
+      </c>
     </row>
     <row r="421" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B421" s="2">
         <v>33450</v>
       </c>
-      <c r="C421" s="3"/>
+      <c r="C421" s="3">
+        <v>4.485935984481082</v>
+      </c>
     </row>
     <row r="422" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B422" s="2">
         <v>33417</v>
       </c>
-      <c r="C422" s="3"/>
+      <c r="C422" s="3">
+        <v>-4.789267116435358</v>
+      </c>
     </row>
     <row r="423" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B423" s="2">
         <v>33389</v>
       </c>
-      <c r="C423" s="3"/>
+      <c r="C423" s="3">
+        <v>3.8577327827361119</v>
+      </c>
     </row>
     <row r="424" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B424" s="2">
         <v>33358</v>
       </c>
-      <c r="C424" s="3"/>
+      <c r="C424" s="3">
+        <v>3.4646340813382359E-2</v>
+      </c>
     </row>
     <row r="425" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B425" s="2">
         <v>33326</v>
       </c>
-      <c r="C425" s="3"/>
+      <c r="C425" s="3">
+        <v>2.2202849592720897</v>
+      </c>
     </row>
     <row r="426" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B426" s="2">
         <v>33297</v>
       </c>
-      <c r="C426" s="3"/>
+      <c r="C426" s="3">
+        <v>6.728113278864889</v>
+      </c>
     </row>
     <row r="427" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B427" s="2">
         <v>33269</v>
       </c>
-      <c r="C427" s="3"/>
+      <c r="C427" s="3">
+        <v>4.1517776028102471</v>
+      </c>
     </row>
     <row r="428" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B428" s="2">
         <v>33238</v>
       </c>
-      <c r="C428" s="3"/>
+      <c r="C428" s="3">
+        <v>2.482775743280996</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
